--- a/data_item.xlsx
+++ b/data_item.xlsx
@@ -1,29 +1,278 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="22527"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ACER\Documents\shar\Dropbox\bot\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\dropbox\Dropbox\bot\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7C2AE0E8-F614-4800-8309-09FC77B91181}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{99DBFED7-B505-465C-A3AB-909157732C77}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11310" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$E$185</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0">Sheet1!$A$1:$E$185</definedName>
   </definedNames>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
+<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>OpenAI</author>
+  </authors>
+  <commentList>
+    <comment ref="B186" authorId="0" shapeId="0" xr:uid="{D91BBC24-A9E5-4D53-B937-1F067C567D9B}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>Source: https://mwstats.info/modules/missile-battery/bgm-109-tomahawk-nuclear-warhead-6q85mujh</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B187" authorId="0" shapeId="0" xr:uid="{9D99CC71-603D-4B5B-8E7C-661433AE63E3}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>Source: https://mwstats.info/modules/missile-battery/p-800-onyx-cluster-warhead-2uks6ve6</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B188" authorId="0" shapeId="0" xr:uid="{691C2DB7-4F41-4044-8EBA-61569EE59F8B}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>Source: https://mwstats.info/modules/missile-battery/smart-324mm-7so2o2i3</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B189" authorId="0" shapeId="0" xr:uid="{BF645BBE-4ABC-4801-B401-8C3FCBBEEB85}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>Source: https://mwstats.info/modules/missile-battery/ssm-700k-c-star-9jpko8ox</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B190" authorId="0" shapeId="0" xr:uid="{2A1A22E9-A86F-47D4-9FBA-76A3C5C409AB}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>Source: https://mwstats.info/modules/missile-battery/p-500-bazalt-hzcn1hja</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B191" authorId="0" shapeId="0" xr:uid="{0E4746AF-C4DD-4AE8-B8C2-0879B0C0B1F9}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>Source: https://mwstats.info/modules/missile-battery/jl-1-7l4zpqpi</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B192" authorId="0" shapeId="0" xr:uid="{62614BE6-586C-4C64-8825-C77A4456B2FA}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>Source: https://mwstats.info/modules/missile-battery/p-270-moskit-7tbixs1p</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B193" authorId="0" shapeId="0" xr:uid="{5983B393-94B3-4449-A1E0-96E6C490A0B8}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>Source: https://mwstats.info/modules/missile-battery/pj-10-brahmos-1qteddlk</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B194" authorId="0" shapeId="0" xr:uid="{ECBAE1E2-C692-4180-BA90-C94192AFBCC8}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>Source: https://mwstats.info/modules/missile-battery/agm-119-penguin-9wtog8he</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B195" authorId="0" shapeId="0" xr:uid="{36F0638B-FB46-4BDC-B30E-86CD0D911046}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>Source: https://wikiwiki.jp/mwjp_wiki/Otomat
+https://wiki.modernwarships.com/en/weapons/Otomat</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B196" authorId="0" shapeId="0" xr:uid="{ED370D96-CC03-4534-ABE6-548E5929878C}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>Source: https://modern-warships.fandom.com/wiki/BGM-109_Tomahawk</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B197" authorId="0" shapeId="0" xr:uid="{24ECF8EA-8D24-42ED-870F-7BC6E88D0EB8}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>Source: https://modern-warships.fandom.com/wiki/P-800_Onyx</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B198" authorId="0" shapeId="0" xr:uid="{1B1F5B76-3B1F-463A-A497-88E1D5D6A962}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>Source: https://modern-warships.fandom.com/wiki/CJ-20</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B199" authorId="0" shapeId="0" xr:uid="{CA1816CD-415E-4631-B173-B3AF43610459}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>Source: https://mwstats.info/modules/missile-battery/ugm-27-polaris-a-3-8r5fh8wl</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B200" authorId="0" shapeId="0" xr:uid="{E3FEFB70-0EA2-4A13-B2C7-6D1F1DA0415D}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>Source: https://mwstats.info/modules/missile-battery/s-300-3y3xdu9n</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B201" authorId="0" shapeId="0" xr:uid="{47311B58-7E6F-4EFA-BD5A-DF519B8B7DCC}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>Source: https://mwstats.info/modules/missile-battery/type-90-ssm-1b-4w86isj8</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B202" authorId="0" shapeId="0" xr:uid="{92B16729-A918-4AA2-8F91-304639399A85}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>Source: https://mwstats.info/modules/missile-battery/mansup-7ax8mpkk</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="558" uniqueCount="222">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1034" uniqueCount="354">
   <si>
     <t>type</t>
   </si>
@@ -689,13 +938,409 @@
   </si>
   <si>
     <t>Oerlikon Skyranger Buckshot</t>
+  </si>
+  <si>
+    <t>BGM-109 Tomahawk (Nuclear warhead)</t>
+  </si>
+  <si>
+    <t>USA</t>
+  </si>
+  <si>
+    <t>P-800 Onyx (Cluster warhead)</t>
+  </si>
+  <si>
+    <t>Russia</t>
+  </si>
+  <si>
+    <t>SMART (324mm)</t>
+  </si>
+  <si>
+    <t>India</t>
+  </si>
+  <si>
+    <t>SSM-700K C-Star</t>
+  </si>
+  <si>
+    <t>South Korea</t>
+  </si>
+  <si>
+    <t>P-500 Bazalt</t>
+  </si>
+  <si>
+    <t>JL-1</t>
+  </si>
+  <si>
+    <t>China</t>
+  </si>
+  <si>
+    <t>P-270 Moskit</t>
+  </si>
+  <si>
+    <t>PJ-10 BrahMos</t>
+  </si>
+  <si>
+    <t>AGM-119 Penguin</t>
+  </si>
+  <si>
+    <t>Sweden</t>
+  </si>
+  <si>
+    <t>Otomat</t>
+  </si>
+  <si>
+    <t>Italy</t>
+  </si>
+  <si>
+    <t>BGM-109 Tomahawk</t>
+  </si>
+  <si>
+    <t>P-800 Onyx</t>
+  </si>
+  <si>
+    <t>CJ-20</t>
+  </si>
+  <si>
+    <t>UGM-27 Polaris A-3</t>
+  </si>
+  <si>
+    <t>S-300</t>
+  </si>
+  <si>
+    <t>Type 90 SSM-1B</t>
+  </si>
+  <si>
+    <t>Japan</t>
+  </si>
+  <si>
+    <t>MANSUP</t>
+  </si>
+  <si>
+    <t>Brazil</t>
+  </si>
+  <si>
+    <t>YJ-83A</t>
+  </si>
+  <si>
+    <t>C-705</t>
+  </si>
+  <si>
+    <t>Exocet</t>
+  </si>
+  <si>
+    <t>France</t>
+  </si>
+  <si>
+    <t>3M-54 Kalibr</t>
+  </si>
+  <si>
+    <t>AGM-176 Griffin</t>
+  </si>
+  <si>
+    <t>CJ-10</t>
+  </si>
+  <si>
+    <t>RGM-84 Harpoon</t>
+  </si>
+  <si>
+    <t>Bofors NAG Stealth (57mm)</t>
+  </si>
+  <si>
+    <t>A-190 (100mm)</t>
+  </si>
+  <si>
+    <t>AK-100 (100mm)</t>
+  </si>
+  <si>
+    <t>Mark 45 (127mm)</t>
+  </si>
+  <si>
+    <t>H/PJ-87 (100mm)</t>
+  </si>
+  <si>
+    <t>Melara Rapid (76mm)</t>
+  </si>
+  <si>
+    <t>Bofors 57 Mk3</t>
+  </si>
+  <si>
+    <t>OTO Melara 127/64</t>
+  </si>
+  <si>
+    <t>H/PJ-38</t>
+  </si>
+  <si>
+    <t>AK-726 (76mm)</t>
+  </si>
+  <si>
+    <t>OTO Melara (76mm)</t>
+  </si>
+  <si>
+    <t>Mk 45 (127mm)</t>
+  </si>
+  <si>
+    <t>H/PJ-26 (76mm)</t>
+  </si>
+  <si>
+    <t>RBU-6000</t>
+  </si>
+  <si>
+    <t>RBU-2500</t>
+  </si>
+  <si>
+    <t>Type 87 ASW</t>
+  </si>
+  <si>
+    <t>Mk 32</t>
+  </si>
+  <si>
+    <t>Bofors ASW</t>
+  </si>
+  <si>
+    <t>H/JJ12 (122 mm)</t>
+  </si>
+  <si>
+    <t>RBU-1000 (300 mm)</t>
+  </si>
+  <si>
+    <t>Type 726-4A</t>
+  </si>
+  <si>
+    <t>Ikara</t>
+  </si>
+  <si>
+    <t>Australia</t>
+  </si>
+  <si>
+    <t>RUR-5B ASROC</t>
+  </si>
+  <si>
+    <t>HWHH-003B (300 mm)</t>
+  </si>
+  <si>
+    <t>RBU-12000 (300 mm)</t>
+  </si>
+  <si>
+    <t>Mark-46 (324 mm)</t>
+  </si>
+  <si>
+    <t>Yu-3 (324 mm)</t>
+  </si>
+  <si>
+    <t>SET-65 (533 mm)</t>
+  </si>
+  <si>
+    <t>A244 SLWT (324 mm)</t>
+  </si>
+  <si>
+    <t>Yu-7 (324 mm)</t>
+  </si>
+  <si>
+    <t>Type-12 (533 mm)</t>
+  </si>
+  <si>
+    <t>Black Shark (533 mm)</t>
+  </si>
+  <si>
+    <t>UGST Physic (533 mm)</t>
+  </si>
+  <si>
+    <t>Varunastra (533 mm)</t>
+  </si>
+  <si>
+    <t>Mark-48 (533 mm)</t>
+  </si>
+  <si>
+    <t>TA 53-65K (533 mm)</t>
+  </si>
+  <si>
+    <t>Spearfish</t>
+  </si>
+  <si>
+    <t>UK</t>
+  </si>
+  <si>
+    <t>Type-12</t>
+  </si>
+  <si>
+    <t>Black Shark</t>
+  </si>
+  <si>
+    <t>A244 SLWT</t>
+  </si>
+  <si>
+    <t>Varunastra</t>
+  </si>
+  <si>
+    <t>Type 73 (324 mm)</t>
+  </si>
+  <si>
+    <t>Type 89 (533 mm)</t>
+  </si>
+  <si>
+    <t>RAPIDFire (40 mm)</t>
+  </si>
+  <si>
+    <t>H/PJ-17 (30 mm)</t>
+  </si>
+  <si>
+    <t>3M-47 Gibka (Anti-Tank)</t>
+  </si>
+  <si>
+    <t>OTO Marlin 40 (40 mm)</t>
+  </si>
+  <si>
+    <t>MK-46 (30 mm)</t>
+  </si>
+  <si>
+    <t>Oerlikon Millennium (35 mm)</t>
+  </si>
+  <si>
+    <t>Switzerland</t>
+  </si>
+  <si>
+    <t>DP-65 (55 mm)</t>
+  </si>
+  <si>
+    <t>MK-19 (40 mm)</t>
+  </si>
+  <si>
+    <t>Oerlikon KCB (30 mm)</t>
+  </si>
+  <si>
+    <t>Bofors L/70 (40mm)</t>
+  </si>
+  <si>
+    <t>M242 Bushmaster (25 mm)</t>
+  </si>
+  <si>
+    <t>Bofors 40/L70 Mk.3 (40 mm)</t>
+  </si>
+  <si>
+    <t>Sea Defender (12.7 mm)</t>
+  </si>
+  <si>
+    <t>EU</t>
+  </si>
+  <si>
+    <t>AK-630 AA (30 mm)</t>
+  </si>
+  <si>
+    <t>HHQ-7</t>
+  </si>
+  <si>
+    <t>M-11 Shtorm</t>
+  </si>
+  <si>
+    <t>Mark 26 (SM-2)</t>
+  </si>
+  <si>
+    <t>Hitrole G (12.7 mm)</t>
+  </si>
+  <si>
+    <t>Phalanx CIWS (20 mm)</t>
+  </si>
+  <si>
+    <t>RIM-116 AA missiles</t>
+  </si>
+  <si>
+    <t>OSA-M</t>
+  </si>
+  <si>
+    <t>Kortik (30 mm)</t>
+  </si>
+  <si>
+    <t>H/PJ-12 (30 mm)</t>
+  </si>
+  <si>
+    <t>3M-47 Gibka</t>
+  </si>
+  <si>
+    <t>AK-630-2 AA (30 mm)</t>
+  </si>
+  <si>
+    <t>Garpun (30mm)</t>
+  </si>
+  <si>
+    <t>Crotale R440</t>
+  </si>
+  <si>
+    <t>Type 730C</t>
+  </si>
+  <si>
+    <t>3M89 Palash (30 mm)</t>
+  </si>
+  <si>
+    <t>ANSEQ-3</t>
+  </si>
+  <si>
+    <t>Pantsir-M (30 mm)</t>
+  </si>
+  <si>
+    <t>Sea RAM</t>
+  </si>
+  <si>
+    <t>RIM-7 Sea Sparrow</t>
+  </si>
+  <si>
+    <t>H/PJ-11 (30 mm)</t>
+  </si>
+  <si>
+    <t>HQ-10 (FL-3000N)</t>
+  </si>
+  <si>
+    <t>Kashtan-M (30 mm)</t>
+  </si>
+  <si>
+    <t>M-22 Uragan</t>
+  </si>
+  <si>
+    <t>KSAM Block 2</t>
+  </si>
+  <si>
+    <t>Excalibur PERHEL</t>
+  </si>
+  <si>
+    <t>Sea Snake (30 mm)</t>
+  </si>
+  <si>
+    <t>Germany</t>
+  </si>
+  <si>
+    <t>Goalkeeper CIWS</t>
+  </si>
+  <si>
+    <t>Netherlands</t>
+  </si>
+  <si>
+    <t>JS Mogami (FFM-1)</t>
+  </si>
+  <si>
+    <t>ROKS Daegu (FFG-818)</t>
+  </si>
+  <si>
+    <t>TCG Istanbul (F-515)</t>
+  </si>
+  <si>
+    <t>Turkey</t>
+  </si>
+  <si>
+    <t>KRI Raden Eddy Martadinata (331)</t>
+  </si>
+  <si>
+    <t>Indonesia</t>
+  </si>
+  <si>
+    <t>HMS Glasgow (Type 26)</t>
+  </si>
+  <si>
+    <t>RF Rusich-3000</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -718,6 +1363,11 @@
       <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF008000"/>
+      <name val="Calibri"/>
     </font>
   </fonts>
   <fills count="4">
@@ -778,7 +1428,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -794,21 +1444,28 @@
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1027,17 +1684,16 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <sheetPr filterMode="1">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:E185"/>
+  <dimension ref="A1:E304"/>
   <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="20.42578125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="9" customWidth="1"/>
-    <col min="3" max="3" width="0" hidden="1" customWidth="1"/>
-    <col min="4" max="4" width="11" customWidth="1"/>
+    <col min="4" max="4" width="16.28515625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="31" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="12.75" x14ac:dyDescent="0.2">
@@ -1045,2574 +1701,4635 @@
         <v>196</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="E1" s="1" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" ht="12.75" hidden="1" x14ac:dyDescent="0.2">
+    </row>
+    <row r="2" spans="1:5" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="C2" s="1">
+        <v>3</v>
+      </c>
+      <c r="D2" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="C2" s="1">
-        <v>3</v>
-      </c>
-      <c r="D2" s="1" t="s">
+      <c r="E2" s="1" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="3" spans="1:5" ht="12.75" hidden="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:5" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A3" s="9" t="s">
         <v>45</v>
       </c>
-      <c r="B3" s="11" t="s">
+      <c r="C3" s="1">
+        <v>3</v>
+      </c>
+      <c r="D3" s="11" t="s">
         <v>43</v>
       </c>
-      <c r="C3" s="1">
-        <v>3</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" ht="12.75" hidden="1" x14ac:dyDescent="0.2">
+      <c r="E3" s="1" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A4" s="9" t="s">
         <v>52</v>
       </c>
-      <c r="B4" s="11" t="s">
+      <c r="C4" s="1">
+        <v>3</v>
+      </c>
+      <c r="D4" s="11" t="s">
         <v>43</v>
       </c>
-      <c r="C4" s="1">
-        <v>3</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" ht="12.75" hidden="1" x14ac:dyDescent="0.2">
+      <c r="E4" s="1" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A5" s="9" t="s">
         <v>56</v>
       </c>
-      <c r="B5" s="11" t="s">
+      <c r="C5" s="1">
+        <v>3</v>
+      </c>
+      <c r="D5" s="11" t="s">
         <v>43</v>
       </c>
-      <c r="C5" s="1">
-        <v>3</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" ht="12.75" hidden="1" x14ac:dyDescent="0.2">
+      <c r="E5" s="1" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A6" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="B6" s="11" t="s">
+      <c r="C6" s="1">
+        <v>3</v>
+      </c>
+      <c r="D6" s="11" t="s">
         <v>60</v>
       </c>
-      <c r="C6" s="1">
-        <v>3</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" ht="12.75" hidden="1" x14ac:dyDescent="0.2">
+      <c r="E6" s="1" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A7" s="9" t="s">
         <v>191</v>
       </c>
-      <c r="B7" s="11" t="s">
+      <c r="C7" s="12">
+        <v>3</v>
+      </c>
+      <c r="D7" s="11" t="s">
         <v>60</v>
       </c>
-      <c r="C7" s="12">
-        <v>3</v>
-      </c>
-      <c r="D7" s="1" t="s">
+      <c r="E7" s="1" t="s">
         <v>185</v>
       </c>
     </row>
-    <row r="8" spans="1:5" ht="12.75" hidden="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:5" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A8" s="10" t="s">
         <v>82</v>
       </c>
-      <c r="B8" s="11" t="s">
+      <c r="C8" s="1">
+        <v>3</v>
+      </c>
+      <c r="D8" s="11" t="s">
         <v>83</v>
       </c>
-      <c r="C8" s="1">
-        <v>3</v>
-      </c>
-      <c r="D8" s="1" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" ht="12.75" hidden="1" x14ac:dyDescent="0.2">
+      <c r="E8" s="1" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A9" s="10" t="s">
         <v>85</v>
       </c>
-      <c r="B9" s="11" t="s">
+      <c r="C9" s="1">
+        <v>3</v>
+      </c>
+      <c r="D9" s="11" t="s">
         <v>83</v>
       </c>
-      <c r="C9" s="1">
-        <v>3</v>
-      </c>
-      <c r="D9" s="1" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" ht="12.75" hidden="1" x14ac:dyDescent="0.2">
+      <c r="E9" s="1" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A10" s="10" t="s">
         <v>103</v>
       </c>
-      <c r="B10" s="11" t="s">
+      <c r="C10" s="1">
+        <v>3</v>
+      </c>
+      <c r="D10" s="11" t="s">
         <v>83</v>
       </c>
-      <c r="C10" s="1">
-        <v>3</v>
-      </c>
-      <c r="D10" s="1" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" ht="12.75" hidden="1" x14ac:dyDescent="0.2">
+      <c r="E10" s="1" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A11" s="7" t="s">
         <v>140</v>
       </c>
-      <c r="B11" s="11" t="s">
+      <c r="C11" s="1">
+        <v>3</v>
+      </c>
+      <c r="D11" s="11" t="s">
         <v>83</v>
       </c>
-      <c r="C11" s="1">
-        <v>3</v>
-      </c>
-      <c r="D11" s="1" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" ht="12.75" hidden="1" x14ac:dyDescent="0.2">
+      <c r="E11" s="1" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A12" s="9" t="s">
         <v>162</v>
       </c>
-      <c r="B12" s="11" t="s">
+      <c r="C12" s="12">
+        <v>3</v>
+      </c>
+      <c r="D12" s="11" t="s">
         <v>83</v>
       </c>
-      <c r="C12" s="12">
-        <v>3</v>
-      </c>
-      <c r="D12" s="1" t="s">
+      <c r="E12" s="1" t="s">
         <v>175</v>
       </c>
     </row>
-    <row r="13" spans="1:5" ht="12.75" hidden="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:5" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A13" s="9" t="s">
         <v>166</v>
       </c>
-      <c r="B13" s="11" t="s">
+      <c r="C13" s="12">
+        <v>3</v>
+      </c>
+      <c r="D13" s="11" t="s">
         <v>83</v>
       </c>
-      <c r="C13" s="12">
-        <v>3</v>
-      </c>
-      <c r="D13" s="1" t="s">
+      <c r="E13" s="1" t="s">
         <v>175</v>
       </c>
     </row>
-    <row r="14" spans="1:5" ht="12.75" hidden="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:5" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A14" s="7" t="s">
         <v>172</v>
       </c>
-      <c r="B14" s="11" t="s">
+      <c r="C14" s="12">
+        <v>3</v>
+      </c>
+      <c r="D14" s="11" t="s">
         <v>83</v>
       </c>
-      <c r="C14" s="12">
-        <v>3</v>
-      </c>
-      <c r="D14" s="1" t="s">
+      <c r="E14" s="1" t="s">
         <v>175</v>
       </c>
     </row>
-    <row r="15" spans="1:5" ht="12.75" hidden="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:5" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A15" s="9" t="s">
         <v>180</v>
       </c>
-      <c r="B15" s="11" t="s">
+      <c r="C15" s="12">
+        <v>3</v>
+      </c>
+      <c r="D15" s="11" t="s">
         <v>83</v>
       </c>
-      <c r="C15" s="12">
-        <v>3</v>
-      </c>
-      <c r="D15" s="1" t="s">
+      <c r="E15" s="1" t="s">
         <v>185</v>
       </c>
     </row>
-    <row r="16" spans="1:5" ht="12.75" hidden="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:5" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A16" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="B16" s="1" t="s">
+      <c r="C16" s="1">
+        <v>3</v>
+      </c>
+      <c r="D16" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="C16" s="1">
-        <v>3</v>
-      </c>
-      <c r="D16" s="1" t="s">
+      <c r="E16" s="1" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="17" spans="1:4" ht="12.75" hidden="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:5" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A17" s="9" t="s">
         <v>54</v>
       </c>
-      <c r="B17" s="11" t="s">
+      <c r="C17" s="1">
+        <v>3</v>
+      </c>
+      <c r="D17" s="11" t="s">
         <v>11</v>
       </c>
-      <c r="C17" s="1">
-        <v>3</v>
-      </c>
-      <c r="D17" s="1" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4" ht="12.75" hidden="1" x14ac:dyDescent="0.2">
+      <c r="E17" s="1" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A18" s="9" t="s">
         <v>58</v>
       </c>
-      <c r="B18" s="11" t="s">
+      <c r="C18" s="1">
+        <v>3</v>
+      </c>
+      <c r="D18" s="11" t="s">
         <v>11</v>
       </c>
-      <c r="C18" s="1">
-        <v>3</v>
-      </c>
-      <c r="D18" s="1" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="E18" s="1" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A19" s="10" t="s">
         <v>86</v>
       </c>
-      <c r="B19" s="11" t="s">
+      <c r="C19" s="1">
+        <v>3</v>
+      </c>
+      <c r="D19" s="11" t="s">
         <v>87</v>
       </c>
-      <c r="C19" s="1">
-        <v>3</v>
-      </c>
-      <c r="D19" s="1" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="E19" s="1" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A20" s="9" t="s">
         <v>220</v>
       </c>
-      <c r="B20" s="11" t="s">
+      <c r="C20" s="1">
+        <v>3</v>
+      </c>
+      <c r="D20" s="11" t="s">
         <v>87</v>
       </c>
-      <c r="C20" s="1">
-        <v>3</v>
-      </c>
-      <c r="D20" s="1" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="E20" s="1" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A21" s="9" t="s">
         <v>219</v>
       </c>
-      <c r="B21" s="11" t="s">
+      <c r="C21" s="12">
+        <v>3</v>
+      </c>
+      <c r="D21" s="11" t="s">
         <v>87</v>
       </c>
-      <c r="C21" s="12">
-        <v>3</v>
-      </c>
-      <c r="D21" s="1" t="s">
+      <c r="E21" s="1" t="s">
         <v>175</v>
       </c>
     </row>
-    <row r="22" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:5" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A22" s="7" t="s">
         <v>174</v>
       </c>
-      <c r="B22" s="11" t="s">
+      <c r="C22" s="12">
+        <v>3</v>
+      </c>
+      <c r="D22" s="11" t="s">
         <v>87</v>
       </c>
-      <c r="C22" s="12">
-        <v>3</v>
-      </c>
-      <c r="D22" s="1" t="s">
+      <c r="E22" s="1" t="s">
         <v>175</v>
       </c>
     </row>
-    <row r="23" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:5" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A23" s="9" t="s">
         <v>221</v>
       </c>
-      <c r="B23" s="11" t="s">
+      <c r="C23" s="12">
+        <v>3</v>
+      </c>
+      <c r="D23" s="11" t="s">
         <v>87</v>
       </c>
-      <c r="C23" s="12">
-        <v>3</v>
-      </c>
-      <c r="D23" s="1" t="s">
+      <c r="E23" s="1" t="s">
         <v>185</v>
       </c>
     </row>
-    <row r="24" spans="1:4" ht="12.75" hidden="1" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:5" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A24" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="B24" s="1" t="s">
+      <c r="C24" s="1">
+        <v>3</v>
+      </c>
+      <c r="D24" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="C24" s="1">
-        <v>3</v>
-      </c>
-      <c r="D24" s="1" t="s">
+      <c r="E24" s="1" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="25" spans="1:4" ht="12.75" hidden="1" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:5" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A25" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="B25" s="1" t="s">
+      <c r="C25" s="1">
+        <v>3</v>
+      </c>
+      <c r="D25" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="C25" s="1">
-        <v>3</v>
-      </c>
-      <c r="D25" s="1" t="s">
+      <c r="E25" s="1" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="26" spans="1:4" ht="12.75" hidden="1" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:5" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A26" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="B26" s="1" t="s">
+      <c r="C26" s="1">
+        <v>3</v>
+      </c>
+      <c r="D26" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="C26" s="1">
-        <v>3</v>
-      </c>
-      <c r="D26" s="1" t="s">
+      <c r="E26" s="1" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="27" spans="1:4" ht="12.75" hidden="1" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:5" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A27" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="B27" s="1" t="s">
+      <c r="C27" s="1">
+        <v>3</v>
+      </c>
+      <c r="D27" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="C27" s="1">
-        <v>3</v>
-      </c>
-      <c r="D27" s="1" t="s">
+      <c r="E27" s="1" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="28" spans="1:4" ht="12.75" hidden="1" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:5" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A28" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="B28" s="1" t="s">
+      <c r="C28" s="1">
+        <v>3</v>
+      </c>
+      <c r="D28" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="C28" s="1">
-        <v>3</v>
-      </c>
-      <c r="D28" s="1" t="s">
+      <c r="E28" s="1" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="29" spans="1:4" ht="12.75" hidden="1" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:5" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A29" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="B29" s="1" t="s">
+      <c r="C29" s="1">
+        <v>3</v>
+      </c>
+      <c r="D29" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="C29" s="1">
-        <v>3</v>
-      </c>
-      <c r="D29" s="1" t="s">
+      <c r="E29" s="1" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="30" spans="1:4" ht="12.75" hidden="1" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:5" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A30" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="B30" s="1" t="s">
+      <c r="C30" s="1">
+        <v>3</v>
+      </c>
+      <c r="D30" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="C30" s="1">
-        <v>3</v>
-      </c>
-      <c r="D30" s="1" t="s">
+      <c r="E30" s="1" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="31" spans="1:4" ht="12.75" hidden="1" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:5" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A31" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="B31" s="1" t="s">
+      <c r="C31" s="1">
+        <v>3</v>
+      </c>
+      <c r="D31" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="C31" s="1">
-        <v>3</v>
-      </c>
-      <c r="D31" s="1" t="s">
+      <c r="E31" s="1" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="32" spans="1:4" ht="12.75" hidden="1" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:5" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A32" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="B32" s="1" t="s">
+      <c r="C32" s="1">
+        <v>3</v>
+      </c>
+      <c r="D32" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="C32" s="1">
-        <v>3</v>
-      </c>
-      <c r="D32" s="1" t="s">
+      <c r="E32" s="1" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="33" spans="1:4" ht="12.75" hidden="1" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:5" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A33" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="B33" s="1" t="s">
+      <c r="C33" s="1">
+        <v>3</v>
+      </c>
+      <c r="D33" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="C33" s="1">
-        <v>3</v>
-      </c>
-      <c r="D33" s="1" t="s">
+      <c r="E33" s="1" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="34" spans="1:4" ht="12.75" hidden="1" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:5" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A34" s="9" t="s">
         <v>63</v>
       </c>
-      <c r="B34" s="11" t="s">
+      <c r="C34" s="1">
+        <v>3</v>
+      </c>
+      <c r="D34" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="C34" s="1">
-        <v>3</v>
-      </c>
-      <c r="D34" s="1" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="35" spans="1:4" ht="12.75" hidden="1" x14ac:dyDescent="0.2">
+      <c r="E34" s="1" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A35" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="B35" s="3" t="s">
+      <c r="C35" s="1">
+        <v>3</v>
+      </c>
+      <c r="D35" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="C35" s="1">
-        <v>3</v>
-      </c>
-      <c r="D35" s="1" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="36" spans="1:4" ht="12.75" hidden="1" x14ac:dyDescent="0.2">
+      <c r="E35" s="1" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A36" s="2" t="s">
         <v>187</v>
       </c>
-      <c r="B36" s="3" t="s">
+      <c r="C36" s="12">
+        <v>3</v>
+      </c>
+      <c r="D36" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="C36" s="12">
-        <v>3</v>
-      </c>
-      <c r="D36" s="1" t="s">
+      <c r="E36" s="1" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="37" spans="1:4" ht="12.75" hidden="1" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:5" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A37" s="2" t="s">
         <v>188</v>
       </c>
-      <c r="B37" s="3" t="s">
+      <c r="C37" s="12">
+        <v>3</v>
+      </c>
+      <c r="D37" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="C37" s="12">
-        <v>3</v>
-      </c>
-      <c r="D37" s="1" t="s">
+      <c r="E37" s="1" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="38" spans="1:4" ht="12.75" hidden="1" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:5" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A38" s="2" t="s">
         <v>143</v>
       </c>
-      <c r="B38" s="3" t="s">
+      <c r="C38" s="12">
+        <v>3</v>
+      </c>
+      <c r="D38" s="3" t="s">
         <v>144</v>
       </c>
-      <c r="C38" s="12">
-        <v>3</v>
-      </c>
-      <c r="D38" s="1" t="s">
+      <c r="E38" s="1" t="s">
         <v>175</v>
       </c>
     </row>
-    <row r="39" spans="1:4" ht="12.75" hidden="1" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:5" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A39" s="5" t="s">
         <v>197</v>
       </c>
-      <c r="B39" s="3" t="s">
+      <c r="C39" s="1">
+        <v>3</v>
+      </c>
+      <c r="D39" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="C39" s="1">
-        <v>3</v>
-      </c>
-      <c r="D39" s="1" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="40" spans="1:4" ht="12.75" hidden="1" x14ac:dyDescent="0.2">
+      <c r="E39" s="1" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A40" s="4" t="s">
         <v>198</v>
       </c>
-      <c r="B40" s="3" t="s">
+      <c r="C40" s="1">
+        <v>3</v>
+      </c>
+      <c r="D40" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="C40" s="1">
-        <v>3</v>
-      </c>
-      <c r="D40" s="1" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="41" spans="1:4" ht="12.75" hidden="1" x14ac:dyDescent="0.2">
+      <c r="E40" s="1" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A41" s="5" t="s">
         <v>111</v>
       </c>
-      <c r="B41" s="3" t="s">
+      <c r="C41" s="1">
+        <v>3</v>
+      </c>
+      <c r="D41" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="C41" s="1">
-        <v>3</v>
-      </c>
-      <c r="D41" s="1" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="42" spans="1:4" ht="12.75" hidden="1" x14ac:dyDescent="0.2">
+      <c r="E41" s="1" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A42" s="5" t="s">
         <v>116</v>
       </c>
-      <c r="B42" s="3" t="s">
+      <c r="C42" s="1">
+        <v>3</v>
+      </c>
+      <c r="D42" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="C42" s="1">
-        <v>3</v>
-      </c>
-      <c r="D42" s="1" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="43" spans="1:4" ht="12.75" hidden="1" x14ac:dyDescent="0.2">
+      <c r="E42" s="1" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A43" s="5" t="s">
         <v>124</v>
       </c>
-      <c r="B43" s="3" t="s">
+      <c r="C43" s="1">
+        <v>3</v>
+      </c>
+      <c r="D43" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="C43" s="1">
-        <v>3</v>
-      </c>
-      <c r="D43" s="1" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="44" spans="1:4" ht="12.75" hidden="1" x14ac:dyDescent="0.2">
+      <c r="E43" s="1" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A44" s="5" t="s">
         <v>127</v>
       </c>
-      <c r="B44" s="3" t="s">
+      <c r="C44" s="1">
+        <v>3</v>
+      </c>
+      <c r="D44" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="C44" s="1">
-        <v>3</v>
-      </c>
-      <c r="D44" s="1" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="45" spans="1:4" ht="12.75" hidden="1" x14ac:dyDescent="0.2">
+      <c r="E44" s="1" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A45" s="2" t="s">
         <v>128</v>
       </c>
-      <c r="B45" s="3" t="s">
+      <c r="C45" s="1">
+        <v>3</v>
+      </c>
+      <c r="D45" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="C45" s="1">
-        <v>3</v>
-      </c>
-      <c r="D45" s="1" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="46" spans="1:4" ht="12.75" hidden="1" x14ac:dyDescent="0.2">
+      <c r="E45" s="1" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A46" s="2" t="s">
         <v>133</v>
       </c>
-      <c r="B46" s="3" t="s">
+      <c r="C46" s="1">
+        <v>3</v>
+      </c>
+      <c r="D46" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="C46" s="1">
-        <v>3</v>
-      </c>
-      <c r="D46" s="1" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="47" spans="1:4" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E46" s="1" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A47" s="2" t="s">
         <v>136</v>
       </c>
-      <c r="B47" s="3" t="s">
+      <c r="C47" s="1">
+        <v>3</v>
+      </c>
+      <c r="D47" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="C47" s="1">
-        <v>3</v>
-      </c>
-      <c r="D47" s="1" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="48" spans="1:4" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E47" s="1" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A48" s="2" t="s">
         <v>155</v>
       </c>
-      <c r="B48" s="3" t="s">
+      <c r="C48" s="12">
+        <v>3</v>
+      </c>
+      <c r="D48" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="C48" s="12">
-        <v>3</v>
-      </c>
-      <c r="D48" s="1" t="s">
+      <c r="E48" s="1" t="s">
         <v>175</v>
       </c>
     </row>
-    <row r="49" spans="1:4" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A49" s="2" t="s">
         <v>158</v>
       </c>
-      <c r="B49" s="3" t="s">
+      <c r="C49" s="12">
+        <v>3</v>
+      </c>
+      <c r="D49" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="C49" s="12">
-        <v>3</v>
-      </c>
-      <c r="D49" s="1" t="s">
+      <c r="E49" s="1" t="s">
         <v>175</v>
       </c>
     </row>
-    <row r="50" spans="1:4" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A50" s="2" t="s">
         <v>161</v>
       </c>
-      <c r="B50" s="3" t="s">
+      <c r="C50" s="12">
+        <v>3</v>
+      </c>
+      <c r="D50" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="C50" s="12">
-        <v>3</v>
-      </c>
-      <c r="D50" s="1" t="s">
+      <c r="E50" s="1" t="s">
         <v>175</v>
       </c>
     </row>
-    <row r="51" spans="1:4" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A51" s="2" t="s">
         <v>163</v>
       </c>
-      <c r="B51" s="3" t="s">
+      <c r="C51" s="12">
+        <v>3</v>
+      </c>
+      <c r="D51" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="C51" s="12">
-        <v>3</v>
-      </c>
-      <c r="D51" s="1" t="s">
+      <c r="E51" s="1" t="s">
         <v>175</v>
       </c>
     </row>
-    <row r="52" spans="1:4" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A52" s="2" t="s">
         <v>164</v>
       </c>
-      <c r="B52" s="3" t="s">
+      <c r="C52" s="12">
+        <v>3</v>
+      </c>
+      <c r="D52" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="C52" s="12">
-        <v>3</v>
-      </c>
-      <c r="D52" s="1" t="s">
+      <c r="E52" s="1" t="s">
         <v>175</v>
       </c>
     </row>
-    <row r="53" spans="1:4" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A53" s="2" t="s">
         <v>182</v>
       </c>
-      <c r="B53" s="3" t="s">
+      <c r="C53" s="12">
+        <v>3</v>
+      </c>
+      <c r="D53" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="C53" s="12">
-        <v>3</v>
-      </c>
-      <c r="D53" s="1" t="s">
+      <c r="E53" s="1" t="s">
         <v>185</v>
       </c>
     </row>
-    <row r="54" spans="1:4" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A54" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="B54" s="3" t="s">
+      <c r="C54" s="1">
+        <v>3</v>
+      </c>
+      <c r="D54" s="3" t="s">
         <v>73</v>
       </c>
-      <c r="C54" s="1">
-        <v>3</v>
-      </c>
-      <c r="D54" s="1" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="55" spans="1:4" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E54" s="1" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A55" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="B55" s="8" t="s">
+      <c r="C55" s="1">
+        <v>3</v>
+      </c>
+      <c r="D55" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="C55" s="1">
-        <v>3</v>
-      </c>
-      <c r="D55" s="1" t="s">
+      <c r="E55" s="1" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="56" spans="1:4" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A56" s="8" t="s">
         <v>199</v>
       </c>
-      <c r="B56" s="8" t="s">
+      <c r="C56" s="1">
+        <v>3</v>
+      </c>
+      <c r="D56" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="C56" s="1">
-        <v>3</v>
-      </c>
-      <c r="D56" s="1" t="s">
+      <c r="E56" s="1" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="57" spans="1:4" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A57" s="8" t="s">
         <v>200</v>
       </c>
-      <c r="B57" s="8" t="s">
+      <c r="C57" s="1">
+        <v>3</v>
+      </c>
+      <c r="D57" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="C57" s="1">
-        <v>3</v>
-      </c>
-      <c r="D57" s="1" t="s">
+      <c r="E57" s="1" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="58" spans="1:4" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A58" s="8" t="s">
         <v>201</v>
       </c>
-      <c r="B58" s="8" t="s">
+      <c r="C58" s="1">
+        <v>3</v>
+      </c>
+      <c r="D58" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="C58" s="1">
-        <v>3</v>
-      </c>
-      <c r="D58" s="1" t="s">
+      <c r="E58" s="1" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="59" spans="1:4" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A59" s="8" t="s">
         <v>29</v>
       </c>
-      <c r="B59" s="8" t="s">
+      <c r="C59" s="1">
+        <v>3</v>
+      </c>
+      <c r="D59" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="C59" s="1">
-        <v>3</v>
-      </c>
-      <c r="D59" s="1" t="s">
+      <c r="E59" s="1" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="60" spans="1:4" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A60" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="B60" s="8" t="s">
+      <c r="C60" s="1">
+        <v>3</v>
+      </c>
+      <c r="D60" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="C60" s="1">
-        <v>3</v>
-      </c>
-      <c r="D60" s="1" t="s">
+      <c r="E60" s="1" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="61" spans="1:4" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A61" s="8" t="s">
         <v>35</v>
       </c>
-      <c r="B61" s="8" t="s">
+      <c r="C61" s="1">
+        <v>3</v>
+      </c>
+      <c r="D61" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="C61" s="1">
-        <v>3</v>
-      </c>
-      <c r="D61" s="1" t="s">
+      <c r="E61" s="1" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="62" spans="1:4" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A62" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="B62" s="8" t="s">
+      <c r="C62" s="1">
+        <v>3</v>
+      </c>
+      <c r="D62" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="C62" s="1">
-        <v>3</v>
-      </c>
-      <c r="D62" s="1" t="s">
+      <c r="E62" s="1" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="63" spans="1:4" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A63" s="8" t="s">
         <v>39</v>
       </c>
-      <c r="B63" s="8" t="s">
+      <c r="C63" s="1">
+        <v>3</v>
+      </c>
+      <c r="D63" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="C63" s="1">
-        <v>3</v>
-      </c>
-      <c r="D63" s="1" t="s">
+      <c r="E63" s="1" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="64" spans="1:4" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A64" s="8" t="s">
         <v>44</v>
       </c>
-      <c r="B64" s="8" t="s">
+      <c r="C64" s="1">
+        <v>3</v>
+      </c>
+      <c r="D64" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="C64" s="1">
-        <v>3</v>
-      </c>
-      <c r="D64" s="1" t="s">
+      <c r="E64" s="1" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="65" spans="1:4" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A65" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="B65" s="3" t="s">
+      <c r="C65" s="1">
+        <v>3</v>
+      </c>
+      <c r="D65" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="C65" s="1">
-        <v>3</v>
-      </c>
-      <c r="D65" s="1" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="66" spans="1:4" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E65" s="1" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A66" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="B66" s="3" t="s">
+      <c r="C66" s="1">
+        <v>3</v>
+      </c>
+      <c r="D66" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="C66" s="1">
-        <v>3</v>
-      </c>
-      <c r="D66" s="1" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="67" spans="1:4" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E66" s="1" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A67" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="B67" s="3" t="s">
+      <c r="C67" s="1">
+        <v>3</v>
+      </c>
+      <c r="D67" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="C67" s="1">
-        <v>3</v>
-      </c>
-      <c r="D67" s="1" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="68" spans="1:4" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E67" s="1" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A68" s="2" t="s">
         <v>186</v>
       </c>
-      <c r="B68" s="3" t="s">
+      <c r="C68" s="12">
+        <v>3</v>
+      </c>
+      <c r="D68" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="C68" s="12">
-        <v>3</v>
-      </c>
-      <c r="D68" s="1" t="s">
+      <c r="E68" s="1" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="69" spans="1:4" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A69" s="2" t="s">
         <v>192</v>
       </c>
-      <c r="B69" s="3" t="s">
+      <c r="C69" s="12">
+        <v>3</v>
+      </c>
+      <c r="D69" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="C69" s="12">
-        <v>3</v>
-      </c>
-      <c r="D69" s="1" t="s">
+      <c r="E69" s="1" t="s">
         <v>185</v>
       </c>
     </row>
-    <row r="70" spans="1:4" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A70" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="B70" s="8" t="s">
+      <c r="C70" s="1">
+        <v>3</v>
+      </c>
+      <c r="D70" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="C70" s="1">
-        <v>3</v>
-      </c>
-      <c r="D70" s="1" t="s">
+      <c r="E70" s="1" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="71" spans="1:4" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A71" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="B71" s="8" t="s">
+      <c r="C71" s="1">
+        <v>3</v>
+      </c>
+      <c r="D71" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="C71" s="1">
-        <v>3</v>
-      </c>
-      <c r="D71" s="1" t="s">
+      <c r="E71" s="1" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="72" spans="1:4" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A72" s="8" t="s">
         <v>24</v>
       </c>
-      <c r="B72" s="8" t="s">
+      <c r="C72" s="1">
+        <v>3</v>
+      </c>
+      <c r="D72" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="C72" s="1">
-        <v>3</v>
-      </c>
-      <c r="D72" s="1" t="s">
+      <c r="E72" s="1" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="73" spans="1:4" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A73" s="8" t="s">
         <v>30</v>
       </c>
-      <c r="B73" s="8" t="s">
+      <c r="C73" s="1">
+        <v>3</v>
+      </c>
+      <c r="D73" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="C73" s="1">
-        <v>3</v>
-      </c>
-      <c r="D73" s="1" t="s">
+      <c r="E73" s="1" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="74" spans="1:4" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A74" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="B74" s="8" t="s">
+      <c r="C74" s="1">
+        <v>3</v>
+      </c>
+      <c r="D74" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="C74" s="1">
-        <v>3</v>
-      </c>
-      <c r="D74" s="1" t="s">
+      <c r="E74" s="1" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="75" spans="1:4" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A75" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="B75" s="3" t="s">
+      <c r="C75" s="1">
+        <v>3</v>
+      </c>
+      <c r="D75" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="C75" s="1">
-        <v>3</v>
-      </c>
-      <c r="D75" s="1" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="76" spans="1:4" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E75" s="1" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="76" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A76" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="B76" s="3" t="s">
+      <c r="C76" s="1">
+        <v>3</v>
+      </c>
+      <c r="D76" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="C76" s="1">
-        <v>3</v>
-      </c>
-      <c r="D76" s="1" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="77" spans="1:4" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E76" s="1" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="77" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A77" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="B77" s="3" t="s">
+      <c r="C77" s="1">
+        <v>3</v>
+      </c>
+      <c r="D77" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="C77" s="1">
-        <v>3</v>
-      </c>
-      <c r="D77" s="1" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="78" spans="1:4" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E77" s="1" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="78" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A78" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="B78" s="3" t="s">
+      <c r="C78" s="1">
+        <v>3</v>
+      </c>
+      <c r="D78" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="C78" s="1">
-        <v>3</v>
-      </c>
-      <c r="D78" s="1" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="79" spans="1:4" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E78" s="1" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="79" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A79" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="B79" s="3" t="s">
+      <c r="C79" s="1">
+        <v>3</v>
+      </c>
+      <c r="D79" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="C79" s="1">
-        <v>3</v>
-      </c>
-      <c r="D79" s="1" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="80" spans="1:4" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E79" s="1" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="80" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A80" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="B80" s="3" t="s">
+      <c r="C80" s="1">
+        <v>3</v>
+      </c>
+      <c r="D80" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="C80" s="1">
-        <v>3</v>
-      </c>
-      <c r="D80" s="1" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="81" spans="1:4" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E80" s="1" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="81" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A81" s="4" t="s">
         <v>77</v>
       </c>
-      <c r="B81" s="3" t="s">
+      <c r="C81" s="1">
+        <v>3</v>
+      </c>
+      <c r="D81" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="C81" s="1">
-        <v>3</v>
-      </c>
-      <c r="D81" s="1" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="82" spans="1:4" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E81" s="1" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="82" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A82" s="4" t="s">
         <v>78</v>
       </c>
-      <c r="B82" s="3" t="s">
+      <c r="C82" s="1">
+        <v>3</v>
+      </c>
+      <c r="D82" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="C82" s="1">
-        <v>3</v>
-      </c>
-      <c r="D82" s="1" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="83" spans="1:4" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E82" s="1" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="83" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A83" s="2" t="s">
         <v>189</v>
       </c>
-      <c r="B83" s="3" t="s">
+      <c r="C83" s="12">
+        <v>3</v>
+      </c>
+      <c r="D83" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="C83" s="12">
-        <v>3</v>
-      </c>
-      <c r="D83" s="1" t="s">
+      <c r="E83" s="1" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="84" spans="1:4" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A84" s="2" t="s">
         <v>190</v>
       </c>
-      <c r="B84" s="3" t="s">
+      <c r="C84" s="12">
+        <v>3</v>
+      </c>
+      <c r="D84" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="C84" s="12">
-        <v>3</v>
-      </c>
-      <c r="D84" s="1" t="s">
+      <c r="E84" s="1" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="85" spans="1:4" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A85" s="2" t="s">
         <v>195</v>
       </c>
-      <c r="B85" s="3" t="s">
+      <c r="C85" s="12">
+        <v>3</v>
+      </c>
+      <c r="D85" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="C85" s="12">
-        <v>3</v>
-      </c>
-      <c r="D85" s="1" t="s">
+      <c r="E85" s="1" t="s">
         <v>185</v>
       </c>
     </row>
-    <row r="86" spans="1:4" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A86" s="2" t="s">
         <v>145</v>
       </c>
-      <c r="B86" s="3" t="s">
+      <c r="C86" s="12">
+        <v>3</v>
+      </c>
+      <c r="D86" s="3" t="s">
         <v>146</v>
       </c>
-      <c r="C86" s="12">
-        <v>3</v>
-      </c>
-      <c r="D86" s="1" t="s">
+      <c r="E86" s="1" t="s">
         <v>175</v>
       </c>
     </row>
-    <row r="87" spans="1:4" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A87" s="2" t="s">
         <v>150</v>
       </c>
-      <c r="B87" s="3" t="s">
+      <c r="C87" s="12">
+        <v>3</v>
+      </c>
+      <c r="D87" s="3" t="s">
         <v>146</v>
       </c>
-      <c r="C87" s="12">
-        <v>3</v>
-      </c>
-      <c r="D87" s="1" t="s">
+      <c r="E87" s="1" t="s">
         <v>175</v>
       </c>
     </row>
-    <row r="88" spans="1:4" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A88" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="B88" s="8" t="s">
+      <c r="C88" s="1">
+        <v>3</v>
+      </c>
+      <c r="D88" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="C88" s="1">
-        <v>3</v>
-      </c>
-      <c r="D88" s="1" t="s">
+      <c r="E88" s="1" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="89" spans="1:4" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A89" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="B89" s="3" t="s">
+      <c r="C89" s="1">
+        <v>3</v>
+      </c>
+      <c r="D89" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C89" s="1">
-        <v>3</v>
-      </c>
-      <c r="D89" s="1" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="90" spans="1:4" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E89" s="1" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="90" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A90" s="2" t="s">
         <v>167</v>
       </c>
-      <c r="B90" s="3" t="s">
+      <c r="C90" s="12">
+        <v>3</v>
+      </c>
+      <c r="D90" s="3" t="s">
         <v>168</v>
       </c>
-      <c r="C90" s="12">
-        <v>3</v>
-      </c>
-      <c r="D90" s="1" t="s">
+      <c r="E90" s="1" t="s">
         <v>175</v>
       </c>
     </row>
-    <row r="91" spans="1:4" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A91" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="B91" s="3" t="s">
+      <c r="C91" s="1">
+        <v>3</v>
+      </c>
+      <c r="D91" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="C91" s="1">
-        <v>3</v>
-      </c>
-      <c r="D91" s="1" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="92" spans="1:4" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E91" s="1" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="92" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A92" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="B92" s="3" t="s">
+      <c r="C92" s="1">
+        <v>3</v>
+      </c>
+      <c r="D92" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="C92" s="1">
-        <v>3</v>
-      </c>
-      <c r="D92" s="1" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="93" spans="1:4" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E92" s="1" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="93" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A93" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="B93" s="3" t="s">
+      <c r="C93" s="1">
+        <v>3</v>
+      </c>
+      <c r="D93" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="C93" s="1">
-        <v>3</v>
-      </c>
-      <c r="D93" s="1" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="94" spans="1:4" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E93" s="1" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="94" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A94" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="B94" s="3" t="s">
+      <c r="C94" s="1">
+        <v>3</v>
+      </c>
+      <c r="D94" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="C94" s="1">
-        <v>3</v>
-      </c>
-      <c r="D94" s="1" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="95" spans="1:4" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E94" s="1" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="95" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A95" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="B95" s="3" t="s">
+      <c r="C95" s="1">
+        <v>3</v>
+      </c>
+      <c r="D95" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="C95" s="1">
-        <v>3</v>
-      </c>
-      <c r="D95" s="1" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="96" spans="1:4" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E95" s="1" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="96" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A96" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="B96" s="3" t="s">
+      <c r="C96" s="1">
+        <v>3</v>
+      </c>
+      <c r="D96" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="C96" s="1">
-        <v>3</v>
-      </c>
-      <c r="D96" s="1" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="97" spans="1:4" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E96" s="1" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="97" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A97" s="4" t="s">
         <v>76</v>
       </c>
-      <c r="B97" s="3" t="s">
+      <c r="C97" s="1">
+        <v>3</v>
+      </c>
+      <c r="D97" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="C97" s="1">
-        <v>3</v>
-      </c>
-      <c r="D97" s="1" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="98" spans="1:4" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E97" s="1" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="98" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A98" s="2" t="s">
         <v>193</v>
       </c>
-      <c r="B98" s="3" t="s">
+      <c r="C98" s="12">
+        <v>3</v>
+      </c>
+      <c r="D98" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="C98" s="12">
-        <v>3</v>
-      </c>
-      <c r="D98" s="1" t="s">
+      <c r="E98" s="1" t="s">
         <v>185</v>
       </c>
     </row>
-    <row r="99" spans="1:4" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="99" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A99" s="2" t="s">
         <v>99</v>
       </c>
-      <c r="B99" s="3" t="s">
+      <c r="C99" s="1">
+        <v>3</v>
+      </c>
+      <c r="D99" s="3" t="s">
         <v>100</v>
       </c>
-      <c r="C99" s="1">
-        <v>3</v>
-      </c>
-      <c r="D99" s="1" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="100" spans="1:4" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E99" s="1" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="100" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A100" s="5" t="s">
         <v>120</v>
       </c>
-      <c r="B100" s="3" t="s">
+      <c r="C100" s="1">
+        <v>3</v>
+      </c>
+      <c r="D100" s="3" t="s">
         <v>100</v>
       </c>
-      <c r="C100" s="1">
-        <v>3</v>
-      </c>
-      <c r="D100" s="1" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="101" spans="1:4" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E100" s="1" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="101" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A101" s="2" t="s">
         <v>132</v>
       </c>
-      <c r="B101" s="3" t="s">
+      <c r="C101" s="1">
+        <v>3</v>
+      </c>
+      <c r="D101" s="3" t="s">
         <v>100</v>
       </c>
-      <c r="C101" s="1">
-        <v>3</v>
-      </c>
-      <c r="D101" s="1" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="102" spans="1:4" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E101" s="1" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="102" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A102" s="2" t="s">
         <v>134</v>
       </c>
-      <c r="B102" s="3" t="s">
+      <c r="C102" s="1">
+        <v>3</v>
+      </c>
+      <c r="D102" s="3" t="s">
         <v>100</v>
       </c>
-      <c r="C102" s="1">
-        <v>3</v>
-      </c>
-      <c r="D102" s="1" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="103" spans="1:4" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E102" s="1" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="103" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A103" s="4" t="s">
         <v>138</v>
       </c>
-      <c r="B103" s="3" t="s">
+      <c r="C103" s="1">
+        <v>3</v>
+      </c>
+      <c r="D103" s="3" t="s">
         <v>100</v>
       </c>
-      <c r="C103" s="1">
-        <v>3</v>
-      </c>
-      <c r="D103" s="1" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="104" spans="1:4" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E103" s="1" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="104" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A104" s="2" t="s">
         <v>154</v>
       </c>
-      <c r="B104" s="3" t="s">
+      <c r="C104" s="12">
+        <v>3</v>
+      </c>
+      <c r="D104" s="3" t="s">
         <v>100</v>
       </c>
-      <c r="C104" s="12">
-        <v>3</v>
-      </c>
-      <c r="D104" s="1" t="s">
+      <c r="E104" s="1" t="s">
         <v>175</v>
       </c>
     </row>
-    <row r="105" spans="1:4" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="105" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A105" s="2" t="s">
         <v>157</v>
       </c>
-      <c r="B105" s="3" t="s">
+      <c r="C105" s="12">
+        <v>3</v>
+      </c>
+      <c r="D105" s="3" t="s">
         <v>100</v>
       </c>
-      <c r="C105" s="12">
-        <v>3</v>
-      </c>
-      <c r="D105" s="1" t="s">
+      <c r="E105" s="1" t="s">
         <v>175</v>
       </c>
     </row>
-    <row r="106" spans="1:4" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="106" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A106" s="2" t="s">
         <v>170</v>
       </c>
-      <c r="B106" s="3" t="s">
+      <c r="C106" s="12">
+        <v>3</v>
+      </c>
+      <c r="D106" s="3" t="s">
         <v>100</v>
       </c>
-      <c r="C106" s="12">
-        <v>3</v>
-      </c>
-      <c r="D106" s="1" t="s">
+      <c r="E106" s="1" t="s">
         <v>175</v>
       </c>
     </row>
-    <row r="107" spans="1:4" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="107" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A107" s="2" t="s">
         <v>179</v>
       </c>
-      <c r="B107" s="3" t="s">
+      <c r="C107" s="12">
+        <v>3</v>
+      </c>
+      <c r="D107" s="3" t="s">
         <v>100</v>
       </c>
-      <c r="C107" s="12">
-        <v>3</v>
-      </c>
-      <c r="D107" s="1" t="s">
+      <c r="E107" s="1" t="s">
         <v>185</v>
       </c>
     </row>
-    <row r="108" spans="1:4" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="108" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A108" s="2" t="s">
         <v>181</v>
       </c>
-      <c r="B108" s="3" t="s">
+      <c r="C108" s="12">
+        <v>3</v>
+      </c>
+      <c r="D108" s="3" t="s">
         <v>100</v>
       </c>
-      <c r="C108" s="12">
-        <v>3</v>
-      </c>
-      <c r="D108" s="1" t="s">
+      <c r="E108" s="1" t="s">
         <v>185</v>
       </c>
     </row>
-    <row r="109" spans="1:4" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="109" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A109" s="5" t="s">
         <v>95</v>
       </c>
-      <c r="B109" s="3" t="s">
+      <c r="C109" s="1">
+        <v>3</v>
+      </c>
+      <c r="D109" s="3" t="s">
         <v>96</v>
       </c>
-      <c r="C109" s="1">
-        <v>3</v>
-      </c>
-      <c r="D109" s="1" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="110" spans="1:4" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E109" s="1" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="110" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A110" s="2" t="s">
         <v>142</v>
       </c>
-      <c r="B110" s="3" t="s">
+      <c r="C110" s="12">
+        <v>3</v>
+      </c>
+      <c r="D110" s="3" t="s">
         <v>96</v>
       </c>
-      <c r="C110" s="12">
-        <v>3</v>
-      </c>
-      <c r="D110" s="1" t="s">
+      <c r="E110" s="1" t="s">
         <v>175</v>
       </c>
     </row>
-    <row r="111" spans="1:4" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="111" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A111" s="2" t="s">
         <v>147</v>
       </c>
-      <c r="B111" s="3" t="s">
+      <c r="C111" s="12">
+        <v>3</v>
+      </c>
+      <c r="D111" s="3" t="s">
         <v>96</v>
       </c>
-      <c r="C111" s="12">
-        <v>3</v>
-      </c>
-      <c r="D111" s="1" t="s">
+      <c r="E111" s="1" t="s">
         <v>175</v>
       </c>
     </row>
-    <row r="112" spans="1:4" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="112" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A112" s="2" t="s">
         <v>148</v>
       </c>
-      <c r="B112" s="3" t="s">
+      <c r="C112" s="12">
+        <v>3</v>
+      </c>
+      <c r="D112" s="3" t="s">
         <v>96</v>
       </c>
-      <c r="C112" s="12">
-        <v>3</v>
-      </c>
-      <c r="D112" s="1" t="s">
+      <c r="E112" s="1" t="s">
         <v>175</v>
       </c>
     </row>
-    <row r="113" spans="1:5" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="113" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A113" s="2" t="s">
         <v>151</v>
       </c>
-      <c r="B113" s="3" t="s">
+      <c r="C113" s="12">
+        <v>3</v>
+      </c>
+      <c r="D113" s="3" t="s">
         <v>96</v>
       </c>
-      <c r="C113" s="12">
-        <v>3</v>
-      </c>
-      <c r="D113" s="1" t="s">
+      <c r="E113" s="1" t="s">
         <v>175</v>
       </c>
     </row>
-    <row r="114" spans="1:5" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="114" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A114" s="2" t="s">
         <v>153</v>
       </c>
-      <c r="B114" s="3" t="s">
+      <c r="C114" s="12">
+        <v>3</v>
+      </c>
+      <c r="D114" s="3" t="s">
         <v>96</v>
       </c>
-      <c r="C114" s="12">
-        <v>3</v>
-      </c>
-      <c r="D114" s="1" t="s">
+      <c r="E114" s="1" t="s">
         <v>175</v>
       </c>
     </row>
-    <row r="115" spans="1:5" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="115" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A115" s="2" t="s">
         <v>156</v>
       </c>
-      <c r="B115" s="3" t="s">
+      <c r="C115" s="12">
+        <v>3</v>
+      </c>
+      <c r="D115" s="3" t="s">
         <v>96</v>
       </c>
-      <c r="C115" s="12">
-        <v>3</v>
-      </c>
-      <c r="D115" s="1" t="s">
+      <c r="E115" s="1" t="s">
         <v>175</v>
       </c>
     </row>
-    <row r="116" spans="1:5" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="116" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A116" s="4" t="s">
         <v>171</v>
       </c>
-      <c r="B116" s="3" t="s">
+      <c r="C116" s="12">
+        <v>3</v>
+      </c>
+      <c r="D116" s="3" t="s">
         <v>96</v>
       </c>
-      <c r="C116" s="12">
-        <v>3</v>
-      </c>
-      <c r="D116" s="1" t="s">
+      <c r="E116" s="1" t="s">
         <v>175</v>
       </c>
     </row>
-    <row r="117" spans="1:5" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="117" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A117" s="2" t="s">
         <v>183</v>
       </c>
-      <c r="B117" s="3" t="s">
+      <c r="C117" s="12">
+        <v>3</v>
+      </c>
+      <c r="D117" s="3" t="s">
         <v>96</v>
       </c>
-      <c r="C117" s="12">
-        <v>3</v>
-      </c>
-      <c r="D117" s="1" t="s">
+      <c r="E117" s="1" t="s">
         <v>185</v>
       </c>
     </row>
-    <row r="118" spans="1:5" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="118" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A118" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="B118" s="8" t="s">
+      <c r="C118" s="1">
+        <v>3</v>
+      </c>
+      <c r="D118" s="8" t="s">
         <v>27</v>
       </c>
-      <c r="C118" s="1">
-        <v>3</v>
-      </c>
-      <c r="D118" s="1" t="s">
+      <c r="E118" s="1" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="119" spans="1:5" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="119" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A119" s="8" t="s">
         <v>36</v>
       </c>
-      <c r="B119" s="8" t="s">
+      <c r="C119" s="1">
+        <v>3</v>
+      </c>
+      <c r="D119" s="8" t="s">
         <v>27</v>
       </c>
-      <c r="C119" s="1">
-        <v>3</v>
-      </c>
-      <c r="D119" s="1" t="s">
+      <c r="E119" s="1" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="120" spans="1:5" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="120" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A120" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="B120" s="8" t="s">
+      <c r="B120" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C120" s="1">
+        <v>3</v>
+      </c>
+      <c r="D120" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="C120" s="1">
-        <v>3</v>
-      </c>
-      <c r="D120" s="1" t="s">
+      <c r="E120" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="E120" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="121" spans="1:5" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    </row>
+    <row r="121" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A121" s="5" t="s">
         <v>90</v>
       </c>
-      <c r="B121" s="3" t="s">
+      <c r="C121" s="8">
+        <v>3</v>
+      </c>
+      <c r="D121" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C121" s="8">
-        <v>3</v>
-      </c>
-      <c r="D121" s="1" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="122" spans="1:5" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E121" s="1" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="122" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A122" s="5" t="s">
         <v>93</v>
       </c>
-      <c r="B122" s="3" t="s">
+      <c r="C122" s="8">
+        <v>3</v>
+      </c>
+      <c r="D122" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C122" s="8">
-        <v>3</v>
-      </c>
-      <c r="D122" s="1" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="123" spans="1:5" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E122" s="1" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="123" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A123" s="5" t="s">
         <v>94</v>
       </c>
-      <c r="B123" s="3" t="s">
+      <c r="C123" s="8">
+        <v>3</v>
+      </c>
+      <c r="D123" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C123" s="8">
-        <v>3</v>
-      </c>
-      <c r="D123" s="1" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="124" spans="1:5" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E123" s="1" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="124" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A124" s="2" t="s">
         <v>101</v>
       </c>
-      <c r="B124" s="3" t="s">
+      <c r="C124" s="8">
+        <v>3</v>
+      </c>
+      <c r="D124" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C124" s="8">
-        <v>3</v>
-      </c>
-      <c r="D124" s="1" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="125" spans="1:5" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E124" s="1" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="125" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A125" s="5" t="s">
         <v>104</v>
       </c>
-      <c r="B125" s="3" t="s">
+      <c r="C125" s="8">
+        <v>3</v>
+      </c>
+      <c r="D125" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C125" s="8">
-        <v>3</v>
-      </c>
-      <c r="D125" s="1" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="126" spans="1:5" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E125" s="1" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="126" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A126" s="4" t="s">
         <v>107</v>
       </c>
-      <c r="B126" s="3" t="s">
+      <c r="C126" s="8">
+        <v>3</v>
+      </c>
+      <c r="D126" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C126" s="8">
-        <v>3</v>
-      </c>
-      <c r="D126" s="1" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="127" spans="1:5" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E126" s="1" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="127" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A127" s="4" t="s">
         <v>109</v>
       </c>
-      <c r="B127" s="3" t="s">
+      <c r="C127" s="8">
+        <v>3</v>
+      </c>
+      <c r="D127" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C127" s="8">
-        <v>3</v>
-      </c>
-      <c r="D127" s="1" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="128" spans="1:5" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E127" s="1" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="128" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A128" s="5" t="s">
         <v>115</v>
       </c>
-      <c r="B128" s="3" t="s">
+      <c r="C128" s="8">
+        <v>3</v>
+      </c>
+      <c r="D128" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C128" s="8">
-        <v>3</v>
-      </c>
-      <c r="D128" s="1" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="129" spans="1:4" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E128" s="1" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="129" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A129" s="5" t="s">
         <v>117</v>
       </c>
-      <c r="B129" s="3" t="s">
+      <c r="C129" s="8">
+        <v>3</v>
+      </c>
+      <c r="D129" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C129" s="8">
-        <v>3</v>
-      </c>
-      <c r="D129" s="1" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="130" spans="1:4" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E129" s="1" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="130" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A130" s="5" t="s">
         <v>119</v>
       </c>
-      <c r="B130" s="3" t="s">
+      <c r="C130" s="8">
+        <v>3</v>
+      </c>
+      <c r="D130" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C130" s="8">
-        <v>3</v>
-      </c>
-      <c r="D130" s="1" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="131" spans="1:4" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E130" s="1" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="131" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A131" s="5" t="s">
         <v>123</v>
       </c>
-      <c r="B131" s="3" t="s">
+      <c r="C131" s="8">
+        <v>3</v>
+      </c>
+      <c r="D131" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C131" s="8">
-        <v>3</v>
-      </c>
-      <c r="D131" s="1" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="132" spans="1:4" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E131" s="1" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="132" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A132" s="5" t="s">
         <v>125</v>
       </c>
-      <c r="B132" s="3" t="s">
+      <c r="C132" s="8">
+        <v>3</v>
+      </c>
+      <c r="D132" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C132" s="8">
-        <v>3</v>
-      </c>
-      <c r="D132" s="1" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="133" spans="1:4" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E132" s="1" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="133" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A133" s="5" t="s">
         <v>126</v>
       </c>
-      <c r="B133" s="3" t="s">
+      <c r="C133" s="8">
+        <v>3</v>
+      </c>
+      <c r="D133" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C133" s="8">
-        <v>3</v>
-      </c>
-      <c r="D133" s="1" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="134" spans="1:4" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E133" s="1" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="134" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A134" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="B134" s="3" t="s">
+      <c r="C134" s="8">
+        <v>3</v>
+      </c>
+      <c r="D134" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C134" s="8">
-        <v>3</v>
-      </c>
-      <c r="D134" s="1" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="135" spans="1:4" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E134" s="1" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="135" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A135" s="2" t="s">
         <v>130</v>
       </c>
-      <c r="B135" s="3" t="s">
+      <c r="C135" s="8">
+        <v>3</v>
+      </c>
+      <c r="D135" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C135" s="8">
-        <v>3</v>
-      </c>
-      <c r="D135" s="1" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="136" spans="1:4" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E135" s="1" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="136" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A136" s="2" t="s">
         <v>131</v>
       </c>
-      <c r="B136" s="3" t="s">
+      <c r="C136" s="8">
+        <v>3</v>
+      </c>
+      <c r="D136" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C136" s="8">
-        <v>3</v>
-      </c>
-      <c r="D136" s="1" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="137" spans="1:4" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E136" s="1" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="137" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A137" s="2" t="s">
         <v>135</v>
       </c>
-      <c r="B137" s="3" t="s">
+      <c r="C137" s="8">
+        <v>3</v>
+      </c>
+      <c r="D137" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C137" s="8">
-        <v>3</v>
-      </c>
-      <c r="D137" s="1" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="138" spans="1:4" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E137" s="1" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="138" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A138" s="2" t="s">
         <v>137</v>
       </c>
-      <c r="B138" s="3" t="s">
+      <c r="C138" s="8">
+        <v>3</v>
+      </c>
+      <c r="D138" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C138" s="8">
-        <v>3</v>
-      </c>
-      <c r="D138" s="1" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="139" spans="1:4" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E138" s="1" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="139" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A139" s="4" t="s">
         <v>139</v>
       </c>
-      <c r="B139" s="3" t="s">
+      <c r="C139" s="8">
+        <v>3</v>
+      </c>
+      <c r="D139" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C139" s="8">
-        <v>3</v>
-      </c>
-      <c r="D139" s="1" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="140" spans="1:4" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E139" s="1" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="140" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A140" s="4" t="s">
         <v>141</v>
       </c>
-      <c r="B140" s="3" t="s">
+      <c r="C140" s="8">
+        <v>3</v>
+      </c>
+      <c r="D140" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C140" s="8">
-        <v>3</v>
-      </c>
-      <c r="D140" s="1" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="141" spans="1:4" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E140" s="1" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="141" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A141" s="2" t="s">
         <v>152</v>
       </c>
-      <c r="B141" s="3" t="s">
+      <c r="C141" s="6">
+        <v>3</v>
+      </c>
+      <c r="D141" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C141" s="6">
-        <v>3</v>
-      </c>
-      <c r="D141" s="1" t="s">
+      <c r="E141" s="1" t="s">
         <v>175</v>
       </c>
     </row>
-    <row r="142" spans="1:4" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="142" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A142" s="2" t="s">
         <v>159</v>
       </c>
-      <c r="B142" s="3" t="s">
+      <c r="C142" s="6">
+        <v>3</v>
+      </c>
+      <c r="D142" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C142" s="6">
-        <v>3</v>
-      </c>
-      <c r="D142" s="1" t="s">
+      <c r="E142" s="1" t="s">
         <v>175</v>
       </c>
     </row>
-    <row r="143" spans="1:4" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="143" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A143" s="2" t="s">
         <v>160</v>
       </c>
-      <c r="B143" s="3" t="s">
+      <c r="C143" s="6">
+        <v>3</v>
+      </c>
+      <c r="D143" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C143" s="6">
-        <v>3</v>
-      </c>
-      <c r="D143" s="1" t="s">
+      <c r="E143" s="1" t="s">
         <v>175</v>
       </c>
     </row>
-    <row r="144" spans="1:4" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="144" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A144" s="2" t="s">
         <v>165</v>
       </c>
-      <c r="B144" s="3" t="s">
+      <c r="C144" s="6">
+        <v>3</v>
+      </c>
+      <c r="D144" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C144" s="6">
-        <v>3</v>
-      </c>
-      <c r="D144" s="1" t="s">
+      <c r="E144" s="1" t="s">
         <v>175</v>
       </c>
     </row>
-    <row r="145" spans="1:4" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="145" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A145" s="2" t="s">
         <v>169</v>
       </c>
-      <c r="B145" s="3" t="s">
+      <c r="C145" s="6">
+        <v>3</v>
+      </c>
+      <c r="D145" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C145" s="6">
-        <v>3</v>
-      </c>
-      <c r="D145" s="1" t="s">
+      <c r="E145" s="1" t="s">
         <v>175</v>
       </c>
     </row>
-    <row r="146" spans="1:4" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="146" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A146" s="2" t="s">
         <v>178</v>
       </c>
-      <c r="B146" s="3" t="s">
+      <c r="C146" s="6">
+        <v>3</v>
+      </c>
+      <c r="D146" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C146" s="6">
-        <v>3</v>
-      </c>
-      <c r="D146" s="1" t="s">
+      <c r="E146" s="1" t="s">
         <v>185</v>
       </c>
     </row>
-    <row r="147" spans="1:4" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="147" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A147" s="5" t="s">
         <v>112</v>
       </c>
-      <c r="B147" s="3" t="s">
+      <c r="C147" s="8">
+        <v>3</v>
+      </c>
+      <c r="D147" s="3" t="s">
         <v>113</v>
       </c>
-      <c r="C147" s="8">
-        <v>3</v>
-      </c>
-      <c r="D147" s="1" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="148" spans="1:4" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E147" s="1" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="148" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A148" s="5" t="s">
         <v>91</v>
       </c>
-      <c r="B148" s="3" t="s">
+      <c r="C148" s="8">
+        <v>3</v>
+      </c>
+      <c r="D148" s="3" t="s">
         <v>92</v>
       </c>
-      <c r="C148" s="8">
-        <v>3</v>
-      </c>
-      <c r="D148" s="1" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="149" spans="1:4" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E148" s="1" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="149" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A149" s="2" t="s">
         <v>97</v>
       </c>
-      <c r="B149" s="3" t="s">
+      <c r="C149" s="8">
+        <v>3</v>
+      </c>
+      <c r="D149" s="3" t="s">
         <v>92</v>
       </c>
-      <c r="C149" s="8">
-        <v>3</v>
-      </c>
-      <c r="D149" s="1" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="150" spans="1:4" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E149" s="1" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="150" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A150" s="5" t="s">
         <v>121</v>
       </c>
-      <c r="B150" s="3" t="s">
+      <c r="C150" s="8">
+        <v>3</v>
+      </c>
+      <c r="D150" s="3" t="s">
         <v>92</v>
       </c>
-      <c r="C150" s="8">
-        <v>3</v>
-      </c>
-      <c r="D150" s="1" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="151" spans="1:4" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E150" s="1" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="151" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A151" s="2" t="s">
         <v>149</v>
       </c>
-      <c r="B151" s="3" t="s">
+      <c r="C151" s="6">
+        <v>3</v>
+      </c>
+      <c r="D151" s="3" t="s">
         <v>92</v>
       </c>
-      <c r="C151" s="6">
-        <v>3</v>
-      </c>
-      <c r="D151" s="1" t="s">
+      <c r="E151" s="1" t="s">
         <v>175</v>
       </c>
     </row>
-    <row r="152" spans="1:4" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="152" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A152" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="B152" s="8" t="s">
+      <c r="C152" s="8">
+        <v>3</v>
+      </c>
+      <c r="D152" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="C152" s="8">
-        <v>3</v>
-      </c>
-      <c r="D152" s="1" t="s">
+      <c r="E152" s="1" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="153" spans="1:4" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="153" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A153" s="8" t="s">
         <v>25</v>
       </c>
-      <c r="B153" s="8" t="s">
+      <c r="C153" s="8">
+        <v>3</v>
+      </c>
+      <c r="D153" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="C153" s="8">
-        <v>3</v>
-      </c>
-      <c r="D153" s="1" t="s">
+      <c r="E153" s="1" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="154" spans="1:4" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="154" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A154" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="B154" s="3" t="s">
+      <c r="C154" s="8">
+        <v>3</v>
+      </c>
+      <c r="D154" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="C154" s="8">
-        <v>3</v>
-      </c>
-      <c r="D154" s="1" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="155" spans="1:4" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E154" s="1" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="155" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A155" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="B155" s="3" t="s">
+      <c r="C155" s="8">
+        <v>3</v>
+      </c>
+      <c r="D155" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="C155" s="8">
-        <v>3</v>
-      </c>
-      <c r="D155" s="1" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="156" spans="1:4" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E155" s="1" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="156" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A156" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="B156" s="3" t="s">
+      <c r="C156" s="8">
+        <v>3</v>
+      </c>
+      <c r="D156" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="C156" s="8">
-        <v>3</v>
-      </c>
-      <c r="D156" s="1" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="157" spans="1:4" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E156" s="1" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="157" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A157" s="4" t="s">
         <v>79</v>
       </c>
-      <c r="B157" s="3" t="s">
+      <c r="C157" s="8">
+        <v>3</v>
+      </c>
+      <c r="D157" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="C157" s="8">
-        <v>3</v>
-      </c>
-      <c r="D157" s="1" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="158" spans="1:4" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E157" s="1" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="158" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A158" s="2" t="s">
         <v>194</v>
       </c>
-      <c r="B158" s="3" t="s">
+      <c r="C158" s="6">
+        <v>3</v>
+      </c>
+      <c r="D158" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="C158" s="6">
-        <v>3</v>
-      </c>
-      <c r="D158" s="1" t="s">
+      <c r="E158" s="1" t="s">
         <v>185</v>
       </c>
     </row>
-    <row r="159" spans="1:4" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="159" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A159" s="5" t="s">
         <v>88</v>
       </c>
-      <c r="B159" s="3" t="s">
+      <c r="C159" s="8">
+        <v>3</v>
+      </c>
+      <c r="D159" s="3" t="s">
         <v>89</v>
       </c>
-      <c r="C159" s="8">
-        <v>3</v>
-      </c>
-      <c r="D159" s="1" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="160" spans="1:4" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E159" s="1" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="160" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A160" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="B160" s="3" t="s">
+      <c r="C160" s="8">
+        <v>3</v>
+      </c>
+      <c r="D160" s="3" t="s">
         <v>89</v>
       </c>
-      <c r="C160" s="8">
-        <v>3</v>
-      </c>
-      <c r="D160" s="1" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="161" spans="1:4" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E160" s="1" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="161" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A161" s="2" t="s">
         <v>102</v>
       </c>
-      <c r="B161" s="3" t="s">
+      <c r="C161" s="8">
+        <v>3</v>
+      </c>
+      <c r="D161" s="3" t="s">
         <v>89</v>
       </c>
-      <c r="C161" s="8">
-        <v>3</v>
-      </c>
-      <c r="D161" s="1" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="162" spans="1:4" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E161" s="1" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="162" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A162" s="4" t="s">
         <v>108</v>
       </c>
-      <c r="B162" s="3" t="s">
+      <c r="C162" s="8">
+        <v>3</v>
+      </c>
+      <c r="D162" s="3" t="s">
         <v>89</v>
       </c>
-      <c r="C162" s="8">
-        <v>3</v>
-      </c>
-      <c r="D162" s="1" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="163" spans="1:4" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E162" s="1" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="163" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A163" s="5" t="s">
         <v>110</v>
       </c>
-      <c r="B163" s="3" t="s">
+      <c r="C163" s="8">
+        <v>3</v>
+      </c>
+      <c r="D163" s="3" t="s">
         <v>89</v>
       </c>
-      <c r="C163" s="8">
-        <v>3</v>
-      </c>
-      <c r="D163" s="1" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="164" spans="1:4" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E163" s="1" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="164" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A164" s="5" t="s">
         <v>114</v>
       </c>
-      <c r="B164" s="3" t="s">
+      <c r="C164" s="8">
+        <v>3</v>
+      </c>
+      <c r="D164" s="3" t="s">
         <v>89</v>
       </c>
-      <c r="C164" s="8">
-        <v>3</v>
-      </c>
-      <c r="D164" s="1" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="165" spans="1:4" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E164" s="1" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="165" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A165" s="5" t="s">
         <v>118</v>
       </c>
-      <c r="B165" s="3" t="s">
+      <c r="C165" s="8">
+        <v>3</v>
+      </c>
+      <c r="D165" s="3" t="s">
         <v>89</v>
       </c>
-      <c r="C165" s="8">
-        <v>3</v>
-      </c>
-      <c r="D165" s="1" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="166" spans="1:4" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E165" s="1" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="166" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A166" s="2" t="s">
         <v>177</v>
       </c>
-      <c r="B166" s="3" t="s">
+      <c r="C166" s="6">
+        <v>3</v>
+      </c>
+      <c r="D166" s="3" t="s">
         <v>89</v>
       </c>
-      <c r="C166" s="6">
-        <v>3</v>
-      </c>
-      <c r="D166" s="1" t="s">
+      <c r="E166" s="1" t="s">
         <v>185</v>
       </c>
     </row>
-    <row r="167" spans="1:4" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="167" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A167" s="5" t="s">
         <v>105</v>
       </c>
-      <c r="B167" s="3" t="s">
+      <c r="C167" s="8">
+        <v>3</v>
+      </c>
+      <c r="D167" s="3" t="s">
         <v>106</v>
       </c>
-      <c r="C167" s="8">
-        <v>3</v>
-      </c>
-      <c r="D167" s="1" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="168" spans="1:4" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E167" s="1" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="168" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A168" s="5" t="s">
         <v>122</v>
       </c>
-      <c r="B168" s="3" t="s">
+      <c r="C168" s="8">
+        <v>3</v>
+      </c>
+      <c r="D168" s="3" t="s">
         <v>106</v>
       </c>
-      <c r="C168" s="8">
-        <v>3</v>
-      </c>
-      <c r="D168" s="1" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="169" spans="1:4" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E168" s="1" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="169" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A169" s="4" t="s">
         <v>173</v>
       </c>
-      <c r="B169" s="3" t="s">
+      <c r="C169" s="6">
+        <v>3</v>
+      </c>
+      <c r="D169" s="3" t="s">
         <v>106</v>
       </c>
-      <c r="C169" s="6">
-        <v>3</v>
-      </c>
-      <c r="D169" s="1" t="s">
+      <c r="E169" s="1" t="s">
         <v>175</v>
       </c>
     </row>
-    <row r="170" spans="1:4" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="170" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A170" s="2" t="s">
         <v>176</v>
       </c>
-      <c r="B170" s="3" t="s">
+      <c r="C170" s="6">
+        <v>3</v>
+      </c>
+      <c r="D170" s="3" t="s">
         <v>106</v>
       </c>
-      <c r="C170" s="6">
-        <v>3</v>
-      </c>
-      <c r="D170" s="1" t="s">
+      <c r="E170" s="1" t="s">
         <v>185</v>
       </c>
     </row>
-    <row r="171" spans="1:4" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="171" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A171" s="2" t="s">
         <v>184</v>
       </c>
-      <c r="B171" s="3" t="s">
+      <c r="C171" s="6">
+        <v>3</v>
+      </c>
+      <c r="D171" s="3" t="s">
         <v>106</v>
       </c>
-      <c r="C171" s="6">
-        <v>3</v>
-      </c>
-      <c r="D171" s="1" t="s">
+      <c r="E171" s="1" t="s">
         <v>185</v>
       </c>
     </row>
-    <row r="172" spans="1:4" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="172" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A172" s="13" t="s">
         <v>202</v>
       </c>
-      <c r="B172" s="3" t="s">
+      <c r="C172" s="6">
+        <v>3</v>
+      </c>
+      <c r="D172" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="D172" s="1" t="s">
+      <c r="E172" s="1" t="s">
         <v>217</v>
       </c>
     </row>
-    <row r="173" spans="1:4" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="173" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A173" s="13" t="s">
         <v>203</v>
       </c>
-      <c r="B173" s="3" t="s">
+      <c r="C173" s="6">
+        <v>3</v>
+      </c>
+      <c r="D173" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="D173" s="1" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="174" spans="1:4" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E173" s="1" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="174" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A174" s="13" t="s">
         <v>204</v>
       </c>
-      <c r="B174" s="3" t="s">
+      <c r="C174" s="6">
+        <v>3</v>
+      </c>
+      <c r="D174" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="D174" s="1" t="s">
+      <c r="E174" s="1" t="s">
         <v>205</v>
       </c>
     </row>
-    <row r="175" spans="1:4" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="175" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A175" s="13" t="s">
         <v>206</v>
       </c>
-      <c r="B175" s="3" t="s">
+      <c r="C175" s="6">
+        <v>3</v>
+      </c>
+      <c r="D175" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="D175" s="1" t="s">
+      <c r="E175" s="1" t="s">
         <v>217</v>
       </c>
     </row>
-    <row r="176" spans="1:4" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="176" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A176" s="13" t="s">
         <v>207</v>
       </c>
-      <c r="B176" s="3" t="s">
+      <c r="C176" s="6">
+        <v>3</v>
+      </c>
+      <c r="D176" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="D176" s="1" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="177" spans="1:4" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E176" s="1" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="177" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A177" s="13" t="s">
         <v>208</v>
       </c>
-      <c r="B177" s="3" t="s">
+      <c r="C177" s="6">
+        <v>3</v>
+      </c>
+      <c r="D177" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="D177" s="1" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="178" spans="1:4" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E177" s="1" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="178" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A178" s="13" t="s">
         <v>209</v>
       </c>
-      <c r="B178" s="3" t="s">
+      <c r="C178" s="6">
+        <v>3</v>
+      </c>
+      <c r="D178" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="D178" s="1" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="179" spans="1:4" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E178" s="1" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="179" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A179" s="13" t="s">
         <v>210</v>
       </c>
-      <c r="B179" s="3" t="s">
+      <c r="C179" s="6">
+        <v>3</v>
+      </c>
+      <c r="D179" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="D179" s="1" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="180" spans="1:4" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E179" s="1" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="180" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A180" s="13" t="s">
         <v>211</v>
       </c>
-      <c r="B180" s="3" t="s">
+      <c r="C180" s="6">
+        <v>3</v>
+      </c>
+      <c r="D180" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="D180" s="1" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="181" spans="1:4" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E180" s="1" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="181" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A181" s="13" t="s">
         <v>212</v>
       </c>
-      <c r="B181" s="3" t="s">
+      <c r="C181" s="6">
+        <v>3</v>
+      </c>
+      <c r="D181" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="D181" s="1" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="182" spans="1:4" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E181" s="1" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="182" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A182" s="13" t="s">
         <v>213</v>
       </c>
-      <c r="B182" s="3" t="s">
+      <c r="C182" s="6">
+        <v>3</v>
+      </c>
+      <c r="D182" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="D182" s="1" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="183" spans="1:4" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E182" s="1" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="183" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A183" s="13" t="s">
         <v>214</v>
       </c>
-      <c r="B183" s="3" t="s">
+      <c r="C183" s="6">
+        <v>3</v>
+      </c>
+      <c r="D183" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="D183" s="1" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="184" spans="1:4" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E183" s="1" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="184" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A184" s="13" t="s">
         <v>215</v>
       </c>
-      <c r="B184" s="3" t="s">
+      <c r="C184" s="6">
+        <v>3</v>
+      </c>
+      <c r="D184" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="D184" s="1" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="185" spans="1:4" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E184" s="1" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="185" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A185" s="13" t="s">
         <v>216</v>
       </c>
-      <c r="B185" s="3" t="s">
+      <c r="C185" s="6">
+        <v>3</v>
+      </c>
+      <c r="D185" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="D185" s="1" t="s">
-        <v>218</v>
+      <c r="E185" s="1" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="186" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A186" s="14" t="s">
+        <v>222</v>
+      </c>
+      <c r="B186" s="14" t="s">
+        <v>223</v>
+      </c>
+      <c r="C186" s="15">
+        <v>2</v>
+      </c>
+      <c r="D186" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E186" s="1" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="187" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A187" s="14" t="s">
+        <v>224</v>
+      </c>
+      <c r="B187" s="14" t="s">
+        <v>225</v>
+      </c>
+      <c r="C187" s="15">
+        <v>2</v>
+      </c>
+      <c r="D187" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E187" s="1" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="188" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A188" s="14" t="s">
+        <v>226</v>
+      </c>
+      <c r="B188" s="14" t="s">
+        <v>227</v>
+      </c>
+      <c r="C188" s="15">
+        <v>2</v>
+      </c>
+      <c r="D188" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E188" s="1" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="189" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A189" s="14" t="s">
+        <v>228</v>
+      </c>
+      <c r="B189" s="14" t="s">
+        <v>229</v>
+      </c>
+      <c r="C189" s="15">
+        <v>2</v>
+      </c>
+      <c r="D189" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E189" s="1" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="190" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A190" s="14" t="s">
+        <v>230</v>
+      </c>
+      <c r="B190" s="14" t="s">
+        <v>225</v>
+      </c>
+      <c r="C190" s="15">
+        <v>2</v>
+      </c>
+      <c r="D190" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E190" s="1" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="191" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A191" s="14" t="s">
+        <v>231</v>
+      </c>
+      <c r="B191" s="14" t="s">
+        <v>232</v>
+      </c>
+      <c r="C191" s="15">
+        <v>2</v>
+      </c>
+      <c r="D191" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E191" s="1" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="192" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A192" s="14" t="s">
+        <v>233</v>
+      </c>
+      <c r="B192" s="14" t="s">
+        <v>225</v>
+      </c>
+      <c r="C192" s="15">
+        <v>2</v>
+      </c>
+      <c r="D192" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E192" s="1" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="193" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A193" s="14" t="s">
+        <v>234</v>
+      </c>
+      <c r="B193" s="14" t="s">
+        <v>227</v>
+      </c>
+      <c r="C193" s="15">
+        <v>2</v>
+      </c>
+      <c r="D193" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E193" s="1" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="194" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A194" s="14" t="s">
+        <v>235</v>
+      </c>
+      <c r="B194" s="14" t="s">
+        <v>236</v>
+      </c>
+      <c r="C194" s="15">
+        <v>2</v>
+      </c>
+      <c r="D194" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E194" s="1" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="195" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A195" s="14" t="s">
+        <v>237</v>
+      </c>
+      <c r="B195" s="14" t="s">
+        <v>238</v>
+      </c>
+      <c r="C195" s="15">
+        <v>2</v>
+      </c>
+      <c r="D195" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E195" s="1" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="196" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A196" s="14" t="s">
+        <v>239</v>
+      </c>
+      <c r="B196" s="14" t="s">
+        <v>223</v>
+      </c>
+      <c r="C196" s="15">
+        <v>2</v>
+      </c>
+      <c r="D196" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E196" s="1" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="197" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A197" s="14" t="s">
+        <v>240</v>
+      </c>
+      <c r="B197" s="14" t="s">
+        <v>225</v>
+      </c>
+      <c r="C197" s="15">
+        <v>2</v>
+      </c>
+      <c r="D197" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E197" s="1" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="198" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A198" s="14" t="s">
+        <v>241</v>
+      </c>
+      <c r="B198" s="14" t="s">
+        <v>232</v>
+      </c>
+      <c r="C198" s="15">
+        <v>2</v>
+      </c>
+      <c r="D198" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E198" s="1" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="199" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A199" s="16" t="s">
+        <v>242</v>
+      </c>
+      <c r="B199" s="16" t="s">
+        <v>223</v>
+      </c>
+      <c r="C199" s="15">
+        <v>2</v>
+      </c>
+      <c r="D199" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E199" s="1" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="200" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A200" s="16" t="s">
+        <v>243</v>
+      </c>
+      <c r="B200" s="16" t="s">
+        <v>225</v>
+      </c>
+      <c r="C200" s="15">
+        <v>2</v>
+      </c>
+      <c r="D200" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E200" s="1" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="201" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A201" s="16" t="s">
+        <v>244</v>
+      </c>
+      <c r="B201" s="16" t="s">
+        <v>245</v>
+      </c>
+      <c r="C201" s="15">
+        <v>2</v>
+      </c>
+      <c r="D201" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E201" s="1" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="202" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A202" s="16" t="s">
+        <v>246</v>
+      </c>
+      <c r="B202" s="16" t="s">
+        <v>247</v>
+      </c>
+      <c r="C202" s="15">
+        <v>2</v>
+      </c>
+      <c r="D202" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E202" s="1" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="203" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A203" t="s">
+        <v>248</v>
+      </c>
+      <c r="B203" t="s">
+        <v>232</v>
+      </c>
+      <c r="C203" s="15">
+        <v>1</v>
+      </c>
+      <c r="D203" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E203" s="1" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="204" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A204" t="s">
+        <v>249</v>
+      </c>
+      <c r="B204" t="s">
+        <v>232</v>
+      </c>
+      <c r="C204" s="15">
+        <v>1</v>
+      </c>
+      <c r="D204" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E204" s="1" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="205" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A205" t="s">
+        <v>250</v>
+      </c>
+      <c r="B205" t="s">
+        <v>251</v>
+      </c>
+      <c r="C205" s="15">
+        <v>1</v>
+      </c>
+      <c r="D205" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E205" s="1" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="206" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A206" t="s">
+        <v>252</v>
+      </c>
+      <c r="B206" t="s">
+        <v>225</v>
+      </c>
+      <c r="C206" s="15">
+        <v>1</v>
+      </c>
+      <c r="D206" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E206" s="1" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="207" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A207" t="s">
+        <v>253</v>
+      </c>
+      <c r="B207" t="s">
+        <v>223</v>
+      </c>
+      <c r="C207" s="15">
+        <v>1</v>
+      </c>
+      <c r="D207" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E207" s="1" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="208" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A208" t="s">
+        <v>254</v>
+      </c>
+      <c r="B208" t="s">
+        <v>232</v>
+      </c>
+      <c r="C208" s="15">
+        <v>1</v>
+      </c>
+      <c r="D208" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E208" s="1" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="209" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A209" t="s">
+        <v>255</v>
+      </c>
+      <c r="B209" t="s">
+        <v>223</v>
+      </c>
+      <c r="C209" s="15">
+        <v>1</v>
+      </c>
+      <c r="D209" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E209" s="1" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="210" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A210" t="s">
+        <v>256</v>
+      </c>
+      <c r="B210" t="s">
+        <v>236</v>
+      </c>
+      <c r="C210" s="15">
+        <v>2</v>
+      </c>
+      <c r="D210" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="E210" s="1" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="211" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A211" t="s">
+        <v>257</v>
+      </c>
+      <c r="B211" t="s">
+        <v>225</v>
+      </c>
+      <c r="C211" s="15">
+        <v>2</v>
+      </c>
+      <c r="D211" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="E211" s="1" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="212" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A212" t="s">
+        <v>258</v>
+      </c>
+      <c r="B212" t="s">
+        <v>225</v>
+      </c>
+      <c r="C212" s="15">
+        <v>2</v>
+      </c>
+      <c r="D212" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="E212" s="1" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="213" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A213" t="s">
+        <v>259</v>
+      </c>
+      <c r="B213" t="s">
+        <v>223</v>
+      </c>
+      <c r="C213" s="15">
+        <v>2</v>
+      </c>
+      <c r="D213" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="E213" s="1" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="214" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A214" t="s">
+        <v>260</v>
+      </c>
+      <c r="B214" t="s">
+        <v>232</v>
+      </c>
+      <c r="C214" s="15">
+        <v>2</v>
+      </c>
+      <c r="D214" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="E214" s="1" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="215" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A215" t="s">
+        <v>261</v>
+      </c>
+      <c r="B215" t="s">
+        <v>238</v>
+      </c>
+      <c r="C215" s="15">
+        <v>2</v>
+      </c>
+      <c r="D215" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="E215" s="1" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="216" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A216" t="s">
+        <v>262</v>
+      </c>
+      <c r="B216" t="s">
+        <v>236</v>
+      </c>
+      <c r="C216" s="15">
+        <v>2</v>
+      </c>
+      <c r="D216" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="E216" s="1" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="217" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A217" t="s">
+        <v>263</v>
+      </c>
+      <c r="B217" t="s">
+        <v>238</v>
+      </c>
+      <c r="C217" s="15">
+        <v>2</v>
+      </c>
+      <c r="D217" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="E217" s="1" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="218" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A218" t="s">
+        <v>214</v>
+      </c>
+      <c r="B218" t="s">
+        <v>225</v>
+      </c>
+      <c r="C218" s="15">
+        <v>2</v>
+      </c>
+      <c r="D218" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="E218" s="1" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="219" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A219" t="s">
+        <v>264</v>
+      </c>
+      <c r="B219" t="s">
+        <v>232</v>
+      </c>
+      <c r="C219" s="15">
+        <v>2</v>
+      </c>
+      <c r="D219" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="E219" s="1" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="220" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A220" t="s">
+        <v>265</v>
+      </c>
+      <c r="B220" t="s">
+        <v>225</v>
+      </c>
+      <c r="C220" s="15">
+        <v>1</v>
+      </c>
+      <c r="D220" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="E220" s="1" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="221" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A221" t="s">
+        <v>266</v>
+      </c>
+      <c r="B221" t="s">
+        <v>238</v>
+      </c>
+      <c r="C221" s="15">
+        <v>1</v>
+      </c>
+      <c r="D221" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="E221" s="1" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="222" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A222" t="s">
+        <v>267</v>
+      </c>
+      <c r="B222" t="s">
+        <v>223</v>
+      </c>
+      <c r="C222" s="15">
+        <v>1</v>
+      </c>
+      <c r="D222" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="E222" s="1" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="223" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A223" t="s">
+        <v>268</v>
+      </c>
+      <c r="B223" t="s">
+        <v>232</v>
+      </c>
+      <c r="C223" s="15">
+        <v>1</v>
+      </c>
+      <c r="D223" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="E223" s="1" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="224" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A224" t="s">
+        <v>269</v>
+      </c>
+      <c r="B224" t="s">
+        <v>225</v>
+      </c>
+      <c r="C224" s="15">
+        <v>2</v>
+      </c>
+      <c r="D224" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="E224" s="1" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="225" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A225" t="s">
+        <v>270</v>
+      </c>
+      <c r="B225" t="s">
+        <v>225</v>
+      </c>
+      <c r="C225" s="15">
+        <v>2</v>
+      </c>
+      <c r="D225" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="E225" s="1" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="226" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A226" t="s">
+        <v>271</v>
+      </c>
+      <c r="B226" t="s">
+        <v>232</v>
+      </c>
+      <c r="C226" s="15">
+        <v>2</v>
+      </c>
+      <c r="D226" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="E226" s="1" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="227" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A227" t="s">
+        <v>272</v>
+      </c>
+      <c r="B227" t="s">
+        <v>223</v>
+      </c>
+      <c r="C227" s="15">
+        <v>2</v>
+      </c>
+      <c r="D227" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="E227" s="1" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="228" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A228" t="s">
+        <v>273</v>
+      </c>
+      <c r="B228" t="s">
+        <v>236</v>
+      </c>
+      <c r="C228" s="15">
+        <v>2</v>
+      </c>
+      <c r="D228" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="E228" s="1" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="229" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A229" t="s">
+        <v>274</v>
+      </c>
+      <c r="B229" t="s">
+        <v>232</v>
+      </c>
+      <c r="C229" s="15">
+        <v>2</v>
+      </c>
+      <c r="D229" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="E229" s="1" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="230" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A230" t="s">
+        <v>275</v>
+      </c>
+      <c r="B230" t="s">
+        <v>225</v>
+      </c>
+      <c r="C230" s="15">
+        <v>1</v>
+      </c>
+      <c r="D230" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="E230" s="1" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="231" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A231" t="s">
+        <v>276</v>
+      </c>
+      <c r="B231" t="s">
+        <v>232</v>
+      </c>
+      <c r="C231" s="15">
+        <v>3</v>
+      </c>
+      <c r="D231" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="E231" s="1" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="232" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A232" t="s">
+        <v>277</v>
+      </c>
+      <c r="B232" t="s">
+        <v>278</v>
+      </c>
+      <c r="C232" s="15">
+        <v>3</v>
+      </c>
+      <c r="D232" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="E232" s="1" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="233" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A233" t="s">
+        <v>279</v>
+      </c>
+      <c r="B233" t="s">
+        <v>223</v>
+      </c>
+      <c r="C233" s="15">
+        <v>3</v>
+      </c>
+      <c r="D233" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="E233" s="1" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="234" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A234" t="s">
+        <v>280</v>
+      </c>
+      <c r="B234" t="s">
+        <v>232</v>
+      </c>
+      <c r="C234" s="15">
+        <v>3</v>
+      </c>
+      <c r="D234" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="E234" s="1" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="235" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A235" t="s">
+        <v>281</v>
+      </c>
+      <c r="B235" t="s">
+        <v>225</v>
+      </c>
+      <c r="C235" s="15">
+        <v>3</v>
+      </c>
+      <c r="D235" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="E235" s="1" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="236" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A236" t="s">
+        <v>282</v>
+      </c>
+      <c r="B236" t="s">
+        <v>223</v>
+      </c>
+      <c r="C236">
+        <v>1</v>
+      </c>
+      <c r="D236" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="E236" s="1" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="237" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A237" t="s">
+        <v>283</v>
+      </c>
+      <c r="B237" t="s">
+        <v>232</v>
+      </c>
+      <c r="C237">
+        <v>1</v>
+      </c>
+      <c r="D237" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="E237" s="1" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="238" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A238" t="s">
+        <v>284</v>
+      </c>
+      <c r="B238" t="s">
+        <v>225</v>
+      </c>
+      <c r="C238">
+        <v>1</v>
+      </c>
+      <c r="D238" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="E238" s="1" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="239" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A239" t="s">
+        <v>285</v>
+      </c>
+      <c r="B239" t="s">
+        <v>238</v>
+      </c>
+      <c r="C239">
+        <v>2</v>
+      </c>
+      <c r="D239" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="E239" s="1" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="240" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A240" t="s">
+        <v>286</v>
+      </c>
+      <c r="B240" t="s">
+        <v>232</v>
+      </c>
+      <c r="C240">
+        <v>2</v>
+      </c>
+      <c r="D240" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="E240" s="1" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="241" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A241" t="s">
+        <v>287</v>
+      </c>
+      <c r="B241" t="s">
+        <v>245</v>
+      </c>
+      <c r="C241">
+        <v>2</v>
+      </c>
+      <c r="D241" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="E241" s="1" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="242" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A242" t="s">
+        <v>288</v>
+      </c>
+      <c r="B242" t="s">
+        <v>238</v>
+      </c>
+      <c r="C242">
+        <v>2</v>
+      </c>
+      <c r="D242" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="E242" s="1" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="243" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A243" t="s">
+        <v>289</v>
+      </c>
+      <c r="B243" t="s">
+        <v>225</v>
+      </c>
+      <c r="C243">
+        <v>2</v>
+      </c>
+      <c r="D243" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="E243" s="1" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="244" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A244" t="s">
+        <v>290</v>
+      </c>
+      <c r="B244" t="s">
+        <v>227</v>
+      </c>
+      <c r="C244">
+        <v>2</v>
+      </c>
+      <c r="D244" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="E244" s="1" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="245" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A245" t="s">
+        <v>291</v>
+      </c>
+      <c r="B245" t="s">
+        <v>223</v>
+      </c>
+      <c r="C245">
+        <v>2</v>
+      </c>
+      <c r="D245" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="E245" s="1" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="246" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A246" t="s">
+        <v>292</v>
+      </c>
+      <c r="B246" t="s">
+        <v>225</v>
+      </c>
+      <c r="C246">
+        <v>2</v>
+      </c>
+      <c r="D246" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="E246" s="1" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="247" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A247" t="s">
+        <v>293</v>
+      </c>
+      <c r="B247" t="s">
+        <v>294</v>
+      </c>
+      <c r="C247">
+        <v>3</v>
+      </c>
+      <c r="D247" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="E247" s="1" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="248" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A248" t="s">
+        <v>286</v>
+      </c>
+      <c r="B248" t="s">
+        <v>232</v>
+      </c>
+      <c r="C248">
+        <v>3</v>
+      </c>
+      <c r="D248" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="E248" s="1" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="249" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A249" t="s">
+        <v>295</v>
+      </c>
+      <c r="B249" t="s">
+        <v>245</v>
+      </c>
+      <c r="C249">
+        <v>3</v>
+      </c>
+      <c r="D249" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="E249" s="1" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="250" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A250" t="s">
+        <v>296</v>
+      </c>
+      <c r="B250" t="s">
+        <v>238</v>
+      </c>
+      <c r="C250">
+        <v>3</v>
+      </c>
+      <c r="D250" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="E250" s="1" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="251" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A251" t="s">
+        <v>289</v>
+      </c>
+      <c r="B251" t="s">
+        <v>225</v>
+      </c>
+      <c r="C251">
+        <v>3</v>
+      </c>
+      <c r="D251" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="E251" s="1" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="252" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A252" t="s">
+        <v>297</v>
+      </c>
+      <c r="B252" t="s">
+        <v>238</v>
+      </c>
+      <c r="C252">
+        <v>3</v>
+      </c>
+      <c r="D252" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="E252" s="1" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="253" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A253" t="s">
+        <v>298</v>
+      </c>
+      <c r="B253" t="s">
+        <v>227</v>
+      </c>
+      <c r="C253">
+        <v>3</v>
+      </c>
+      <c r="D253" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="E253" s="1" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="254" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A254" t="s">
+        <v>291</v>
+      </c>
+      <c r="B254" t="s">
+        <v>223</v>
+      </c>
+      <c r="C254">
+        <v>3</v>
+      </c>
+      <c r="D254" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="E254" s="1" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="255" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A255" t="s">
+        <v>292</v>
+      </c>
+      <c r="B255" t="s">
+        <v>225</v>
+      </c>
+      <c r="C255">
+        <v>3</v>
+      </c>
+      <c r="D255" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="E255" s="1" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="256" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A256" t="s">
+        <v>299</v>
+      </c>
+      <c r="B256" t="s">
+        <v>245</v>
+      </c>
+      <c r="C256">
+        <v>2</v>
+      </c>
+      <c r="D256" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="E256" s="1" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="257" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A257" t="s">
+        <v>300</v>
+      </c>
+      <c r="B257" t="s">
+        <v>245</v>
+      </c>
+      <c r="C257">
+        <v>3</v>
+      </c>
+      <c r="D257" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="E257" s="1" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="258" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A258" t="s">
+        <v>301</v>
+      </c>
+      <c r="B258" t="s">
+        <v>251</v>
+      </c>
+      <c r="C258">
+        <v>3</v>
+      </c>
+      <c r="D258" s="11" t="s">
+        <v>87</v>
+      </c>
+      <c r="E258" s="1" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="259" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A259" t="s">
+        <v>302</v>
+      </c>
+      <c r="B259" t="s">
+        <v>232</v>
+      </c>
+      <c r="C259">
+        <v>3</v>
+      </c>
+      <c r="D259" s="11" t="s">
+        <v>87</v>
+      </c>
+      <c r="E259" s="1" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="260" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A260" t="s">
+        <v>303</v>
+      </c>
+      <c r="B260" t="s">
+        <v>225</v>
+      </c>
+      <c r="C260">
+        <v>3</v>
+      </c>
+      <c r="D260" s="11" t="s">
+        <v>87</v>
+      </c>
+      <c r="E260" s="1" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="261" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A261" t="s">
+        <v>304</v>
+      </c>
+      <c r="B261" t="s">
+        <v>238</v>
+      </c>
+      <c r="C261">
+        <v>3</v>
+      </c>
+      <c r="D261" s="11" t="s">
+        <v>87</v>
+      </c>
+      <c r="E261" s="1" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="262" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A262" t="s">
+        <v>305</v>
+      </c>
+      <c r="B262" t="s">
+        <v>223</v>
+      </c>
+      <c r="C262">
+        <v>3</v>
+      </c>
+      <c r="D262" s="11" t="s">
+        <v>87</v>
+      </c>
+      <c r="E262" s="1" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="263" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A263" t="s">
+        <v>306</v>
+      </c>
+      <c r="B263" t="s">
+        <v>307</v>
+      </c>
+      <c r="C263">
+        <v>3</v>
+      </c>
+      <c r="D263" s="11" t="s">
+        <v>87</v>
+      </c>
+      <c r="E263" s="1" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="264" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A264" t="s">
+        <v>308</v>
+      </c>
+      <c r="B264" t="s">
+        <v>225</v>
+      </c>
+      <c r="C264">
+        <v>2</v>
+      </c>
+      <c r="D264" s="11" t="s">
+        <v>87</v>
+      </c>
+      <c r="E264" s="1" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="265" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A265" t="s">
+        <v>309</v>
+      </c>
+      <c r="B265" t="s">
+        <v>223</v>
+      </c>
+      <c r="C265">
+        <v>2</v>
+      </c>
+      <c r="D265" s="11" t="s">
+        <v>87</v>
+      </c>
+      <c r="E265" s="1" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="266" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A266" t="s">
+        <v>310</v>
+      </c>
+      <c r="B266" t="s">
+        <v>307</v>
+      </c>
+      <c r="C266">
+        <v>2</v>
+      </c>
+      <c r="D266" s="11" t="s">
+        <v>87</v>
+      </c>
+      <c r="E266" s="1" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="267" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A267" t="s">
+        <v>311</v>
+      </c>
+      <c r="B267" t="s">
+        <v>236</v>
+      </c>
+      <c r="C267">
+        <v>1</v>
+      </c>
+      <c r="D267" s="11" t="s">
+        <v>87</v>
+      </c>
+      <c r="E267" s="1" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="268" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A268" t="s">
+        <v>312</v>
+      </c>
+      <c r="B268" t="s">
+        <v>223</v>
+      </c>
+      <c r="C268">
+        <v>1</v>
+      </c>
+      <c r="D268" s="11" t="s">
+        <v>87</v>
+      </c>
+      <c r="E268" s="1" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="269" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A269" t="s">
+        <v>313</v>
+      </c>
+      <c r="B269" t="s">
+        <v>236</v>
+      </c>
+      <c r="C269">
+        <v>3</v>
+      </c>
+      <c r="D269" s="11" t="s">
+        <v>87</v>
+      </c>
+      <c r="E269" s="1" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="270" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A270" t="s">
+        <v>314</v>
+      </c>
+      <c r="B270" t="s">
+        <v>315</v>
+      </c>
+      <c r="C270">
+        <v>2</v>
+      </c>
+      <c r="D270" s="11" t="s">
+        <v>87</v>
+      </c>
+      <c r="E270" s="1" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="271" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A271" t="s">
+        <v>316</v>
+      </c>
+      <c r="B271" t="s">
+        <v>225</v>
+      </c>
+      <c r="C271">
+        <v>1</v>
+      </c>
+      <c r="D271" s="11" t="s">
+        <v>83</v>
+      </c>
+      <c r="E271" s="1" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="272" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A272" t="s">
+        <v>317</v>
+      </c>
+      <c r="B272" t="s">
+        <v>232</v>
+      </c>
+      <c r="C272">
+        <v>2</v>
+      </c>
+      <c r="D272" s="11" t="s">
+        <v>83</v>
+      </c>
+      <c r="E272" s="1" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="273" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A273" t="s">
+        <v>318</v>
+      </c>
+      <c r="B273" t="s">
+        <v>225</v>
+      </c>
+      <c r="C273">
+        <v>2</v>
+      </c>
+      <c r="D273" s="11" t="s">
+        <v>83</v>
+      </c>
+      <c r="E273" s="1" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="274" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A274" t="s">
+        <v>319</v>
+      </c>
+      <c r="B274" t="s">
+        <v>223</v>
+      </c>
+      <c r="C274">
+        <v>2</v>
+      </c>
+      <c r="D274" s="11" t="s">
+        <v>83</v>
+      </c>
+      <c r="E274" s="1" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="275" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A275" t="s">
+        <v>320</v>
+      </c>
+      <c r="B275" t="s">
+        <v>238</v>
+      </c>
+      <c r="C275">
+        <v>2</v>
+      </c>
+      <c r="D275" s="11" t="s">
+        <v>83</v>
+      </c>
+      <c r="E275" s="1" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="276" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A276" t="s">
+        <v>321</v>
+      </c>
+      <c r="B276" t="s">
+        <v>223</v>
+      </c>
+      <c r="C276">
+        <v>2</v>
+      </c>
+      <c r="D276" s="11" t="s">
+        <v>83</v>
+      </c>
+      <c r="E276" s="1" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="277" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A277" t="s">
+        <v>322</v>
+      </c>
+      <c r="B277" t="s">
+        <v>223</v>
+      </c>
+      <c r="C277">
+        <v>2</v>
+      </c>
+      <c r="D277" s="11" t="s">
+        <v>83</v>
+      </c>
+      <c r="E277" s="1" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="278" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A278" t="s">
+        <v>323</v>
+      </c>
+      <c r="B278" t="s">
+        <v>225</v>
+      </c>
+      <c r="C278">
+        <v>2</v>
+      </c>
+      <c r="D278" s="11" t="s">
+        <v>83</v>
+      </c>
+      <c r="E278" s="1" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="279" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A279" t="s">
+        <v>324</v>
+      </c>
+      <c r="B279" t="s">
+        <v>225</v>
+      </c>
+      <c r="C279">
+        <v>2</v>
+      </c>
+      <c r="D279" s="11" t="s">
+        <v>83</v>
+      </c>
+      <c r="E279" s="1" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="280" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A280" t="s">
+        <v>325</v>
+      </c>
+      <c r="B280" t="s">
+        <v>232</v>
+      </c>
+      <c r="C280">
+        <v>2</v>
+      </c>
+      <c r="D280" s="11" t="s">
+        <v>83</v>
+      </c>
+      <c r="E280" s="1" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="281" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A281" t="s">
+        <v>326</v>
+      </c>
+      <c r="B281" t="s">
+        <v>225</v>
+      </c>
+      <c r="C281">
+        <v>2</v>
+      </c>
+      <c r="D281" s="11" t="s">
+        <v>83</v>
+      </c>
+      <c r="E281" s="1" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="282" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A282" t="s">
+        <v>327</v>
+      </c>
+      <c r="B282" t="s">
+        <v>225</v>
+      </c>
+      <c r="C282">
+        <v>2</v>
+      </c>
+      <c r="D282" s="11" t="s">
+        <v>83</v>
+      </c>
+      <c r="E282" s="1" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="283" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A283" t="s">
+        <v>328</v>
+      </c>
+      <c r="B283" t="s">
+        <v>225</v>
+      </c>
+      <c r="C283">
+        <v>3</v>
+      </c>
+      <c r="D283" s="11" t="s">
+        <v>83</v>
+      </c>
+      <c r="E283" s="1" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="284" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A284" t="s">
+        <v>329</v>
+      </c>
+      <c r="B284" t="s">
+        <v>251</v>
+      </c>
+      <c r="C284">
+        <v>3</v>
+      </c>
+      <c r="D284" s="11" t="s">
+        <v>83</v>
+      </c>
+      <c r="E284" s="1" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="285" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A285" t="s">
+        <v>330</v>
+      </c>
+      <c r="B285" t="s">
+        <v>232</v>
+      </c>
+      <c r="C285">
+        <v>3</v>
+      </c>
+      <c r="D285" s="11" t="s">
+        <v>83</v>
+      </c>
+      <c r="E285" s="1" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="286" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A286" t="s">
+        <v>331</v>
+      </c>
+      <c r="B286" t="s">
+        <v>225</v>
+      </c>
+      <c r="C286">
+        <v>3</v>
+      </c>
+      <c r="D286" s="11" t="s">
+        <v>83</v>
+      </c>
+      <c r="E286" s="1" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="287" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A287" t="s">
+        <v>332</v>
+      </c>
+      <c r="B287" t="s">
+        <v>223</v>
+      </c>
+      <c r="C287">
+        <v>3</v>
+      </c>
+      <c r="D287" s="11" t="s">
+        <v>83</v>
+      </c>
+      <c r="E287" s="1" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="288" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A288" t="s">
+        <v>333</v>
+      </c>
+      <c r="B288" t="s">
+        <v>225</v>
+      </c>
+      <c r="C288">
+        <v>3</v>
+      </c>
+      <c r="D288" s="11" t="s">
+        <v>83</v>
+      </c>
+      <c r="E288" s="1" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="289" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A289" t="s">
+        <v>334</v>
+      </c>
+      <c r="B289" t="s">
+        <v>223</v>
+      </c>
+      <c r="C289">
+        <v>3</v>
+      </c>
+      <c r="D289" s="11" t="s">
+        <v>83</v>
+      </c>
+      <c r="E289" s="1" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="290" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A290" t="s">
+        <v>335</v>
+      </c>
+      <c r="B290" t="s">
+        <v>223</v>
+      </c>
+      <c r="C290">
+        <v>3</v>
+      </c>
+      <c r="D290" s="11" t="s">
+        <v>83</v>
+      </c>
+      <c r="E290" s="1" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="291" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A291" t="s">
+        <v>336</v>
+      </c>
+      <c r="B291" t="s">
+        <v>232</v>
+      </c>
+      <c r="C291">
+        <v>3</v>
+      </c>
+      <c r="D291" s="11" t="s">
+        <v>83</v>
+      </c>
+      <c r="E291" s="1" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="292" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A292" t="s">
+        <v>337</v>
+      </c>
+      <c r="B292" t="s">
+        <v>232</v>
+      </c>
+      <c r="C292">
+        <v>3</v>
+      </c>
+      <c r="D292" s="11" t="s">
+        <v>83</v>
+      </c>
+      <c r="E292" s="1" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="293" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A293" t="s">
+        <v>338</v>
+      </c>
+      <c r="B293" t="s">
+        <v>225</v>
+      </c>
+      <c r="C293">
+        <v>3</v>
+      </c>
+      <c r="D293" s="11" t="s">
+        <v>83</v>
+      </c>
+      <c r="E293" s="1" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="294" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A294" t="s">
+        <v>339</v>
+      </c>
+      <c r="B294" t="s">
+        <v>225</v>
+      </c>
+      <c r="C294">
+        <v>3</v>
+      </c>
+      <c r="D294" s="11" t="s">
+        <v>83</v>
+      </c>
+      <c r="E294" s="1" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="295" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A295" t="s">
+        <v>340</v>
+      </c>
+      <c r="B295" t="s">
+        <v>229</v>
+      </c>
+      <c r="C295">
+        <v>3</v>
+      </c>
+      <c r="D295" s="11" t="s">
+        <v>83</v>
+      </c>
+      <c r="E295" s="1" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="296" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A296" t="s">
+        <v>341</v>
+      </c>
+      <c r="B296" t="s">
+        <v>223</v>
+      </c>
+      <c r="C296">
+        <v>3</v>
+      </c>
+      <c r="D296" s="11" t="s">
+        <v>83</v>
+      </c>
+      <c r="E296" s="1" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="297" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A297" t="s">
+        <v>342</v>
+      </c>
+      <c r="B297" t="s">
+        <v>343</v>
+      </c>
+      <c r="C297">
+        <v>2</v>
+      </c>
+      <c r="D297" s="11" t="s">
+        <v>83</v>
+      </c>
+      <c r="E297" s="1" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="298" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A298" t="s">
+        <v>344</v>
+      </c>
+      <c r="B298" t="s">
+        <v>345</v>
+      </c>
+      <c r="C298">
+        <v>2</v>
+      </c>
+      <c r="D298" s="11" t="s">
+        <v>83</v>
+      </c>
+      <c r="E298" s="1" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="299" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A299" t="s">
+        <v>346</v>
+      </c>
+      <c r="B299" t="s">
+        <v>245</v>
+      </c>
+      <c r="C299">
+        <v>2</v>
+      </c>
+      <c r="D299" s="11" t="s">
+        <v>47</v>
+      </c>
+      <c r="E299" s="1" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="300" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A300" t="s">
+        <v>347</v>
+      </c>
+      <c r="B300" t="s">
+        <v>229</v>
+      </c>
+      <c r="C300">
+        <v>2</v>
+      </c>
+      <c r="D300" s="11" t="s">
+        <v>47</v>
+      </c>
+      <c r="E300" s="1" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="301" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A301" t="s">
+        <v>348</v>
+      </c>
+      <c r="B301" t="s">
+        <v>349</v>
+      </c>
+      <c r="C301">
+        <v>2</v>
+      </c>
+      <c r="D301" s="11" t="s">
+        <v>47</v>
+      </c>
+      <c r="E301" s="1" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="302" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A302" t="s">
+        <v>350</v>
+      </c>
+      <c r="B302" t="s">
+        <v>351</v>
+      </c>
+      <c r="C302">
+        <v>2</v>
+      </c>
+      <c r="D302" s="11" t="s">
+        <v>47</v>
+      </c>
+      <c r="E302" s="1" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="303" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A303" t="s">
+        <v>352</v>
+      </c>
+      <c r="B303" t="s">
+        <v>294</v>
+      </c>
+      <c r="C303">
+        <v>3</v>
+      </c>
+      <c r="D303" s="11" t="s">
+        <v>47</v>
+      </c>
+      <c r="E303" s="1" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="304" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A304" t="s">
+        <v>353</v>
+      </c>
+      <c r="B304" t="s">
+        <v>225</v>
+      </c>
+      <c r="C304">
+        <v>3</v>
+      </c>
+      <c r="D304" s="11" t="s">
+        <v>47</v>
+      </c>
+      <c r="E304" s="1" t="s">
+        <v>217</v>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:E185" xr:uid="{9FC02C4D-B240-46EA-A4A7-1A5D0B5C9EF3}">
-    <filterColumn colId="1">
-      <filters>
-        <filter val="Autocannon"/>
-      </filters>
-    </filterColumn>
     <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:E171">
-      <sortCondition ref="B1"/>
+      <sortCondition ref="D1"/>
     </sortState>
   </autoFilter>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="B3:B185" xr:uid="{00000000-0002-0000-0000-000000000000}">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="D3:D298" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>"Corvette,Frigate,Destroyer,Cruiser,Battleship,Aircraft Carrier,Assault Carrier,Submarine,Ekranoplan,ALS,Howercraft,Missile,Missile-torpedo,Cannon,Torpedo,Grenade Launcher,Autocannon,Anti Air,UUV,Bomber,Drone,Fighter,Strike Fighter,Fighter,Helicopter,None"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="C121:C171" xr:uid="{A9B099F8-3DBD-4897-922B-2A7A6F698378}">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="C121:C185" xr:uid="{A9B099F8-3DBD-4897-922B-2A7A6F698378}">
       <formula1>"1,2,3"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <legacyDrawing r:id="rId1"/>
 </worksheet>
 </file>
--- a/data_item.xlsx
+++ b/data_item.xlsx
@@ -8,17 +8,31 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\dropbox\Dropbox\bot\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5D2AA3AB-DE0F-4106-B0ED-B5B10ABAAAF1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{5CA103DD-A181-B04A-8A89-912A552CBF8F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0">Sheet1!$B$1:$F$185</definedName>
   </definedNames>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191028"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -272,7 +286,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1299" uniqueCount="427">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1506" uniqueCount="500">
   <si>
     <t>type</t>
   </si>
@@ -1553,17 +1567,189 @@
   </si>
   <si>
     <t>Bofors L/46 (120mm)</t>
+  </si>
+  <si>
+    <t>PHL-191 (370 mm)</t>
+  </si>
+  <si>
+    <t>LARS-2 (110 mm)</t>
+  </si>
+  <si>
+    <t>Fire Dragon 480</t>
+  </si>
+  <si>
+    <t>TRG-230 (230 mm)</t>
+  </si>
+  <si>
+    <t>RBU-2500 (212 mm)</t>
+  </si>
+  <si>
+    <t>CH-901</t>
+  </si>
+  <si>
+    <t>C-AS</t>
+  </si>
+  <si>
+    <t>RUR-5C ASROC</t>
+  </si>
+  <si>
+    <t>RPK-1 Vikhr</t>
+  </si>
+  <si>
+    <t>SR-5 122/300</t>
+  </si>
+  <si>
+    <t>PKX-B (130mm)</t>
+  </si>
+  <si>
+    <t>FQF-6000</t>
+  </si>
+  <si>
+    <t>Roketsan ASW</t>
+  </si>
+  <si>
+    <t>H/JJ30-8-300 (300 mm)</t>
+  </si>
+  <si>
+    <t>A-22 (140 mm)</t>
+  </si>
+  <si>
+    <t>A-215 Grad M (122mm)</t>
+  </si>
+  <si>
+    <t>Happy Launcher</t>
+  </si>
+  <si>
+    <t>Name</t>
+  </si>
+  <si>
+    <t>Country</t>
+  </si>
+  <si>
+    <t>Tier</t>
+  </si>
+  <si>
+    <t>YU-12 (324 mm)</t>
+  </si>
+  <si>
+    <t>DTCN L5 (533 mm)</t>
+  </si>
+  <si>
+    <t>Type 65-76A Kit</t>
+  </si>
+  <si>
+    <t>Spearfish Mod1</t>
+  </si>
+  <si>
+    <t>Tiger Shark (533mm)</t>
+  </si>
+  <si>
+    <t>F21 Artemis (533 mm)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Torpedo </t>
+  </si>
+  <si>
+    <t>3M47-03E Komar</t>
+  </si>
+  <si>
+    <t>AFGS</t>
+  </si>
+  <si>
+    <t>Denel 35DPG (35 mm)</t>
+  </si>
+  <si>
+    <t>South Africa</t>
+  </si>
+  <si>
+    <t>CS/AN-3 (30 mm)</t>
+  </si>
+  <si>
+    <t>Bofors 40/L70 Mk.4 (40mm)</t>
+  </si>
+  <si>
+    <t>Seahawk Sigma (30 mm)</t>
+  </si>
+  <si>
+    <t>Type-30 JEAG (40 mm)</t>
+  </si>
+  <si>
+    <t>Typhoon MLS-NLOS</t>
+  </si>
+  <si>
+    <t>Autocanon</t>
+  </si>
+  <si>
+    <t>CIWS-II (30mm)</t>
+  </si>
+  <si>
+    <t>JRNG-6 CIWS</t>
+  </si>
+  <si>
+    <t>Helios Laser</t>
+  </si>
+  <si>
+    <t>OSU-35K (35 mm)</t>
+  </si>
+  <si>
+    <t>Poland</t>
+  </si>
+  <si>
+    <t>Type 2030 (30 mm)</t>
+  </si>
+  <si>
+    <t>Oerlikon HEL</t>
+  </si>
+  <si>
+    <t>THEL</t>
+  </si>
+  <si>
+    <t>Iron Beam</t>
+  </si>
+  <si>
+    <t>ALKA (DEWS)</t>
+  </si>
+  <si>
+    <t>SPYDER-MR</t>
+  </si>
+  <si>
+    <t>HPLS 100</t>
+  </si>
+  <si>
+    <t>Myriad CIWS (25 mm)</t>
+  </si>
+  <si>
+    <t>GOKDENIZ ER</t>
+  </si>
+  <si>
+    <t>HELMA-P</t>
+  </si>
+  <si>
+    <t>Type 93 Kin SAM</t>
+  </si>
+  <si>
+    <t>RIM-162D</t>
+  </si>
+  <si>
+    <t>Silent Hunter</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -1649,42 +1835,42 @@
   </cellStyleXfs>
   <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1700,10 +1886,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<x18tc:personList xmlns:x18tc="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1907,16 +2089,16 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:F571"/>
-  <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:F569"/>
+  <sheetFormatPr defaultColWidth="12.5390625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="4" hidden="1" customWidth="1"/>
-    <col min="2" max="2" width="20.42578125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="16.28515625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="31" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="4.04296875" hidden="1" customWidth="1"/>
+    <col min="2" max="2" width="20.359375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="16.31640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="15.1015625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:6" ht="12.75" x14ac:dyDescent="0.15">
       <c r="A1" t="s">
         <v>354</v>
       </c>
@@ -1936,7 +2118,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:6" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:6" ht="12.75" x14ac:dyDescent="0.15">
       <c r="A2">
         <v>1</v>
       </c>
@@ -1953,7 +2135,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="3" spans="1:6" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:6" ht="12.75" x14ac:dyDescent="0.15">
       <c r="A3">
         <v>2</v>
       </c>
@@ -1970,7 +2152,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="4" spans="1:6" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:6" ht="12.75" x14ac:dyDescent="0.15">
       <c r="A4">
         <v>3</v>
       </c>
@@ -1987,7 +2169,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="5" spans="1:6" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:6" ht="12.75" x14ac:dyDescent="0.15">
       <c r="A5">
         <v>4</v>
       </c>
@@ -2004,7 +2186,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="6" spans="1:6" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:6" ht="12.75" x14ac:dyDescent="0.15">
       <c r="A6">
         <v>5</v>
       </c>
@@ -2021,7 +2203,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="7" spans="1:6" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:6" ht="12.75" x14ac:dyDescent="0.15">
       <c r="A7">
         <v>6</v>
       </c>
@@ -2038,7 +2220,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="8" spans="1:6" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:6" ht="12.75" x14ac:dyDescent="0.15">
       <c r="A8">
         <v>7</v>
       </c>
@@ -2055,7 +2237,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="9" spans="1:6" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:6" ht="12.75" x14ac:dyDescent="0.15">
       <c r="A9">
         <v>8</v>
       </c>
@@ -2072,7 +2254,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="10" spans="1:6" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:6" ht="12.75" x14ac:dyDescent="0.15">
       <c r="A10">
         <v>9</v>
       </c>
@@ -2089,7 +2271,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="11" spans="1:6" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:6" ht="12.75" x14ac:dyDescent="0.15">
       <c r="A11">
         <v>10</v>
       </c>
@@ -2106,7 +2288,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="12" spans="1:6" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:6" ht="12.75" x14ac:dyDescent="0.15">
       <c r="A12">
         <v>11</v>
       </c>
@@ -2123,7 +2305,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="13" spans="1:6" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:6" ht="12.75" x14ac:dyDescent="0.15">
       <c r="A13">
         <v>12</v>
       </c>
@@ -2140,7 +2322,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="14" spans="1:6" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:6" ht="12.75" x14ac:dyDescent="0.15">
       <c r="A14">
         <v>13</v>
       </c>
@@ -2157,7 +2339,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="15" spans="1:6" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:6" ht="12.75" x14ac:dyDescent="0.15">
       <c r="A15">
         <v>14</v>
       </c>
@@ -2174,7 +2356,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="16" spans="1:6" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:6" ht="12.75" x14ac:dyDescent="0.15">
       <c r="A16">
         <v>15</v>
       </c>
@@ -2191,7 +2373,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="17" spans="1:6" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:6" ht="12.75" x14ac:dyDescent="0.15">
       <c r="A17">
         <v>16</v>
       </c>
@@ -2208,7 +2390,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="18" spans="1:6" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:6" ht="12.75" x14ac:dyDescent="0.15">
       <c r="A18">
         <v>17</v>
       </c>
@@ -2225,7 +2407,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="19" spans="1:6" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:6" ht="12.75" x14ac:dyDescent="0.15">
       <c r="A19">
         <v>18</v>
       </c>
@@ -2242,7 +2424,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="20" spans="1:6" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:6" ht="12.75" x14ac:dyDescent="0.15">
       <c r="A20">
         <v>19</v>
       </c>
@@ -2259,7 +2441,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="21" spans="1:6" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:6" ht="12.75" x14ac:dyDescent="0.15">
       <c r="A21">
         <v>20</v>
       </c>
@@ -2276,7 +2458,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="22" spans="1:6" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:6" ht="12.75" x14ac:dyDescent="0.15">
       <c r="A22">
         <v>21</v>
       </c>
@@ -2293,7 +2475,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="23" spans="1:6" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:6" ht="12.75" x14ac:dyDescent="0.15">
       <c r="A23">
         <v>22</v>
       </c>
@@ -2310,7 +2492,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="24" spans="1:6" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:6" ht="12.75" x14ac:dyDescent="0.15">
       <c r="A24">
         <v>23</v>
       </c>
@@ -2327,7 +2509,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="25" spans="1:6" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:6" ht="12.75" x14ac:dyDescent="0.15">
       <c r="A25">
         <v>24</v>
       </c>
@@ -2344,7 +2526,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="26" spans="1:6" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:6" ht="12.75" x14ac:dyDescent="0.15">
       <c r="A26">
         <v>25</v>
       </c>
@@ -2361,7 +2543,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="27" spans="1:6" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:6" ht="12.75" x14ac:dyDescent="0.15">
       <c r="A27">
         <v>26</v>
       </c>
@@ -2378,7 +2560,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="28" spans="1:6" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:6" ht="12.75" x14ac:dyDescent="0.15">
       <c r="A28">
         <v>27</v>
       </c>
@@ -2395,7 +2577,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="29" spans="1:6" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:6" ht="12.75" x14ac:dyDescent="0.15">
       <c r="A29">
         <v>28</v>
       </c>
@@ -2412,7 +2594,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="30" spans="1:6" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:6" ht="12.75" x14ac:dyDescent="0.15">
       <c r="A30">
         <v>29</v>
       </c>
@@ -2429,7 +2611,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="31" spans="1:6" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:6" ht="12.75" x14ac:dyDescent="0.15">
       <c r="A31">
         <v>30</v>
       </c>
@@ -2446,7 +2628,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="32" spans="1:6" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:6" ht="12.75" x14ac:dyDescent="0.15">
       <c r="A32">
         <v>31</v>
       </c>
@@ -2463,7 +2645,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="33" spans="1:6" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:6" ht="12.75" x14ac:dyDescent="0.15">
       <c r="A33">
         <v>32</v>
       </c>
@@ -2480,7 +2662,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="34" spans="1:6" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:6" ht="12.75" x14ac:dyDescent="0.15">
       <c r="A34">
         <v>33</v>
       </c>
@@ -2497,7 +2679,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="35" spans="1:6" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:6" ht="12.75" x14ac:dyDescent="0.15">
       <c r="A35">
         <v>34</v>
       </c>
@@ -2514,7 +2696,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="36" spans="1:6" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:6" ht="12.75" x14ac:dyDescent="0.15">
       <c r="A36">
         <v>35</v>
       </c>
@@ -2531,7 +2713,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="37" spans="1:6" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:6" ht="12.75" x14ac:dyDescent="0.15">
       <c r="A37">
         <v>36</v>
       </c>
@@ -2548,7 +2730,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="38" spans="1:6" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:6" ht="12.75" x14ac:dyDescent="0.15">
       <c r="A38">
         <v>37</v>
       </c>
@@ -2565,7 +2747,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="39" spans="1:6" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:6" ht="12.75" x14ac:dyDescent="0.15">
       <c r="A39">
         <v>38</v>
       </c>
@@ -2582,7 +2764,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="40" spans="1:6" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:6" ht="12.75" x14ac:dyDescent="0.15">
       <c r="A40">
         <v>39</v>
       </c>
@@ -2599,7 +2781,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="41" spans="1:6" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:6" ht="12.75" x14ac:dyDescent="0.15">
       <c r="A41">
         <v>40</v>
       </c>
@@ -2616,7 +2798,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="42" spans="1:6" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:6" ht="12.75" x14ac:dyDescent="0.15">
       <c r="A42">
         <v>41</v>
       </c>
@@ -2633,7 +2815,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="43" spans="1:6" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:6" ht="12.75" x14ac:dyDescent="0.15">
       <c r="A43">
         <v>42</v>
       </c>
@@ -2650,7 +2832,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="44" spans="1:6" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:6" ht="12.75" x14ac:dyDescent="0.15">
       <c r="A44">
         <v>43</v>
       </c>
@@ -2667,7 +2849,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="45" spans="1:6" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:6" ht="12.75" x14ac:dyDescent="0.15">
       <c r="A45">
         <v>44</v>
       </c>
@@ -2684,7 +2866,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="46" spans="1:6" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:6" ht="12.75" x14ac:dyDescent="0.15">
       <c r="A46">
         <v>45</v>
       </c>
@@ -2701,7 +2883,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="47" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A47">
         <v>46</v>
       </c>
@@ -2718,7 +2900,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="48" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A48">
         <v>47</v>
       </c>
@@ -2735,7 +2917,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="49" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A49">
         <v>48</v>
       </c>
@@ -2752,7 +2934,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="50" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A50">
         <v>49</v>
       </c>
@@ -2769,7 +2951,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="51" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A51">
         <v>50</v>
       </c>
@@ -2786,7 +2968,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="52" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A52">
         <v>51</v>
       </c>
@@ -2803,7 +2985,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="53" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A53">
         <v>52</v>
       </c>
@@ -2820,7 +3002,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="54" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A54">
         <v>53</v>
       </c>
@@ -2837,7 +3019,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="55" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A55">
         <v>54</v>
       </c>
@@ -2854,7 +3036,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="56" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A56">
         <v>55</v>
       </c>
@@ -2871,7 +3053,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="57" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A57">
         <v>56</v>
       </c>
@@ -2888,7 +3070,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="58" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A58">
         <v>57</v>
       </c>
@@ -2905,7 +3087,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="59" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A59">
         <v>58</v>
       </c>
@@ -2922,7 +3104,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="60" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A60">
         <v>59</v>
       </c>
@@ -2939,7 +3121,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="61" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A61">
         <v>60</v>
       </c>
@@ -2956,7 +3138,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="62" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A62">
         <v>61</v>
       </c>
@@ -2973,7 +3155,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="63" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A63">
         <v>62</v>
       </c>
@@ -2990,7 +3172,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="64" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A64">
         <v>63</v>
       </c>
@@ -3007,7 +3189,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="65" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A65">
         <v>64</v>
       </c>
@@ -3024,7 +3206,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="66" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A66">
         <v>65</v>
       </c>
@@ -3041,7 +3223,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="67" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A67">
         <v>66</v>
       </c>
@@ -3058,7 +3240,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="68" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A68">
         <v>67</v>
       </c>
@@ -3075,7 +3257,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="69" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A69">
         <v>68</v>
       </c>
@@ -3092,7 +3274,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="70" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A70">
         <v>69</v>
       </c>
@@ -3109,7 +3291,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="71" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A71">
         <v>70</v>
       </c>
@@ -3126,7 +3308,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="72" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A72">
         <v>71</v>
       </c>
@@ -3143,7 +3325,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="73" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A73">
         <v>72</v>
       </c>
@@ -3160,7 +3342,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="74" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A74">
         <v>73</v>
       </c>
@@ -3177,7 +3359,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="75" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A75">
         <v>74</v>
       </c>
@@ -3194,7 +3376,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="76" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A76">
         <v>75</v>
       </c>
@@ -3211,7 +3393,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="77" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A77">
         <v>76</v>
       </c>
@@ -3228,7 +3410,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="78" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A78">
         <v>77</v>
       </c>
@@ -3245,7 +3427,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="79" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A79">
         <v>78</v>
       </c>
@@ -3262,7 +3444,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="80" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A80">
         <v>79</v>
       </c>
@@ -3279,7 +3461,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="81" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A81">
         <v>80</v>
       </c>
@@ -3296,7 +3478,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="82" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A82">
         <v>81</v>
       </c>
@@ -3313,7 +3495,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="83" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A83">
         <v>82</v>
       </c>
@@ -3330,7 +3512,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="84" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A84">
         <v>83</v>
       </c>
@@ -3347,7 +3529,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="85" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A85">
         <v>84</v>
       </c>
@@ -3364,7 +3546,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="86" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A86">
         <v>85</v>
       </c>
@@ -3381,7 +3563,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="87" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A87">
         <v>86</v>
       </c>
@@ -3398,7 +3580,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="88" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A88">
         <v>87</v>
       </c>
@@ -3415,7 +3597,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="89" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A89">
         <v>88</v>
       </c>
@@ -3432,7 +3614,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="90" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A90">
         <v>89</v>
       </c>
@@ -3449,7 +3631,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="91" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A91">
         <v>90</v>
       </c>
@@ -3466,7 +3648,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="92" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A92">
         <v>91</v>
       </c>
@@ -3483,7 +3665,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="93" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A93">
         <v>92</v>
       </c>
@@ -3500,7 +3682,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="94" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A94">
         <v>93</v>
       </c>
@@ -3517,7 +3699,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="95" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A95">
         <v>94</v>
       </c>
@@ -3534,7 +3716,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="96" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A96">
         <v>95</v>
       </c>
@@ -3551,7 +3733,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="97" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="97" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A97">
         <v>96</v>
       </c>
@@ -3568,7 +3750,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="98" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="98" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A98">
         <v>97</v>
       </c>
@@ -3585,7 +3767,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="99" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="99" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A99">
         <v>98</v>
       </c>
@@ -3602,7 +3784,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="100" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="100" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A100">
         <v>99</v>
       </c>
@@ -3619,7 +3801,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="101" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="101" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A101">
         <v>100</v>
       </c>
@@ -3636,7 +3818,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="102" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A102">
         <v>101</v>
       </c>
@@ -3653,7 +3835,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="103" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="103" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A103">
         <v>102</v>
       </c>
@@ -3670,7 +3852,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="104" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="104" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A104">
         <v>103</v>
       </c>
@@ -3687,7 +3869,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="105" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="105" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A105">
         <v>104</v>
       </c>
@@ -3704,7 +3886,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="106" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="106" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A106">
         <v>105</v>
       </c>
@@ -3721,7 +3903,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="107" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="107" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A107">
         <v>106</v>
       </c>
@@ -3738,7 +3920,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="108" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="108" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A108">
         <v>107</v>
       </c>
@@ -3755,7 +3937,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="109" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="109" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A109">
         <v>108</v>
       </c>
@@ -3772,7 +3954,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="110" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="110" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A110">
         <v>109</v>
       </c>
@@ -3789,7 +3971,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="111" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="111" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A111">
         <v>110</v>
       </c>
@@ -3806,7 +3988,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="112" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="112" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A112">
         <v>111</v>
       </c>
@@ -3823,7 +4005,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="113" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="113" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A113">
         <v>112</v>
       </c>
@@ -3840,7 +4022,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="114" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="114" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A114">
         <v>113</v>
       </c>
@@ -3857,7 +4039,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="115" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="115" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A115">
         <v>114</v>
       </c>
@@ -3874,7 +4056,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="116" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="116" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A116">
         <v>115</v>
       </c>
@@ -3891,7 +4073,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="117" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="117" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A117">
         <v>116</v>
       </c>
@@ -3908,7 +4090,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="118" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="118" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A118">
         <v>117</v>
       </c>
@@ -3925,7 +4107,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="119" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="119" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A119">
         <v>118</v>
       </c>
@@ -3942,7 +4124,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="120" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="120" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A120">
         <v>119</v>
       </c>
@@ -3962,7 +4144,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="121" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="121" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A121">
         <v>120</v>
       </c>
@@ -3979,7 +4161,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="122" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="122" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A122">
         <v>121</v>
       </c>
@@ -3996,7 +4178,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="123" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="123" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A123">
         <v>122</v>
       </c>
@@ -4013,7 +4195,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="124" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="124" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A124">
         <v>123</v>
       </c>
@@ -4030,7 +4212,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="125" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="125" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A125">
         <v>124</v>
       </c>
@@ -4047,7 +4229,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="126" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="126" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A126">
         <v>125</v>
       </c>
@@ -4064,7 +4246,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="127" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="127" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A127">
         <v>126</v>
       </c>
@@ -4081,7 +4263,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="128" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="128" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A128">
         <v>127</v>
       </c>
@@ -4098,7 +4280,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="129" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="129" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A129">
         <v>128</v>
       </c>
@@ -4115,7 +4297,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="130" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="130" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A130">
         <v>129</v>
       </c>
@@ -4132,7 +4314,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="131" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="131" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A131">
         <v>130</v>
       </c>
@@ -4149,7 +4331,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="132" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="132" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A132">
         <v>131</v>
       </c>
@@ -4166,7 +4348,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="133" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="133" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A133">
         <v>132</v>
       </c>
@@ -4183,7 +4365,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="134" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="134" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A134">
         <v>133</v>
       </c>
@@ -4200,7 +4382,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="135" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="135" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A135">
         <v>134</v>
       </c>
@@ -4217,7 +4399,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="136" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="136" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A136">
         <v>135</v>
       </c>
@@ -4234,7 +4416,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="137" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="137" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A137">
         <v>136</v>
       </c>
@@ -4251,7 +4433,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="138" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="138" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A138">
         <v>137</v>
       </c>
@@ -4268,7 +4450,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="139" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="139" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A139">
         <v>138</v>
       </c>
@@ -4285,7 +4467,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="140" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="140" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A140">
         <v>139</v>
       </c>
@@ -4302,7 +4484,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="141" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="141" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A141">
         <v>140</v>
       </c>
@@ -4319,7 +4501,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="142" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="142" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A142">
         <v>141</v>
       </c>
@@ -4336,7 +4518,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="143" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="143" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A143">
         <v>142</v>
       </c>
@@ -4353,7 +4535,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="144" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="144" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A144">
         <v>143</v>
       </c>
@@ -4370,7 +4552,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="145" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="145" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A145">
         <v>144</v>
       </c>
@@ -4387,7 +4569,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="146" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="146" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A146">
         <v>145</v>
       </c>
@@ -4404,7 +4586,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="147" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="147" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A147">
         <v>146</v>
       </c>
@@ -4421,7 +4603,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="148" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="148" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A148">
         <v>147</v>
       </c>
@@ -4438,7 +4620,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="149" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="149" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A149">
         <v>148</v>
       </c>
@@ -4455,7 +4637,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="150" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="150" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A150">
         <v>149</v>
       </c>
@@ -4472,7 +4654,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="151" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="151" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A151">
         <v>150</v>
       </c>
@@ -4489,7 +4671,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="152" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="152" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A152">
         <v>151</v>
       </c>
@@ -4506,7 +4688,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="153" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="153" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A153">
         <v>152</v>
       </c>
@@ -4523,7 +4705,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="154" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="154" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A154">
         <v>153</v>
       </c>
@@ -4540,7 +4722,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="155" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="155" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A155">
         <v>154</v>
       </c>
@@ -4557,7 +4739,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="156" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="156" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A156">
         <v>155</v>
       </c>
@@ -4574,7 +4756,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="157" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="157" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A157">
         <v>156</v>
       </c>
@@ -4591,7 +4773,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="158" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="158" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A158">
         <v>157</v>
       </c>
@@ -4608,7 +4790,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="159" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="159" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A159">
         <v>158</v>
       </c>
@@ -4625,7 +4807,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="160" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="160" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A160">
         <v>159</v>
       </c>
@@ -4642,7 +4824,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="161" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="161" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A161">
         <v>160</v>
       </c>
@@ -4659,7 +4841,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="162" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="162" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A162">
         <v>161</v>
       </c>
@@ -4676,7 +4858,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="163" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="163" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A163">
         <v>162</v>
       </c>
@@ -4693,7 +4875,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="164" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="164" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A164">
         <v>163</v>
       </c>
@@ -4710,7 +4892,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="165" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="165" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A165">
         <v>164</v>
       </c>
@@ -4727,7 +4909,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="166" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="166" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A166">
         <v>165</v>
       </c>
@@ -4744,7 +4926,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="167" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="167" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A167">
         <v>166</v>
       </c>
@@ -4761,7 +4943,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="168" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="168" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A168">
         <v>167</v>
       </c>
@@ -4778,7 +4960,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="169" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="169" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A169">
         <v>168</v>
       </c>
@@ -4795,7 +4977,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="170" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="170" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A170">
         <v>169</v>
       </c>
@@ -4812,7 +4994,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="171" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="171" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A171">
         <v>170</v>
       </c>
@@ -4829,7 +5011,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="172" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="172" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A172">
         <v>171</v>
       </c>
@@ -4846,7 +5028,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="173" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="173" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A173">
         <v>172</v>
       </c>
@@ -4863,7 +5045,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="174" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="174" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A174">
         <v>173</v>
       </c>
@@ -4880,7 +5062,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="175" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="175" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A175">
         <v>174</v>
       </c>
@@ -4897,7 +5079,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="176" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="176" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A176">
         <v>175</v>
       </c>
@@ -4914,7 +5096,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="177" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="177" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A177">
         <v>176</v>
       </c>
@@ -4931,7 +5113,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="178" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="178" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A178">
         <v>177</v>
       </c>
@@ -4948,7 +5130,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="179" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="179" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A179">
         <v>178</v>
       </c>
@@ -4965,7 +5147,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="180" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="180" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A180">
         <v>179</v>
       </c>
@@ -4982,7 +5164,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="181" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="181" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A181">
         <v>180</v>
       </c>
@@ -4999,7 +5181,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="182" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="182" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A182">
         <v>181</v>
       </c>
@@ -5016,7 +5198,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="183" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="183" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A183">
         <v>182</v>
       </c>
@@ -5033,7 +5215,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="184" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="184" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A184">
         <v>183</v>
       </c>
@@ -5050,7 +5232,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="185" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="185" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A185">
         <v>184</v>
       </c>
@@ -5067,7 +5249,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="186" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="186" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A186">
         <v>185</v>
       </c>
@@ -5087,7 +5269,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="187" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="187" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A187">
         <v>186</v>
       </c>
@@ -5107,7 +5289,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="188" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="188" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A188">
         <v>187</v>
       </c>
@@ -5127,7 +5309,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="189" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="189" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A189">
         <v>188</v>
       </c>
@@ -5147,7 +5329,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="190" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="190" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A190">
         <v>189</v>
       </c>
@@ -5167,7 +5349,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="191" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="191" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A191">
         <v>190</v>
       </c>
@@ -5187,7 +5369,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="192" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="192" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A192">
         <v>191</v>
       </c>
@@ -5207,7 +5389,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="193" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="193" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A193">
         <v>192</v>
       </c>
@@ -5227,7 +5409,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="194" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="194" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A194">
         <v>193</v>
       </c>
@@ -5247,7 +5429,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="195" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="195" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A195">
         <v>194</v>
       </c>
@@ -5267,7 +5449,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="196" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="196" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A196">
         <v>195</v>
       </c>
@@ -5287,7 +5469,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="197" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="197" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A197">
         <v>196</v>
       </c>
@@ -5307,7 +5489,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="198" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="198" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A198">
         <v>197</v>
       </c>
@@ -5327,7 +5509,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="199" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A199">
         <v>198</v>
       </c>
@@ -5347,7 +5529,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="200" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A200">
         <v>199</v>
       </c>
@@ -5367,7 +5549,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="201" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A201">
         <v>200</v>
       </c>
@@ -5387,7 +5569,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="202" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A202">
         <v>201</v>
       </c>
@@ -5407,7 +5589,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="203" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="203" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A203">
         <v>202</v>
       </c>
@@ -5427,7 +5609,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="204" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="204" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A204">
         <v>203</v>
       </c>
@@ -5447,7 +5629,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="205" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="205" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A205">
         <v>204</v>
       </c>
@@ -5467,7 +5649,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="206" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="206" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A206">
         <v>205</v>
       </c>
@@ -5487,7 +5669,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="207" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="207" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A207">
         <v>206</v>
       </c>
@@ -5507,7 +5689,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="208" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="208" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A208">
         <v>207</v>
       </c>
@@ -5527,7 +5709,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="209" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="209" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A209">
         <v>208</v>
       </c>
@@ -5547,7 +5729,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="210" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="210" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A210">
         <v>209</v>
       </c>
@@ -5567,7 +5749,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="211" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="211" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A211">
         <v>210</v>
       </c>
@@ -5587,7 +5769,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="212" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="212" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A212">
         <v>211</v>
       </c>
@@ -5607,7 +5789,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="213" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="213" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A213">
         <v>212</v>
       </c>
@@ -5627,7 +5809,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="214" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="214" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A214">
         <v>213</v>
       </c>
@@ -5647,7 +5829,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="215" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="215" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A215">
         <v>214</v>
       </c>
@@ -5667,7 +5849,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="216" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="216" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A216">
         <v>215</v>
       </c>
@@ -5687,7 +5869,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="217" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="217" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A217">
         <v>216</v>
       </c>
@@ -5707,7 +5889,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="218" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="218" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A218">
         <v>217</v>
       </c>
@@ -5727,7 +5909,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="219" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="219" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A219">
         <v>218</v>
       </c>
@@ -5747,7 +5929,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="220" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="220" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A220">
         <v>219</v>
       </c>
@@ -5767,7 +5949,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="221" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="221" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A221">
         <v>220</v>
       </c>
@@ -5787,7 +5969,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="222" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="222" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A222">
         <v>221</v>
       </c>
@@ -5807,7 +5989,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="223" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="223" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A223">
         <v>222</v>
       </c>
@@ -5827,7 +6009,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="224" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="224" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A224">
         <v>223</v>
       </c>
@@ -5847,7 +6029,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="225" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="225" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A225">
         <v>224</v>
       </c>
@@ -5867,7 +6049,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="226" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="226" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A226">
         <v>225</v>
       </c>
@@ -5887,7 +6069,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="227" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="227" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A227">
         <v>226</v>
       </c>
@@ -5907,7 +6089,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="228" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="228" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A228">
         <v>227</v>
       </c>
@@ -5927,7 +6109,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="229" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="229" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A229">
         <v>228</v>
       </c>
@@ -5947,7 +6129,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="230" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="230" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A230">
         <v>229</v>
       </c>
@@ -5967,7 +6149,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="231" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="231" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A231">
         <v>230</v>
       </c>
@@ -5987,7 +6169,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="232" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="232" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A232">
         <v>231</v>
       </c>
@@ -6007,7 +6189,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="233" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="233" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A233">
         <v>232</v>
       </c>
@@ -6027,7 +6209,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="234" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="234" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A234">
         <v>233</v>
       </c>
@@ -6047,7 +6229,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="235" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="235" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A235">
         <v>234</v>
       </c>
@@ -6067,7 +6249,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="236" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="236" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A236">
         <v>235</v>
       </c>
@@ -6087,7 +6269,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="237" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="237" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A237">
         <v>236</v>
       </c>
@@ -6107,7 +6289,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="238" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="238" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A238">
         <v>237</v>
       </c>
@@ -6127,7 +6309,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="239" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="239" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A239">
         <v>238</v>
       </c>
@@ -6147,7 +6329,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="240" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="240" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A240">
         <v>239</v>
       </c>
@@ -6167,7 +6349,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="241" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="241" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A241">
         <v>240</v>
       </c>
@@ -6187,7 +6369,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="242" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="242" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A242">
         <v>241</v>
       </c>
@@ -6207,7 +6389,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="243" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="243" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A243">
         <v>242</v>
       </c>
@@ -6227,7 +6409,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="244" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="244" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A244">
         <v>243</v>
       </c>
@@ -6247,7 +6429,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="245" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="245" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A245">
         <v>244</v>
       </c>
@@ -6267,7 +6449,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="246" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="246" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A246">
         <v>245</v>
       </c>
@@ -6287,7 +6469,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="247" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="247" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A247">
         <v>246</v>
       </c>
@@ -6307,7 +6489,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="248" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="248" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A248">
         <v>247</v>
       </c>
@@ -6327,7 +6509,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="249" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="249" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A249">
         <v>248</v>
       </c>
@@ -6347,7 +6529,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="250" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="250" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A250">
         <v>249</v>
       </c>
@@ -6367,7 +6549,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="251" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="251" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A251">
         <v>250</v>
       </c>
@@ -6387,7 +6569,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="252" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="252" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A252">
         <v>251</v>
       </c>
@@ -6407,7 +6589,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="253" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="253" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A253">
         <v>252</v>
       </c>
@@ -6427,7 +6609,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="254" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="254" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A254">
         <v>253</v>
       </c>
@@ -6447,7 +6629,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="255" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="255" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A255">
         <v>254</v>
       </c>
@@ -6467,7 +6649,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="256" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="256" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A256">
         <v>255</v>
       </c>
@@ -6487,7 +6669,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="257" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="257" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A257">
         <v>256</v>
       </c>
@@ -6507,7 +6689,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="258" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="258" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A258">
         <v>257</v>
       </c>
@@ -6527,7 +6709,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="259" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="259" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A259">
         <v>258</v>
       </c>
@@ -6547,7 +6729,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="260" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="260" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A260">
         <v>259</v>
       </c>
@@ -6567,7 +6749,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="261" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="261" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A261">
         <v>260</v>
       </c>
@@ -6587,7 +6769,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="262" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="262" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A262">
         <v>261</v>
       </c>
@@ -6607,7 +6789,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="263" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="263" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A263">
         <v>262</v>
       </c>
@@ -6627,7 +6809,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="264" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="264" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A264">
         <v>263</v>
       </c>
@@ -6647,7 +6829,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="265" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="265" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A265">
         <v>264</v>
       </c>
@@ -6667,7 +6849,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="266" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="266" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A266">
         <v>265</v>
       </c>
@@ -6687,7 +6869,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="267" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="267" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A267">
         <v>266</v>
       </c>
@@ -6707,7 +6889,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="268" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="268" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A268">
         <v>267</v>
       </c>
@@ -6727,7 +6909,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="269" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="269" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A269">
         <v>268</v>
       </c>
@@ -6747,7 +6929,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="270" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="270" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A270">
         <v>269</v>
       </c>
@@ -6767,7 +6949,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="271" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="271" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A271">
         <v>270</v>
       </c>
@@ -6787,7 +6969,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="272" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="272" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A272">
         <v>271</v>
       </c>
@@ -6807,7 +6989,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="273" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="273" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A273">
         <v>272</v>
       </c>
@@ -6827,7 +7009,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="274" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="274" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A274">
         <v>273</v>
       </c>
@@ -6847,7 +7029,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="275" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="275" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A275">
         <v>274</v>
       </c>
@@ -6867,7 +7049,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="276" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="276" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A276">
         <v>275</v>
       </c>
@@ -6887,7 +7069,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="277" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="277" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A277">
         <v>276</v>
       </c>
@@ -6907,7 +7089,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="278" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="278" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A278">
         <v>277</v>
       </c>
@@ -6927,7 +7109,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="279" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="279" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A279">
         <v>278</v>
       </c>
@@ -6947,7 +7129,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="280" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="280" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A280">
         <v>279</v>
       </c>
@@ -6967,7 +7149,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="281" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="281" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A281">
         <v>280</v>
       </c>
@@ -6987,7 +7169,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="282" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="282" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A282">
         <v>281</v>
       </c>
@@ -7007,7 +7189,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="283" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="283" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A283">
         <v>282</v>
       </c>
@@ -7027,7 +7209,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="284" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="284" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A284">
         <v>283</v>
       </c>
@@ -7047,7 +7229,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="285" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="285" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A285">
         <v>284</v>
       </c>
@@ -7067,7 +7249,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="286" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="286" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A286">
         <v>285</v>
       </c>
@@ -7087,7 +7269,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="287" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="287" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A287">
         <v>286</v>
       </c>
@@ -7107,7 +7289,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="288" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="288" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A288">
         <v>287</v>
       </c>
@@ -7127,7 +7309,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="289" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="289" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A289">
         <v>288</v>
       </c>
@@ -7147,7 +7329,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="290" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="290" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A290">
         <v>289</v>
       </c>
@@ -7167,7 +7349,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="291" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="291" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A291">
         <v>290</v>
       </c>
@@ -7187,7 +7369,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="292" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="292" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A292">
         <v>291</v>
       </c>
@@ -7207,7 +7389,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="293" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="293" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A293">
         <v>292</v>
       </c>
@@ -7227,7 +7409,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="294" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="294" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A294">
         <v>293</v>
       </c>
@@ -7247,7 +7429,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="295" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="295" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A295">
         <v>294</v>
       </c>
@@ -7267,7 +7449,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="296" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="296" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A296">
         <v>295</v>
       </c>
@@ -7287,7 +7469,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="297" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="297" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A297">
         <v>296</v>
       </c>
@@ -7307,7 +7489,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="298" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="298" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A298">
         <v>297</v>
       </c>
@@ -7327,7 +7509,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="299" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="299" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A299">
         <v>298</v>
       </c>
@@ -7347,7 +7529,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="300" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="300" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A300">
         <v>299</v>
       </c>
@@ -7367,7 +7549,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="301" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="301" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A301">
         <v>300</v>
       </c>
@@ -7387,7 +7569,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="302" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="302" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A302">
         <v>301</v>
       </c>
@@ -7407,7 +7589,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="303" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="303" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A303">
         <v>302</v>
       </c>
@@ -7427,7 +7609,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="304" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="304" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A304">
         <v>303</v>
       </c>
@@ -7447,7 +7629,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="305" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="305" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A305">
         <v>304</v>
       </c>
@@ -7467,7 +7649,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="306" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="306" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A306">
         <v>305</v>
       </c>
@@ -7487,7 +7669,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="307" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="307" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A307">
         <v>306</v>
       </c>
@@ -7507,7 +7689,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="308" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="308" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A308">
         <v>307</v>
       </c>
@@ -7527,7 +7709,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="309" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="309" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A309">
         <v>308</v>
       </c>
@@ -7547,7 +7729,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="310" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="310" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A310">
         <v>309</v>
       </c>
@@ -7567,7 +7749,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="311" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="311" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A311">
         <v>310</v>
       </c>
@@ -7587,7 +7769,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="312" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="312" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A312">
         <v>311</v>
       </c>
@@ -7607,7 +7789,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="313" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="313" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A313">
         <v>312</v>
       </c>
@@ -7627,7 +7809,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="314" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="314" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A314">
         <v>313</v>
       </c>
@@ -7647,7 +7829,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="315" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="315" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A315">
         <v>314</v>
       </c>
@@ -7667,7 +7849,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="316" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="316" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A316">
         <v>315</v>
       </c>
@@ -7687,7 +7869,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="317" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="317" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A317">
         <v>316</v>
       </c>
@@ -7707,7 +7889,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="318" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="318" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A318">
         <v>317</v>
       </c>
@@ -7727,7 +7909,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="319" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="319" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A319">
         <v>318</v>
       </c>
@@ -7747,7 +7929,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="320" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="320" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A320">
         <v>319</v>
       </c>
@@ -7767,7 +7949,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="321" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="321" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A321">
         <v>320</v>
       </c>
@@ -7787,7 +7969,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="322" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="322" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A322">
         <v>321</v>
       </c>
@@ -7807,7 +7989,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="323" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="323" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A323">
         <v>322</v>
       </c>
@@ -7827,7 +8009,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="324" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="324" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A324">
         <v>323</v>
       </c>
@@ -7847,7 +8029,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="325" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="325" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A325">
         <v>324</v>
       </c>
@@ -7867,7 +8049,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="326" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="326" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A326">
         <v>325</v>
       </c>
@@ -7887,7 +8069,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="327" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="327" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A327">
         <v>326</v>
       </c>
@@ -7907,7 +8089,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="328" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="328" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A328">
         <v>327</v>
       </c>
@@ -7927,7 +8109,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="329" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="329" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A329">
         <v>328</v>
       </c>
@@ -7947,7 +8129,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="330" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="330" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A330">
         <v>329</v>
       </c>
@@ -7967,7 +8149,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="331" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="331" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A331">
         <v>330</v>
       </c>
@@ -7987,7 +8169,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="332" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="332" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A332">
         <v>331</v>
       </c>
@@ -8007,7 +8189,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="333" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="333" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B333" t="s">
         <v>385</v>
       </c>
@@ -8024,7 +8206,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="334" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="334" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B334" t="s">
         <v>386</v>
       </c>
@@ -8041,7 +8223,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="335" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="335" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B335" t="s">
         <v>387</v>
       </c>
@@ -8058,7 +8240,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="336" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="336" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B336" t="s">
         <v>388</v>
       </c>
@@ -8075,7 +8257,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="337" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="337" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B337" t="s">
         <v>389</v>
       </c>
@@ -8092,7 +8274,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="338" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="338" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B338" t="s">
         <v>390</v>
       </c>
@@ -8109,7 +8291,7 @@
         <v>411</v>
       </c>
     </row>
-    <row r="339" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="339" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B339" t="s">
         <v>391</v>
       </c>
@@ -8126,7 +8308,7 @@
         <v>411</v>
       </c>
     </row>
-    <row r="340" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="340" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B340" t="s">
         <v>392</v>
       </c>
@@ -8143,7 +8325,7 @@
         <v>411</v>
       </c>
     </row>
-    <row r="341" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="341" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B341" t="s">
         <v>394</v>
       </c>
@@ -8160,7 +8342,7 @@
         <v>411</v>
       </c>
     </row>
-    <row r="342" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="342" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B342" t="s">
         <v>395</v>
       </c>
@@ -8177,7 +8359,7 @@
         <v>411</v>
       </c>
     </row>
-    <row r="343" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="343" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B343" t="s">
         <v>396</v>
       </c>
@@ -8194,7 +8376,7 @@
         <v>411</v>
       </c>
     </row>
-    <row r="344" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="344" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B344" t="s">
         <v>398</v>
       </c>
@@ -8211,7 +8393,7 @@
         <v>411</v>
       </c>
     </row>
-    <row r="345" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="345" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B345" t="s">
         <v>399</v>
       </c>
@@ -8228,7 +8410,7 @@
         <v>411</v>
       </c>
     </row>
-    <row r="346" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="346" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B346" t="s">
         <v>400</v>
       </c>
@@ -8245,7 +8427,7 @@
         <v>411</v>
       </c>
     </row>
-    <row r="347" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="347" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B347" t="s">
         <v>401</v>
       </c>
@@ -8262,7 +8444,7 @@
         <v>411</v>
       </c>
     </row>
-    <row r="348" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="348" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B348" t="s">
         <v>402</v>
       </c>
@@ -8279,7 +8461,7 @@
         <v>411</v>
       </c>
     </row>
-    <row r="349" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="349" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B349" t="s">
         <v>403</v>
       </c>
@@ -8296,7 +8478,7 @@
         <v>411</v>
       </c>
     </row>
-    <row r="350" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="350" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B350" t="s">
         <v>404</v>
       </c>
@@ -8313,7 +8495,7 @@
         <v>411</v>
       </c>
     </row>
-    <row r="351" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="351" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B351" t="s">
         <v>405</v>
       </c>
@@ -8330,7 +8512,7 @@
         <v>411</v>
       </c>
     </row>
-    <row r="352" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="352" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B352" t="s">
         <v>406</v>
       </c>
@@ -8347,7 +8529,7 @@
         <v>411</v>
       </c>
     </row>
-    <row r="353" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="353" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A353">
         <v>352</v>
       </c>
@@ -8367,7 +8549,7 @@
         <v>411</v>
       </c>
     </row>
-    <row r="354" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="354" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A354">
         <v>353</v>
       </c>
@@ -8387,7 +8569,7 @@
         <v>411</v>
       </c>
     </row>
-    <row r="355" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="355" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A355">
         <v>354</v>
       </c>
@@ -8407,7 +8589,7 @@
         <v>411</v>
       </c>
     </row>
-    <row r="356" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="356" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A356">
         <v>355</v>
       </c>
@@ -8427,7 +8609,7 @@
         <v>411</v>
       </c>
     </row>
-    <row r="357" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="357" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A357">
         <v>356</v>
       </c>
@@ -8447,7 +8629,7 @@
         <v>411</v>
       </c>
     </row>
-    <row r="358" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="358" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A358">
         <v>357</v>
       </c>
@@ -8467,7 +8649,7 @@
         <v>411</v>
       </c>
     </row>
-    <row r="359" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="359" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A359">
         <v>358</v>
       </c>
@@ -8487,7 +8669,7 @@
         <v>411</v>
       </c>
     </row>
-    <row r="360" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="360" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A360">
         <v>359</v>
       </c>
@@ -8507,7 +8689,7 @@
         <v>411</v>
       </c>
     </row>
-    <row r="361" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="361" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A361">
         <v>360</v>
       </c>
@@ -8527,7 +8709,7 @@
         <v>411</v>
       </c>
     </row>
-    <row r="362" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="362" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A362">
         <v>361</v>
       </c>
@@ -8547,7 +8729,7 @@
         <v>411</v>
       </c>
     </row>
-    <row r="363" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="363" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A363">
         <v>362</v>
       </c>
@@ -8567,7 +8749,7 @@
         <v>411</v>
       </c>
     </row>
-    <row r="364" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="364" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A364">
         <v>363</v>
       </c>
@@ -8587,7 +8769,7 @@
         <v>411</v>
       </c>
     </row>
-    <row r="365" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="365" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A365">
         <v>364</v>
       </c>
@@ -8607,7 +8789,7 @@
         <v>411</v>
       </c>
     </row>
-    <row r="366" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="366" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A366">
         <v>365</v>
       </c>
@@ -8627,7 +8809,7 @@
         <v>411</v>
       </c>
     </row>
-    <row r="367" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="367" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A367">
         <v>366</v>
       </c>
@@ -8647,7 +8829,7 @@
         <v>411</v>
       </c>
     </row>
-    <row r="368" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="368" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A368">
         <v>367</v>
       </c>
@@ -8667,7 +8849,7 @@
         <v>411</v>
       </c>
     </row>
-    <row r="369" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="369" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A369">
         <v>368</v>
       </c>
@@ -8687,7 +8869,7 @@
         <v>411</v>
       </c>
     </row>
-    <row r="370" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="370" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A370">
         <v>369</v>
       </c>
@@ -8707,1008 +8889,1718 @@
         <v>411</v>
       </c>
     </row>
-    <row r="371" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="371" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A371">
         <v>370</v>
       </c>
-    </row>
-    <row r="372" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B371" t="s">
+        <v>427</v>
+      </c>
+      <c r="C371" t="s">
+        <v>232</v>
+      </c>
+      <c r="D371">
+        <v>3</v>
+      </c>
+      <c r="E371" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="F371" s="1" t="s">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="372" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A372">
         <v>371</v>
       </c>
-    </row>
-    <row r="373" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B372" t="s">
+        <v>428</v>
+      </c>
+      <c r="C372" t="s">
+        <v>343</v>
+      </c>
+      <c r="D372">
+        <v>3</v>
+      </c>
+      <c r="E372" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="F372" s="1" t="s">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="373" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A373">
         <v>372</v>
       </c>
-    </row>
-    <row r="374" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B373" t="s">
+        <v>429</v>
+      </c>
+      <c r="C373" t="s">
+        <v>232</v>
+      </c>
+      <c r="D373">
+        <v>3</v>
+      </c>
+      <c r="E373" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="F373" s="1" t="s">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="374" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A374">
         <v>373</v>
       </c>
-    </row>
-    <row r="375" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B374" t="s">
+        <v>430</v>
+      </c>
+      <c r="C374" t="s">
+        <v>349</v>
+      </c>
+      <c r="D374">
+        <v>3</v>
+      </c>
+      <c r="E374" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="F374" s="1" t="s">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="375" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A375">
         <v>374</v>
       </c>
-    </row>
-    <row r="376" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B375" t="s">
+        <v>431</v>
+      </c>
+      <c r="C375" t="s">
+        <v>225</v>
+      </c>
+      <c r="D375">
+        <v>3</v>
+      </c>
+      <c r="E375" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="F375" s="1" t="s">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="376" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A376">
         <v>375</v>
       </c>
-    </row>
-    <row r="377" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B376" t="s">
+        <v>432</v>
+      </c>
+      <c r="C376" t="s">
+        <v>232</v>
+      </c>
+      <c r="D376">
+        <v>3</v>
+      </c>
+      <c r="E376" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="F376" s="1" t="s">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="377" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A377">
         <v>376</v>
       </c>
-    </row>
-    <row r="378" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B377" t="s">
+        <v>433</v>
+      </c>
+      <c r="C377" t="s">
+        <v>397</v>
+      </c>
+      <c r="D377">
+        <v>3</v>
+      </c>
+      <c r="E377" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="F377" s="1" t="s">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="378" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A378">
         <v>377</v>
       </c>
-    </row>
-    <row r="379" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B378" t="s">
+        <v>434</v>
+      </c>
+      <c r="C378" t="s">
+        <v>223</v>
+      </c>
+      <c r="D378">
+        <v>3</v>
+      </c>
+      <c r="E378" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="F378" s="1" t="s">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="379" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A379">
         <v>378</v>
       </c>
-    </row>
-    <row r="380" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B379" t="s">
+        <v>435</v>
+      </c>
+      <c r="C379" t="s">
+        <v>225</v>
+      </c>
+      <c r="D379">
+        <v>3</v>
+      </c>
+      <c r="E379" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="F379" s="1" t="s">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="380" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A380">
         <v>379</v>
       </c>
-    </row>
-    <row r="381" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B380" t="s">
+        <v>436</v>
+      </c>
+      <c r="C380" t="s">
+        <v>232</v>
+      </c>
+      <c r="D380">
+        <v>3</v>
+      </c>
+      <c r="E380" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="F380" s="1" t="s">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="381" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A381">
         <v>380</v>
       </c>
-    </row>
-    <row r="382" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B381" t="s">
+        <v>437</v>
+      </c>
+      <c r="C381" t="s">
+        <v>229</v>
+      </c>
+      <c r="D381">
+        <v>3</v>
+      </c>
+      <c r="E381" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="F381" s="1" t="s">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="382" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A382">
         <v>381</v>
       </c>
-    </row>
-    <row r="383" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B382" t="s">
+        <v>438</v>
+      </c>
+      <c r="C382" t="s">
+        <v>232</v>
+      </c>
+      <c r="D382">
+        <v>3</v>
+      </c>
+      <c r="E382" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="F382" s="1" t="s">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="383" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A383">
         <v>382</v>
       </c>
-    </row>
-    <row r="384" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B383" t="s">
+        <v>439</v>
+      </c>
+      <c r="C383" t="s">
+        <v>349</v>
+      </c>
+      <c r="D383">
+        <v>3</v>
+      </c>
+      <c r="E383" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="F383" s="1" t="s">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="384" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A384">
         <v>383</v>
       </c>
-    </row>
-    <row r="385" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B384" t="s">
+        <v>440</v>
+      </c>
+      <c r="C384" t="s">
+        <v>232</v>
+      </c>
+      <c r="D384">
+        <v>3</v>
+      </c>
+      <c r="E384" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="F384" s="1" t="s">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="385" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A385">
         <v>384</v>
       </c>
-    </row>
-    <row r="386" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B385" t="s">
+        <v>441</v>
+      </c>
+      <c r="C385" t="s">
+        <v>225</v>
+      </c>
+      <c r="D385">
+        <v>3</v>
+      </c>
+      <c r="E385" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="F385" s="1" t="s">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="386" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A386">
         <v>385</v>
       </c>
-    </row>
-    <row r="387" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B386" t="s">
+        <v>442</v>
+      </c>
+      <c r="C386" t="s">
+        <v>225</v>
+      </c>
+      <c r="D386">
+        <v>2</v>
+      </c>
+      <c r="E386" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="F386" s="1" t="s">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="387" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A387">
         <v>386</v>
       </c>
-    </row>
-    <row r="388" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B387" t="s">
+        <v>443</v>
+      </c>
+      <c r="C387" t="s">
+        <v>409</v>
+      </c>
+      <c r="D387">
+        <v>2</v>
+      </c>
+      <c r="E387" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="F387" s="1" t="s">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="388" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A388">
         <v>387</v>
       </c>
-    </row>
-    <row r="389" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B388" t="s">
+        <v>447</v>
+      </c>
+      <c r="C388" t="s">
+        <v>232</v>
+      </c>
+      <c r="D388">
+        <v>3</v>
+      </c>
+      <c r="E388" t="s">
+        <v>453</v>
+      </c>
+      <c r="F388" s="1" t="s">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="389" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A389">
         <v>388</v>
       </c>
-    </row>
-    <row r="390" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B389" t="s">
+        <v>448</v>
+      </c>
+      <c r="C389" t="s">
+        <v>251</v>
+      </c>
+      <c r="D389">
+        <v>3</v>
+      </c>
+      <c r="E389" t="s">
+        <v>453</v>
+      </c>
+      <c r="F389" s="1" t="s">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="390" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A390">
         <v>389</v>
       </c>
-    </row>
-    <row r="391" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B390" t="s">
+        <v>449</v>
+      </c>
+      <c r="C390" t="s">
+        <v>225</v>
+      </c>
+      <c r="D390">
+        <v>3</v>
+      </c>
+      <c r="E390" t="s">
+        <v>453</v>
+      </c>
+      <c r="F390" s="1" t="s">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="391" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A391">
         <v>390</v>
       </c>
-    </row>
-    <row r="392" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B391" t="s">
+        <v>450</v>
+      </c>
+      <c r="C391" t="s">
+        <v>358</v>
+      </c>
+      <c r="D391">
+        <v>3</v>
+      </c>
+      <c r="E391" t="s">
+        <v>453</v>
+      </c>
+      <c r="F391" s="1" t="s">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="392" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A392">
         <v>391</v>
       </c>
-    </row>
-    <row r="393" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B392" t="s">
+        <v>451</v>
+      </c>
+      <c r="C392" t="s">
+        <v>229</v>
+      </c>
+      <c r="D392">
+        <v>3</v>
+      </c>
+      <c r="E392" t="s">
+        <v>453</v>
+      </c>
+      <c r="F392" s="1" t="s">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="393" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A393">
         <v>392</v>
       </c>
-    </row>
-    <row r="394" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B393" t="s">
+        <v>452</v>
+      </c>
+      <c r="C393" t="s">
+        <v>251</v>
+      </c>
+      <c r="D393">
+        <v>3</v>
+      </c>
+      <c r="E393" t="s">
+        <v>453</v>
+      </c>
+      <c r="F393" s="1" t="s">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="394" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A394">
-        <v>393</v>
-      </c>
-    </row>
-    <row r="395" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+        <v>394</v>
+      </c>
+      <c r="B394" t="s">
+        <v>454</v>
+      </c>
+      <c r="C394" t="s">
+        <v>225</v>
+      </c>
+      <c r="D394">
+        <v>3</v>
+      </c>
+      <c r="E394" t="s">
+        <v>463</v>
+      </c>
+      <c r="F394" s="1" t="s">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="395" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A395">
-        <v>394</v>
-      </c>
-    </row>
-    <row r="396" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+        <v>395</v>
+      </c>
+      <c r="B395" t="s">
+        <v>455</v>
+      </c>
+      <c r="C395" t="s">
+        <v>232</v>
+      </c>
+      <c r="D395">
+        <v>3</v>
+      </c>
+      <c r="E395" t="s">
+        <v>463</v>
+      </c>
+      <c r="F395" s="1" t="s">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="396" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A396">
-        <v>395</v>
-      </c>
-    </row>
-    <row r="397" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+        <v>396</v>
+      </c>
+      <c r="B396" t="s">
+        <v>456</v>
+      </c>
+      <c r="C396" t="s">
+        <v>457</v>
+      </c>
+      <c r="D396">
+        <v>3</v>
+      </c>
+      <c r="E396" t="s">
+        <v>463</v>
+      </c>
+      <c r="F396" s="1" t="s">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="397" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A397">
-        <v>396</v>
-      </c>
-    </row>
-    <row r="398" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+        <v>397</v>
+      </c>
+      <c r="B397" t="s">
+        <v>458</v>
+      </c>
+      <c r="C397" t="s">
+        <v>232</v>
+      </c>
+      <c r="D397">
+        <v>3</v>
+      </c>
+      <c r="E397" t="s">
+        <v>463</v>
+      </c>
+      <c r="F397" s="1" t="s">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="398" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A398">
+        <v>398</v>
+      </c>
+      <c r="B398" t="s">
+        <v>459</v>
+      </c>
+      <c r="C398" t="s">
+        <v>236</v>
+      </c>
+      <c r="D398">
+        <v>3</v>
+      </c>
+      <c r="E398" t="s">
+        <v>463</v>
+      </c>
+      <c r="F398" s="1" t="s">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="399" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A399">
+        <v>399</v>
+      </c>
+      <c r="B399" t="s">
+        <v>460</v>
+      </c>
+      <c r="C399" t="s">
+        <v>223</v>
+      </c>
+      <c r="D399">
+        <v>3</v>
+      </c>
+      <c r="E399" t="s">
+        <v>463</v>
+      </c>
+      <c r="F399" s="1" t="s">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="400" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A400">
+        <v>400</v>
+      </c>
+      <c r="B400" t="s">
+        <v>461</v>
+      </c>
+      <c r="C400" t="s">
+        <v>245</v>
+      </c>
+      <c r="D400">
+        <v>3</v>
+      </c>
+      <c r="E400" t="s">
+        <v>463</v>
+      </c>
+      <c r="F400" s="1" t="s">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="401" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A401">
+        <v>401</v>
+      </c>
+      <c r="B401" t="s">
+        <v>462</v>
+      </c>
+      <c r="C401" t="s">
         <v>397</v>
       </c>
-    </row>
-    <row r="399" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A399">
-        <v>398</v>
-      </c>
-    </row>
-    <row r="400" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A400">
-        <v>399</v>
-      </c>
-    </row>
-    <row r="401" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A401">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="402" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D401">
+        <v>3</v>
+      </c>
+      <c r="E401" t="s">
+        <v>463</v>
+      </c>
+      <c r="F401" s="1" t="s">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="402" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A402">
-        <v>401</v>
-      </c>
-    </row>
-    <row r="403" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+        <v>403</v>
+      </c>
+      <c r="B402" t="s">
+        <v>464</v>
+      </c>
+      <c r="C402" t="s">
+        <v>229</v>
+      </c>
+      <c r="D402">
+        <v>3</v>
+      </c>
+      <c r="E402" t="s">
+        <v>83</v>
+      </c>
+      <c r="F402" s="1" t="s">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="403" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A403">
-        <v>402</v>
-      </c>
-    </row>
-    <row r="404" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+        <v>404</v>
+      </c>
+      <c r="B403" t="s">
+        <v>465</v>
+      </c>
+      <c r="C403" t="s">
+        <v>232</v>
+      </c>
+      <c r="D403">
+        <v>3</v>
+      </c>
+      <c r="E403" t="s">
+        <v>83</v>
+      </c>
+      <c r="F403" s="1" t="s">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="404" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A404">
-        <v>403</v>
-      </c>
-    </row>
-    <row r="405" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+        <v>405</v>
+      </c>
+      <c r="B404" t="s">
+        <v>466</v>
+      </c>
+      <c r="C404" t="s">
+        <v>223</v>
+      </c>
+      <c r="D404">
+        <v>3</v>
+      </c>
+      <c r="E404" t="s">
+        <v>83</v>
+      </c>
+      <c r="F404" s="1" t="s">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="405" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A405">
-        <v>404</v>
-      </c>
-    </row>
-    <row r="406" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+        <v>406</v>
+      </c>
+      <c r="B405" t="s">
+        <v>467</v>
+      </c>
+      <c r="C405" t="s">
+        <v>468</v>
+      </c>
+      <c r="D405">
+        <v>3</v>
+      </c>
+      <c r="E405" t="s">
+        <v>83</v>
+      </c>
+      <c r="F405" s="1" t="s">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="406" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A406">
-        <v>405</v>
-      </c>
-    </row>
-    <row r="407" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+        <v>407</v>
+      </c>
+      <c r="B406" t="s">
+        <v>469</v>
+      </c>
+      <c r="C406" t="s">
+        <v>232</v>
+      </c>
+      <c r="D406">
+        <v>3</v>
+      </c>
+      <c r="E406" t="s">
+        <v>83</v>
+      </c>
+      <c r="F406" s="1" t="s">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="407" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A407">
-        <v>406</v>
-      </c>
-    </row>
-    <row r="408" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+        <v>408</v>
+      </c>
+      <c r="B407" t="s">
+        <v>470</v>
+      </c>
+      <c r="C407" t="s">
+        <v>307</v>
+      </c>
+      <c r="D407">
+        <v>3</v>
+      </c>
+      <c r="E407" t="s">
+        <v>83</v>
+      </c>
+      <c r="F407" s="1" t="s">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="408" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A408">
-        <v>407</v>
-      </c>
-    </row>
-    <row r="409" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+        <v>409</v>
+      </c>
+      <c r="B408" t="s">
+        <v>471</v>
+      </c>
+      <c r="C408" t="s">
+        <v>223</v>
+      </c>
+      <c r="D408">
+        <v>3</v>
+      </c>
+      <c r="E408" t="s">
+        <v>83</v>
+      </c>
+      <c r="F408" s="1" t="s">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="409" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A409">
-        <v>408</v>
-      </c>
-    </row>
-    <row r="410" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+        <v>410</v>
+      </c>
+      <c r="B409" t="s">
+        <v>472</v>
+      </c>
+      <c r="C409" t="s">
+        <v>397</v>
+      </c>
+      <c r="D409">
+        <v>3</v>
+      </c>
+      <c r="E409" t="s">
+        <v>83</v>
+      </c>
+      <c r="F409" s="1" t="s">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="410" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A410">
-        <v>409</v>
-      </c>
-    </row>
-    <row r="411" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+        <v>411</v>
+      </c>
+      <c r="B410" t="s">
+        <v>473</v>
+      </c>
+      <c r="C410" t="s">
+        <v>349</v>
+      </c>
+      <c r="D410">
+        <v>3</v>
+      </c>
+      <c r="E410" t="s">
+        <v>83</v>
+      </c>
+      <c r="F410" s="1" t="s">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="411" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A411">
-        <v>410</v>
-      </c>
-    </row>
-    <row r="412" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+        <v>412</v>
+      </c>
+      <c r="B411" t="s">
+        <v>474</v>
+      </c>
+      <c r="C411" t="s">
+        <v>397</v>
+      </c>
+      <c r="D411">
+        <v>3</v>
+      </c>
+      <c r="E411" t="s">
+        <v>83</v>
+      </c>
+      <c r="F411" s="1" t="s">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="412" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A412">
+        <v>413</v>
+      </c>
+      <c r="B412" t="s">
+        <v>475</v>
+      </c>
+      <c r="C412" t="s">
+        <v>245</v>
+      </c>
+      <c r="D412">
+        <v>3</v>
+      </c>
+      <c r="E412" t="s">
+        <v>83</v>
+      </c>
+      <c r="F412" s="1" t="s">
         <v>411</v>
       </c>
     </row>
-    <row r="413" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="413" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A413">
-        <v>412</v>
-      </c>
-    </row>
-    <row r="414" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+        <v>414</v>
+      </c>
+      <c r="B413" t="s">
+        <v>476</v>
+      </c>
+      <c r="C413" t="s">
+        <v>238</v>
+      </c>
+      <c r="D413">
+        <v>3</v>
+      </c>
+      <c r="E413" t="s">
+        <v>83</v>
+      </c>
+      <c r="F413" s="1" t="s">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="414" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A414">
-        <v>413</v>
-      </c>
-    </row>
-    <row r="415" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+        <v>415</v>
+      </c>
+      <c r="B414" t="s">
+        <v>477</v>
+      </c>
+      <c r="C414" t="s">
+        <v>349</v>
+      </c>
+      <c r="D414">
+        <v>3</v>
+      </c>
+      <c r="E414" t="s">
+        <v>83</v>
+      </c>
+      <c r="F414" s="1" t="s">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="415" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A415">
-        <v>414</v>
-      </c>
-    </row>
-    <row r="416" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+        <v>416</v>
+      </c>
+      <c r="B415" t="s">
+        <v>478</v>
+      </c>
+      <c r="C415" t="s">
+        <v>251</v>
+      </c>
+      <c r="D415">
+        <v>3</v>
+      </c>
+      <c r="E415" t="s">
+        <v>83</v>
+      </c>
+      <c r="F415" s="1" t="s">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="416" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A416">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="417" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+        <v>417</v>
+      </c>
+      <c r="B416" t="s">
+        <v>479</v>
+      </c>
+      <c r="C416" t="s">
+        <v>245</v>
+      </c>
+      <c r="D416">
+        <v>3</v>
+      </c>
+      <c r="E416" t="s">
+        <v>83</v>
+      </c>
+      <c r="F416" s="1" t="s">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="417" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A417">
-        <v>416</v>
-      </c>
-    </row>
-    <row r="418" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+        <v>418</v>
+      </c>
+      <c r="B417" t="s">
+        <v>480</v>
+      </c>
+      <c r="C417" t="s">
+        <v>223</v>
+      </c>
+      <c r="D417">
+        <v>3</v>
+      </c>
+      <c r="E417" t="s">
+        <v>83</v>
+      </c>
+      <c r="F417" s="1" t="s">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="418" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A418">
-        <v>417</v>
-      </c>
-    </row>
-    <row r="419" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+        <v>419</v>
+      </c>
+      <c r="B418" t="s">
+        <v>481</v>
+      </c>
+      <c r="C418" t="s">
+        <v>232</v>
+      </c>
+      <c r="D418">
+        <v>3</v>
+      </c>
+      <c r="E418" t="s">
+        <v>83</v>
+      </c>
+      <c r="F418" s="1" t="s">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="419" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A419">
-        <v>418</v>
-      </c>
-    </row>
-    <row r="420" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="420" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A420">
-        <v>419</v>
-      </c>
-    </row>
-    <row r="421" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="421" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A421">
-        <v>420</v>
-      </c>
-    </row>
-    <row r="422" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="422" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A422">
-        <v>421</v>
-      </c>
-    </row>
-    <row r="423" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="423" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A423">
-        <v>422</v>
-      </c>
-    </row>
-    <row r="424" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="424" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A424">
-        <v>423</v>
-      </c>
-    </row>
-    <row r="425" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="425" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A425">
-        <v>424</v>
-      </c>
-    </row>
-    <row r="426" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+        <v>426</v>
+      </c>
+    </row>
+    <row r="426" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A426">
-        <v>425</v>
-      </c>
-    </row>
-    <row r="427" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+        <v>427</v>
+      </c>
+    </row>
+    <row r="427" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A427">
-        <v>426</v>
-      </c>
-    </row>
-    <row r="428" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="428" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A428">
-        <v>427</v>
-      </c>
-    </row>
-    <row r="429" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+        <v>429</v>
+      </c>
+    </row>
+    <row r="429" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A429">
-        <v>428</v>
-      </c>
-    </row>
-    <row r="430" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="430" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A430">
-        <v>429</v>
-      </c>
-    </row>
-    <row r="431" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="431" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A431">
-        <v>430</v>
-      </c>
-    </row>
-    <row r="432" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="432" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A432">
-        <v>431</v>
-      </c>
-    </row>
-    <row r="433" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="433" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A433">
-        <v>432</v>
-      </c>
-    </row>
-    <row r="434" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+        <v>434</v>
+      </c>
+    </row>
+    <row r="434" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A434">
-        <v>433</v>
-      </c>
-    </row>
-    <row r="435" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="435" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A435">
-        <v>434</v>
-      </c>
-    </row>
-    <row r="436" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="436" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A436">
-        <v>435</v>
-      </c>
-    </row>
-    <row r="437" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="437" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A437">
-        <v>436</v>
-      </c>
-    </row>
-    <row r="438" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="438" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A438">
-        <v>437</v>
-      </c>
-    </row>
-    <row r="439" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="439" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A439">
-        <v>438</v>
-      </c>
-    </row>
-    <row r="440" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="440" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A440">
-        <v>439</v>
-      </c>
-    </row>
-    <row r="441" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="441" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A441">
-        <v>440</v>
-      </c>
-    </row>
-    <row r="442" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="442" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A442">
-        <v>441</v>
-      </c>
-    </row>
-    <row r="443" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="443" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A443">
-        <v>442</v>
-      </c>
-    </row>
-    <row r="444" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="444" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A444">
-        <v>443</v>
-      </c>
-    </row>
-    <row r="445" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="445" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A445">
-        <v>444</v>
-      </c>
-    </row>
-    <row r="446" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="446" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A446">
-        <v>445</v>
-      </c>
-    </row>
-    <row r="447" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="447" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A447">
-        <v>446</v>
-      </c>
-    </row>
-    <row r="448" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="448" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A448">
-        <v>447</v>
-      </c>
-    </row>
-    <row r="449" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="449" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A449">
-        <v>448</v>
-      </c>
-    </row>
-    <row r="450" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="450" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A450">
-        <v>449</v>
-      </c>
-    </row>
-    <row r="451" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+        <v>451</v>
+      </c>
+    </row>
+    <row r="451" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A451">
-        <v>450</v>
-      </c>
-    </row>
-    <row r="452" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="452" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A452">
-        <v>451</v>
-      </c>
-    </row>
-    <row r="453" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+        <v>453</v>
+      </c>
+    </row>
+    <row r="453" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A453">
-        <v>452</v>
-      </c>
-    </row>
-    <row r="454" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="454" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A454">
-        <v>453</v>
-      </c>
-    </row>
-    <row r="455" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+        <v>455</v>
+      </c>
+    </row>
+    <row r="455" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A455">
-        <v>454</v>
-      </c>
-    </row>
-    <row r="456" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="456" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A456">
-        <v>455</v>
-      </c>
-    </row>
-    <row r="457" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+        <v>457</v>
+      </c>
+    </row>
+    <row r="457" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A457">
-        <v>456</v>
-      </c>
-    </row>
-    <row r="458" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+        <v>458</v>
+      </c>
+    </row>
+    <row r="458" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A458">
-        <v>457</v>
-      </c>
-    </row>
-    <row r="459" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+        <v>459</v>
+      </c>
+    </row>
+    <row r="459" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A459">
-        <v>458</v>
-      </c>
-    </row>
-    <row r="460" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+        <v>460</v>
+      </c>
+    </row>
+    <row r="460" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A460">
-        <v>459</v>
-      </c>
-    </row>
-    <row r="461" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="461" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A461">
-        <v>460</v>
-      </c>
-    </row>
-    <row r="462" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="462" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A462">
-        <v>461</v>
-      </c>
-    </row>
-    <row r="463" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="463" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A463">
-        <v>462</v>
-      </c>
-    </row>
-    <row r="464" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="464" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A464">
-        <v>463</v>
-      </c>
-    </row>
-    <row r="465" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="465" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A465">
-        <v>464</v>
-      </c>
-    </row>
-    <row r="466" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="466" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A466">
-        <v>465</v>
-      </c>
-    </row>
-    <row r="467" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="467" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A467">
-        <v>466</v>
-      </c>
-    </row>
-    <row r="468" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="468" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A468">
-        <v>467</v>
-      </c>
-    </row>
-    <row r="469" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="469" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A469">
-        <v>468</v>
-      </c>
-    </row>
-    <row r="470" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+        <v>470</v>
+      </c>
+    </row>
+    <row r="470" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A470">
-        <v>469</v>
-      </c>
-    </row>
-    <row r="471" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="471" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A471">
-        <v>470</v>
-      </c>
-    </row>
-    <row r="472" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+        <v>472</v>
+      </c>
+    </row>
+    <row r="472" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A472">
-        <v>471</v>
-      </c>
-    </row>
-    <row r="473" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="473" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A473">
-        <v>472</v>
-      </c>
-    </row>
-    <row r="474" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+        <v>474</v>
+      </c>
+    </row>
+    <row r="474" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A474">
-        <v>473</v>
-      </c>
-    </row>
-    <row r="475" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+        <v>475</v>
+      </c>
+    </row>
+    <row r="475" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A475">
-        <v>474</v>
-      </c>
-    </row>
-    <row r="476" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+        <v>476</v>
+      </c>
+    </row>
+    <row r="476" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A476">
-        <v>475</v>
-      </c>
-    </row>
-    <row r="477" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+        <v>477</v>
+      </c>
+    </row>
+    <row r="477" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A477">
-        <v>476</v>
-      </c>
-    </row>
-    <row r="478" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+        <v>478</v>
+      </c>
+    </row>
+    <row r="478" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A478">
-        <v>477</v>
-      </c>
-    </row>
-    <row r="479" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="479" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A479">
-        <v>478</v>
-      </c>
-    </row>
-    <row r="480" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="480" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A480">
-        <v>479</v>
-      </c>
-    </row>
-    <row r="481" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="481" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A481">
-        <v>480</v>
-      </c>
-    </row>
-    <row r="482" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="482" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A482">
-        <v>481</v>
-      </c>
-    </row>
-    <row r="483" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+        <v>483</v>
+      </c>
+    </row>
+    <row r="483" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A483">
-        <v>482</v>
-      </c>
-    </row>
-    <row r="484" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+        <v>484</v>
+      </c>
+    </row>
+    <row r="484" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A484">
-        <v>483</v>
-      </c>
-    </row>
-    <row r="485" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+        <v>485</v>
+      </c>
+    </row>
+    <row r="485" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A485">
-        <v>484</v>
-      </c>
-    </row>
-    <row r="486" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+        <v>486</v>
+      </c>
+    </row>
+    <row r="486" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A486">
-        <v>485</v>
-      </c>
-    </row>
-    <row r="487" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="487" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A487">
-        <v>486</v>
-      </c>
-    </row>
-    <row r="488" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+        <v>488</v>
+      </c>
+    </row>
+    <row r="488" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A488">
-        <v>487</v>
-      </c>
-    </row>
-    <row r="489" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+        <v>489</v>
+      </c>
+    </row>
+    <row r="489" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A489">
-        <v>488</v>
-      </c>
-    </row>
-    <row r="490" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+        <v>490</v>
+      </c>
+    </row>
+    <row r="490" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A490">
-        <v>489</v>
-      </c>
-    </row>
-    <row r="491" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+        <v>491</v>
+      </c>
+    </row>
+    <row r="491" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A491">
-        <v>490</v>
-      </c>
-    </row>
-    <row r="492" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+        <v>492</v>
+      </c>
+    </row>
+    <row r="492" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A492">
-        <v>491</v>
-      </c>
-    </row>
-    <row r="493" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="493" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A493">
-        <v>492</v>
-      </c>
-    </row>
-    <row r="494" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+        <v>494</v>
+      </c>
+    </row>
+    <row r="494" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A494">
-        <v>493</v>
-      </c>
-    </row>
-    <row r="495" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="495" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A495">
-        <v>494</v>
-      </c>
-    </row>
-    <row r="496" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+        <v>496</v>
+      </c>
+    </row>
+    <row r="496" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A496">
-        <v>495</v>
-      </c>
-    </row>
-    <row r="497" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+        <v>497</v>
+      </c>
+    </row>
+    <row r="497" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A497">
-        <v>496</v>
-      </c>
-    </row>
-    <row r="498" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+        <v>498</v>
+      </c>
+    </row>
+    <row r="498" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A498">
-        <v>497</v>
-      </c>
-    </row>
-    <row r="499" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+        <v>499</v>
+      </c>
+    </row>
+    <row r="499" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A499">
-        <v>498</v>
-      </c>
-    </row>
-    <row r="500" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="500" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A500">
-        <v>499</v>
-      </c>
-    </row>
-    <row r="501" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+        <v>501</v>
+      </c>
+    </row>
+    <row r="501" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A501">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="502" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+        <v>502</v>
+      </c>
+    </row>
+    <row r="502" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A502">
-        <v>501</v>
-      </c>
-    </row>
-    <row r="503" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+        <v>503</v>
+      </c>
+    </row>
+    <row r="503" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A503">
-        <v>502</v>
-      </c>
-    </row>
-    <row r="504" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+        <v>504</v>
+      </c>
+    </row>
+    <row r="504" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A504">
-        <v>503</v>
-      </c>
-    </row>
-    <row r="505" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+        <v>505</v>
+      </c>
+    </row>
+    <row r="505" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A505">
-        <v>504</v>
-      </c>
-    </row>
-    <row r="506" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+        <v>506</v>
+      </c>
+    </row>
+    <row r="506" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A506">
-        <v>505</v>
-      </c>
-    </row>
-    <row r="507" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+        <v>507</v>
+      </c>
+    </row>
+    <row r="507" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A507">
-        <v>506</v>
-      </c>
-    </row>
-    <row r="508" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+        <v>508</v>
+      </c>
+    </row>
+    <row r="508" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A508">
-        <v>507</v>
-      </c>
-    </row>
-    <row r="509" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+        <v>509</v>
+      </c>
+    </row>
+    <row r="509" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A509">
-        <v>508</v>
-      </c>
-    </row>
-    <row r="510" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+        <v>510</v>
+      </c>
+    </row>
+    <row r="510" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A510">
-        <v>509</v>
-      </c>
-    </row>
-    <row r="511" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+        <v>511</v>
+      </c>
+    </row>
+    <row r="511" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A511">
-        <v>510</v>
-      </c>
-    </row>
-    <row r="512" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+        <v>512</v>
+      </c>
+    </row>
+    <row r="512" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A512">
-        <v>511</v>
-      </c>
-    </row>
-    <row r="513" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+        <v>513</v>
+      </c>
+    </row>
+    <row r="513" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A513">
-        <v>512</v>
-      </c>
-    </row>
-    <row r="514" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+        <v>514</v>
+      </c>
+    </row>
+    <row r="514" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A514">
-        <v>513</v>
-      </c>
-    </row>
-    <row r="515" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+        <v>515</v>
+      </c>
+    </row>
+    <row r="515" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A515">
-        <v>514</v>
-      </c>
-    </row>
-    <row r="516" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+        <v>516</v>
+      </c>
+    </row>
+    <row r="516" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A516">
-        <v>515</v>
-      </c>
-    </row>
-    <row r="517" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+        <v>517</v>
+      </c>
+    </row>
+    <row r="517" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A517">
-        <v>516</v>
-      </c>
-    </row>
-    <row r="518" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+        <v>518</v>
+      </c>
+    </row>
+    <row r="518" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A518">
-        <v>517</v>
-      </c>
-    </row>
-    <row r="519" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+        <v>519</v>
+      </c>
+    </row>
+    <row r="519" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A519">
-        <v>518</v>
-      </c>
-    </row>
-    <row r="520" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="520" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A520">
-        <v>519</v>
-      </c>
-    </row>
-    <row r="521" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+        <v>521</v>
+      </c>
+    </row>
+    <row r="521" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A521">
-        <v>520</v>
-      </c>
-    </row>
-    <row r="522" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+        <v>522</v>
+      </c>
+    </row>
+    <row r="522" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A522">
-        <v>521</v>
-      </c>
-    </row>
-    <row r="523" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+        <v>523</v>
+      </c>
+    </row>
+    <row r="523" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A523">
-        <v>522</v>
-      </c>
-    </row>
-    <row r="524" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+        <v>524</v>
+      </c>
+    </row>
+    <row r="524" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A524">
-        <v>523</v>
-      </c>
-    </row>
-    <row r="525" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+        <v>525</v>
+      </c>
+    </row>
+    <row r="525" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A525">
-        <v>524</v>
-      </c>
-    </row>
-    <row r="526" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+        <v>526</v>
+      </c>
+    </row>
+    <row r="526" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A526">
-        <v>525</v>
-      </c>
-    </row>
-    <row r="527" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+        <v>527</v>
+      </c>
+    </row>
+    <row r="527" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A527">
-        <v>526</v>
-      </c>
-    </row>
-    <row r="528" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+        <v>528</v>
+      </c>
+    </row>
+    <row r="528" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A528">
-        <v>527</v>
-      </c>
-    </row>
-    <row r="529" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+        <v>529</v>
+      </c>
+    </row>
+    <row r="529" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A529">
-        <v>528</v>
-      </c>
-    </row>
-    <row r="530" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+        <v>530</v>
+      </c>
+    </row>
+    <row r="530" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A530">
-        <v>529</v>
-      </c>
-    </row>
-    <row r="531" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+        <v>531</v>
+      </c>
+    </row>
+    <row r="531" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A531">
-        <v>530</v>
-      </c>
-    </row>
-    <row r="532" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+        <v>532</v>
+      </c>
+    </row>
+    <row r="532" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A532">
-        <v>531</v>
-      </c>
-    </row>
-    <row r="533" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="533" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A533">
-        <v>532</v>
-      </c>
-    </row>
-    <row r="534" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+        <v>534</v>
+      </c>
+    </row>
+    <row r="534" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A534">
-        <v>533</v>
-      </c>
-    </row>
-    <row r="535" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="535" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A535">
-        <v>534</v>
-      </c>
-    </row>
-    <row r="536" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+        <v>536</v>
+      </c>
+    </row>
+    <row r="536" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A536">
-        <v>535</v>
-      </c>
-    </row>
-    <row r="537" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+        <v>537</v>
+      </c>
+    </row>
+    <row r="537" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A537">
-        <v>536</v>
-      </c>
-    </row>
-    <row r="538" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+        <v>538</v>
+      </c>
+    </row>
+    <row r="538" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A538">
-        <v>537</v>
-      </c>
-    </row>
-    <row r="539" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="539" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A539">
-        <v>538</v>
-      </c>
-    </row>
-    <row r="540" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+        <v>540</v>
+      </c>
+    </row>
+    <row r="540" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A540">
-        <v>539</v>
-      </c>
-    </row>
-    <row r="541" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+        <v>541</v>
+      </c>
+    </row>
+    <row r="541" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A541">
-        <v>540</v>
-      </c>
-    </row>
-    <row r="542" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+        <v>542</v>
+      </c>
+    </row>
+    <row r="542" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A542">
-        <v>541</v>
-      </c>
-    </row>
-    <row r="543" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+        <v>543</v>
+      </c>
+    </row>
+    <row r="543" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A543">
-        <v>542</v>
-      </c>
-    </row>
-    <row r="544" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="544" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A544">
-        <v>543</v>
-      </c>
-    </row>
-    <row r="545" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+        <v>545</v>
+      </c>
+    </row>
+    <row r="545" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A545">
-        <v>544</v>
-      </c>
-    </row>
-    <row r="546" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+        <v>546</v>
+      </c>
+    </row>
+    <row r="546" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A546">
-        <v>545</v>
-      </c>
-    </row>
-    <row r="547" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+        <v>547</v>
+      </c>
+    </row>
+    <row r="547" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A547">
-        <v>546</v>
-      </c>
-    </row>
-    <row r="548" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+        <v>548</v>
+      </c>
+    </row>
+    <row r="548" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A548">
-        <v>547</v>
-      </c>
-    </row>
-    <row r="549" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+        <v>549</v>
+      </c>
+    </row>
+    <row r="549" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A549">
-        <v>548</v>
-      </c>
-    </row>
-    <row r="550" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+        <v>550</v>
+      </c>
+    </row>
+    <row r="550" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A550">
-        <v>549</v>
-      </c>
-    </row>
-    <row r="551" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+        <v>551</v>
+      </c>
+    </row>
+    <row r="551" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A551">
-        <v>550</v>
-      </c>
-    </row>
-    <row r="552" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+        <v>552</v>
+      </c>
+    </row>
+    <row r="552" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A552">
-        <v>551</v>
-      </c>
-    </row>
-    <row r="553" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+        <v>553</v>
+      </c>
+    </row>
+    <row r="553" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A553">
-        <v>552</v>
-      </c>
-    </row>
-    <row r="554" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+        <v>554</v>
+      </c>
+    </row>
+    <row r="554" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A554">
-        <v>553</v>
-      </c>
-    </row>
-    <row r="555" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+        <v>555</v>
+      </c>
+    </row>
+    <row r="555" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A555">
-        <v>554</v>
-      </c>
-    </row>
-    <row r="556" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+        <v>556</v>
+      </c>
+    </row>
+    <row r="556" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A556">
-        <v>555</v>
-      </c>
-    </row>
-    <row r="557" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+        <v>557</v>
+      </c>
+    </row>
+    <row r="557" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A557">
-        <v>556</v>
-      </c>
-    </row>
-    <row r="558" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+        <v>558</v>
+      </c>
+    </row>
+    <row r="558" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A558">
-        <v>557</v>
-      </c>
-    </row>
-    <row r="559" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+        <v>559</v>
+      </c>
+    </row>
+    <row r="559" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A559">
-        <v>558</v>
-      </c>
-    </row>
-    <row r="560" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+        <v>560</v>
+      </c>
+    </row>
+    <row r="560" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A560">
-        <v>559</v>
-      </c>
-    </row>
-    <row r="561" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="561" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A561">
-        <v>560</v>
-      </c>
-    </row>
-    <row r="562" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+        <v>562</v>
+      </c>
+    </row>
+    <row r="562" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A562">
-        <v>561</v>
-      </c>
-    </row>
-    <row r="563" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+        <v>563</v>
+      </c>
+    </row>
+    <row r="563" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A563">
-        <v>562</v>
-      </c>
-    </row>
-    <row r="564" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+        <v>564</v>
+      </c>
+    </row>
+    <row r="564" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A564">
-        <v>563</v>
-      </c>
-    </row>
-    <row r="565" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+        <v>565</v>
+      </c>
+    </row>
+    <row r="565" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A565">
-        <v>564</v>
-      </c>
-    </row>
-    <row r="566" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+        <v>566</v>
+      </c>
+    </row>
+    <row r="566" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A566">
-        <v>565</v>
-      </c>
-    </row>
-    <row r="567" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+        <v>567</v>
+      </c>
+    </row>
+    <row r="567" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A567">
-        <v>566</v>
-      </c>
-    </row>
-    <row r="568" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+        <v>568</v>
+      </c>
+    </row>
+    <row r="568" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A568">
-        <v>567</v>
-      </c>
-    </row>
-    <row r="569" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+        <v>569</v>
+      </c>
+    </row>
+    <row r="569" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A569">
-        <v>568</v>
-      </c>
-    </row>
-    <row r="570" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A570">
-        <v>569</v>
-      </c>
-    </row>
-    <row r="571" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A571">
         <v>570</v>
       </c>
     </row>
@@ -9719,7 +10611,7 @@
     </sortState>
   </autoFilter>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="E3:E298 E305:E370" xr:uid="{00000000-0002-0000-0000-000000000000}">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="E3:E298 E305:E387" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>"Corvette,Frigate,Destroyer,Cruiser,Battleship,Aircraft Carrier,Assault Carrier,Submarine,Ekranoplan,ALS,Howercraft,Missile,Missile-torpedo,Cannon,Torpedo,Grenade Launcher,Autocannon,Anti Air,UUV,Bomber,Drone,Fighter,Strike Fighter,Fighter,Helicopter,None"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="D121:D185" xr:uid="{A9B099F8-3DBD-4897-922B-2A7A6F698378}">
@@ -9729,4 +10621,91 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FCDF2F3A-4366-AC43-9F29-FDBD67CC7E9A}">
+  <dimension ref="A1:C7"/>
+  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.15"/>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A1" t="s">
+        <v>444</v>
+      </c>
+      <c r="B1" t="s">
+        <v>445</v>
+      </c>
+      <c r="C1" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A2" t="s">
+        <v>447</v>
+      </c>
+      <c r="B2" t="s">
+        <v>232</v>
+      </c>
+      <c r="C2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A3" t="s">
+        <v>448</v>
+      </c>
+      <c r="B3" t="s">
+        <v>251</v>
+      </c>
+      <c r="C3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A4" t="s">
+        <v>449</v>
+      </c>
+      <c r="B4" t="s">
+        <v>225</v>
+      </c>
+      <c r="C4">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A5" t="s">
+        <v>450</v>
+      </c>
+      <c r="B5" t="s">
+        <v>358</v>
+      </c>
+      <c r="C5">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A6" t="s">
+        <v>451</v>
+      </c>
+      <c r="B6" t="s">
+        <v>229</v>
+      </c>
+      <c r="C6">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A7" t="s">
+        <v>452</v>
+      </c>
+      <c r="B7" t="s">
+        <v>251</v>
+      </c>
+      <c r="C7">
+        <v>3</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/data_item.xlsx
+++ b/data_item.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="22527"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\LENOVO\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\PEJUANG RUPIAH\Desktop\check-item-bot\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{796A23BE-A404-4777-856E-93907453BFD1}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8D2E00C2-20B9-4C69-9C99-8EC6A3401F94}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,14 +20,6 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="0">Sheet1!$B$1:$F$165</definedName>
   </definedNames>
   <calcPr calcId="191028"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
 </workbook>
 </file>
 
@@ -281,7 +273,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1750" uniqueCount="541">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1802" uniqueCount="561">
   <si>
     <t>type</t>
   </si>
@@ -1904,6 +1896,66 @@
   </si>
   <si>
     <t>Pan Spatial Zeus</t>
+  </si>
+  <si>
+    <t>Ka-58 Black Ghost</t>
+  </si>
+  <si>
+    <t>helicopter</t>
+  </si>
+  <si>
+    <t>russia</t>
+  </si>
+  <si>
+    <t>shop-dollars</t>
+  </si>
+  <si>
+    <t>MUH-1 Marineon</t>
+  </si>
+  <si>
+    <t>south korea</t>
+  </si>
+  <si>
+    <t>RAH-66 Comanche</t>
+  </si>
+  <si>
+    <t>usa</t>
+  </si>
+  <si>
+    <t>WZ-19 CAIC</t>
+  </si>
+  <si>
+    <t>china</t>
+  </si>
+  <si>
+    <t>S-97 Raider</t>
+  </si>
+  <si>
+    <t>WG-13 Super Lynx</t>
+  </si>
+  <si>
+    <t>uk</t>
+  </si>
+  <si>
+    <t>AH-64 Apache</t>
+  </si>
+  <si>
+    <t>Ka-52 Alligator</t>
+  </si>
+  <si>
+    <t>SV-22 Osprey</t>
+  </si>
+  <si>
+    <t>WZ-10 CAIC</t>
+  </si>
+  <si>
+    <t>Ka-27</t>
+  </si>
+  <si>
+    <t>SH-60 Seahawk</t>
+  </si>
+  <si>
+    <t>WZ-9 Harbin</t>
   </si>
 </sst>
 </file>
@@ -11198,108 +11250,303 @@
       <c r="A475">
         <v>505</v>
       </c>
+      <c r="B475" t="s">
+        <v>541</v>
+      </c>
+      <c r="C475" t="s">
+        <v>543</v>
+      </c>
+      <c r="D475">
+        <v>3</v>
+      </c>
+      <c r="E475" t="s">
+        <v>542</v>
+      </c>
+      <c r="F475" t="s">
+        <v>544</v>
+      </c>
     </row>
     <row r="476" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A476">
         <v>506</v>
       </c>
+      <c r="B476" t="s">
+        <v>545</v>
+      </c>
+      <c r="C476" t="s">
+        <v>546</v>
+      </c>
+      <c r="D476">
+        <v>3</v>
+      </c>
+      <c r="E476" t="s">
+        <v>542</v>
+      </c>
+      <c r="F476" t="s">
+        <v>544</v>
+      </c>
     </row>
     <row r="477" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A477">
         <v>507</v>
       </c>
+      <c r="B477" t="s">
+        <v>547</v>
+      </c>
+      <c r="C477" t="s">
+        <v>548</v>
+      </c>
+      <c r="D477">
+        <v>3</v>
+      </c>
+      <c r="E477" t="s">
+        <v>542</v>
+      </c>
+      <c r="F477" t="s">
+        <v>544</v>
+      </c>
     </row>
     <row r="478" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A478">
         <v>508</v>
       </c>
+      <c r="B478" t="s">
+        <v>549</v>
+      </c>
+      <c r="C478" t="s">
+        <v>550</v>
+      </c>
+      <c r="D478">
+        <v>3</v>
+      </c>
+      <c r="E478" t="s">
+        <v>542</v>
+      </c>
+      <c r="F478" t="s">
+        <v>544</v>
+      </c>
     </row>
     <row r="479" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A479">
         <v>509</v>
       </c>
+      <c r="B479" t="s">
+        <v>551</v>
+      </c>
+      <c r="C479" t="s">
+        <v>548</v>
+      </c>
+      <c r="D479">
+        <v>2</v>
+      </c>
+      <c r="E479" t="s">
+        <v>542</v>
+      </c>
+      <c r="F479" t="s">
+        <v>544</v>
+      </c>
     </row>
     <row r="480" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A480">
         <v>510</v>
       </c>
-    </row>
-    <row r="481" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B480" t="s">
+        <v>552</v>
+      </c>
+      <c r="C480" t="s">
+        <v>553</v>
+      </c>
+      <c r="D480">
+        <v>2</v>
+      </c>
+      <c r="E480" t="s">
+        <v>542</v>
+      </c>
+      <c r="F480" t="s">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="481" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A481">
         <v>511</v>
       </c>
-    </row>
-    <row r="482" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B481" t="s">
+        <v>554</v>
+      </c>
+      <c r="C481" t="s">
+        <v>548</v>
+      </c>
+      <c r="D481">
+        <v>2</v>
+      </c>
+      <c r="E481" t="s">
+        <v>542</v>
+      </c>
+      <c r="F481" t="s">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="482" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A482">
         <v>512</v>
       </c>
-    </row>
-    <row r="483" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B482" t="s">
+        <v>555</v>
+      </c>
+      <c r="C482" t="s">
+        <v>543</v>
+      </c>
+      <c r="D482">
+        <v>2</v>
+      </c>
+      <c r="E482" t="s">
+        <v>542</v>
+      </c>
+      <c r="F482" t="s">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="483" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A483">
         <v>513</v>
       </c>
-    </row>
-    <row r="484" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B483" t="s">
+        <v>556</v>
+      </c>
+      <c r="C483" t="s">
+        <v>548</v>
+      </c>
+      <c r="D483">
+        <v>2</v>
+      </c>
+      <c r="E483" t="s">
+        <v>542</v>
+      </c>
+      <c r="F483" t="s">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="484" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A484">
         <v>514</v>
       </c>
-    </row>
-    <row r="485" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B484" t="s">
+        <v>557</v>
+      </c>
+      <c r="C484" t="s">
+        <v>550</v>
+      </c>
+      <c r="D484">
+        <v>2</v>
+      </c>
+      <c r="E484" t="s">
+        <v>542</v>
+      </c>
+      <c r="F484" t="s">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="485" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A485">
         <v>515</v>
       </c>
-    </row>
-    <row r="486" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B485" t="s">
+        <v>558</v>
+      </c>
+      <c r="C485" t="s">
+        <v>543</v>
+      </c>
+      <c r="D485">
+        <v>1</v>
+      </c>
+      <c r="E485" t="s">
+        <v>542</v>
+      </c>
+      <c r="F485" t="s">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="486" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A486">
         <v>516</v>
       </c>
-    </row>
-    <row r="487" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B486" t="s">
+        <v>559</v>
+      </c>
+      <c r="C486" t="s">
+        <v>548</v>
+      </c>
+      <c r="D486">
+        <v>1</v>
+      </c>
+      <c r="E486" t="s">
+        <v>542</v>
+      </c>
+      <c r="F486" t="s">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="487" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A487">
         <v>517</v>
       </c>
-    </row>
-    <row r="488" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B487" t="s">
+        <v>560</v>
+      </c>
+      <c r="C487" t="s">
+        <v>550</v>
+      </c>
+      <c r="D487">
+        <v>1</v>
+      </c>
+      <c r="E487" t="s">
+        <v>542</v>
+      </c>
+      <c r="F487" t="s">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="488" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A488">
         <v>518</v>
       </c>
     </row>
-    <row r="489" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="489" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A489">
         <v>519</v>
       </c>
     </row>
-    <row r="490" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="490" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A490">
         <v>520</v>
       </c>
     </row>
-    <row r="491" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="491" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A491">
         <v>521</v>
       </c>
     </row>
-    <row r="492" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="492" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A492">
         <v>522</v>
       </c>
     </row>
-    <row r="493" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="493" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A493">
         <v>523</v>
       </c>
     </row>
-    <row r="494" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="494" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A494">
         <v>524</v>
       </c>
     </row>
-    <row r="495" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="495" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A495">
         <v>525</v>
       </c>
     </row>
-    <row r="496" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="496" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A496">
         <v>526</v>
       </c>

--- a/data_item.xlsx
+++ b/data_item.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\PEJUANG RUPIAH\Desktop\check-item-bot\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8D2E00C2-20B9-4C69-9C99-8EC6A3401F94}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{946B9E90-65D8-426D-B9F6-1E116356B14A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -17,7 +17,7 @@
     <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0">Sheet1!$B$1:$F$165</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$B$1:$F$540</definedName>
   </definedNames>
   <calcPr calcId="191028"/>
 </workbook>
@@ -273,7 +273,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1802" uniqueCount="561">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1823" uniqueCount="562">
   <si>
     <t>type</t>
   </si>
@@ -1956,6 +1956,9 @@
   </si>
   <si>
     <t>WZ-9 Harbin</t>
+  </si>
+  <si>
+    <t>North Korea</t>
   </si>
 </sst>
 </file>
@@ -2342,6 +2345,9 @@
       <c r="B2" s="1" t="s">
         <v>23</v>
       </c>
+      <c r="C2" t="s">
+        <v>212</v>
+      </c>
       <c r="D2" s="1">
         <v>3</v>
       </c>
@@ -2359,6 +2365,9 @@
       <c r="B3" s="9" t="s">
         <v>26</v>
       </c>
+      <c r="C3" t="s">
+        <v>218</v>
+      </c>
       <c r="D3" s="1">
         <v>3</v>
       </c>
@@ -2375,6 +2384,9 @@
       </c>
       <c r="B4" s="9" t="s">
         <v>33</v>
+      </c>
+      <c r="C4" t="s">
+        <v>212</v>
       </c>
       <c r="D4" s="1">
         <v>3</v>
@@ -2393,6 +2405,9 @@
       <c r="B5" s="9" t="s">
         <v>37</v>
       </c>
+      <c r="C5" t="s">
+        <v>231</v>
+      </c>
       <c r="D5" s="1">
         <v>3</v>
       </c>
@@ -2410,6 +2425,9 @@
       <c r="B6" s="9" t="s">
         <v>40</v>
       </c>
+      <c r="C6" t="s">
+        <v>203</v>
+      </c>
       <c r="D6" s="1">
         <v>3</v>
       </c>
@@ -2427,6 +2445,9 @@
       <c r="B7" s="9" t="s">
         <v>172</v>
       </c>
+      <c r="C7" t="s">
+        <v>212</v>
+      </c>
       <c r="D7" s="12">
         <v>3</v>
       </c>
@@ -2444,6 +2465,9 @@
       <c r="B8" s="10" t="s">
         <v>63</v>
       </c>
+      <c r="C8" t="s">
+        <v>203</v>
+      </c>
       <c r="D8" s="1">
         <v>3</v>
       </c>
@@ -2461,6 +2485,9 @@
       <c r="B9" s="10" t="s">
         <v>66</v>
       </c>
+      <c r="C9" t="s">
+        <v>212</v>
+      </c>
       <c r="D9" s="1">
         <v>3</v>
       </c>
@@ -2478,6 +2505,9 @@
       <c r="B10" s="10" t="s">
         <v>84</v>
       </c>
+      <c r="C10" t="s">
+        <v>205</v>
+      </c>
       <c r="D10" s="1">
         <v>3</v>
       </c>
@@ -2495,6 +2525,9 @@
       <c r="B11" s="7" t="s">
         <v>121</v>
       </c>
+      <c r="C11" t="s">
+        <v>212</v>
+      </c>
       <c r="D11" s="1">
         <v>3</v>
       </c>
@@ -2512,6 +2545,9 @@
       <c r="B12" s="9" t="s">
         <v>143</v>
       </c>
+      <c r="C12" t="s">
+        <v>231</v>
+      </c>
       <c r="D12" s="12">
         <v>3</v>
       </c>
@@ -2529,6 +2565,9 @@
       <c r="B13" s="9" t="s">
         <v>147</v>
       </c>
+      <c r="C13" t="s">
+        <v>338</v>
+      </c>
       <c r="D13" s="12">
         <v>3</v>
       </c>
@@ -2546,6 +2585,9 @@
       <c r="B14" s="7" t="s">
         <v>153</v>
       </c>
+      <c r="C14" t="s">
+        <v>338</v>
+      </c>
       <c r="D14" s="12">
         <v>3</v>
       </c>
@@ -2563,6 +2605,9 @@
       <c r="B15" s="9" t="s">
         <v>161</v>
       </c>
+      <c r="C15" t="s">
+        <v>338</v>
+      </c>
       <c r="D15" s="12">
         <v>3</v>
       </c>
@@ -2580,6 +2625,9 @@
       <c r="B16" s="9" t="s">
         <v>35</v>
       </c>
+      <c r="C16" t="s">
+        <v>212</v>
+      </c>
       <c r="D16" s="1">
         <v>3</v>
       </c>
@@ -2597,6 +2645,9 @@
       <c r="B17" s="9" t="s">
         <v>39</v>
       </c>
+      <c r="C17" t="s">
+        <v>212</v>
+      </c>
       <c r="D17" s="1">
         <v>3</v>
       </c>
@@ -2614,6 +2665,9 @@
       <c r="B18" s="10" t="s">
         <v>67</v>
       </c>
+      <c r="C18" t="s">
+        <v>203</v>
+      </c>
       <c r="D18" s="1">
         <v>3</v>
       </c>
@@ -2631,6 +2685,9 @@
       <c r="B19" s="9" t="s">
         <v>200</v>
       </c>
+      <c r="C19" t="s">
+        <v>338</v>
+      </c>
       <c r="D19" s="1">
         <v>3</v>
       </c>
@@ -2648,6 +2705,9 @@
       <c r="B20" s="9" t="s">
         <v>199</v>
       </c>
+      <c r="C20" t="s">
+        <v>561</v>
+      </c>
       <c r="D20" s="12">
         <v>3</v>
       </c>
@@ -2665,6 +2725,9 @@
       <c r="B21" s="7" t="s">
         <v>155</v>
       </c>
+      <c r="C21" t="s">
+        <v>323</v>
+      </c>
       <c r="D21" s="12">
         <v>3</v>
       </c>
@@ -2682,6 +2745,9 @@
       <c r="B22" s="9" t="s">
         <v>201</v>
       </c>
+      <c r="C22" t="s">
+        <v>323</v>
+      </c>
       <c r="D22" s="12">
         <v>3</v>
       </c>
@@ -11772,7 +11838,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="B1:F165" xr:uid="{9FC02C4D-B240-46EA-A4A7-1A5D0B5C9EF3}">
+  <autoFilter ref="B1:F540" xr:uid="{9FC02C4D-B240-46EA-A4A7-1A5D0B5C9EF3}">
     <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B2:F151">
       <sortCondition ref="E1"/>
     </sortState>

--- a/data_item.xlsx
+++ b/data_item.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\PEJUANG RUPIAH\Desktop\check-item-bot\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{946B9E90-65D8-426D-B9F6-1E116356B14A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2636D168-7501-4FF7-A203-760F1F09B0EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -273,7 +273,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1823" uniqueCount="562">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1853" uniqueCount="570">
   <si>
     <t>type</t>
   </si>
@@ -551,9 +551,6 @@
     <t>UGSTPhysic2</t>
   </si>
   <si>
-    <t>K76L62</t>
-  </si>
-  <si>
     <t>RedShark</t>
   </si>
   <si>
@@ -566,9 +563,6 @@
     <t>Iskander</t>
   </si>
   <si>
-    <t>A220M</t>
-  </si>
-  <si>
     <t>DF12</t>
   </si>
   <si>
@@ -590,21 +584,12 @@
     <t>DF100</t>
   </si>
   <si>
-    <t xml:space="preserve">Mark71 </t>
-  </si>
-  <si>
     <t>UUM125SeaLance</t>
   </si>
   <si>
     <t>ASN4G</t>
   </si>
   <si>
-    <t>MRPGKonigEMRG</t>
-  </si>
-  <si>
-    <t>RG30Buckshot</t>
-  </si>
-  <si>
     <t>Feitian1</t>
   </si>
   <si>
@@ -617,18 +602,12 @@
     <t>TRG300Tiger</t>
   </si>
   <si>
-    <t>ERSTensho</t>
-  </si>
-  <si>
     <t>Swarmer2Atlas</t>
   </si>
   <si>
     <t>S10Granat</t>
   </si>
   <si>
-    <t>Archer</t>
-  </si>
-  <si>
     <t>Pukguksong4SLBM</t>
   </si>
   <si>
@@ -683,36 +662,21 @@
     <t>RBU10000</t>
   </si>
   <si>
-    <t>SH16</t>
-  </si>
-  <si>
     <t>MI8TV</t>
   </si>
   <si>
     <t>AstrosIIMK6</t>
   </si>
   <si>
-    <t>DanaM2</t>
-  </si>
-  <si>
     <t>Pralay</t>
   </si>
   <si>
     <t>PLRKOtvet</t>
   </si>
   <si>
-    <t>JRVG1</t>
-  </si>
-  <si>
     <t>Roland2</t>
   </si>
   <si>
-    <t>Mark42</t>
-  </si>
-  <si>
-    <t>Mark5512</t>
-  </si>
-  <si>
     <t>Nirbhay</t>
   </si>
   <si>
@@ -740,9 +704,6 @@
     <t>HSU100</t>
   </si>
   <si>
-    <t xml:space="preserve">Skyranger30  </t>
-  </si>
-  <si>
     <t>EVENT PASS</t>
   </si>
   <si>
@@ -764,9 +725,6 @@
     <t>WS3</t>
   </si>
   <si>
-    <t>A200</t>
-  </si>
-  <si>
     <t>Z6B</t>
   </si>
   <si>
@@ -809,12 +767,6 @@
     <t>name</t>
   </si>
   <si>
-    <t>MKE 76</t>
-  </si>
-  <si>
-    <t>PLZ-05</t>
-  </si>
-  <si>
     <t>FGS Admiral Graf Spee</t>
   </si>
   <si>
@@ -1958,14 +1910,86 @@
     <t>WZ-9 Harbin</t>
   </si>
   <si>
-    <t>North Korea</t>
+    <t>france</t>
+  </si>
+  <si>
+    <t>switzerland</t>
+  </si>
+  <si>
+    <t>Oerlikon Skyranger 30 Hybrid</t>
+  </si>
+  <si>
+    <t>germany</t>
+  </si>
+  <si>
+    <t>pan spatial</t>
+  </si>
+  <si>
+    <t>indonesia</t>
+  </si>
+  <si>
+    <t>united kingdom</t>
+  </si>
+  <si>
+    <t>MKE 76 mm Naval Gun</t>
+  </si>
+  <si>
+    <t>turkiye</t>
+  </si>
+  <si>
+    <t>PLZ-05 155 mm</t>
+  </si>
+  <si>
+    <t>K-76L/62</t>
+  </si>
+  <si>
+    <t>A-220M 57 mm</t>
+  </si>
+  <si>
+    <t>Mark 71 8-inch Gun</t>
+  </si>
+  <si>
+    <t>EMRG Konig</t>
+  </si>
+  <si>
+    <t>RG-30 Buckshot</t>
+  </si>
+  <si>
+    <t>ERS Tensho 155 mm</t>
+  </si>
+  <si>
+    <t>Archer 155 mm</t>
+  </si>
+  <si>
+    <t>sweden</t>
+  </si>
+  <si>
+    <t>SH-16 155 mm</t>
+  </si>
+  <si>
+    <t>Dana M2 152 mm</t>
+  </si>
+  <si>
+    <t>czech republic</t>
+  </si>
+  <si>
+    <t>JRVG-1 130 mm</t>
+  </si>
+  <si>
+    <t>Mark 42 5-inch Gun</t>
+  </si>
+  <si>
+    <t>Mark 55/12</t>
+  </si>
+  <si>
+    <t>A-200 Navigator</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -1993,6 +2017,13 @@
       <sz val="11"/>
       <color rgb="FF008000"/>
       <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="4">
@@ -2053,7 +2084,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -2091,6 +2122,7 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2320,10 +2352,10 @@
   <sheetData>
     <row r="1" spans="1:6" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
-        <v>334</v>
+        <v>318</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>177</v>
+        <v>163</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>3</v>
@@ -2346,7 +2378,7 @@
         <v>23</v>
       </c>
       <c r="C2" t="s">
-        <v>212</v>
+        <v>196</v>
       </c>
       <c r="D2" s="1">
         <v>3</v>
@@ -2366,7 +2398,7 @@
         <v>26</v>
       </c>
       <c r="C3" t="s">
-        <v>218</v>
+        <v>202</v>
       </c>
       <c r="D3" s="1">
         <v>3</v>
@@ -2386,7 +2418,7 @@
         <v>33</v>
       </c>
       <c r="C4" t="s">
-        <v>212</v>
+        <v>196</v>
       </c>
       <c r="D4" s="1">
         <v>3</v>
@@ -2406,7 +2438,7 @@
         <v>37</v>
       </c>
       <c r="C5" t="s">
-        <v>231</v>
+        <v>215</v>
       </c>
       <c r="D5" s="1">
         <v>3</v>
@@ -2426,7 +2458,7 @@
         <v>40</v>
       </c>
       <c r="C6" t="s">
-        <v>203</v>
+        <v>187</v>
       </c>
       <c r="D6" s="1">
         <v>3</v>
@@ -2443,10 +2475,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="9" t="s">
-        <v>172</v>
+        <v>158</v>
       </c>
       <c r="C7" t="s">
-        <v>212</v>
+        <v>196</v>
       </c>
       <c r="D7" s="12">
         <v>3</v>
@@ -2455,7 +2487,7 @@
         <v>41</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>166</v>
+        <v>152</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="12.75" x14ac:dyDescent="0.2">
@@ -2466,7 +2498,7 @@
         <v>63</v>
       </c>
       <c r="C8" t="s">
-        <v>203</v>
+        <v>187</v>
       </c>
       <c r="D8" s="1">
         <v>3</v>
@@ -2486,7 +2518,7 @@
         <v>66</v>
       </c>
       <c r="C9" t="s">
-        <v>212</v>
+        <v>196</v>
       </c>
       <c r="D9" s="1">
         <v>3</v>
@@ -2506,7 +2538,7 @@
         <v>84</v>
       </c>
       <c r="C10" t="s">
-        <v>205</v>
+        <v>189</v>
       </c>
       <c r="D10" s="1">
         <v>3</v>
@@ -2523,10 +2555,10 @@
         <v>10</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>121</v>
+        <v>114</v>
       </c>
       <c r="C11" t="s">
-        <v>212</v>
+        <v>196</v>
       </c>
       <c r="D11" s="1">
         <v>3</v>
@@ -2543,10 +2575,10 @@
         <v>11</v>
       </c>
       <c r="B12" s="9" t="s">
-        <v>143</v>
+        <v>133</v>
       </c>
       <c r="C12" t="s">
-        <v>231</v>
+        <v>215</v>
       </c>
       <c r="D12" s="12">
         <v>3</v>
@@ -2555,7 +2587,7 @@
         <v>64</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>156</v>
+        <v>143</v>
       </c>
     </row>
     <row r="13" spans="1:6" ht="12.75" x14ac:dyDescent="0.2">
@@ -2563,10 +2595,10 @@
         <v>12</v>
       </c>
       <c r="B13" s="9" t="s">
-        <v>147</v>
+        <v>135</v>
       </c>
       <c r="C13" t="s">
-        <v>338</v>
+        <v>322</v>
       </c>
       <c r="D13" s="12">
         <v>3</v>
@@ -2575,7 +2607,7 @@
         <v>64</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>156</v>
+        <v>143</v>
       </c>
     </row>
     <row r="14" spans="1:6" ht="12.75" x14ac:dyDescent="0.2">
@@ -2583,10 +2615,10 @@
         <v>13</v>
       </c>
       <c r="B14" s="7" t="s">
-        <v>153</v>
+        <v>141</v>
       </c>
       <c r="C14" t="s">
-        <v>338</v>
+        <v>322</v>
       </c>
       <c r="D14" s="12">
         <v>3</v>
@@ -2595,7 +2627,7 @@
         <v>64</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>156</v>
+        <v>143</v>
       </c>
     </row>
     <row r="15" spans="1:6" ht="12.75" x14ac:dyDescent="0.2">
@@ -2603,10 +2635,10 @@
         <v>14</v>
       </c>
       <c r="B15" s="9" t="s">
-        <v>161</v>
+        <v>148</v>
       </c>
       <c r="C15" t="s">
-        <v>338</v>
+        <v>322</v>
       </c>
       <c r="D15" s="12">
         <v>3</v>
@@ -2615,7 +2647,7 @@
         <v>64</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>166</v>
+        <v>152</v>
       </c>
     </row>
     <row r="16" spans="1:6" ht="12.75" x14ac:dyDescent="0.2">
@@ -2626,7 +2658,7 @@
         <v>35</v>
       </c>
       <c r="C16" t="s">
-        <v>212</v>
+        <v>196</v>
       </c>
       <c r="D16" s="1">
         <v>3</v>
@@ -2646,7 +2678,7 @@
         <v>39</v>
       </c>
       <c r="C17" t="s">
-        <v>212</v>
+        <v>196</v>
       </c>
       <c r="D17" s="1">
         <v>3</v>
@@ -2666,7 +2698,7 @@
         <v>67</v>
       </c>
       <c r="C18" t="s">
-        <v>203</v>
+        <v>534</v>
       </c>
       <c r="D18" s="1">
         <v>3</v>
@@ -2683,10 +2715,10 @@
         <v>19</v>
       </c>
       <c r="B19" s="9" t="s">
-        <v>200</v>
+        <v>184</v>
       </c>
       <c r="C19" t="s">
-        <v>338</v>
+        <v>545</v>
       </c>
       <c r="D19" s="1">
         <v>3</v>
@@ -2703,10 +2735,10 @@
         <v>20</v>
       </c>
       <c r="B20" s="9" t="s">
-        <v>199</v>
+        <v>183</v>
       </c>
       <c r="C20" t="s">
-        <v>561</v>
+        <v>527</v>
       </c>
       <c r="D20" s="12">
         <v>3</v>
@@ -2715,7 +2747,7 @@
         <v>68</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>156</v>
+        <v>143</v>
       </c>
     </row>
     <row r="21" spans="1:6" ht="12.75" x14ac:dyDescent="0.2">
@@ -2723,10 +2755,10 @@
         <v>21</v>
       </c>
       <c r="B21" s="7" t="s">
-        <v>155</v>
+        <v>547</v>
       </c>
       <c r="C21" t="s">
-        <v>323</v>
+        <v>546</v>
       </c>
       <c r="D21" s="12">
         <v>3</v>
@@ -2735,7 +2767,7 @@
         <v>68</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>156</v>
+        <v>143</v>
       </c>
     </row>
     <row r="22" spans="1:6" ht="12.75" x14ac:dyDescent="0.2">
@@ -2743,10 +2775,10 @@
         <v>22</v>
       </c>
       <c r="B22" s="9" t="s">
-        <v>201</v>
+        <v>185</v>
       </c>
       <c r="C22" t="s">
-        <v>323</v>
+        <v>546</v>
       </c>
       <c r="D22" s="12">
         <v>3</v>
@@ -2755,7 +2787,7 @@
         <v>68</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>166</v>
+        <v>152</v>
       </c>
     </row>
     <row r="23" spans="1:6" ht="12.75" x14ac:dyDescent="0.2">
@@ -2765,6 +2797,9 @@
       <c r="B23" s="1" t="s">
         <v>9</v>
       </c>
+      <c r="C23" t="s">
+        <v>527</v>
+      </c>
       <c r="D23" s="1">
         <v>3</v>
       </c>
@@ -2782,6 +2817,9 @@
       <c r="B24" s="1" t="s">
         <v>12</v>
       </c>
+      <c r="C24" t="s">
+        <v>548</v>
+      </c>
       <c r="D24" s="1">
         <v>3</v>
       </c>
@@ -2799,6 +2837,9 @@
       <c r="B25" s="1" t="s">
         <v>14</v>
       </c>
+      <c r="C25" t="s">
+        <v>534</v>
+      </c>
       <c r="D25" s="1">
         <v>3</v>
       </c>
@@ -2816,6 +2857,9 @@
       <c r="B26" s="1" t="s">
         <v>15</v>
       </c>
+      <c r="C26" t="s">
+        <v>549</v>
+      </c>
       <c r="D26" s="1">
         <v>3</v>
       </c>
@@ -2833,6 +2877,9 @@
       <c r="B27" s="1" t="s">
         <v>17</v>
       </c>
+      <c r="C27" t="s">
+        <v>532</v>
+      </c>
       <c r="D27" s="1">
         <v>3</v>
       </c>
@@ -2850,6 +2897,9 @@
       <c r="B28" s="1" t="s">
         <v>18</v>
       </c>
+      <c r="C28" t="s">
+        <v>527</v>
+      </c>
       <c r="D28" s="1">
         <v>3</v>
       </c>
@@ -2867,6 +2917,9 @@
       <c r="B29" s="1" t="s">
         <v>19</v>
       </c>
+      <c r="C29" t="s">
+        <v>6</v>
+      </c>
       <c r="D29" s="1">
         <v>3</v>
       </c>
@@ -2884,6 +2937,9 @@
       <c r="B30" s="1" t="s">
         <v>20</v>
       </c>
+      <c r="C30" t="s">
+        <v>545</v>
+      </c>
       <c r="D30" s="1">
         <v>3</v>
       </c>
@@ -2901,6 +2957,9 @@
       <c r="B31" s="1" t="s">
         <v>21</v>
       </c>
+      <c r="C31" t="s">
+        <v>550</v>
+      </c>
       <c r="D31" s="1">
         <v>3</v>
       </c>
@@ -2918,6 +2977,9 @@
       <c r="B32" s="1" t="s">
         <v>22</v>
       </c>
+      <c r="C32" t="s">
+        <v>551</v>
+      </c>
       <c r="D32" s="1">
         <v>3</v>
       </c>
@@ -2935,6 +2997,9 @@
       <c r="B33" s="9" t="s">
         <v>44</v>
       </c>
+      <c r="C33" t="s">
+        <v>545</v>
+      </c>
       <c r="D33" s="1">
         <v>3</v>
       </c>
@@ -2952,6 +3017,9 @@
       <c r="B34" s="2" t="s">
         <v>51</v>
       </c>
+      <c r="C34" t="s">
+        <v>532</v>
+      </c>
       <c r="D34" s="1">
         <v>3</v>
       </c>
@@ -2967,7 +3035,10 @@
         <v>35</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>168</v>
+        <v>154</v>
+      </c>
+      <c r="C35" t="s">
+        <v>6</v>
       </c>
       <c r="D35" s="12">
         <v>3</v>
@@ -2984,7 +3055,10 @@
         <v>36</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>169</v>
+        <v>155</v>
+      </c>
+      <c r="C36" t="s">
+        <v>527</v>
       </c>
       <c r="D36" s="12">
         <v>3</v>
@@ -3001,24 +3075,30 @@
         <v>37</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>124</v>
+        <v>117</v>
+      </c>
+      <c r="C37" s="17" t="s">
+        <v>215</v>
       </c>
       <c r="D37" s="12">
         <v>3</v>
       </c>
       <c r="E37" s="3" t="s">
-        <v>125</v>
+        <v>118</v>
       </c>
       <c r="F37" s="1" t="s">
-        <v>156</v>
+        <v>143</v>
       </c>
     </row>
     <row r="38" spans="1:6" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A38">
         <v>38</v>
       </c>
-      <c r="B38" s="5" t="s">
-        <v>178</v>
+      <c r="B38" t="s">
+        <v>552</v>
+      </c>
+      <c r="C38" t="s">
+        <v>553</v>
       </c>
       <c r="D38" s="1">
         <v>3</v>
@@ -3034,8 +3114,11 @@
       <c r="A39">
         <v>39</v>
       </c>
-      <c r="B39" s="4" t="s">
-        <v>179</v>
+      <c r="B39" t="s">
+        <v>554</v>
+      </c>
+      <c r="C39" t="s">
+        <v>534</v>
       </c>
       <c r="D39" s="1">
         <v>3</v>
@@ -3051,8 +3134,11 @@
       <c r="A40">
         <v>40</v>
       </c>
-      <c r="B40" s="5" t="s">
-        <v>92</v>
+      <c r="B40" t="s">
+        <v>555</v>
+      </c>
+      <c r="C40" t="s">
+        <v>530</v>
       </c>
       <c r="D40" s="1">
         <v>3</v>
@@ -3068,8 +3154,11 @@
       <c r="A41">
         <v>41</v>
       </c>
-      <c r="B41" s="5" t="s">
-        <v>97</v>
+      <c r="B41" t="s">
+        <v>556</v>
+      </c>
+      <c r="C41" t="s">
+        <v>527</v>
       </c>
       <c r="D41" s="1">
         <v>3</v>
@@ -3085,8 +3174,11 @@
       <c r="A42">
         <v>42</v>
       </c>
-      <c r="B42" s="5" t="s">
-        <v>105</v>
+      <c r="B42" t="s">
+        <v>557</v>
+      </c>
+      <c r="C42" t="s">
+        <v>532</v>
       </c>
       <c r="D42" s="1">
         <v>3</v>
@@ -3102,8 +3194,11 @@
       <c r="A43">
         <v>43</v>
       </c>
-      <c r="B43" s="5" t="s">
-        <v>108</v>
+      <c r="B43" t="s">
+        <v>558</v>
+      </c>
+      <c r="C43" t="s">
+        <v>548</v>
       </c>
       <c r="D43" s="1">
         <v>3</v>
@@ -3119,8 +3214,11 @@
       <c r="A44">
         <v>44</v>
       </c>
-      <c r="B44" s="2" t="s">
-        <v>109</v>
+      <c r="B44" t="s">
+        <v>559</v>
+      </c>
+      <c r="C44" t="s">
+        <v>532</v>
       </c>
       <c r="D44" s="1">
         <v>3</v>
@@ -3136,8 +3234,11 @@
       <c r="A45">
         <v>45</v>
       </c>
-      <c r="B45" s="2" t="s">
-        <v>114</v>
+      <c r="B45" t="s">
+        <v>560</v>
+      </c>
+      <c r="C45" t="s">
+        <v>6</v>
       </c>
       <c r="D45" s="1">
         <v>3</v>
@@ -3153,8 +3254,11 @@
       <c r="A46">
         <v>46</v>
       </c>
-      <c r="B46" s="2" t="s">
-        <v>117</v>
+      <c r="B46" t="s">
+        <v>561</v>
+      </c>
+      <c r="C46" t="s">
+        <v>562</v>
       </c>
       <c r="D46" s="1">
         <v>3</v>
@@ -3170,8 +3274,11 @@
       <c r="A47">
         <v>47</v>
       </c>
-      <c r="B47" s="2" t="s">
-        <v>136</v>
+      <c r="B47" t="s">
+        <v>563</v>
+      </c>
+      <c r="C47" t="s">
+        <v>534</v>
       </c>
       <c r="D47" s="12">
         <v>3</v>
@@ -3180,15 +3287,18 @@
         <v>65</v>
       </c>
       <c r="F47" s="1" t="s">
-        <v>156</v>
+        <v>143</v>
       </c>
     </row>
     <row r="48" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A48">
         <v>48</v>
       </c>
-      <c r="B48" s="2" t="s">
-        <v>139</v>
+      <c r="B48" t="s">
+        <v>564</v>
+      </c>
+      <c r="C48" t="s">
+        <v>565</v>
       </c>
       <c r="D48" s="12">
         <v>3</v>
@@ -3197,15 +3307,18 @@
         <v>65</v>
       </c>
       <c r="F48" s="1" t="s">
-        <v>156</v>
+        <v>143</v>
       </c>
     </row>
     <row r="49" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A49">
         <v>49</v>
       </c>
-      <c r="B49" s="2" t="s">
-        <v>142</v>
+      <c r="B49" t="s">
+        <v>566</v>
+      </c>
+      <c r="C49" t="s">
+        <v>534</v>
       </c>
       <c r="D49" s="12">
         <v>3</v>
@@ -3214,15 +3327,18 @@
         <v>65</v>
       </c>
       <c r="F49" s="1" t="s">
-        <v>156</v>
+        <v>143</v>
       </c>
     </row>
     <row r="50" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A50">
         <v>50</v>
       </c>
-      <c r="B50" s="2" t="s">
-        <v>144</v>
+      <c r="B50" t="s">
+        <v>567</v>
+      </c>
+      <c r="C50" t="s">
+        <v>532</v>
       </c>
       <c r="D50" s="12">
         <v>3</v>
@@ -3231,15 +3347,18 @@
         <v>65</v>
       </c>
       <c r="F50" s="1" t="s">
-        <v>156</v>
+        <v>143</v>
       </c>
     </row>
     <row r="51" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A51">
         <v>51</v>
       </c>
-      <c r="B51" s="2" t="s">
-        <v>145</v>
+      <c r="B51" t="s">
+        <v>568</v>
+      </c>
+      <c r="C51" t="s">
+        <v>532</v>
       </c>
       <c r="D51" s="12">
         <v>3</v>
@@ -3248,15 +3367,18 @@
         <v>65</v>
       </c>
       <c r="F51" s="1" t="s">
-        <v>156</v>
+        <v>143</v>
       </c>
     </row>
     <row r="52" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A52">
         <v>52</v>
       </c>
-      <c r="B52" s="2" t="s">
-        <v>163</v>
+      <c r="B52" t="s">
+        <v>569</v>
+      </c>
+      <c r="C52" t="s">
+        <v>527</v>
       </c>
       <c r="D52" s="12">
         <v>3</v>
@@ -3265,7 +3387,7 @@
         <v>65</v>
       </c>
       <c r="F52" s="1" t="s">
-        <v>166</v>
+        <v>152</v>
       </c>
     </row>
     <row r="53" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -3358,7 +3480,7 @@
         <v>67</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>167</v>
+        <v>153</v>
       </c>
       <c r="D58" s="12">
         <v>3</v>
@@ -3375,7 +3497,7 @@
         <v>68</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>173</v>
+        <v>159</v>
       </c>
       <c r="D59" s="12">
         <v>3</v>
@@ -3384,7 +3506,7 @@
         <v>11</v>
       </c>
       <c r="F59" s="1" t="s">
-        <v>166</v>
+        <v>152</v>
       </c>
     </row>
     <row r="60" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -3528,7 +3650,7 @@
         <v>82</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>170</v>
+        <v>156</v>
       </c>
       <c r="D68" s="12">
         <v>3</v>
@@ -3545,7 +3667,7 @@
         <v>83</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>171</v>
+        <v>157</v>
       </c>
       <c r="D69" s="12">
         <v>3</v>
@@ -3562,7 +3684,7 @@
         <v>84</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>176</v>
+        <v>162</v>
       </c>
       <c r="D70" s="12">
         <v>3</v>
@@ -3571,7 +3693,7 @@
         <v>13</v>
       </c>
       <c r="F70" s="1" t="s">
-        <v>166</v>
+        <v>152</v>
       </c>
     </row>
     <row r="71" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -3579,16 +3701,16 @@
         <v>85</v>
       </c>
       <c r="B71" s="2" t="s">
-        <v>126</v>
+        <v>119</v>
       </c>
       <c r="D71" s="12">
         <v>3</v>
       </c>
       <c r="E71" s="3" t="s">
-        <v>127</v>
+        <v>120</v>
       </c>
       <c r="F71" s="1" t="s">
-        <v>156</v>
+        <v>143</v>
       </c>
     </row>
     <row r="72" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -3596,16 +3718,16 @@
         <v>86</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>131</v>
+        <v>124</v>
       </c>
       <c r="D72" s="12">
         <v>3</v>
       </c>
       <c r="E72" s="3" t="s">
-        <v>127</v>
+        <v>120</v>
       </c>
       <c r="F72" s="1" t="s">
-        <v>156</v>
+        <v>143</v>
       </c>
     </row>
     <row r="73" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -3630,16 +3752,16 @@
         <v>89</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>148</v>
+        <v>136</v>
       </c>
       <c r="D74" s="12">
         <v>3</v>
       </c>
       <c r="E74" s="3" t="s">
-        <v>149</v>
+        <v>137</v>
       </c>
       <c r="F74" s="1" t="s">
-        <v>156</v>
+        <v>143</v>
       </c>
     </row>
     <row r="75" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -3766,7 +3888,7 @@
         <v>97</v>
       </c>
       <c r="B82" s="2" t="s">
-        <v>174</v>
+        <v>160</v>
       </c>
       <c r="D82" s="12">
         <v>3</v>
@@ -3775,7 +3897,7 @@
         <v>28</v>
       </c>
       <c r="F82" s="1" t="s">
-        <v>166</v>
+        <v>152</v>
       </c>
     </row>
     <row r="83" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -3800,7 +3922,7 @@
         <v>99</v>
       </c>
       <c r="B84" s="5" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="D84" s="1">
         <v>3</v>
@@ -3817,7 +3939,7 @@
         <v>100</v>
       </c>
       <c r="B85" s="2" t="s">
-        <v>113</v>
+        <v>108</v>
       </c>
       <c r="D85" s="1">
         <v>3</v>
@@ -3834,7 +3956,7 @@
         <v>101</v>
       </c>
       <c r="B86" s="2" t="s">
-        <v>115</v>
+        <v>109</v>
       </c>
       <c r="D86" s="1">
         <v>3</v>
@@ -3851,7 +3973,7 @@
         <v>102</v>
       </c>
       <c r="B87" s="4" t="s">
-        <v>119</v>
+        <v>112</v>
       </c>
       <c r="D87" s="1">
         <v>3</v>
@@ -3868,7 +3990,7 @@
         <v>103</v>
       </c>
       <c r="B88" s="2" t="s">
-        <v>135</v>
+        <v>128</v>
       </c>
       <c r="D88" s="12">
         <v>3</v>
@@ -3877,7 +3999,7 @@
         <v>81</v>
       </c>
       <c r="F88" s="1" t="s">
-        <v>156</v>
+        <v>143</v>
       </c>
     </row>
     <row r="89" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -3885,7 +4007,7 @@
         <v>104</v>
       </c>
       <c r="B89" s="2" t="s">
-        <v>138</v>
+        <v>130</v>
       </c>
       <c r="D89" s="12">
         <v>3</v>
@@ -3894,7 +4016,7 @@
         <v>81</v>
       </c>
       <c r="F89" s="1" t="s">
-        <v>156</v>
+        <v>143</v>
       </c>
     </row>
     <row r="90" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -3902,7 +4024,7 @@
         <v>105</v>
       </c>
       <c r="B90" s="2" t="s">
-        <v>151</v>
+        <v>139</v>
       </c>
       <c r="D90" s="12">
         <v>3</v>
@@ -3911,7 +4033,7 @@
         <v>81</v>
       </c>
       <c r="F90" s="1" t="s">
-        <v>156</v>
+        <v>143</v>
       </c>
     </row>
     <row r="91" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -3919,7 +4041,7 @@
         <v>106</v>
       </c>
       <c r="B91" s="2" t="s">
-        <v>160</v>
+        <v>147</v>
       </c>
       <c r="D91" s="12">
         <v>3</v>
@@ -3928,7 +4050,7 @@
         <v>81</v>
       </c>
       <c r="F91" s="1" t="s">
-        <v>166</v>
+        <v>152</v>
       </c>
     </row>
     <row r="92" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -3936,7 +4058,7 @@
         <v>107</v>
       </c>
       <c r="B92" s="2" t="s">
-        <v>162</v>
+        <v>149</v>
       </c>
       <c r="D92" s="12">
         <v>3</v>
@@ -3945,7 +4067,7 @@
         <v>81</v>
       </c>
       <c r="F92" s="1" t="s">
-        <v>166</v>
+        <v>152</v>
       </c>
     </row>
     <row r="93" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -3970,7 +4092,7 @@
         <v>109</v>
       </c>
       <c r="B94" s="2" t="s">
-        <v>123</v>
+        <v>116</v>
       </c>
       <c r="D94" s="12">
         <v>3</v>
@@ -3979,7 +4101,7 @@
         <v>77</v>
       </c>
       <c r="F94" s="1" t="s">
-        <v>156</v>
+        <v>143</v>
       </c>
     </row>
     <row r="95" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -3987,7 +4109,7 @@
         <v>110</v>
       </c>
       <c r="B95" s="2" t="s">
-        <v>128</v>
+        <v>121</v>
       </c>
       <c r="D95" s="12">
         <v>3</v>
@@ -3996,7 +4118,7 @@
         <v>77</v>
       </c>
       <c r="F95" s="1" t="s">
-        <v>156</v>
+        <v>143</v>
       </c>
     </row>
     <row r="96" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -4004,7 +4126,7 @@
         <v>111</v>
       </c>
       <c r="B96" s="2" t="s">
-        <v>129</v>
+        <v>122</v>
       </c>
       <c r="D96" s="12">
         <v>3</v>
@@ -4013,7 +4135,7 @@
         <v>77</v>
       </c>
       <c r="F96" s="1" t="s">
-        <v>156</v>
+        <v>143</v>
       </c>
     </row>
     <row r="97" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -4021,7 +4143,7 @@
         <v>112</v>
       </c>
       <c r="B97" s="2" t="s">
-        <v>132</v>
+        <v>125</v>
       </c>
       <c r="D97" s="12">
         <v>3</v>
@@ -4030,7 +4152,7 @@
         <v>77</v>
       </c>
       <c r="F97" s="1" t="s">
-        <v>156</v>
+        <v>143</v>
       </c>
     </row>
     <row r="98" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -4038,7 +4160,7 @@
         <v>113</v>
       </c>
       <c r="B98" s="2" t="s">
-        <v>134</v>
+        <v>127</v>
       </c>
       <c r="D98" s="12">
         <v>3</v>
@@ -4047,7 +4169,7 @@
         <v>77</v>
       </c>
       <c r="F98" s="1" t="s">
-        <v>156</v>
+        <v>143</v>
       </c>
     </row>
     <row r="99" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -4055,7 +4177,7 @@
         <v>114</v>
       </c>
       <c r="B99" s="2" t="s">
-        <v>137</v>
+        <v>129</v>
       </c>
       <c r="D99" s="12">
         <v>3</v>
@@ -4064,7 +4186,7 @@
         <v>77</v>
       </c>
       <c r="F99" s="1" t="s">
-        <v>156</v>
+        <v>143</v>
       </c>
     </row>
     <row r="100" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -4072,7 +4194,7 @@
         <v>115</v>
       </c>
       <c r="B100" s="4" t="s">
-        <v>152</v>
+        <v>140</v>
       </c>
       <c r="D100" s="12">
         <v>3</v>
@@ -4081,7 +4203,7 @@
         <v>77</v>
       </c>
       <c r="F100" s="1" t="s">
-        <v>156</v>
+        <v>143</v>
       </c>
     </row>
     <row r="101" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -4089,7 +4211,7 @@
         <v>116</v>
       </c>
       <c r="B101" s="2" t="s">
-        <v>164</v>
+        <v>150</v>
       </c>
       <c r="D101" s="12">
         <v>3</v>
@@ -4098,7 +4220,7 @@
         <v>77</v>
       </c>
       <c r="F101" s="1" t="s">
-        <v>166</v>
+        <v>152</v>
       </c>
     </row>
     <row r="102" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -4118,7 +4240,7 @@
         <v>5</v>
       </c>
       <c r="F102" s="1" t="s">
-        <v>156</v>
+        <v>143</v>
       </c>
     </row>
     <row r="103" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -4245,7 +4367,7 @@
         <v>127</v>
       </c>
       <c r="B110" s="5" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D110" s="8">
         <v>3</v>
@@ -4262,7 +4384,7 @@
         <v>128</v>
       </c>
       <c r="B111" s="5" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="D111" s="8">
         <v>3</v>
@@ -4279,7 +4401,7 @@
         <v>129</v>
       </c>
       <c r="B112" s="5" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="D112" s="8">
         <v>3</v>
@@ -4296,7 +4418,7 @@
         <v>130</v>
       </c>
       <c r="B113" s="5" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="D113" s="8">
         <v>3</v>
@@ -4313,7 +4435,7 @@
         <v>131</v>
       </c>
       <c r="B114" s="5" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="D114" s="8">
         <v>3</v>
@@ -4330,7 +4452,7 @@
         <v>132</v>
       </c>
       <c r="B115" s="5" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="D115" s="8">
         <v>3</v>
@@ -4347,7 +4469,7 @@
         <v>133</v>
       </c>
       <c r="B116" s="2" t="s">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="D116" s="8">
         <v>3</v>
@@ -4364,7 +4486,7 @@
         <v>134</v>
       </c>
       <c r="B117" s="2" t="s">
-        <v>111</v>
+        <v>106</v>
       </c>
       <c r="D117" s="8">
         <v>3</v>
@@ -4381,7 +4503,7 @@
         <v>135</v>
       </c>
       <c r="B118" s="2" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
       <c r="D118" s="8">
         <v>3</v>
@@ -4398,7 +4520,7 @@
         <v>136</v>
       </c>
       <c r="B119" s="2" t="s">
-        <v>116</v>
+        <v>110</v>
       </c>
       <c r="D119" s="8">
         <v>3</v>
@@ -4415,7 +4537,7 @@
         <v>137</v>
       </c>
       <c r="B120" s="2" t="s">
-        <v>118</v>
+        <v>111</v>
       </c>
       <c r="D120" s="8">
         <v>3</v>
@@ -4432,7 +4554,7 @@
         <v>138</v>
       </c>
       <c r="B121" s="4" t="s">
-        <v>120</v>
+        <v>113</v>
       </c>
       <c r="D121" s="8">
         <v>3</v>
@@ -4449,7 +4571,7 @@
         <v>139</v>
       </c>
       <c r="B122" s="4" t="s">
-        <v>122</v>
+        <v>115</v>
       </c>
       <c r="D122" s="8">
         <v>3</v>
@@ -4466,7 +4588,7 @@
         <v>140</v>
       </c>
       <c r="B123" s="2" t="s">
-        <v>133</v>
+        <v>126</v>
       </c>
       <c r="D123" s="6">
         <v>3</v>
@@ -4475,7 +4597,7 @@
         <v>5</v>
       </c>
       <c r="F123" s="1" t="s">
-        <v>156</v>
+        <v>143</v>
       </c>
     </row>
     <row r="124" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -4483,7 +4605,7 @@
         <v>141</v>
       </c>
       <c r="B124" s="2" t="s">
-        <v>140</v>
+        <v>131</v>
       </c>
       <c r="D124" s="6">
         <v>3</v>
@@ -4492,7 +4614,7 @@
         <v>5</v>
       </c>
       <c r="F124" s="1" t="s">
-        <v>156</v>
+        <v>143</v>
       </c>
     </row>
     <row r="125" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -4500,7 +4622,7 @@
         <v>142</v>
       </c>
       <c r="B125" s="2" t="s">
-        <v>141</v>
+        <v>132</v>
       </c>
       <c r="D125" s="6">
         <v>3</v>
@@ -4509,7 +4631,7 @@
         <v>5</v>
       </c>
       <c r="F125" s="1" t="s">
-        <v>156</v>
+        <v>143</v>
       </c>
     </row>
     <row r="126" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -4517,7 +4639,7 @@
         <v>143</v>
       </c>
       <c r="B126" s="2" t="s">
-        <v>146</v>
+        <v>134</v>
       </c>
       <c r="D126" s="6">
         <v>3</v>
@@ -4526,7 +4648,7 @@
         <v>5</v>
       </c>
       <c r="F126" s="1" t="s">
-        <v>156</v>
+        <v>143</v>
       </c>
     </row>
     <row r="127" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -4534,7 +4656,7 @@
         <v>144</v>
       </c>
       <c r="B127" s="2" t="s">
-        <v>150</v>
+        <v>138</v>
       </c>
       <c r="D127" s="6">
         <v>3</v>
@@ -4543,7 +4665,7 @@
         <v>5</v>
       </c>
       <c r="F127" s="1" t="s">
-        <v>156</v>
+        <v>143</v>
       </c>
     </row>
     <row r="128" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -4551,7 +4673,7 @@
         <v>145</v>
       </c>
       <c r="B128" s="2" t="s">
-        <v>159</v>
+        <v>146</v>
       </c>
       <c r="D128" s="6">
         <v>3</v>
@@ -4560,7 +4682,7 @@
         <v>5</v>
       </c>
       <c r="F128" s="1" t="s">
-        <v>166</v>
+        <v>152</v>
       </c>
     </row>
     <row r="129" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -4568,13 +4690,13 @@
         <v>146</v>
       </c>
       <c r="B129" s="5" t="s">
+        <v>92</v>
+      </c>
+      <c r="D129" s="8">
+        <v>3</v>
+      </c>
+      <c r="E129" s="3" t="s">
         <v>93</v>
-      </c>
-      <c r="D129" s="8">
-        <v>3</v>
-      </c>
-      <c r="E129" s="3" t="s">
-        <v>94</v>
       </c>
       <c r="F129" s="1" t="s">
         <v>61</v>
@@ -4619,7 +4741,7 @@
         <v>149</v>
       </c>
       <c r="B132" s="5" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="D132" s="8">
         <v>3</v>
@@ -4636,7 +4758,7 @@
         <v>150</v>
       </c>
       <c r="B133" s="2" t="s">
-        <v>130</v>
+        <v>123</v>
       </c>
       <c r="D133" s="6">
         <v>3</v>
@@ -4645,7 +4767,7 @@
         <v>73</v>
       </c>
       <c r="F133" s="1" t="s">
-        <v>156</v>
+        <v>143</v>
       </c>
     </row>
     <row r="134" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -4721,7 +4843,7 @@
         <v>157</v>
       </c>
       <c r="B138" s="2" t="s">
-        <v>175</v>
+        <v>161</v>
       </c>
       <c r="D138" s="6">
         <v>3</v>
@@ -4730,7 +4852,7 @@
         <v>16</v>
       </c>
       <c r="F138" s="1" t="s">
-        <v>166</v>
+        <v>152</v>
       </c>
     </row>
     <row r="139" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -4823,7 +4945,7 @@
         <v>163</v>
       </c>
       <c r="B144" s="5" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D144" s="8">
         <v>3</v>
@@ -4840,7 +4962,7 @@
         <v>164</v>
       </c>
       <c r="B145" s="5" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="D145" s="8">
         <v>3</v>
@@ -4857,7 +4979,7 @@
         <v>165</v>
       </c>
       <c r="B146" s="2" t="s">
-        <v>158</v>
+        <v>145</v>
       </c>
       <c r="D146" s="6">
         <v>3</v>
@@ -4866,7 +4988,7 @@
         <v>70</v>
       </c>
       <c r="F146" s="1" t="s">
-        <v>166</v>
+        <v>152</v>
       </c>
     </row>
     <row r="147" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -4891,7 +5013,7 @@
         <v>167</v>
       </c>
       <c r="B148" s="5" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D148" s="8">
         <v>3</v>
@@ -4908,7 +5030,7 @@
         <v>168</v>
       </c>
       <c r="B149" s="4" t="s">
-        <v>154</v>
+        <v>142</v>
       </c>
       <c r="D149" s="6">
         <v>3</v>
@@ -4917,7 +5039,7 @@
         <v>87</v>
       </c>
       <c r="F149" s="1" t="s">
-        <v>156</v>
+        <v>143</v>
       </c>
     </row>
     <row r="150" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -4925,7 +5047,7 @@
         <v>169</v>
       </c>
       <c r="B150" s="2" t="s">
-        <v>157</v>
+        <v>144</v>
       </c>
       <c r="D150" s="6">
         <v>3</v>
@@ -4934,7 +5056,7 @@
         <v>87</v>
       </c>
       <c r="F150" s="1" t="s">
-        <v>166</v>
+        <v>152</v>
       </c>
     </row>
     <row r="151" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -4942,7 +5064,7 @@
         <v>170</v>
       </c>
       <c r="B151" s="2" t="s">
-        <v>165</v>
+        <v>151</v>
       </c>
       <c r="D151" s="6">
         <v>3</v>
@@ -4951,7 +5073,7 @@
         <v>87</v>
       </c>
       <c r="F151" s="1" t="s">
-        <v>166</v>
+        <v>152</v>
       </c>
     </row>
     <row r="152" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -4959,7 +5081,7 @@
         <v>171</v>
       </c>
       <c r="B152" s="13" t="s">
-        <v>182</v>
+        <v>166</v>
       </c>
       <c r="D152" s="6">
         <v>3</v>
@@ -4968,7 +5090,7 @@
         <v>65</v>
       </c>
       <c r="F152" s="1" t="s">
-        <v>197</v>
+        <v>181</v>
       </c>
     </row>
     <row r="153" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -4976,7 +5098,7 @@
         <v>172</v>
       </c>
       <c r="B153" s="13" t="s">
-        <v>183</v>
+        <v>167</v>
       </c>
       <c r="D153" s="6">
         <v>3</v>
@@ -4985,7 +5107,7 @@
         <v>65</v>
       </c>
       <c r="F153" s="1" t="s">
-        <v>198</v>
+        <v>182</v>
       </c>
     </row>
     <row r="154" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -4993,7 +5115,7 @@
         <v>173</v>
       </c>
       <c r="B154" s="13" t="s">
-        <v>184</v>
+        <v>168</v>
       </c>
       <c r="D154" s="6">
         <v>3</v>
@@ -5002,7 +5124,7 @@
         <v>65</v>
       </c>
       <c r="F154" s="1" t="s">
-        <v>185</v>
+        <v>169</v>
       </c>
     </row>
     <row r="155" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -5010,7 +5132,7 @@
         <v>174</v>
       </c>
       <c r="B155" s="13" t="s">
-        <v>186</v>
+        <v>170</v>
       </c>
       <c r="D155" s="6">
         <v>3</v>
@@ -5019,7 +5141,7 @@
         <v>65</v>
       </c>
       <c r="F155" s="1" t="s">
-        <v>197</v>
+        <v>181</v>
       </c>
     </row>
     <row r="156" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -5027,7 +5149,7 @@
         <v>175</v>
       </c>
       <c r="B156" s="13" t="s">
-        <v>187</v>
+        <v>171</v>
       </c>
       <c r="D156" s="6">
         <v>3</v>
@@ -5036,7 +5158,7 @@
         <v>65</v>
       </c>
       <c r="F156" s="1" t="s">
-        <v>198</v>
+        <v>182</v>
       </c>
     </row>
     <row r="157" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -5044,7 +5166,7 @@
         <v>176</v>
       </c>
       <c r="B157" s="13" t="s">
-        <v>188</v>
+        <v>172</v>
       </c>
       <c r="D157" s="6">
         <v>3</v>
@@ -5053,7 +5175,7 @@
         <v>65</v>
       </c>
       <c r="F157" s="1" t="s">
-        <v>198</v>
+        <v>182</v>
       </c>
     </row>
     <row r="158" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -5061,7 +5183,7 @@
         <v>177</v>
       </c>
       <c r="B158" s="13" t="s">
-        <v>189</v>
+        <v>173</v>
       </c>
       <c r="D158" s="6">
         <v>3</v>
@@ -5070,7 +5192,7 @@
         <v>65</v>
       </c>
       <c r="F158" s="1" t="s">
-        <v>198</v>
+        <v>182</v>
       </c>
     </row>
     <row r="159" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -5078,7 +5200,7 @@
         <v>178</v>
       </c>
       <c r="B159" s="13" t="s">
-        <v>190</v>
+        <v>174</v>
       </c>
       <c r="D159" s="6">
         <v>3</v>
@@ -5087,7 +5209,7 @@
         <v>65</v>
       </c>
       <c r="F159" s="1" t="s">
-        <v>198</v>
+        <v>182</v>
       </c>
     </row>
     <row r="160" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -5095,7 +5217,7 @@
         <v>179</v>
       </c>
       <c r="B160" s="13" t="s">
-        <v>191</v>
+        <v>175</v>
       </c>
       <c r="D160" s="6">
         <v>3</v>
@@ -5104,7 +5226,7 @@
         <v>65</v>
       </c>
       <c r="F160" s="1" t="s">
-        <v>198</v>
+        <v>182</v>
       </c>
     </row>
     <row r="161" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -5112,7 +5234,7 @@
         <v>180</v>
       </c>
       <c r="B161" s="13" t="s">
-        <v>192</v>
+        <v>176</v>
       </c>
       <c r="D161" s="6">
         <v>3</v>
@@ -5121,7 +5243,7 @@
         <v>65</v>
       </c>
       <c r="F161" s="1" t="s">
-        <v>198</v>
+        <v>182</v>
       </c>
     </row>
     <row r="162" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -5129,7 +5251,7 @@
         <v>181</v>
       </c>
       <c r="B162" s="13" t="s">
-        <v>193</v>
+        <v>177</v>
       </c>
       <c r="D162" s="6">
         <v>3</v>
@@ -5138,7 +5260,7 @@
         <v>65</v>
       </c>
       <c r="F162" s="1" t="s">
-        <v>198</v>
+        <v>182</v>
       </c>
     </row>
     <row r="163" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -5146,7 +5268,7 @@
         <v>182</v>
       </c>
       <c r="B163" s="13" t="s">
-        <v>194</v>
+        <v>178</v>
       </c>
       <c r="D163" s="6">
         <v>3</v>
@@ -5155,7 +5277,7 @@
         <v>65</v>
       </c>
       <c r="F163" s="1" t="s">
-        <v>198</v>
+        <v>182</v>
       </c>
     </row>
     <row r="164" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -5163,7 +5285,7 @@
         <v>183</v>
       </c>
       <c r="B164" s="13" t="s">
-        <v>195</v>
+        <v>179</v>
       </c>
       <c r="D164" s="6">
         <v>3</v>
@@ -5172,7 +5294,7 @@
         <v>65</v>
       </c>
       <c r="F164" s="1" t="s">
-        <v>198</v>
+        <v>182</v>
       </c>
     </row>
     <row r="165" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -5180,7 +5302,7 @@
         <v>184</v>
       </c>
       <c r="B165" s="13" t="s">
-        <v>196</v>
+        <v>180</v>
       </c>
       <c r="D165" s="6">
         <v>3</v>
@@ -5189,7 +5311,7 @@
         <v>65</v>
       </c>
       <c r="F165" s="1" t="s">
-        <v>198</v>
+        <v>182</v>
       </c>
     </row>
     <row r="166" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -5197,10 +5319,10 @@
         <v>185</v>
       </c>
       <c r="B166" s="14" t="s">
-        <v>202</v>
+        <v>186</v>
       </c>
       <c r="C166" s="14" t="s">
-        <v>203</v>
+        <v>187</v>
       </c>
       <c r="D166" s="15">
         <v>2</v>
@@ -5209,7 +5331,7 @@
         <v>5</v>
       </c>
       <c r="F166" s="1" t="s">
-        <v>198</v>
+        <v>182</v>
       </c>
     </row>
     <row r="167" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -5217,10 +5339,10 @@
         <v>186</v>
       </c>
       <c r="B167" s="14" t="s">
-        <v>204</v>
+        <v>188</v>
       </c>
       <c r="C167" s="14" t="s">
-        <v>205</v>
+        <v>189</v>
       </c>
       <c r="D167" s="15">
         <v>2</v>
@@ -5229,7 +5351,7 @@
         <v>5</v>
       </c>
       <c r="F167" s="1" t="s">
-        <v>198</v>
+        <v>182</v>
       </c>
     </row>
     <row r="168" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -5237,10 +5359,10 @@
         <v>187</v>
       </c>
       <c r="B168" s="14" t="s">
-        <v>206</v>
+        <v>190</v>
       </c>
       <c r="C168" s="14" t="s">
-        <v>207</v>
+        <v>191</v>
       </c>
       <c r="D168" s="15">
         <v>2</v>
@@ -5249,7 +5371,7 @@
         <v>5</v>
       </c>
       <c r="F168" s="1" t="s">
-        <v>198</v>
+        <v>182</v>
       </c>
     </row>
     <row r="169" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -5257,10 +5379,10 @@
         <v>188</v>
       </c>
       <c r="B169" s="14" t="s">
-        <v>208</v>
+        <v>192</v>
       </c>
       <c r="C169" s="14" t="s">
-        <v>209</v>
+        <v>193</v>
       </c>
       <c r="D169" s="15">
         <v>2</v>
@@ -5269,7 +5391,7 @@
         <v>5</v>
       </c>
       <c r="F169" s="1" t="s">
-        <v>198</v>
+        <v>182</v>
       </c>
     </row>
     <row r="170" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -5277,10 +5399,10 @@
         <v>189</v>
       </c>
       <c r="B170" s="14" t="s">
-        <v>210</v>
+        <v>194</v>
       </c>
       <c r="C170" s="14" t="s">
-        <v>205</v>
+        <v>189</v>
       </c>
       <c r="D170" s="15">
         <v>2</v>
@@ -5289,7 +5411,7 @@
         <v>5</v>
       </c>
       <c r="F170" s="1" t="s">
-        <v>198</v>
+        <v>182</v>
       </c>
     </row>
     <row r="171" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -5297,10 +5419,10 @@
         <v>190</v>
       </c>
       <c r="B171" s="14" t="s">
-        <v>211</v>
+        <v>195</v>
       </c>
       <c r="C171" s="14" t="s">
-        <v>212</v>
+        <v>196</v>
       </c>
       <c r="D171" s="15">
         <v>2</v>
@@ -5309,7 +5431,7 @@
         <v>5</v>
       </c>
       <c r="F171" s="1" t="s">
-        <v>198</v>
+        <v>182</v>
       </c>
     </row>
     <row r="172" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -5317,10 +5439,10 @@
         <v>191</v>
       </c>
       <c r="B172" s="14" t="s">
-        <v>213</v>
+        <v>197</v>
       </c>
       <c r="C172" s="14" t="s">
-        <v>205</v>
+        <v>189</v>
       </c>
       <c r="D172" s="15">
         <v>2</v>
@@ -5329,7 +5451,7 @@
         <v>5</v>
       </c>
       <c r="F172" s="1" t="s">
-        <v>198</v>
+        <v>182</v>
       </c>
     </row>
     <row r="173" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -5337,10 +5459,10 @@
         <v>192</v>
       </c>
       <c r="B173" s="14" t="s">
-        <v>214</v>
+        <v>198</v>
       </c>
       <c r="C173" s="14" t="s">
-        <v>207</v>
+        <v>191</v>
       </c>
       <c r="D173" s="15">
         <v>2</v>
@@ -5349,7 +5471,7 @@
         <v>5</v>
       </c>
       <c r="F173" s="1" t="s">
-        <v>198</v>
+        <v>182</v>
       </c>
     </row>
     <row r="174" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -5357,10 +5479,10 @@
         <v>193</v>
       </c>
       <c r="B174" s="14" t="s">
-        <v>215</v>
+        <v>199</v>
       </c>
       <c r="C174" s="14" t="s">
-        <v>216</v>
+        <v>200</v>
       </c>
       <c r="D174" s="15">
         <v>2</v>
@@ -5369,7 +5491,7 @@
         <v>5</v>
       </c>
       <c r="F174" s="1" t="s">
-        <v>198</v>
+        <v>182</v>
       </c>
     </row>
     <row r="175" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -5377,10 +5499,10 @@
         <v>194</v>
       </c>
       <c r="B175" s="14" t="s">
-        <v>217</v>
+        <v>201</v>
       </c>
       <c r="C175" s="14" t="s">
-        <v>218</v>
+        <v>202</v>
       </c>
       <c r="D175" s="15">
         <v>2</v>
@@ -5389,7 +5511,7 @@
         <v>5</v>
       </c>
       <c r="F175" s="1" t="s">
-        <v>198</v>
+        <v>182</v>
       </c>
     </row>
     <row r="176" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -5397,10 +5519,10 @@
         <v>195</v>
       </c>
       <c r="B176" s="14" t="s">
-        <v>219</v>
+        <v>203</v>
       </c>
       <c r="C176" s="14" t="s">
-        <v>203</v>
+        <v>187</v>
       </c>
       <c r="D176" s="15">
         <v>2</v>
@@ -5409,7 +5531,7 @@
         <v>5</v>
       </c>
       <c r="F176" s="1" t="s">
-        <v>198</v>
+        <v>182</v>
       </c>
     </row>
     <row r="177" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -5417,10 +5539,10 @@
         <v>196</v>
       </c>
       <c r="B177" s="14" t="s">
-        <v>220</v>
+        <v>204</v>
       </c>
       <c r="C177" s="14" t="s">
-        <v>205</v>
+        <v>189</v>
       </c>
       <c r="D177" s="15">
         <v>2</v>
@@ -5429,7 +5551,7 @@
         <v>5</v>
       </c>
       <c r="F177" s="1" t="s">
-        <v>198</v>
+        <v>182</v>
       </c>
     </row>
     <row r="178" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -5437,10 +5559,10 @@
         <v>197</v>
       </c>
       <c r="B178" s="14" t="s">
-        <v>221</v>
+        <v>205</v>
       </c>
       <c r="C178" s="14" t="s">
-        <v>212</v>
+        <v>196</v>
       </c>
       <c r="D178" s="15">
         <v>2</v>
@@ -5449,7 +5571,7 @@
         <v>5</v>
       </c>
       <c r="F178" s="1" t="s">
-        <v>198</v>
+        <v>182</v>
       </c>
     </row>
     <row r="179" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -5457,10 +5579,10 @@
         <v>198</v>
       </c>
       <c r="B179" s="16" t="s">
-        <v>222</v>
+        <v>206</v>
       </c>
       <c r="C179" s="16" t="s">
-        <v>203</v>
+        <v>187</v>
       </c>
       <c r="D179" s="15">
         <v>2</v>
@@ -5469,7 +5591,7 @@
         <v>5</v>
       </c>
       <c r="F179" s="1" t="s">
-        <v>197</v>
+        <v>181</v>
       </c>
     </row>
     <row r="180" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -5477,10 +5599,10 @@
         <v>199</v>
       </c>
       <c r="B180" s="16" t="s">
-        <v>223</v>
+        <v>207</v>
       </c>
       <c r="C180" s="16" t="s">
-        <v>205</v>
+        <v>189</v>
       </c>
       <c r="D180" s="15">
         <v>2</v>
@@ -5489,7 +5611,7 @@
         <v>5</v>
       </c>
       <c r="F180" s="1" t="s">
-        <v>197</v>
+        <v>181</v>
       </c>
     </row>
     <row r="181" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -5497,10 +5619,10 @@
         <v>200</v>
       </c>
       <c r="B181" s="16" t="s">
-        <v>224</v>
+        <v>208</v>
       </c>
       <c r="C181" s="16" t="s">
-        <v>225</v>
+        <v>209</v>
       </c>
       <c r="D181" s="15">
         <v>2</v>
@@ -5509,7 +5631,7 @@
         <v>5</v>
       </c>
       <c r="F181" s="1" t="s">
-        <v>197</v>
+        <v>181</v>
       </c>
     </row>
     <row r="182" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -5517,10 +5639,10 @@
         <v>201</v>
       </c>
       <c r="B182" s="16" t="s">
-        <v>226</v>
+        <v>210</v>
       </c>
       <c r="C182" s="16" t="s">
-        <v>227</v>
+        <v>211</v>
       </c>
       <c r="D182" s="15">
         <v>2</v>
@@ -5529,7 +5651,7 @@
         <v>5</v>
       </c>
       <c r="F182" s="1" t="s">
-        <v>197</v>
+        <v>181</v>
       </c>
     </row>
     <row r="183" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -5537,10 +5659,10 @@
         <v>202</v>
       </c>
       <c r="B183" t="s">
-        <v>228</v>
+        <v>212</v>
       </c>
       <c r="C183" t="s">
-        <v>212</v>
+        <v>196</v>
       </c>
       <c r="D183" s="15">
         <v>1</v>
@@ -5549,7 +5671,7 @@
         <v>5</v>
       </c>
       <c r="F183" s="1" t="s">
-        <v>198</v>
+        <v>182</v>
       </c>
     </row>
     <row r="184" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -5557,10 +5679,10 @@
         <v>203</v>
       </c>
       <c r="B184" t="s">
-        <v>229</v>
+        <v>213</v>
       </c>
       <c r="C184" t="s">
-        <v>212</v>
+        <v>196</v>
       </c>
       <c r="D184" s="15">
         <v>1</v>
@@ -5569,7 +5691,7 @@
         <v>5</v>
       </c>
       <c r="F184" s="1" t="s">
-        <v>198</v>
+        <v>182</v>
       </c>
     </row>
     <row r="185" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -5577,10 +5699,10 @@
         <v>204</v>
       </c>
       <c r="B185" t="s">
-        <v>230</v>
+        <v>214</v>
       </c>
       <c r="C185" t="s">
-        <v>231</v>
+        <v>215</v>
       </c>
       <c r="D185" s="15">
         <v>1</v>
@@ -5589,7 +5711,7 @@
         <v>5</v>
       </c>
       <c r="F185" s="1" t="s">
-        <v>198</v>
+        <v>182</v>
       </c>
     </row>
     <row r="186" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -5597,10 +5719,10 @@
         <v>205</v>
       </c>
       <c r="B186" t="s">
-        <v>232</v>
+        <v>216</v>
       </c>
       <c r="C186" t="s">
-        <v>205</v>
+        <v>189</v>
       </c>
       <c r="D186" s="15">
         <v>1</v>
@@ -5609,7 +5731,7 @@
         <v>5</v>
       </c>
       <c r="F186" s="1" t="s">
-        <v>198</v>
+        <v>182</v>
       </c>
     </row>
     <row r="187" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -5617,10 +5739,10 @@
         <v>206</v>
       </c>
       <c r="B187" t="s">
-        <v>233</v>
+        <v>217</v>
       </c>
       <c r="C187" t="s">
-        <v>203</v>
+        <v>187</v>
       </c>
       <c r="D187" s="15">
         <v>1</v>
@@ -5629,7 +5751,7 @@
         <v>5</v>
       </c>
       <c r="F187" s="1" t="s">
-        <v>198</v>
+        <v>182</v>
       </c>
     </row>
     <row r="188" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -5637,10 +5759,10 @@
         <v>207</v>
       </c>
       <c r="B188" t="s">
-        <v>234</v>
+        <v>218</v>
       </c>
       <c r="C188" t="s">
-        <v>212</v>
+        <v>196</v>
       </c>
       <c r="D188" s="15">
         <v>1</v>
@@ -5649,7 +5771,7 @@
         <v>5</v>
       </c>
       <c r="F188" s="1" t="s">
-        <v>198</v>
+        <v>182</v>
       </c>
     </row>
     <row r="189" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -5657,10 +5779,10 @@
         <v>208</v>
       </c>
       <c r="B189" t="s">
-        <v>235</v>
+        <v>219</v>
       </c>
       <c r="C189" t="s">
-        <v>203</v>
+        <v>187</v>
       </c>
       <c r="D189" s="15">
         <v>1</v>
@@ -5669,7 +5791,7 @@
         <v>5</v>
       </c>
       <c r="F189" s="1" t="s">
-        <v>198</v>
+        <v>182</v>
       </c>
     </row>
     <row r="190" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -5677,10 +5799,10 @@
         <v>209</v>
       </c>
       <c r="B190" t="s">
-        <v>236</v>
+        <v>220</v>
       </c>
       <c r="C190" t="s">
-        <v>216</v>
+        <v>200</v>
       </c>
       <c r="D190" s="15">
         <v>2</v>
@@ -5689,7 +5811,7 @@
         <v>65</v>
       </c>
       <c r="F190" s="1" t="s">
-        <v>198</v>
+        <v>182</v>
       </c>
     </row>
     <row r="191" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -5697,10 +5819,10 @@
         <v>210</v>
       </c>
       <c r="B191" t="s">
-        <v>237</v>
+        <v>221</v>
       </c>
       <c r="C191" t="s">
-        <v>205</v>
+        <v>189</v>
       </c>
       <c r="D191" s="15">
         <v>2</v>
@@ -5709,7 +5831,7 @@
         <v>65</v>
       </c>
       <c r="F191" s="1" t="s">
-        <v>198</v>
+        <v>182</v>
       </c>
     </row>
     <row r="192" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -5717,10 +5839,10 @@
         <v>211</v>
       </c>
       <c r="B192" t="s">
-        <v>238</v>
+        <v>222</v>
       </c>
       <c r="C192" t="s">
-        <v>205</v>
+        <v>189</v>
       </c>
       <c r="D192" s="15">
         <v>2</v>
@@ -5729,7 +5851,7 @@
         <v>65</v>
       </c>
       <c r="F192" s="1" t="s">
-        <v>198</v>
+        <v>182</v>
       </c>
     </row>
     <row r="193" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -5737,10 +5859,10 @@
         <v>212</v>
       </c>
       <c r="B193" t="s">
-        <v>239</v>
+        <v>223</v>
       </c>
       <c r="C193" t="s">
-        <v>203</v>
+        <v>187</v>
       </c>
       <c r="D193" s="15">
         <v>2</v>
@@ -5749,7 +5871,7 @@
         <v>65</v>
       </c>
       <c r="F193" s="1" t="s">
-        <v>198</v>
+        <v>182</v>
       </c>
     </row>
     <row r="194" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -5757,10 +5879,10 @@
         <v>213</v>
       </c>
       <c r="B194" t="s">
-        <v>240</v>
+        <v>224</v>
       </c>
       <c r="C194" t="s">
-        <v>212</v>
+        <v>196</v>
       </c>
       <c r="D194" s="15">
         <v>2</v>
@@ -5769,7 +5891,7 @@
         <v>65</v>
       </c>
       <c r="F194" s="1" t="s">
-        <v>198</v>
+        <v>182</v>
       </c>
     </row>
     <row r="195" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -5777,10 +5899,10 @@
         <v>214</v>
       </c>
       <c r="B195" t="s">
-        <v>241</v>
+        <v>225</v>
       </c>
       <c r="C195" t="s">
-        <v>218</v>
+        <v>202</v>
       </c>
       <c r="D195" s="15">
         <v>2</v>
@@ -5789,7 +5911,7 @@
         <v>65</v>
       </c>
       <c r="F195" s="1" t="s">
-        <v>198</v>
+        <v>182</v>
       </c>
     </row>
     <row r="196" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -5797,10 +5919,10 @@
         <v>215</v>
       </c>
       <c r="B196" t="s">
-        <v>242</v>
+        <v>226</v>
       </c>
       <c r="C196" t="s">
-        <v>216</v>
+        <v>200</v>
       </c>
       <c r="D196" s="15">
         <v>2</v>
@@ -5809,7 +5931,7 @@
         <v>65</v>
       </c>
       <c r="F196" s="1" t="s">
-        <v>197</v>
+        <v>181</v>
       </c>
     </row>
     <row r="197" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -5817,10 +5939,10 @@
         <v>216</v>
       </c>
       <c r="B197" t="s">
-        <v>243</v>
+        <v>227</v>
       </c>
       <c r="C197" t="s">
-        <v>218</v>
+        <v>202</v>
       </c>
       <c r="D197" s="15">
         <v>2</v>
@@ -5829,7 +5951,7 @@
         <v>65</v>
       </c>
       <c r="F197" s="1" t="s">
-        <v>197</v>
+        <v>181</v>
       </c>
     </row>
     <row r="198" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -5837,10 +5959,10 @@
         <v>217</v>
       </c>
       <c r="B198" t="s">
-        <v>194</v>
+        <v>178</v>
       </c>
       <c r="C198" t="s">
-        <v>205</v>
+        <v>189</v>
       </c>
       <c r="D198" s="15">
         <v>2</v>
@@ -5849,7 +5971,7 @@
         <v>65</v>
       </c>
       <c r="F198" s="1" t="s">
-        <v>197</v>
+        <v>181</v>
       </c>
     </row>
     <row r="199" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -5857,10 +5979,10 @@
         <v>218</v>
       </c>
       <c r="B199" t="s">
-        <v>244</v>
+        <v>228</v>
       </c>
       <c r="C199" t="s">
-        <v>212</v>
+        <v>196</v>
       </c>
       <c r="D199" s="15">
         <v>2</v>
@@ -5869,7 +5991,7 @@
         <v>65</v>
       </c>
       <c r="F199" s="1" t="s">
-        <v>197</v>
+        <v>181</v>
       </c>
     </row>
     <row r="200" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -5877,10 +5999,10 @@
         <v>219</v>
       </c>
       <c r="B200" t="s">
-        <v>245</v>
+        <v>229</v>
       </c>
       <c r="C200" t="s">
-        <v>205</v>
+        <v>189</v>
       </c>
       <c r="D200" s="15">
         <v>1</v>
@@ -5889,7 +6011,7 @@
         <v>65</v>
       </c>
       <c r="F200" s="1" t="s">
-        <v>198</v>
+        <v>182</v>
       </c>
     </row>
     <row r="201" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -5897,10 +6019,10 @@
         <v>220</v>
       </c>
       <c r="B201" t="s">
-        <v>246</v>
+        <v>230</v>
       </c>
       <c r="C201" t="s">
-        <v>218</v>
+        <v>202</v>
       </c>
       <c r="D201" s="15">
         <v>1</v>
@@ -5909,7 +6031,7 @@
         <v>65</v>
       </c>
       <c r="F201" s="1" t="s">
-        <v>198</v>
+        <v>182</v>
       </c>
     </row>
     <row r="202" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -5917,10 +6039,10 @@
         <v>221</v>
       </c>
       <c r="B202" t="s">
-        <v>247</v>
+        <v>231</v>
       </c>
       <c r="C202" t="s">
-        <v>203</v>
+        <v>187</v>
       </c>
       <c r="D202" s="15">
         <v>1</v>
@@ -5929,7 +6051,7 @@
         <v>65</v>
       </c>
       <c r="F202" s="1" t="s">
-        <v>198</v>
+        <v>182</v>
       </c>
     </row>
     <row r="203" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -5937,10 +6059,10 @@
         <v>222</v>
       </c>
       <c r="B203" t="s">
-        <v>248</v>
+        <v>232</v>
       </c>
       <c r="C203" t="s">
-        <v>212</v>
+        <v>196</v>
       </c>
       <c r="D203" s="15">
         <v>1</v>
@@ -5949,7 +6071,7 @@
         <v>65</v>
       </c>
       <c r="F203" s="1" t="s">
-        <v>198</v>
+        <v>182</v>
       </c>
     </row>
     <row r="204" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -5957,10 +6079,10 @@
         <v>223</v>
       </c>
       <c r="B204" t="s">
-        <v>249</v>
+        <v>233</v>
       </c>
       <c r="C204" t="s">
-        <v>205</v>
+        <v>189</v>
       </c>
       <c r="D204" s="15">
         <v>2</v>
@@ -5969,7 +6091,7 @@
         <v>81</v>
       </c>
       <c r="F204" s="1" t="s">
-        <v>198</v>
+        <v>182</v>
       </c>
     </row>
     <row r="205" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -5977,10 +6099,10 @@
         <v>224</v>
       </c>
       <c r="B205" t="s">
-        <v>250</v>
+        <v>234</v>
       </c>
       <c r="C205" t="s">
-        <v>205</v>
+        <v>189</v>
       </c>
       <c r="D205" s="15">
         <v>2</v>
@@ -5989,7 +6111,7 @@
         <v>81</v>
       </c>
       <c r="F205" s="1" t="s">
-        <v>198</v>
+        <v>182</v>
       </c>
     </row>
     <row r="206" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -5997,10 +6119,10 @@
         <v>225</v>
       </c>
       <c r="B206" t="s">
-        <v>251</v>
+        <v>235</v>
       </c>
       <c r="C206" t="s">
-        <v>212</v>
+        <v>196</v>
       </c>
       <c r="D206" s="15">
         <v>2</v>
@@ -6009,7 +6131,7 @@
         <v>81</v>
       </c>
       <c r="F206" s="1" t="s">
-        <v>198</v>
+        <v>182</v>
       </c>
     </row>
     <row r="207" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -6017,10 +6139,10 @@
         <v>226</v>
       </c>
       <c r="B207" t="s">
-        <v>252</v>
+        <v>236</v>
       </c>
       <c r="C207" t="s">
-        <v>203</v>
+        <v>187</v>
       </c>
       <c r="D207" s="15">
         <v>2</v>
@@ -6029,7 +6151,7 @@
         <v>81</v>
       </c>
       <c r="F207" s="1" t="s">
-        <v>198</v>
+        <v>182</v>
       </c>
     </row>
     <row r="208" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -6037,10 +6159,10 @@
         <v>227</v>
       </c>
       <c r="B208" t="s">
-        <v>253</v>
+        <v>237</v>
       </c>
       <c r="C208" t="s">
-        <v>216</v>
+        <v>200</v>
       </c>
       <c r="D208" s="15">
         <v>2</v>
@@ -6049,7 +6171,7 @@
         <v>81</v>
       </c>
       <c r="F208" s="1" t="s">
-        <v>198</v>
+        <v>182</v>
       </c>
     </row>
     <row r="209" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -6057,10 +6179,10 @@
         <v>228</v>
       </c>
       <c r="B209" t="s">
-        <v>254</v>
+        <v>238</v>
       </c>
       <c r="C209" t="s">
-        <v>212</v>
+        <v>196</v>
       </c>
       <c r="D209" s="15">
         <v>2</v>
@@ -6069,7 +6191,7 @@
         <v>81</v>
       </c>
       <c r="F209" s="1" t="s">
-        <v>197</v>
+        <v>181</v>
       </c>
     </row>
     <row r="210" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -6077,10 +6199,10 @@
         <v>229</v>
       </c>
       <c r="B210" t="s">
-        <v>255</v>
+        <v>239</v>
       </c>
       <c r="C210" t="s">
-        <v>205</v>
+        <v>189</v>
       </c>
       <c r="D210" s="15">
         <v>1</v>
@@ -6089,7 +6211,7 @@
         <v>81</v>
       </c>
       <c r="F210" s="1" t="s">
-        <v>198</v>
+        <v>182</v>
       </c>
     </row>
     <row r="211" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -6097,10 +6219,10 @@
         <v>230</v>
       </c>
       <c r="B211" t="s">
-        <v>256</v>
+        <v>240</v>
       </c>
       <c r="C211" t="s">
-        <v>212</v>
+        <v>196</v>
       </c>
       <c r="D211" s="15">
         <v>3</v>
@@ -6109,7 +6231,7 @@
         <v>81</v>
       </c>
       <c r="F211" s="1" t="s">
-        <v>197</v>
+        <v>181</v>
       </c>
     </row>
     <row r="212" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -6117,10 +6239,10 @@
         <v>231</v>
       </c>
       <c r="B212" t="s">
-        <v>257</v>
+        <v>241</v>
       </c>
       <c r="C212" t="s">
-        <v>258</v>
+        <v>242</v>
       </c>
       <c r="D212" s="15">
         <v>3</v>
@@ -6129,7 +6251,7 @@
         <v>81</v>
       </c>
       <c r="F212" s="1" t="s">
-        <v>197</v>
+        <v>181</v>
       </c>
     </row>
     <row r="213" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -6137,10 +6259,10 @@
         <v>232</v>
       </c>
       <c r="B213" t="s">
-        <v>259</v>
+        <v>243</v>
       </c>
       <c r="C213" t="s">
-        <v>203</v>
+        <v>187</v>
       </c>
       <c r="D213" s="15">
         <v>3</v>
@@ -6149,7 +6271,7 @@
         <v>81</v>
       </c>
       <c r="F213" s="1" t="s">
-        <v>197</v>
+        <v>181</v>
       </c>
     </row>
     <row r="214" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -6157,10 +6279,10 @@
         <v>233</v>
       </c>
       <c r="B214" t="s">
-        <v>260</v>
+        <v>244</v>
       </c>
       <c r="C214" t="s">
-        <v>212</v>
+        <v>196</v>
       </c>
       <c r="D214" s="15">
         <v>3</v>
@@ -6169,7 +6291,7 @@
         <v>81</v>
       </c>
       <c r="F214" s="1" t="s">
-        <v>197</v>
+        <v>181</v>
       </c>
     </row>
     <row r="215" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -6177,10 +6299,10 @@
         <v>234</v>
       </c>
       <c r="B215" t="s">
-        <v>261</v>
+        <v>245</v>
       </c>
       <c r="C215" t="s">
-        <v>205</v>
+        <v>189</v>
       </c>
       <c r="D215" s="15">
         <v>3</v>
@@ -6189,7 +6311,7 @@
         <v>81</v>
       </c>
       <c r="F215" s="1" t="s">
-        <v>197</v>
+        <v>181</v>
       </c>
     </row>
     <row r="216" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -6197,10 +6319,10 @@
         <v>235</v>
       </c>
       <c r="B216" t="s">
-        <v>262</v>
+        <v>246</v>
       </c>
       <c r="C216" t="s">
-        <v>203</v>
+        <v>187</v>
       </c>
       <c r="D216">
         <v>1</v>
@@ -6209,7 +6331,7 @@
         <v>70</v>
       </c>
       <c r="F216" s="1" t="s">
-        <v>198</v>
+        <v>182</v>
       </c>
     </row>
     <row r="217" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -6217,10 +6339,10 @@
         <v>236</v>
       </c>
       <c r="B217" t="s">
-        <v>263</v>
+        <v>247</v>
       </c>
       <c r="C217" t="s">
-        <v>212</v>
+        <v>196</v>
       </c>
       <c r="D217">
         <v>1</v>
@@ -6229,7 +6351,7 @@
         <v>70</v>
       </c>
       <c r="F217" s="1" t="s">
-        <v>198</v>
+        <v>182</v>
       </c>
     </row>
     <row r="218" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -6237,10 +6359,10 @@
         <v>237</v>
       </c>
       <c r="B218" t="s">
-        <v>264</v>
+        <v>248</v>
       </c>
       <c r="C218" t="s">
-        <v>205</v>
+        <v>189</v>
       </c>
       <c r="D218">
         <v>1</v>
@@ -6249,7 +6371,7 @@
         <v>70</v>
       </c>
       <c r="F218" s="1" t="s">
-        <v>198</v>
+        <v>182</v>
       </c>
     </row>
     <row r="219" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -6257,10 +6379,10 @@
         <v>238</v>
       </c>
       <c r="B219" t="s">
-        <v>265</v>
+        <v>249</v>
       </c>
       <c r="C219" t="s">
-        <v>218</v>
+        <v>202</v>
       </c>
       <c r="D219">
         <v>2</v>
@@ -6269,7 +6391,7 @@
         <v>70</v>
       </c>
       <c r="F219" s="1" t="s">
-        <v>198</v>
+        <v>182</v>
       </c>
     </row>
     <row r="220" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -6277,10 +6399,10 @@
         <v>239</v>
       </c>
       <c r="B220" t="s">
-        <v>266</v>
+        <v>250</v>
       </c>
       <c r="C220" t="s">
-        <v>212</v>
+        <v>196</v>
       </c>
       <c r="D220">
         <v>2</v>
@@ -6289,7 +6411,7 @@
         <v>70</v>
       </c>
       <c r="F220" s="1" t="s">
-        <v>198</v>
+        <v>182</v>
       </c>
     </row>
     <row r="221" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -6297,10 +6419,10 @@
         <v>240</v>
       </c>
       <c r="B221" t="s">
-        <v>267</v>
+        <v>251</v>
       </c>
       <c r="C221" t="s">
-        <v>225</v>
+        <v>209</v>
       </c>
       <c r="D221">
         <v>2</v>
@@ -6309,7 +6431,7 @@
         <v>70</v>
       </c>
       <c r="F221" s="1" t="s">
-        <v>198</v>
+        <v>182</v>
       </c>
     </row>
     <row r="222" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -6317,10 +6439,10 @@
         <v>241</v>
       </c>
       <c r="B222" t="s">
-        <v>268</v>
+        <v>252</v>
       </c>
       <c r="C222" t="s">
-        <v>218</v>
+        <v>202</v>
       </c>
       <c r="D222">
         <v>2</v>
@@ -6329,7 +6451,7 @@
         <v>70</v>
       </c>
       <c r="F222" s="1" t="s">
-        <v>198</v>
+        <v>182</v>
       </c>
     </row>
     <row r="223" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -6337,10 +6459,10 @@
         <v>242</v>
       </c>
       <c r="B223" t="s">
-        <v>269</v>
+        <v>253</v>
       </c>
       <c r="C223" t="s">
-        <v>205</v>
+        <v>189</v>
       </c>
       <c r="D223">
         <v>2</v>
@@ -6349,7 +6471,7 @@
         <v>70</v>
       </c>
       <c r="F223" s="1" t="s">
-        <v>198</v>
+        <v>182</v>
       </c>
     </row>
     <row r="224" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -6357,10 +6479,10 @@
         <v>243</v>
       </c>
       <c r="B224" t="s">
-        <v>270</v>
+        <v>254</v>
       </c>
       <c r="C224" t="s">
-        <v>207</v>
+        <v>191</v>
       </c>
       <c r="D224">
         <v>2</v>
@@ -6369,7 +6491,7 @@
         <v>70</v>
       </c>
       <c r="F224" s="1" t="s">
-        <v>198</v>
+        <v>182</v>
       </c>
     </row>
     <row r="225" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -6377,10 +6499,10 @@
         <v>244</v>
       </c>
       <c r="B225" t="s">
-        <v>271</v>
+        <v>255</v>
       </c>
       <c r="C225" t="s">
-        <v>203</v>
+        <v>187</v>
       </c>
       <c r="D225">
         <v>2</v>
@@ -6389,7 +6511,7 @@
         <v>70</v>
       </c>
       <c r="F225" s="1" t="s">
-        <v>198</v>
+        <v>182</v>
       </c>
     </row>
     <row r="226" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -6397,10 +6519,10 @@
         <v>245</v>
       </c>
       <c r="B226" t="s">
-        <v>272</v>
+        <v>256</v>
       </c>
       <c r="C226" t="s">
-        <v>205</v>
+        <v>189</v>
       </c>
       <c r="D226">
         <v>2</v>
@@ -6409,7 +6531,7 @@
         <v>70</v>
       </c>
       <c r="F226" s="1" t="s">
-        <v>198</v>
+        <v>182</v>
       </c>
     </row>
     <row r="227" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -6417,10 +6539,10 @@
         <v>246</v>
       </c>
       <c r="B227" t="s">
-        <v>273</v>
+        <v>257</v>
       </c>
       <c r="C227" t="s">
-        <v>274</v>
+        <v>258</v>
       </c>
       <c r="D227">
         <v>3</v>
@@ -6429,7 +6551,7 @@
         <v>70</v>
       </c>
       <c r="F227" s="1" t="s">
-        <v>198</v>
+        <v>182</v>
       </c>
     </row>
     <row r="228" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -6437,10 +6559,10 @@
         <v>247</v>
       </c>
       <c r="B228" t="s">
-        <v>266</v>
+        <v>250</v>
       </c>
       <c r="C228" t="s">
-        <v>212</v>
+        <v>196</v>
       </c>
       <c r="D228">
         <v>3</v>
@@ -6449,7 +6571,7 @@
         <v>70</v>
       </c>
       <c r="F228" s="1" t="s">
-        <v>198</v>
+        <v>182</v>
       </c>
     </row>
     <row r="229" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -6457,10 +6579,10 @@
         <v>248</v>
       </c>
       <c r="B229" t="s">
-        <v>275</v>
+        <v>259</v>
       </c>
       <c r="C229" t="s">
-        <v>225</v>
+        <v>209</v>
       </c>
       <c r="D229">
         <v>3</v>
@@ -6469,7 +6591,7 @@
         <v>70</v>
       </c>
       <c r="F229" s="1" t="s">
-        <v>198</v>
+        <v>182</v>
       </c>
     </row>
     <row r="230" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -6477,10 +6599,10 @@
         <v>249</v>
       </c>
       <c r="B230" t="s">
-        <v>276</v>
+        <v>260</v>
       </c>
       <c r="C230" t="s">
-        <v>218</v>
+        <v>202</v>
       </c>
       <c r="D230">
         <v>3</v>
@@ -6489,7 +6611,7 @@
         <v>70</v>
       </c>
       <c r="F230" s="1" t="s">
-        <v>198</v>
+        <v>182</v>
       </c>
     </row>
     <row r="231" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -6497,10 +6619,10 @@
         <v>250</v>
       </c>
       <c r="B231" t="s">
-        <v>269</v>
+        <v>253</v>
       </c>
       <c r="C231" t="s">
-        <v>205</v>
+        <v>189</v>
       </c>
       <c r="D231">
         <v>3</v>
@@ -6509,7 +6631,7 @@
         <v>70</v>
       </c>
       <c r="F231" s="1" t="s">
-        <v>198</v>
+        <v>182</v>
       </c>
     </row>
     <row r="232" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -6517,10 +6639,10 @@
         <v>251</v>
       </c>
       <c r="B232" t="s">
-        <v>277</v>
+        <v>261</v>
       </c>
       <c r="C232" t="s">
-        <v>218</v>
+        <v>202</v>
       </c>
       <c r="D232">
         <v>3</v>
@@ -6529,7 +6651,7 @@
         <v>70</v>
       </c>
       <c r="F232" s="1" t="s">
-        <v>198</v>
+        <v>182</v>
       </c>
     </row>
     <row r="233" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -6537,10 +6659,10 @@
         <v>252</v>
       </c>
       <c r="B233" t="s">
-        <v>278</v>
+        <v>262</v>
       </c>
       <c r="C233" t="s">
-        <v>207</v>
+        <v>191</v>
       </c>
       <c r="D233">
         <v>3</v>
@@ -6549,7 +6671,7 @@
         <v>70</v>
       </c>
       <c r="F233" s="1" t="s">
-        <v>198</v>
+        <v>182</v>
       </c>
     </row>
     <row r="234" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -6557,10 +6679,10 @@
         <v>253</v>
       </c>
       <c r="B234" t="s">
-        <v>271</v>
+        <v>255</v>
       </c>
       <c r="C234" t="s">
-        <v>203</v>
+        <v>187</v>
       </c>
       <c r="D234">
         <v>3</v>
@@ -6569,7 +6691,7 @@
         <v>70</v>
       </c>
       <c r="F234" s="1" t="s">
-        <v>198</v>
+        <v>182</v>
       </c>
     </row>
     <row r="235" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -6577,10 +6699,10 @@
         <v>254</v>
       </c>
       <c r="B235" t="s">
-        <v>272</v>
+        <v>256</v>
       </c>
       <c r="C235" t="s">
-        <v>205</v>
+        <v>189</v>
       </c>
       <c r="D235">
         <v>3</v>
@@ -6589,7 +6711,7 @@
         <v>70</v>
       </c>
       <c r="F235" s="1" t="s">
-        <v>198</v>
+        <v>182</v>
       </c>
     </row>
     <row r="236" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -6597,10 +6719,10 @@
         <v>255</v>
       </c>
       <c r="B236" t="s">
-        <v>279</v>
+        <v>263</v>
       </c>
       <c r="C236" t="s">
-        <v>225</v>
+        <v>209</v>
       </c>
       <c r="D236">
         <v>2</v>
@@ -6609,7 +6731,7 @@
         <v>70</v>
       </c>
       <c r="F236" s="1" t="s">
-        <v>197</v>
+        <v>181</v>
       </c>
     </row>
     <row r="237" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -6617,10 +6739,10 @@
         <v>256</v>
       </c>
       <c r="B237" t="s">
-        <v>280</v>
+        <v>264</v>
       </c>
       <c r="C237" t="s">
-        <v>225</v>
+        <v>209</v>
       </c>
       <c r="D237">
         <v>3</v>
@@ -6629,7 +6751,7 @@
         <v>70</v>
       </c>
       <c r="F237" s="1" t="s">
-        <v>197</v>
+        <v>181</v>
       </c>
     </row>
     <row r="238" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -6637,10 +6759,10 @@
         <v>257</v>
       </c>
       <c r="B238" t="s">
-        <v>281</v>
+        <v>265</v>
       </c>
       <c r="C238" t="s">
-        <v>231</v>
+        <v>215</v>
       </c>
       <c r="D238">
         <v>3</v>
@@ -6649,7 +6771,7 @@
         <v>68</v>
       </c>
       <c r="F238" s="1" t="s">
-        <v>198</v>
+        <v>182</v>
       </c>
     </row>
     <row r="239" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -6657,10 +6779,10 @@
         <v>258</v>
       </c>
       <c r="B239" t="s">
-        <v>282</v>
+        <v>266</v>
       </c>
       <c r="C239" t="s">
-        <v>212</v>
+        <v>196</v>
       </c>
       <c r="D239">
         <v>3</v>
@@ -6669,7 +6791,7 @@
         <v>68</v>
       </c>
       <c r="F239" s="1" t="s">
-        <v>198</v>
+        <v>182</v>
       </c>
     </row>
     <row r="240" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -6677,10 +6799,10 @@
         <v>259</v>
       </c>
       <c r="B240" t="s">
-        <v>283</v>
+        <v>267</v>
       </c>
       <c r="C240" t="s">
-        <v>205</v>
+        <v>189</v>
       </c>
       <c r="D240">
         <v>3</v>
@@ -6689,7 +6811,7 @@
         <v>68</v>
       </c>
       <c r="F240" s="1" t="s">
-        <v>198</v>
+        <v>182</v>
       </c>
     </row>
     <row r="241" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -6697,10 +6819,10 @@
         <v>260</v>
       </c>
       <c r="B241" t="s">
-        <v>284</v>
+        <v>268</v>
       </c>
       <c r="C241" t="s">
-        <v>218</v>
+        <v>202</v>
       </c>
       <c r="D241">
         <v>3</v>
@@ -6709,7 +6831,7 @@
         <v>68</v>
       </c>
       <c r="F241" s="1" t="s">
-        <v>198</v>
+        <v>182</v>
       </c>
     </row>
     <row r="242" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -6717,10 +6839,10 @@
         <v>261</v>
       </c>
       <c r="B242" t="s">
-        <v>285</v>
+        <v>269</v>
       </c>
       <c r="C242" t="s">
-        <v>203</v>
+        <v>187</v>
       </c>
       <c r="D242">
         <v>3</v>
@@ -6729,7 +6851,7 @@
         <v>68</v>
       </c>
       <c r="F242" s="1" t="s">
-        <v>198</v>
+        <v>182</v>
       </c>
     </row>
     <row r="243" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -6737,10 +6859,10 @@
         <v>262</v>
       </c>
       <c r="B243" t="s">
-        <v>286</v>
+        <v>270</v>
       </c>
       <c r="C243" t="s">
-        <v>287</v>
+        <v>271</v>
       </c>
       <c r="D243">
         <v>3</v>
@@ -6749,7 +6871,7 @@
         <v>68</v>
       </c>
       <c r="F243" s="1" t="s">
-        <v>198</v>
+        <v>182</v>
       </c>
     </row>
     <row r="244" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -6757,10 +6879,10 @@
         <v>263</v>
       </c>
       <c r="B244" t="s">
-        <v>288</v>
+        <v>272</v>
       </c>
       <c r="C244" t="s">
-        <v>205</v>
+        <v>189</v>
       </c>
       <c r="D244">
         <v>2</v>
@@ -6769,7 +6891,7 @@
         <v>68</v>
       </c>
       <c r="F244" s="1" t="s">
-        <v>198</v>
+        <v>182</v>
       </c>
     </row>
     <row r="245" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -6777,10 +6899,10 @@
         <v>264</v>
       </c>
       <c r="B245" t="s">
-        <v>289</v>
+        <v>273</v>
       </c>
       <c r="C245" t="s">
-        <v>203</v>
+        <v>187</v>
       </c>
       <c r="D245">
         <v>2</v>
@@ -6789,7 +6911,7 @@
         <v>68</v>
       </c>
       <c r="F245" s="1" t="s">
-        <v>198</v>
+        <v>182</v>
       </c>
     </row>
     <row r="246" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -6797,10 +6919,10 @@
         <v>265</v>
       </c>
       <c r="B246" t="s">
-        <v>290</v>
+        <v>274</v>
       </c>
       <c r="C246" t="s">
-        <v>287</v>
+        <v>271</v>
       </c>
       <c r="D246">
         <v>2</v>
@@ -6809,7 +6931,7 @@
         <v>68</v>
       </c>
       <c r="F246" s="1" t="s">
-        <v>198</v>
+        <v>182</v>
       </c>
     </row>
     <row r="247" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -6817,10 +6939,10 @@
         <v>266</v>
       </c>
       <c r="B247" t="s">
-        <v>291</v>
+        <v>275</v>
       </c>
       <c r="C247" t="s">
-        <v>216</v>
+        <v>200</v>
       </c>
       <c r="D247">
         <v>1</v>
@@ -6829,7 +6951,7 @@
         <v>68</v>
       </c>
       <c r="F247" s="1" t="s">
-        <v>198</v>
+        <v>182</v>
       </c>
     </row>
     <row r="248" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -6837,10 +6959,10 @@
         <v>267</v>
       </c>
       <c r="B248" t="s">
-        <v>292</v>
+        <v>276</v>
       </c>
       <c r="C248" t="s">
-        <v>203</v>
+        <v>187</v>
       </c>
       <c r="D248">
         <v>1</v>
@@ -6849,7 +6971,7 @@
         <v>68</v>
       </c>
       <c r="F248" s="1" t="s">
-        <v>198</v>
+        <v>182</v>
       </c>
     </row>
     <row r="249" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -6857,10 +6979,10 @@
         <v>268</v>
       </c>
       <c r="B249" t="s">
-        <v>293</v>
+        <v>277</v>
       </c>
       <c r="C249" t="s">
-        <v>216</v>
+        <v>200</v>
       </c>
       <c r="D249">
         <v>3</v>
@@ -6869,7 +6991,7 @@
         <v>68</v>
       </c>
       <c r="F249" s="1" t="s">
-        <v>197</v>
+        <v>181</v>
       </c>
     </row>
     <row r="250" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -6877,10 +6999,10 @@
         <v>269</v>
       </c>
       <c r="B250" t="s">
-        <v>294</v>
+        <v>278</v>
       </c>
       <c r="C250" t="s">
-        <v>295</v>
+        <v>279</v>
       </c>
       <c r="D250">
         <v>2</v>
@@ -6889,7 +7011,7 @@
         <v>68</v>
       </c>
       <c r="F250" s="1" t="s">
-        <v>197</v>
+        <v>181</v>
       </c>
     </row>
     <row r="251" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -6897,10 +7019,10 @@
         <v>270</v>
       </c>
       <c r="B251" t="s">
-        <v>296</v>
+        <v>280</v>
       </c>
       <c r="C251" t="s">
-        <v>205</v>
+        <v>189</v>
       </c>
       <c r="D251">
         <v>1</v>
@@ -6909,7 +7031,7 @@
         <v>64</v>
       </c>
       <c r="F251" s="1" t="s">
-        <v>198</v>
+        <v>182</v>
       </c>
     </row>
     <row r="252" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -6917,10 +7039,10 @@
         <v>271</v>
       </c>
       <c r="B252" t="s">
-        <v>297</v>
+        <v>281</v>
       </c>
       <c r="C252" t="s">
-        <v>212</v>
+        <v>196</v>
       </c>
       <c r="D252">
         <v>2</v>
@@ -6929,7 +7051,7 @@
         <v>64</v>
       </c>
       <c r="F252" s="1" t="s">
-        <v>198</v>
+        <v>182</v>
       </c>
     </row>
     <row r="253" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -6937,10 +7059,10 @@
         <v>272</v>
       </c>
       <c r="B253" t="s">
-        <v>298</v>
+        <v>282</v>
       </c>
       <c r="C253" t="s">
-        <v>205</v>
+        <v>189</v>
       </c>
       <c r="D253">
         <v>2</v>
@@ -6949,7 +7071,7 @@
         <v>64</v>
       </c>
       <c r="F253" s="1" t="s">
-        <v>198</v>
+        <v>182</v>
       </c>
     </row>
     <row r="254" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -6957,10 +7079,10 @@
         <v>273</v>
       </c>
       <c r="B254" t="s">
-        <v>299</v>
+        <v>283</v>
       </c>
       <c r="C254" t="s">
-        <v>203</v>
+        <v>187</v>
       </c>
       <c r="D254">
         <v>2</v>
@@ -6969,7 +7091,7 @@
         <v>64</v>
       </c>
       <c r="F254" s="1" t="s">
-        <v>198</v>
+        <v>182</v>
       </c>
     </row>
     <row r="255" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -6977,10 +7099,10 @@
         <v>274</v>
       </c>
       <c r="B255" t="s">
-        <v>300</v>
+        <v>284</v>
       </c>
       <c r="C255" t="s">
-        <v>218</v>
+        <v>202</v>
       </c>
       <c r="D255">
         <v>2</v>
@@ -6989,7 +7111,7 @@
         <v>64</v>
       </c>
       <c r="F255" s="1" t="s">
-        <v>198</v>
+        <v>182</v>
       </c>
     </row>
     <row r="256" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -6997,10 +7119,10 @@
         <v>275</v>
       </c>
       <c r="B256" t="s">
-        <v>301</v>
+        <v>285</v>
       </c>
       <c r="C256" t="s">
-        <v>203</v>
+        <v>187</v>
       </c>
       <c r="D256">
         <v>2</v>
@@ -7009,7 +7131,7 @@
         <v>64</v>
       </c>
       <c r="F256" s="1" t="s">
-        <v>198</v>
+        <v>182</v>
       </c>
     </row>
     <row r="257" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -7017,10 +7139,10 @@
         <v>276</v>
       </c>
       <c r="B257" t="s">
-        <v>302</v>
+        <v>286</v>
       </c>
       <c r="C257" t="s">
-        <v>203</v>
+        <v>187</v>
       </c>
       <c r="D257">
         <v>2</v>
@@ -7029,7 +7151,7 @@
         <v>64</v>
       </c>
       <c r="F257" s="1" t="s">
-        <v>198</v>
+        <v>182</v>
       </c>
     </row>
     <row r="258" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -7037,10 +7159,10 @@
         <v>277</v>
       </c>
       <c r="B258" t="s">
-        <v>303</v>
+        <v>287</v>
       </c>
       <c r="C258" t="s">
-        <v>205</v>
+        <v>189</v>
       </c>
       <c r="D258">
         <v>2</v>
@@ -7049,7 +7171,7 @@
         <v>64</v>
       </c>
       <c r="F258" s="1" t="s">
-        <v>198</v>
+        <v>182</v>
       </c>
     </row>
     <row r="259" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -7057,10 +7179,10 @@
         <v>278</v>
       </c>
       <c r="B259" t="s">
-        <v>304</v>
+        <v>288</v>
       </c>
       <c r="C259" t="s">
-        <v>205</v>
+        <v>189</v>
       </c>
       <c r="D259">
         <v>2</v>
@@ -7069,7 +7191,7 @@
         <v>64</v>
       </c>
       <c r="F259" s="1" t="s">
-        <v>198</v>
+        <v>182</v>
       </c>
     </row>
     <row r="260" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -7077,10 +7199,10 @@
         <v>279</v>
       </c>
       <c r="B260" t="s">
-        <v>305</v>
+        <v>289</v>
       </c>
       <c r="C260" t="s">
-        <v>212</v>
+        <v>196</v>
       </c>
       <c r="D260">
         <v>2</v>
@@ -7089,7 +7211,7 @@
         <v>64</v>
       </c>
       <c r="F260" s="1" t="s">
-        <v>198</v>
+        <v>182</v>
       </c>
     </row>
     <row r="261" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -7097,10 +7219,10 @@
         <v>280</v>
       </c>
       <c r="B261" t="s">
-        <v>306</v>
+        <v>290</v>
       </c>
       <c r="C261" t="s">
-        <v>205</v>
+        <v>189</v>
       </c>
       <c r="D261">
         <v>2</v>
@@ -7109,7 +7231,7 @@
         <v>64</v>
       </c>
       <c r="F261" s="1" t="s">
-        <v>198</v>
+        <v>182</v>
       </c>
     </row>
     <row r="262" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -7117,10 +7239,10 @@
         <v>281</v>
       </c>
       <c r="B262" t="s">
-        <v>307</v>
+        <v>291</v>
       </c>
       <c r="C262" t="s">
-        <v>205</v>
+        <v>189</v>
       </c>
       <c r="D262">
         <v>2</v>
@@ -7129,7 +7251,7 @@
         <v>64</v>
       </c>
       <c r="F262" s="1" t="s">
-        <v>198</v>
+        <v>182</v>
       </c>
     </row>
     <row r="263" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -7137,10 +7259,10 @@
         <v>282</v>
       </c>
       <c r="B263" t="s">
-        <v>308</v>
+        <v>292</v>
       </c>
       <c r="C263" t="s">
-        <v>205</v>
+        <v>189</v>
       </c>
       <c r="D263">
         <v>3</v>
@@ -7149,7 +7271,7 @@
         <v>64</v>
       </c>
       <c r="F263" s="1" t="s">
-        <v>198</v>
+        <v>182</v>
       </c>
     </row>
     <row r="264" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -7157,10 +7279,10 @@
         <v>283</v>
       </c>
       <c r="B264" t="s">
-        <v>309</v>
+        <v>293</v>
       </c>
       <c r="C264" t="s">
-        <v>231</v>
+        <v>215</v>
       </c>
       <c r="D264">
         <v>3</v>
@@ -7169,7 +7291,7 @@
         <v>64</v>
       </c>
       <c r="F264" s="1" t="s">
-        <v>198</v>
+        <v>182</v>
       </c>
     </row>
     <row r="265" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -7177,10 +7299,10 @@
         <v>284</v>
       </c>
       <c r="B265" t="s">
-        <v>310</v>
+        <v>294</v>
       </c>
       <c r="C265" t="s">
-        <v>212</v>
+        <v>196</v>
       </c>
       <c r="D265">
         <v>3</v>
@@ -7189,7 +7311,7 @@
         <v>64</v>
       </c>
       <c r="F265" s="1" t="s">
-        <v>198</v>
+        <v>182</v>
       </c>
     </row>
     <row r="266" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -7197,10 +7319,10 @@
         <v>285</v>
       </c>
       <c r="B266" t="s">
-        <v>311</v>
+        <v>295</v>
       </c>
       <c r="C266" t="s">
-        <v>205</v>
+        <v>189</v>
       </c>
       <c r="D266">
         <v>3</v>
@@ -7209,7 +7331,7 @@
         <v>64</v>
       </c>
       <c r="F266" s="1" t="s">
-        <v>198</v>
+        <v>182</v>
       </c>
     </row>
     <row r="267" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -7217,10 +7339,10 @@
         <v>286</v>
       </c>
       <c r="B267" t="s">
-        <v>312</v>
+        <v>296</v>
       </c>
       <c r="C267" t="s">
-        <v>203</v>
+        <v>187</v>
       </c>
       <c r="D267">
         <v>3</v>
@@ -7229,7 +7351,7 @@
         <v>64</v>
       </c>
       <c r="F267" s="1" t="s">
-        <v>185</v>
+        <v>169</v>
       </c>
     </row>
     <row r="268" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -7237,10 +7359,10 @@
         <v>287</v>
       </c>
       <c r="B268" t="s">
-        <v>313</v>
+        <v>297</v>
       </c>
       <c r="C268" t="s">
-        <v>205</v>
+        <v>189</v>
       </c>
       <c r="D268">
         <v>3</v>
@@ -7249,7 +7371,7 @@
         <v>64</v>
       </c>
       <c r="F268" s="1" t="s">
-        <v>198</v>
+        <v>182</v>
       </c>
     </row>
     <row r="269" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -7257,10 +7379,10 @@
         <v>288</v>
       </c>
       <c r="B269" t="s">
-        <v>314</v>
+        <v>298</v>
       </c>
       <c r="C269" t="s">
-        <v>203</v>
+        <v>187</v>
       </c>
       <c r="D269">
         <v>3</v>
@@ -7269,7 +7391,7 @@
         <v>64</v>
       </c>
       <c r="F269" s="1" t="s">
-        <v>198</v>
+        <v>182</v>
       </c>
     </row>
     <row r="270" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -7277,10 +7399,10 @@
         <v>289</v>
       </c>
       <c r="B270" t="s">
-        <v>315</v>
+        <v>299</v>
       </c>
       <c r="C270" t="s">
-        <v>203</v>
+        <v>187</v>
       </c>
       <c r="D270">
         <v>3</v>
@@ -7289,7 +7411,7 @@
         <v>64</v>
       </c>
       <c r="F270" s="1" t="s">
-        <v>198</v>
+        <v>182</v>
       </c>
     </row>
     <row r="271" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -7297,10 +7419,10 @@
         <v>290</v>
       </c>
       <c r="B271" t="s">
-        <v>316</v>
+        <v>300</v>
       </c>
       <c r="C271" t="s">
-        <v>212</v>
+        <v>196</v>
       </c>
       <c r="D271">
         <v>3</v>
@@ -7309,7 +7431,7 @@
         <v>64</v>
       </c>
       <c r="F271" s="1" t="s">
-        <v>198</v>
+        <v>182</v>
       </c>
     </row>
     <row r="272" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -7317,10 +7439,10 @@
         <v>291</v>
       </c>
       <c r="B272" t="s">
-        <v>317</v>
+        <v>301</v>
       </c>
       <c r="C272" t="s">
-        <v>212</v>
+        <v>196</v>
       </c>
       <c r="D272">
         <v>3</v>
@@ -7329,7 +7451,7 @@
         <v>64</v>
       </c>
       <c r="F272" s="1" t="s">
-        <v>198</v>
+        <v>182</v>
       </c>
     </row>
     <row r="273" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -7337,10 +7459,10 @@
         <v>292</v>
       </c>
       <c r="B273" t="s">
-        <v>318</v>
+        <v>302</v>
       </c>
       <c r="C273" t="s">
-        <v>205</v>
+        <v>189</v>
       </c>
       <c r="D273">
         <v>3</v>
@@ -7349,7 +7471,7 @@
         <v>64</v>
       </c>
       <c r="F273" s="1" t="s">
-        <v>198</v>
+        <v>182</v>
       </c>
     </row>
     <row r="274" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -7357,10 +7479,10 @@
         <v>293</v>
       </c>
       <c r="B274" t="s">
-        <v>319</v>
+        <v>303</v>
       </c>
       <c r="C274" t="s">
-        <v>205</v>
+        <v>189</v>
       </c>
       <c r="D274">
         <v>3</v>
@@ -7369,7 +7491,7 @@
         <v>64</v>
       </c>
       <c r="F274" s="1" t="s">
-        <v>198</v>
+        <v>182</v>
       </c>
     </row>
     <row r="275" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -7377,10 +7499,10 @@
         <v>294</v>
       </c>
       <c r="B275" t="s">
-        <v>320</v>
+        <v>304</v>
       </c>
       <c r="C275" t="s">
-        <v>209</v>
+        <v>193</v>
       </c>
       <c r="D275">
         <v>3</v>
@@ -7389,7 +7511,7 @@
         <v>64</v>
       </c>
       <c r="F275" s="1" t="s">
-        <v>197</v>
+        <v>181</v>
       </c>
     </row>
     <row r="276" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -7397,10 +7519,10 @@
         <v>295</v>
       </c>
       <c r="B276" t="s">
-        <v>321</v>
+        <v>305</v>
       </c>
       <c r="C276" t="s">
-        <v>203</v>
+        <v>187</v>
       </c>
       <c r="D276">
         <v>3</v>
@@ -7409,7 +7531,7 @@
         <v>64</v>
       </c>
       <c r="F276" s="1" t="s">
-        <v>197</v>
+        <v>181</v>
       </c>
     </row>
     <row r="277" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -7417,10 +7539,10 @@
         <v>296</v>
       </c>
       <c r="B277" t="s">
-        <v>322</v>
+        <v>306</v>
       </c>
       <c r="C277" t="s">
-        <v>323</v>
+        <v>307</v>
       </c>
       <c r="D277">
         <v>2</v>
@@ -7429,7 +7551,7 @@
         <v>64</v>
       </c>
       <c r="F277" s="1" t="s">
-        <v>197</v>
+        <v>181</v>
       </c>
     </row>
     <row r="278" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -7437,10 +7559,10 @@
         <v>297</v>
       </c>
       <c r="B278" t="s">
-        <v>324</v>
+        <v>308</v>
       </c>
       <c r="C278" t="s">
-        <v>325</v>
+        <v>309</v>
       </c>
       <c r="D278">
         <v>2</v>
@@ -7449,7 +7571,7 @@
         <v>64</v>
       </c>
       <c r="F278" s="1" t="s">
-        <v>197</v>
+        <v>181</v>
       </c>
     </row>
     <row r="279" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -7457,10 +7579,10 @@
         <v>298</v>
       </c>
       <c r="B279" t="s">
-        <v>326</v>
+        <v>310</v>
       </c>
       <c r="C279" t="s">
-        <v>225</v>
+        <v>209</v>
       </c>
       <c r="D279">
         <v>2</v>
@@ -7469,7 +7591,7 @@
         <v>28</v>
       </c>
       <c r="F279" s="1" t="s">
-        <v>197</v>
+        <v>181</v>
       </c>
     </row>
     <row r="280" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -7477,10 +7599,10 @@
         <v>299</v>
       </c>
       <c r="B280" t="s">
-        <v>327</v>
+        <v>311</v>
       </c>
       <c r="C280" t="s">
-        <v>209</v>
+        <v>193</v>
       </c>
       <c r="D280">
         <v>2</v>
@@ -7489,7 +7611,7 @@
         <v>28</v>
       </c>
       <c r="F280" s="1" t="s">
-        <v>197</v>
+        <v>181</v>
       </c>
     </row>
     <row r="281" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -7497,10 +7619,10 @@
         <v>300</v>
       </c>
       <c r="B281" t="s">
-        <v>328</v>
+        <v>312</v>
       </c>
       <c r="C281" t="s">
-        <v>329</v>
+        <v>313</v>
       </c>
       <c r="D281">
         <v>2</v>
@@ -7509,7 +7631,7 @@
         <v>28</v>
       </c>
       <c r="F281" s="1" t="s">
-        <v>197</v>
+        <v>181</v>
       </c>
     </row>
     <row r="282" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -7517,10 +7639,10 @@
         <v>301</v>
       </c>
       <c r="B282" t="s">
-        <v>330</v>
+        <v>314</v>
       </c>
       <c r="C282" t="s">
-        <v>331</v>
+        <v>315</v>
       </c>
       <c r="D282">
         <v>2</v>
@@ -7529,7 +7651,7 @@
         <v>28</v>
       </c>
       <c r="F282" s="1" t="s">
-        <v>197</v>
+        <v>181</v>
       </c>
     </row>
     <row r="283" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -7537,10 +7659,10 @@
         <v>302</v>
       </c>
       <c r="B283" t="s">
-        <v>332</v>
+        <v>316</v>
       </c>
       <c r="C283" t="s">
-        <v>274</v>
+        <v>258</v>
       </c>
       <c r="D283">
         <v>3</v>
@@ -7549,7 +7671,7 @@
         <v>28</v>
       </c>
       <c r="F283" s="1" t="s">
-        <v>197</v>
+        <v>181</v>
       </c>
     </row>
     <row r="284" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -7557,10 +7679,10 @@
         <v>303</v>
       </c>
       <c r="B284" t="s">
-        <v>333</v>
+        <v>317</v>
       </c>
       <c r="C284" t="s">
-        <v>205</v>
+        <v>189</v>
       </c>
       <c r="D284">
         <v>3</v>
@@ -7569,7 +7691,7 @@
         <v>28</v>
       </c>
       <c r="F284" s="1" t="s">
-        <v>197</v>
+        <v>181</v>
       </c>
     </row>
     <row r="285" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -7577,10 +7699,10 @@
         <v>304</v>
       </c>
       <c r="B285" t="s">
-        <v>335</v>
+        <v>319</v>
       </c>
       <c r="C285" t="s">
-        <v>225</v>
+        <v>209</v>
       </c>
       <c r="D285">
         <v>3</v>
@@ -7589,7 +7711,7 @@
         <v>5</v>
       </c>
       <c r="F285" s="1" t="s">
-        <v>198</v>
+        <v>182</v>
       </c>
     </row>
     <row r="286" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -7597,10 +7719,10 @@
         <v>305</v>
       </c>
       <c r="B286" t="s">
-        <v>336</v>
+        <v>320</v>
       </c>
       <c r="C286" t="s">
-        <v>212</v>
+        <v>196</v>
       </c>
       <c r="D286">
         <v>3</v>
@@ -7609,7 +7731,7 @@
         <v>5</v>
       </c>
       <c r="F286" s="1" t="s">
-        <v>198</v>
+        <v>182</v>
       </c>
     </row>
     <row r="287" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -7617,10 +7739,10 @@
         <v>306</v>
       </c>
       <c r="B287" t="s">
-        <v>337</v>
+        <v>321</v>
       </c>
       <c r="C287" t="s">
-        <v>338</v>
+        <v>322</v>
       </c>
       <c r="D287">
         <v>3</v>
@@ -7629,7 +7751,7 @@
         <v>5</v>
       </c>
       <c r="F287" s="1" t="s">
-        <v>198</v>
+        <v>182</v>
       </c>
     </row>
     <row r="288" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -7637,10 +7759,10 @@
         <v>307</v>
       </c>
       <c r="B288" t="s">
-        <v>339</v>
+        <v>323</v>
       </c>
       <c r="C288" t="s">
-        <v>207</v>
+        <v>191</v>
       </c>
       <c r="D288">
         <v>3</v>
@@ -7649,7 +7771,7 @@
         <v>5</v>
       </c>
       <c r="F288" s="1" t="s">
-        <v>198</v>
+        <v>182</v>
       </c>
     </row>
     <row r="289" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -7657,10 +7779,10 @@
         <v>308</v>
       </c>
       <c r="B289" t="s">
-        <v>340</v>
+        <v>324</v>
       </c>
       <c r="C289" t="s">
-        <v>341</v>
+        <v>325</v>
       </c>
       <c r="D289">
         <v>3</v>
@@ -7669,7 +7791,7 @@
         <v>5</v>
       </c>
       <c r="F289" s="1" t="s">
-        <v>198</v>
+        <v>182</v>
       </c>
     </row>
     <row r="290" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -7677,10 +7799,10 @@
         <v>309</v>
       </c>
       <c r="B290" t="s">
-        <v>342</v>
+        <v>326</v>
       </c>
       <c r="C290" t="s">
-        <v>331</v>
+        <v>315</v>
       </c>
       <c r="D290">
         <v>3</v>
@@ -7689,7 +7811,7 @@
         <v>5</v>
       </c>
       <c r="F290" s="1" t="s">
-        <v>198</v>
+        <v>182</v>
       </c>
     </row>
     <row r="291" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -7697,10 +7819,10 @@
         <v>310</v>
       </c>
       <c r="B291" t="s">
-        <v>343</v>
+        <v>327</v>
       </c>
       <c r="C291" t="s">
-        <v>209</v>
+        <v>193</v>
       </c>
       <c r="D291">
         <v>3</v>
@@ -7709,7 +7831,7 @@
         <v>5</v>
       </c>
       <c r="F291" s="1" t="s">
-        <v>198</v>
+        <v>182</v>
       </c>
     </row>
     <row r="292" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -7717,10 +7839,10 @@
         <v>311</v>
       </c>
       <c r="B292" t="s">
-        <v>344</v>
+        <v>328</v>
       </c>
       <c r="C292" t="s">
-        <v>212</v>
+        <v>196</v>
       </c>
       <c r="D292">
         <v>3</v>
@@ -7729,7 +7851,7 @@
         <v>5</v>
       </c>
       <c r="F292" s="1" t="s">
-        <v>198</v>
+        <v>182</v>
       </c>
     </row>
     <row r="293" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -7737,10 +7859,10 @@
         <v>312</v>
       </c>
       <c r="B293" t="s">
-        <v>345</v>
+        <v>329</v>
       </c>
       <c r="C293" t="s">
-        <v>225</v>
+        <v>209</v>
       </c>
       <c r="D293">
         <v>3</v>
@@ -7749,7 +7871,7 @@
         <v>5</v>
       </c>
       <c r="F293" s="1" t="s">
-        <v>198</v>
+        <v>182</v>
       </c>
     </row>
     <row r="294" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -7757,10 +7879,10 @@
         <v>313</v>
       </c>
       <c r="B294" t="s">
-        <v>346</v>
+        <v>330</v>
       </c>
       <c r="C294" t="s">
-        <v>212</v>
+        <v>196</v>
       </c>
       <c r="D294">
         <v>3</v>
@@ -7769,7 +7891,7 @@
         <v>5</v>
       </c>
       <c r="F294" s="1" t="s">
-        <v>198</v>
+        <v>182</v>
       </c>
     </row>
     <row r="295" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -7777,10 +7899,10 @@
         <v>314</v>
       </c>
       <c r="B295" t="s">
-        <v>347</v>
+        <v>331</v>
       </c>
       <c r="C295" t="s">
-        <v>205</v>
+        <v>189</v>
       </c>
       <c r="D295">
         <v>3</v>
@@ -7789,7 +7911,7 @@
         <v>5</v>
       </c>
       <c r="F295" s="1" t="s">
-        <v>185</v>
+        <v>169</v>
       </c>
     </row>
     <row r="296" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -7797,10 +7919,10 @@
         <v>315</v>
       </c>
       <c r="B296" t="s">
-        <v>348</v>
+        <v>332</v>
       </c>
       <c r="C296" t="s">
-        <v>212</v>
+        <v>196</v>
       </c>
       <c r="D296">
         <v>3</v>
@@ -7809,7 +7931,7 @@
         <v>5</v>
       </c>
       <c r="F296" s="1" t="s">
-        <v>198</v>
+        <v>182</v>
       </c>
     </row>
     <row r="297" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -7817,10 +7939,10 @@
         <v>316</v>
       </c>
       <c r="B297" t="s">
-        <v>349</v>
+        <v>333</v>
       </c>
       <c r="C297" t="s">
-        <v>205</v>
+        <v>189</v>
       </c>
       <c r="D297">
         <v>3</v>
@@ -7829,7 +7951,7 @@
         <v>5</v>
       </c>
       <c r="F297" s="1" t="s">
-        <v>198</v>
+        <v>182</v>
       </c>
     </row>
     <row r="298" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -7837,10 +7959,10 @@
         <v>317</v>
       </c>
       <c r="B298" t="s">
-        <v>350</v>
+        <v>334</v>
       </c>
       <c r="C298" t="s">
-        <v>203</v>
+        <v>187</v>
       </c>
       <c r="D298">
         <v>3</v>
@@ -7849,7 +7971,7 @@
         <v>5</v>
       </c>
       <c r="F298" s="1" t="s">
-        <v>198</v>
+        <v>182</v>
       </c>
     </row>
     <row r="299" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -7857,10 +7979,10 @@
         <v>318</v>
       </c>
       <c r="B299" t="s">
-        <v>351</v>
+        <v>335</v>
       </c>
       <c r="C299" t="s">
-        <v>203</v>
+        <v>187</v>
       </c>
       <c r="D299">
         <v>3</v>
@@ -7869,7 +7991,7 @@
         <v>5</v>
       </c>
       <c r="F299" s="1" t="s">
-        <v>198</v>
+        <v>182</v>
       </c>
     </row>
     <row r="300" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -7877,10 +7999,10 @@
         <v>319</v>
       </c>
       <c r="B300" t="s">
-        <v>352</v>
+        <v>336</v>
       </c>
       <c r="C300" t="s">
-        <v>212</v>
+        <v>196</v>
       </c>
       <c r="D300">
         <v>3</v>
@@ -7889,7 +8011,7 @@
         <v>5</v>
       </c>
       <c r="F300" s="1" t="s">
-        <v>198</v>
+        <v>182</v>
       </c>
     </row>
     <row r="301" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -7897,10 +8019,10 @@
         <v>320</v>
       </c>
       <c r="B301" t="s">
-        <v>353</v>
+        <v>337</v>
       </c>
       <c r="C301" t="s">
-        <v>205</v>
+        <v>189</v>
       </c>
       <c r="D301">
         <v>3</v>
@@ -7909,7 +8031,7 @@
         <v>5</v>
       </c>
       <c r="F301" s="1" t="s">
-        <v>198</v>
+        <v>182</v>
       </c>
     </row>
     <row r="302" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -7917,10 +8039,10 @@
         <v>321</v>
       </c>
       <c r="B302" t="s">
-        <v>354</v>
+        <v>338</v>
       </c>
       <c r="C302" t="s">
-        <v>203</v>
+        <v>187</v>
       </c>
       <c r="D302">
         <v>3</v>
@@ -7929,7 +8051,7 @@
         <v>5</v>
       </c>
       <c r="F302" s="1" t="s">
-        <v>198</v>
+        <v>182</v>
       </c>
     </row>
     <row r="303" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -7937,10 +8059,10 @@
         <v>322</v>
       </c>
       <c r="B303" t="s">
-        <v>355</v>
+        <v>339</v>
       </c>
       <c r="C303" t="s">
-        <v>212</v>
+        <v>196</v>
       </c>
       <c r="D303">
         <v>3</v>
@@ -7949,7 +8071,7 @@
         <v>5</v>
       </c>
       <c r="F303" s="1" t="s">
-        <v>198</v>
+        <v>182</v>
       </c>
     </row>
     <row r="304" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -7957,10 +8079,10 @@
         <v>323</v>
       </c>
       <c r="B304" t="s">
-        <v>356</v>
+        <v>340</v>
       </c>
       <c r="C304" t="s">
-        <v>212</v>
+        <v>196</v>
       </c>
       <c r="D304">
         <v>3</v>
@@ -7969,7 +8091,7 @@
         <v>5</v>
       </c>
       <c r="F304" s="1" t="s">
-        <v>198</v>
+        <v>182</v>
       </c>
     </row>
     <row r="305" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -7977,10 +8099,10 @@
         <v>324</v>
       </c>
       <c r="B305" t="s">
-        <v>357</v>
+        <v>341</v>
       </c>
       <c r="C305" t="s">
-        <v>218</v>
+        <v>202</v>
       </c>
       <c r="D305">
         <v>3</v>
@@ -7989,7 +8111,7 @@
         <v>5</v>
       </c>
       <c r="F305" s="1" t="s">
-        <v>198</v>
+        <v>182</v>
       </c>
     </row>
     <row r="306" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -7997,10 +8119,10 @@
         <v>325</v>
       </c>
       <c r="B306" t="s">
-        <v>358</v>
+        <v>342</v>
       </c>
       <c r="C306" t="s">
-        <v>203</v>
+        <v>187</v>
       </c>
       <c r="D306">
         <v>3</v>
@@ -8009,7 +8131,7 @@
         <v>5</v>
       </c>
       <c r="F306" s="1" t="s">
-        <v>198</v>
+        <v>182</v>
       </c>
     </row>
     <row r="307" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -8017,10 +8139,10 @@
         <v>326</v>
       </c>
       <c r="B307" t="s">
-        <v>359</v>
+        <v>343</v>
       </c>
       <c r="C307" t="s">
-        <v>205</v>
+        <v>189</v>
       </c>
       <c r="D307">
         <v>3</v>
@@ -8029,7 +8151,7 @@
         <v>5</v>
       </c>
       <c r="F307" s="1" t="s">
-        <v>198</v>
+        <v>182</v>
       </c>
     </row>
     <row r="308" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -8037,10 +8159,10 @@
         <v>327</v>
       </c>
       <c r="B308" t="s">
-        <v>360</v>
+        <v>344</v>
       </c>
       <c r="C308" t="s">
-        <v>205</v>
+        <v>189</v>
       </c>
       <c r="D308">
         <v>3</v>
@@ -8049,7 +8171,7 @@
         <v>5</v>
       </c>
       <c r="F308" s="1" t="s">
-        <v>198</v>
+        <v>182</v>
       </c>
     </row>
     <row r="309" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -8057,10 +8179,10 @@
         <v>328</v>
       </c>
       <c r="B309" t="s">
-        <v>361</v>
+        <v>345</v>
       </c>
       <c r="C309" t="s">
-        <v>216</v>
+        <v>200</v>
       </c>
       <c r="D309">
         <v>3</v>
@@ -8069,7 +8191,7 @@
         <v>5</v>
       </c>
       <c r="F309" s="1" t="s">
-        <v>198</v>
+        <v>182</v>
       </c>
     </row>
     <row r="310" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -8077,10 +8199,10 @@
         <v>329</v>
       </c>
       <c r="B310" t="s">
-        <v>362</v>
+        <v>346</v>
       </c>
       <c r="C310" t="s">
-        <v>203</v>
+        <v>187</v>
       </c>
       <c r="D310">
         <v>3</v>
@@ -8089,7 +8211,7 @@
         <v>5</v>
       </c>
       <c r="F310" s="1" t="s">
-        <v>198</v>
+        <v>182</v>
       </c>
     </row>
     <row r="311" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -8097,10 +8219,10 @@
         <v>330</v>
       </c>
       <c r="B311" t="s">
-        <v>363</v>
+        <v>347</v>
       </c>
       <c r="C311" t="s">
-        <v>203</v>
+        <v>187</v>
       </c>
       <c r="D311">
         <v>3</v>
@@ -8109,7 +8231,7 @@
         <v>5</v>
       </c>
       <c r="F311" s="1" t="s">
-        <v>198</v>
+        <v>182</v>
       </c>
     </row>
     <row r="312" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -8117,10 +8239,10 @@
         <v>331</v>
       </c>
       <c r="B312" t="s">
-        <v>364</v>
+        <v>348</v>
       </c>
       <c r="C312" t="s">
-        <v>212</v>
+        <v>196</v>
       </c>
       <c r="D312">
         <v>3</v>
@@ -8129,15 +8251,15 @@
         <v>5</v>
       </c>
       <c r="F312" s="1" t="s">
-        <v>198</v>
+        <v>182</v>
       </c>
     </row>
     <row r="313" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B313" t="s">
-        <v>365</v>
+        <v>349</v>
       </c>
       <c r="C313" t="s">
-        <v>203</v>
+        <v>187</v>
       </c>
       <c r="D313">
         <v>3</v>
@@ -8146,15 +8268,15 @@
         <v>5</v>
       </c>
       <c r="F313" s="1" t="s">
-        <v>197</v>
+        <v>181</v>
       </c>
     </row>
     <row r="314" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B314" t="s">
-        <v>366</v>
+        <v>350</v>
       </c>
       <c r="C314" t="s">
-        <v>207</v>
+        <v>191</v>
       </c>
       <c r="D314">
         <v>3</v>
@@ -8163,15 +8285,15 @@
         <v>5</v>
       </c>
       <c r="F314" s="1" t="s">
-        <v>197</v>
+        <v>181</v>
       </c>
     </row>
     <row r="315" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B315" t="s">
-        <v>367</v>
+        <v>351</v>
       </c>
       <c r="C315" t="s">
-        <v>205</v>
+        <v>189</v>
       </c>
       <c r="D315">
         <v>3</v>
@@ -8180,15 +8302,15 @@
         <v>5</v>
       </c>
       <c r="F315" s="1" t="s">
-        <v>197</v>
+        <v>181</v>
       </c>
     </row>
     <row r="316" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B316" t="s">
-        <v>368</v>
+        <v>352</v>
       </c>
       <c r="C316" t="s">
-        <v>225</v>
+        <v>209</v>
       </c>
       <c r="D316">
         <v>3</v>
@@ -8197,15 +8319,15 @@
         <v>5</v>
       </c>
       <c r="F316" s="1" t="s">
-        <v>197</v>
+        <v>181</v>
       </c>
     </row>
     <row r="317" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B317" t="s">
-        <v>369</v>
+        <v>353</v>
       </c>
       <c r="C317" t="s">
-        <v>205</v>
+        <v>189</v>
       </c>
       <c r="D317">
         <v>3</v>
@@ -8214,15 +8336,15 @@
         <v>5</v>
       </c>
       <c r="F317" s="1" t="s">
-        <v>197</v>
+        <v>181</v>
       </c>
     </row>
     <row r="318" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B318" t="s">
-        <v>370</v>
+        <v>354</v>
       </c>
       <c r="C318" t="s">
-        <v>212</v>
+        <v>196</v>
       </c>
       <c r="D318">
         <v>3</v>
@@ -8231,15 +8353,15 @@
         <v>5</v>
       </c>
       <c r="F318" s="1" t="s">
-        <v>391</v>
+        <v>375</v>
       </c>
     </row>
     <row r="319" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B319" t="s">
-        <v>371</v>
+        <v>355</v>
       </c>
       <c r="C319" t="s">
-        <v>205</v>
+        <v>189</v>
       </c>
       <c r="D319">
         <v>3</v>
@@ -8248,15 +8370,15 @@
         <v>5</v>
       </c>
       <c r="F319" s="1" t="s">
-        <v>391</v>
+        <v>375</v>
       </c>
     </row>
     <row r="320" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B320" t="s">
-        <v>372</v>
+        <v>356</v>
       </c>
       <c r="C320" t="s">
-        <v>373</v>
+        <v>357</v>
       </c>
       <c r="D320">
         <v>3</v>
@@ -8265,15 +8387,15 @@
         <v>5</v>
       </c>
       <c r="F320" s="1" t="s">
-        <v>391</v>
+        <v>375</v>
       </c>
     </row>
     <row r="321" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B321" t="s">
-        <v>374</v>
+        <v>358</v>
       </c>
       <c r="C321" t="s">
-        <v>205</v>
+        <v>189</v>
       </c>
       <c r="D321">
         <v>3</v>
@@ -8282,15 +8404,15 @@
         <v>5</v>
       </c>
       <c r="F321" s="1" t="s">
-        <v>391</v>
+        <v>375</v>
       </c>
     </row>
     <row r="322" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B322" t="s">
-        <v>375</v>
+        <v>359</v>
       </c>
       <c r="C322" t="s">
-        <v>212</v>
+        <v>196</v>
       </c>
       <c r="D322">
         <v>3</v>
@@ -8299,15 +8421,15 @@
         <v>5</v>
       </c>
       <c r="F322" s="1" t="s">
-        <v>391</v>
+        <v>375</v>
       </c>
     </row>
     <row r="323" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B323" t="s">
-        <v>376</v>
+        <v>360</v>
       </c>
       <c r="C323" t="s">
-        <v>377</v>
+        <v>361</v>
       </c>
       <c r="D323">
         <v>3</v>
@@ -8316,15 +8438,15 @@
         <v>5</v>
       </c>
       <c r="F323" s="1" t="s">
-        <v>391</v>
+        <v>375</v>
       </c>
     </row>
     <row r="324" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B324" t="s">
-        <v>378</v>
+        <v>362</v>
       </c>
       <c r="C324" t="s">
-        <v>323</v>
+        <v>307</v>
       </c>
       <c r="D324">
         <v>3</v>
@@ -8333,15 +8455,15 @@
         <v>5</v>
       </c>
       <c r="F324" s="1" t="s">
-        <v>391</v>
+        <v>375</v>
       </c>
     </row>
     <row r="325" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B325" t="s">
-        <v>379</v>
+        <v>363</v>
       </c>
       <c r="C325" t="s">
-        <v>205</v>
+        <v>189</v>
       </c>
       <c r="D325">
         <v>3</v>
@@ -8350,15 +8472,15 @@
         <v>5</v>
       </c>
       <c r="F325" s="1" t="s">
-        <v>391</v>
+        <v>375</v>
       </c>
     </row>
     <row r="326" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B326" t="s">
-        <v>380</v>
+        <v>364</v>
       </c>
       <c r="C326" t="s">
-        <v>203</v>
+        <v>187</v>
       </c>
       <c r="D326">
         <v>3</v>
@@ -8367,15 +8489,15 @@
         <v>5</v>
       </c>
       <c r="F326" s="1" t="s">
-        <v>391</v>
+        <v>375</v>
       </c>
     </row>
     <row r="327" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B327" t="s">
-        <v>381</v>
+        <v>365</v>
       </c>
       <c r="C327" t="s">
-        <v>205</v>
+        <v>189</v>
       </c>
       <c r="D327">
         <v>3</v>
@@ -8384,15 +8506,15 @@
         <v>5</v>
       </c>
       <c r="F327" s="1" t="s">
-        <v>391</v>
+        <v>375</v>
       </c>
     </row>
     <row r="328" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B328" t="s">
-        <v>382</v>
+        <v>366</v>
       </c>
       <c r="C328" t="s">
-        <v>212</v>
+        <v>196</v>
       </c>
       <c r="D328">
         <v>3</v>
@@ -8401,15 +8523,15 @@
         <v>5</v>
       </c>
       <c r="F328" s="1" t="s">
-        <v>391</v>
+        <v>375</v>
       </c>
     </row>
     <row r="329" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B329" t="s">
-        <v>383</v>
+        <v>367</v>
       </c>
       <c r="C329" t="s">
-        <v>203</v>
+        <v>187</v>
       </c>
       <c r="D329">
         <v>3</v>
@@ -8418,15 +8540,15 @@
         <v>5</v>
       </c>
       <c r="F329" s="1" t="s">
-        <v>391</v>
+        <v>375</v>
       </c>
     </row>
     <row r="330" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B330" t="s">
-        <v>384</v>
+        <v>368</v>
       </c>
       <c r="C330" t="s">
-        <v>203</v>
+        <v>187</v>
       </c>
       <c r="D330">
         <v>3</v>
@@ -8435,15 +8557,15 @@
         <v>5</v>
       </c>
       <c r="F330" s="1" t="s">
-        <v>391</v>
+        <v>375</v>
       </c>
     </row>
     <row r="331" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B331" t="s">
-        <v>385</v>
+        <v>369</v>
       </c>
       <c r="C331" t="s">
-        <v>373</v>
+        <v>357</v>
       </c>
       <c r="D331">
         <v>3</v>
@@ -8452,15 +8574,15 @@
         <v>5</v>
       </c>
       <c r="F331" s="1" t="s">
-        <v>391</v>
+        <v>375</v>
       </c>
     </row>
     <row r="332" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B332" t="s">
-        <v>386</v>
+        <v>370</v>
       </c>
       <c r="C332" t="s">
-        <v>212</v>
+        <v>196</v>
       </c>
       <c r="D332">
         <v>3</v>
@@ -8469,7 +8591,7 @@
         <v>5</v>
       </c>
       <c r="F332" s="1" t="s">
-        <v>391</v>
+        <v>375</v>
       </c>
     </row>
     <row r="333" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -8477,10 +8599,10 @@
         <v>352</v>
       </c>
       <c r="B333" t="s">
-        <v>387</v>
+        <v>371</v>
       </c>
       <c r="C333" t="s">
-        <v>207</v>
+        <v>191</v>
       </c>
       <c r="D333">
         <v>3</v>
@@ -8489,7 +8611,7 @@
         <v>5</v>
       </c>
       <c r="F333" s="1" t="s">
-        <v>391</v>
+        <v>375</v>
       </c>
     </row>
     <row r="334" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -8497,10 +8619,10 @@
         <v>353</v>
       </c>
       <c r="B334" t="s">
-        <v>388</v>
+        <v>372</v>
       </c>
       <c r="C334" t="s">
-        <v>389</v>
+        <v>373</v>
       </c>
       <c r="D334">
         <v>3</v>
@@ -8509,7 +8631,7 @@
         <v>5</v>
       </c>
       <c r="F334" s="1" t="s">
-        <v>391</v>
+        <v>375</v>
       </c>
     </row>
     <row r="335" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -8517,10 +8639,10 @@
         <v>354</v>
       </c>
       <c r="B335" t="s">
-        <v>390</v>
+        <v>374</v>
       </c>
       <c r="C335" t="s">
-        <v>389</v>
+        <v>373</v>
       </c>
       <c r="D335">
         <v>3</v>
@@ -8529,7 +8651,7 @@
         <v>5</v>
       </c>
       <c r="F335" s="1" t="s">
-        <v>391</v>
+        <v>375</v>
       </c>
     </row>
     <row r="336" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -8537,10 +8659,10 @@
         <v>355</v>
       </c>
       <c r="B336" t="s">
-        <v>392</v>
+        <v>376</v>
       </c>
       <c r="C336" t="s">
-        <v>216</v>
+        <v>200</v>
       </c>
       <c r="D336">
         <v>3</v>
@@ -8549,7 +8671,7 @@
         <v>65</v>
       </c>
       <c r="F336" s="1" t="s">
-        <v>391</v>
+        <v>375</v>
       </c>
     </row>
     <row r="337" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -8557,10 +8679,10 @@
         <v>356</v>
       </c>
       <c r="B337" t="s">
-        <v>393</v>
+        <v>377</v>
       </c>
       <c r="C337" t="s">
-        <v>203</v>
+        <v>187</v>
       </c>
       <c r="D337">
         <v>3</v>
@@ -8569,7 +8691,7 @@
         <v>65</v>
       </c>
       <c r="F337" s="1" t="s">
-        <v>391</v>
+        <v>375</v>
       </c>
     </row>
     <row r="338" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -8577,10 +8699,10 @@
         <v>357</v>
       </c>
       <c r="B338" t="s">
-        <v>394</v>
+        <v>378</v>
       </c>
       <c r="C338" t="s">
-        <v>323</v>
+        <v>307</v>
       </c>
       <c r="D338">
         <v>3</v>
@@ -8589,7 +8711,7 @@
         <v>65</v>
       </c>
       <c r="F338" s="1" t="s">
-        <v>391</v>
+        <v>375</v>
       </c>
     </row>
     <row r="339" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -8597,10 +8719,10 @@
         <v>358</v>
       </c>
       <c r="B339" t="s">
-        <v>395</v>
+        <v>379</v>
       </c>
       <c r="C339" t="s">
-        <v>203</v>
+        <v>187</v>
       </c>
       <c r="D339">
         <v>3</v>
@@ -8609,7 +8731,7 @@
         <v>65</v>
       </c>
       <c r="F339" s="1" t="s">
-        <v>391</v>
+        <v>375</v>
       </c>
     </row>
     <row r="340" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -8617,10 +8739,10 @@
         <v>359</v>
       </c>
       <c r="B340" t="s">
-        <v>396</v>
+        <v>380</v>
       </c>
       <c r="C340" t="s">
-        <v>225</v>
+        <v>209</v>
       </c>
       <c r="D340">
         <v>3</v>
@@ -8629,7 +8751,7 @@
         <v>65</v>
       </c>
       <c r="F340" s="1" t="s">
-        <v>391</v>
+        <v>375</v>
       </c>
     </row>
     <row r="341" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -8637,10 +8759,10 @@
         <v>360</v>
       </c>
       <c r="B341" t="s">
-        <v>397</v>
+        <v>381</v>
       </c>
       <c r="C341" t="s">
-        <v>287</v>
+        <v>271</v>
       </c>
       <c r="D341">
         <v>3</v>
@@ -8649,7 +8771,7 @@
         <v>65</v>
       </c>
       <c r="F341" s="1" t="s">
-        <v>391</v>
+        <v>375</v>
       </c>
     </row>
     <row r="342" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -8657,10 +8779,10 @@
         <v>361</v>
       </c>
       <c r="B342" t="s">
-        <v>398</v>
+        <v>382</v>
       </c>
       <c r="C342" t="s">
-        <v>218</v>
+        <v>202</v>
       </c>
       <c r="D342">
         <v>3</v>
@@ -8669,7 +8791,7 @@
         <v>65</v>
       </c>
       <c r="F342" s="1" t="s">
-        <v>391</v>
+        <v>375</v>
       </c>
     </row>
     <row r="343" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -8677,10 +8799,10 @@
         <v>362</v>
       </c>
       <c r="B343" t="s">
-        <v>399</v>
+        <v>383</v>
       </c>
       <c r="C343" t="s">
-        <v>205</v>
+        <v>189</v>
       </c>
       <c r="D343">
         <v>3</v>
@@ -8689,7 +8811,7 @@
         <v>65</v>
       </c>
       <c r="F343" s="1" t="s">
-        <v>391</v>
+        <v>375</v>
       </c>
     </row>
     <row r="344" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -8697,10 +8819,10 @@
         <v>363</v>
       </c>
       <c r="B344" t="s">
-        <v>400</v>
+        <v>384</v>
       </c>
       <c r="C344" t="s">
-        <v>216</v>
+        <v>200</v>
       </c>
       <c r="D344">
         <v>3</v>
@@ -8709,7 +8831,7 @@
         <v>65</v>
       </c>
       <c r="F344" s="1" t="s">
-        <v>391</v>
+        <v>375</v>
       </c>
     </row>
     <row r="345" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -8717,10 +8839,10 @@
         <v>364</v>
       </c>
       <c r="B345" t="s">
-        <v>401</v>
+        <v>385</v>
       </c>
       <c r="C345" t="s">
-        <v>216</v>
+        <v>200</v>
       </c>
       <c r="D345">
         <v>3</v>
@@ -8729,7 +8851,7 @@
         <v>65</v>
       </c>
       <c r="F345" s="1" t="s">
-        <v>391</v>
+        <v>375</v>
       </c>
     </row>
     <row r="346" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -8737,10 +8859,10 @@
         <v>365</v>
       </c>
       <c r="B346" t="s">
-        <v>402</v>
+        <v>386</v>
       </c>
       <c r="C346" t="s">
-        <v>212</v>
+        <v>196</v>
       </c>
       <c r="D346">
         <v>3</v>
@@ -8749,7 +8871,7 @@
         <v>65</v>
       </c>
       <c r="F346" s="1" t="s">
-        <v>391</v>
+        <v>375</v>
       </c>
     </row>
     <row r="347" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -8757,10 +8879,10 @@
         <v>366</v>
       </c>
       <c r="B347" t="s">
-        <v>403</v>
+        <v>387</v>
       </c>
       <c r="C347" t="s">
-        <v>373</v>
+        <v>357</v>
       </c>
       <c r="D347">
         <v>3</v>
@@ -8769,7 +8891,7 @@
         <v>65</v>
       </c>
       <c r="F347" s="1" t="s">
-        <v>391</v>
+        <v>375</v>
       </c>
     </row>
     <row r="348" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -8777,10 +8899,10 @@
         <v>367</v>
       </c>
       <c r="B348" t="s">
-        <v>404</v>
+        <v>388</v>
       </c>
       <c r="C348" t="s">
-        <v>373</v>
+        <v>357</v>
       </c>
       <c r="D348">
         <v>3</v>
@@ -8789,7 +8911,7 @@
         <v>65</v>
       </c>
       <c r="F348" s="1" t="s">
-        <v>391</v>
+        <v>375</v>
       </c>
     </row>
     <row r="349" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -8797,10 +8919,10 @@
         <v>368</v>
       </c>
       <c r="B349" t="s">
-        <v>405</v>
+        <v>389</v>
       </c>
       <c r="C349" t="s">
-        <v>338</v>
+        <v>322</v>
       </c>
       <c r="D349">
         <v>3</v>
@@ -8809,7 +8931,7 @@
         <v>65</v>
       </c>
       <c r="F349" s="1" t="s">
-        <v>391</v>
+        <v>375</v>
       </c>
     </row>
     <row r="350" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -8817,10 +8939,10 @@
         <v>369</v>
       </c>
       <c r="B350" t="s">
-        <v>406</v>
+        <v>390</v>
       </c>
       <c r="C350" t="s">
-        <v>216</v>
+        <v>200</v>
       </c>
       <c r="D350">
         <v>3</v>
@@ -8829,7 +8951,7 @@
         <v>65</v>
       </c>
       <c r="F350" s="1" t="s">
-        <v>391</v>
+        <v>375</v>
       </c>
     </row>
     <row r="351" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -8837,10 +8959,10 @@
         <v>370</v>
       </c>
       <c r="B351" t="s">
-        <v>407</v>
+        <v>391</v>
       </c>
       <c r="C351" t="s">
-        <v>212</v>
+        <v>196</v>
       </c>
       <c r="D351">
         <v>3</v>
@@ -8849,7 +8971,7 @@
         <v>81</v>
       </c>
       <c r="F351" s="1" t="s">
-        <v>391</v>
+        <v>375</v>
       </c>
     </row>
     <row r="352" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -8857,10 +8979,10 @@
         <v>371</v>
       </c>
       <c r="B352" t="s">
-        <v>408</v>
+        <v>392</v>
       </c>
       <c r="C352" t="s">
-        <v>323</v>
+        <v>307</v>
       </c>
       <c r="D352">
         <v>3</v>
@@ -8869,7 +8991,7 @@
         <v>81</v>
       </c>
       <c r="F352" s="1" t="s">
-        <v>391</v>
+        <v>375</v>
       </c>
     </row>
     <row r="353" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -8877,10 +8999,10 @@
         <v>372</v>
       </c>
       <c r="B353" t="s">
-        <v>409</v>
+        <v>393</v>
       </c>
       <c r="C353" t="s">
-        <v>212</v>
+        <v>196</v>
       </c>
       <c r="D353">
         <v>3</v>
@@ -8889,7 +9011,7 @@
         <v>81</v>
       </c>
       <c r="F353" s="1" t="s">
-        <v>391</v>
+        <v>375</v>
       </c>
     </row>
     <row r="354" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -8897,10 +9019,10 @@
         <v>373</v>
       </c>
       <c r="B354" t="s">
-        <v>410</v>
+        <v>394</v>
       </c>
       <c r="C354" t="s">
-        <v>329</v>
+        <v>313</v>
       </c>
       <c r="D354">
         <v>3</v>
@@ -8909,7 +9031,7 @@
         <v>81</v>
       </c>
       <c r="F354" s="1" t="s">
-        <v>391</v>
+        <v>375</v>
       </c>
     </row>
     <row r="355" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -8917,10 +9039,10 @@
         <v>374</v>
       </c>
       <c r="B355" t="s">
-        <v>411</v>
+        <v>395</v>
       </c>
       <c r="C355" t="s">
-        <v>205</v>
+        <v>189</v>
       </c>
       <c r="D355">
         <v>3</v>
@@ -8929,7 +9051,7 @@
         <v>81</v>
       </c>
       <c r="F355" s="1" t="s">
-        <v>391</v>
+        <v>375</v>
       </c>
     </row>
     <row r="356" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -8937,10 +9059,10 @@
         <v>375</v>
       </c>
       <c r="B356" t="s">
-        <v>412</v>
+        <v>396</v>
       </c>
       <c r="C356" t="s">
-        <v>212</v>
+        <v>196</v>
       </c>
       <c r="D356">
         <v>3</v>
@@ -8949,7 +9071,7 @@
         <v>81</v>
       </c>
       <c r="F356" s="1" t="s">
-        <v>391</v>
+        <v>375</v>
       </c>
     </row>
     <row r="357" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -8957,10 +9079,10 @@
         <v>376</v>
       </c>
       <c r="B357" t="s">
-        <v>413</v>
+        <v>397</v>
       </c>
       <c r="C357" t="s">
-        <v>377</v>
+        <v>361</v>
       </c>
       <c r="D357">
         <v>3</v>
@@ -8969,7 +9091,7 @@
         <v>81</v>
       </c>
       <c r="F357" s="1" t="s">
-        <v>391</v>
+        <v>375</v>
       </c>
     </row>
     <row r="358" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -8977,10 +9099,10 @@
         <v>377</v>
       </c>
       <c r="B358" t="s">
-        <v>414</v>
+        <v>398</v>
       </c>
       <c r="C358" t="s">
-        <v>203</v>
+        <v>187</v>
       </c>
       <c r="D358">
         <v>3</v>
@@ -8989,7 +9111,7 @@
         <v>81</v>
       </c>
       <c r="F358" s="1" t="s">
-        <v>391</v>
+        <v>375</v>
       </c>
     </row>
     <row r="359" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -8997,10 +9119,10 @@
         <v>378</v>
       </c>
       <c r="B359" t="s">
-        <v>415</v>
+        <v>399</v>
       </c>
       <c r="C359" t="s">
-        <v>205</v>
+        <v>189</v>
       </c>
       <c r="D359">
         <v>3</v>
@@ -9009,7 +9131,7 @@
         <v>81</v>
       </c>
       <c r="F359" s="1" t="s">
-        <v>391</v>
+        <v>375</v>
       </c>
     </row>
     <row r="360" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -9017,10 +9139,10 @@
         <v>379</v>
       </c>
       <c r="B360" t="s">
-        <v>416</v>
+        <v>400</v>
       </c>
       <c r="C360" t="s">
-        <v>212</v>
+        <v>196</v>
       </c>
       <c r="D360">
         <v>3</v>
@@ -9029,7 +9151,7 @@
         <v>81</v>
       </c>
       <c r="F360" s="1" t="s">
-        <v>391</v>
+        <v>375</v>
       </c>
     </row>
     <row r="361" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -9037,10 +9159,10 @@
         <v>380</v>
       </c>
       <c r="B361" t="s">
-        <v>417</v>
+        <v>401</v>
       </c>
       <c r="C361" t="s">
-        <v>209</v>
+        <v>193</v>
       </c>
       <c r="D361">
         <v>3</v>
@@ -9049,7 +9171,7 @@
         <v>81</v>
       </c>
       <c r="F361" s="1" t="s">
-        <v>391</v>
+        <v>375</v>
       </c>
     </row>
     <row r="362" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -9057,10 +9179,10 @@
         <v>381</v>
       </c>
       <c r="B362" t="s">
-        <v>418</v>
+        <v>402</v>
       </c>
       <c r="C362" t="s">
-        <v>212</v>
+        <v>196</v>
       </c>
       <c r="D362">
         <v>3</v>
@@ -9069,7 +9191,7 @@
         <v>81</v>
       </c>
       <c r="F362" s="1" t="s">
-        <v>391</v>
+        <v>375</v>
       </c>
     </row>
     <row r="363" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -9077,10 +9199,10 @@
         <v>382</v>
       </c>
       <c r="B363" t="s">
-        <v>419</v>
+        <v>403</v>
       </c>
       <c r="C363" t="s">
-        <v>329</v>
+        <v>313</v>
       </c>
       <c r="D363">
         <v>3</v>
@@ -9089,7 +9211,7 @@
         <v>81</v>
       </c>
       <c r="F363" s="1" t="s">
-        <v>391</v>
+        <v>375</v>
       </c>
     </row>
     <row r="364" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -9097,10 +9219,10 @@
         <v>383</v>
       </c>
       <c r="B364" t="s">
-        <v>420</v>
+        <v>404</v>
       </c>
       <c r="C364" t="s">
-        <v>212</v>
+        <v>196</v>
       </c>
       <c r="D364">
         <v>3</v>
@@ -9109,7 +9231,7 @@
         <v>81</v>
       </c>
       <c r="F364" s="1" t="s">
-        <v>391</v>
+        <v>375</v>
       </c>
     </row>
     <row r="365" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -9117,10 +9239,10 @@
         <v>384</v>
       </c>
       <c r="B365" t="s">
-        <v>421</v>
+        <v>405</v>
       </c>
       <c r="C365" t="s">
-        <v>205</v>
+        <v>189</v>
       </c>
       <c r="D365">
         <v>3</v>
@@ -9129,7 +9251,7 @@
         <v>81</v>
       </c>
       <c r="F365" s="1" t="s">
-        <v>391</v>
+        <v>375</v>
       </c>
     </row>
     <row r="366" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -9137,10 +9259,10 @@
         <v>385</v>
       </c>
       <c r="B366" t="s">
-        <v>422</v>
+        <v>406</v>
       </c>
       <c r="C366" t="s">
-        <v>205</v>
+        <v>189</v>
       </c>
       <c r="D366">
         <v>2</v>
@@ -9149,7 +9271,7 @@
         <v>81</v>
       </c>
       <c r="F366" s="1" t="s">
-        <v>391</v>
+        <v>375</v>
       </c>
     </row>
     <row r="367" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -9157,10 +9279,10 @@
         <v>386</v>
       </c>
       <c r="B367" t="s">
-        <v>423</v>
+        <v>407</v>
       </c>
       <c r="C367" t="s">
-        <v>389</v>
+        <v>373</v>
       </c>
       <c r="D367">
         <v>2</v>
@@ -9169,7 +9291,7 @@
         <v>81</v>
       </c>
       <c r="F367" s="1" t="s">
-        <v>391</v>
+        <v>375</v>
       </c>
     </row>
     <row r="368" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -9177,19 +9299,19 @@
         <v>387</v>
       </c>
       <c r="B368" t="s">
-        <v>427</v>
+        <v>411</v>
       </c>
       <c r="C368" t="s">
-        <v>212</v>
+        <v>196</v>
       </c>
       <c r="D368">
         <v>3</v>
       </c>
       <c r="E368" t="s">
-        <v>433</v>
+        <v>417</v>
       </c>
       <c r="F368" s="1" t="s">
-        <v>391</v>
+        <v>375</v>
       </c>
     </row>
     <row r="369" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -9197,19 +9319,19 @@
         <v>388</v>
       </c>
       <c r="B369" t="s">
-        <v>428</v>
+        <v>412</v>
       </c>
       <c r="C369" t="s">
-        <v>231</v>
+        <v>215</v>
       </c>
       <c r="D369">
         <v>3</v>
       </c>
       <c r="E369" t="s">
-        <v>433</v>
+        <v>417</v>
       </c>
       <c r="F369" s="1" t="s">
-        <v>391</v>
+        <v>375</v>
       </c>
     </row>
     <row r="370" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -9217,19 +9339,19 @@
         <v>389</v>
       </c>
       <c r="B370" t="s">
-        <v>429</v>
+        <v>413</v>
       </c>
       <c r="C370" t="s">
-        <v>205</v>
+        <v>189</v>
       </c>
       <c r="D370">
         <v>3</v>
       </c>
       <c r="E370" t="s">
-        <v>433</v>
+        <v>417</v>
       </c>
       <c r="F370" s="1" t="s">
-        <v>391</v>
+        <v>375</v>
       </c>
     </row>
     <row r="371" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -9237,19 +9359,19 @@
         <v>390</v>
       </c>
       <c r="B371" t="s">
-        <v>430</v>
+        <v>414</v>
       </c>
       <c r="C371" t="s">
-        <v>338</v>
+        <v>322</v>
       </c>
       <c r="D371">
         <v>3</v>
       </c>
       <c r="E371" t="s">
-        <v>433</v>
+        <v>417</v>
       </c>
       <c r="F371" s="1" t="s">
-        <v>391</v>
+        <v>375</v>
       </c>
     </row>
     <row r="372" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -9257,19 +9379,19 @@
         <v>391</v>
       </c>
       <c r="B372" t="s">
-        <v>431</v>
+        <v>415</v>
       </c>
       <c r="C372" t="s">
-        <v>209</v>
+        <v>193</v>
       </c>
       <c r="D372">
         <v>3</v>
       </c>
       <c r="E372" t="s">
-        <v>433</v>
+        <v>417</v>
       </c>
       <c r="F372" s="1" t="s">
-        <v>391</v>
+        <v>375</v>
       </c>
     </row>
     <row r="373" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -9277,19 +9399,19 @@
         <v>392</v>
       </c>
       <c r="B373" t="s">
-        <v>432</v>
+        <v>416</v>
       </c>
       <c r="C373" t="s">
-        <v>231</v>
+        <v>215</v>
       </c>
       <c r="D373">
         <v>3</v>
       </c>
       <c r="E373" t="s">
-        <v>433</v>
+        <v>417</v>
       </c>
       <c r="F373" s="1" t="s">
-        <v>391</v>
+        <v>375</v>
       </c>
     </row>
     <row r="374" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -9297,19 +9419,19 @@
         <v>394</v>
       </c>
       <c r="B374" t="s">
-        <v>434</v>
+        <v>418</v>
       </c>
       <c r="C374" t="s">
-        <v>205</v>
+        <v>189</v>
       </c>
       <c r="D374">
         <v>3</v>
       </c>
       <c r="E374" t="s">
-        <v>443</v>
+        <v>427</v>
       </c>
       <c r="F374" s="1" t="s">
-        <v>391</v>
+        <v>375</v>
       </c>
     </row>
     <row r="375" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -9317,19 +9439,19 @@
         <v>395</v>
       </c>
       <c r="B375" t="s">
-        <v>435</v>
+        <v>419</v>
       </c>
       <c r="C375" t="s">
-        <v>212</v>
+        <v>196</v>
       </c>
       <c r="D375">
         <v>3</v>
       </c>
       <c r="E375" t="s">
-        <v>443</v>
+        <v>427</v>
       </c>
       <c r="F375" s="1" t="s">
-        <v>391</v>
+        <v>375</v>
       </c>
     </row>
     <row r="376" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -9337,19 +9459,19 @@
         <v>396</v>
       </c>
       <c r="B376" t="s">
-        <v>436</v>
+        <v>420</v>
       </c>
       <c r="C376" t="s">
-        <v>437</v>
+        <v>421</v>
       </c>
       <c r="D376">
         <v>3</v>
       </c>
       <c r="E376" t="s">
-        <v>443</v>
+        <v>427</v>
       </c>
       <c r="F376" s="1" t="s">
-        <v>391</v>
+        <v>375</v>
       </c>
     </row>
     <row r="377" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -9357,19 +9479,19 @@
         <v>397</v>
       </c>
       <c r="B377" t="s">
-        <v>438</v>
+        <v>422</v>
       </c>
       <c r="C377" t="s">
-        <v>212</v>
+        <v>196</v>
       </c>
       <c r="D377">
         <v>3</v>
       </c>
       <c r="E377" t="s">
-        <v>443</v>
+        <v>427</v>
       </c>
       <c r="F377" s="1" t="s">
-        <v>391</v>
+        <v>375</v>
       </c>
     </row>
     <row r="378" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -9377,19 +9499,19 @@
         <v>398</v>
       </c>
       <c r="B378" t="s">
-        <v>439</v>
+        <v>423</v>
       </c>
       <c r="C378" t="s">
-        <v>216</v>
+        <v>200</v>
       </c>
       <c r="D378">
         <v>3</v>
       </c>
       <c r="E378" t="s">
-        <v>443</v>
+        <v>427</v>
       </c>
       <c r="F378" s="1" t="s">
-        <v>391</v>
+        <v>375</v>
       </c>
     </row>
     <row r="379" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -9397,19 +9519,19 @@
         <v>399</v>
       </c>
       <c r="B379" t="s">
-        <v>440</v>
+        <v>424</v>
       </c>
       <c r="C379" t="s">
-        <v>203</v>
+        <v>187</v>
       </c>
       <c r="D379">
         <v>3</v>
       </c>
       <c r="E379" t="s">
-        <v>443</v>
+        <v>427</v>
       </c>
       <c r="F379" s="1" t="s">
-        <v>391</v>
+        <v>375</v>
       </c>
     </row>
     <row r="380" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -9417,19 +9539,19 @@
         <v>400</v>
       </c>
       <c r="B380" t="s">
-        <v>441</v>
+        <v>425</v>
       </c>
       <c r="C380" t="s">
-        <v>225</v>
+        <v>209</v>
       </c>
       <c r="D380">
         <v>3</v>
       </c>
       <c r="E380" t="s">
-        <v>443</v>
+        <v>427</v>
       </c>
       <c r="F380" s="1" t="s">
-        <v>391</v>
+        <v>375</v>
       </c>
     </row>
     <row r="381" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -9437,19 +9559,19 @@
         <v>401</v>
       </c>
       <c r="B381" t="s">
-        <v>442</v>
+        <v>426</v>
       </c>
       <c r="C381" t="s">
-        <v>377</v>
+        <v>361</v>
       </c>
       <c r="D381">
         <v>3</v>
       </c>
       <c r="E381" t="s">
-        <v>443</v>
+        <v>427</v>
       </c>
       <c r="F381" s="1" t="s">
-        <v>391</v>
+        <v>375</v>
       </c>
     </row>
     <row r="382" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -9457,10 +9579,10 @@
         <v>403</v>
       </c>
       <c r="B382" t="s">
-        <v>444</v>
+        <v>428</v>
       </c>
       <c r="C382" t="s">
-        <v>209</v>
+        <v>193</v>
       </c>
       <c r="D382">
         <v>3</v>
@@ -9469,7 +9591,7 @@
         <v>64</v>
       </c>
       <c r="F382" s="1" t="s">
-        <v>391</v>
+        <v>375</v>
       </c>
     </row>
     <row r="383" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -9477,10 +9599,10 @@
         <v>404</v>
       </c>
       <c r="B383" t="s">
-        <v>445</v>
+        <v>429</v>
       </c>
       <c r="C383" t="s">
-        <v>212</v>
+        <v>196</v>
       </c>
       <c r="D383">
         <v>3</v>
@@ -9489,7 +9611,7 @@
         <v>64</v>
       </c>
       <c r="F383" s="1" t="s">
-        <v>391</v>
+        <v>375</v>
       </c>
     </row>
     <row r="384" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -9497,10 +9619,10 @@
         <v>405</v>
       </c>
       <c r="B384" t="s">
-        <v>446</v>
+        <v>430</v>
       </c>
       <c r="C384" t="s">
-        <v>203</v>
+        <v>187</v>
       </c>
       <c r="D384">
         <v>3</v>
@@ -9509,7 +9631,7 @@
         <v>64</v>
       </c>
       <c r="F384" s="1" t="s">
-        <v>391</v>
+        <v>375</v>
       </c>
     </row>
     <row r="385" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -9517,10 +9639,10 @@
         <v>406</v>
       </c>
       <c r="B385" t="s">
-        <v>447</v>
+        <v>431</v>
       </c>
       <c r="C385" t="s">
-        <v>448</v>
+        <v>432</v>
       </c>
       <c r="D385">
         <v>3</v>
@@ -9529,7 +9651,7 @@
         <v>64</v>
       </c>
       <c r="F385" s="1" t="s">
-        <v>391</v>
+        <v>375</v>
       </c>
     </row>
     <row r="386" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -9537,10 +9659,10 @@
         <v>407</v>
       </c>
       <c r="B386" t="s">
-        <v>449</v>
+        <v>433</v>
       </c>
       <c r="C386" t="s">
-        <v>212</v>
+        <v>196</v>
       </c>
       <c r="D386">
         <v>3</v>
@@ -9549,7 +9671,7 @@
         <v>64</v>
       </c>
       <c r="F386" s="1" t="s">
-        <v>391</v>
+        <v>375</v>
       </c>
     </row>
     <row r="387" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -9557,10 +9679,10 @@
         <v>408</v>
       </c>
       <c r="B387" t="s">
-        <v>450</v>
+        <v>434</v>
       </c>
       <c r="C387" t="s">
-        <v>287</v>
+        <v>271</v>
       </c>
       <c r="D387">
         <v>3</v>
@@ -9569,7 +9691,7 @@
         <v>64</v>
       </c>
       <c r="F387" s="1" t="s">
-        <v>391</v>
+        <v>375</v>
       </c>
     </row>
     <row r="388" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -9577,10 +9699,10 @@
         <v>409</v>
       </c>
       <c r="B388" t="s">
-        <v>451</v>
+        <v>435</v>
       </c>
       <c r="C388" t="s">
-        <v>203</v>
+        <v>187</v>
       </c>
       <c r="D388">
         <v>3</v>
@@ -9589,7 +9711,7 @@
         <v>64</v>
       </c>
       <c r="F388" s="1" t="s">
-        <v>391</v>
+        <v>375</v>
       </c>
     </row>
     <row r="389" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -9597,10 +9719,10 @@
         <v>410</v>
       </c>
       <c r="B389" t="s">
-        <v>452</v>
+        <v>436</v>
       </c>
       <c r="C389" t="s">
-        <v>377</v>
+        <v>361</v>
       </c>
       <c r="D389">
         <v>3</v>
@@ -9609,7 +9731,7 @@
         <v>64</v>
       </c>
       <c r="F389" s="1" t="s">
-        <v>391</v>
+        <v>375</v>
       </c>
     </row>
     <row r="390" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -9617,10 +9739,10 @@
         <v>411</v>
       </c>
       <c r="B390" t="s">
-        <v>453</v>
+        <v>437</v>
       </c>
       <c r="C390" t="s">
-        <v>329</v>
+        <v>313</v>
       </c>
       <c r="D390">
         <v>3</v>
@@ -9629,7 +9751,7 @@
         <v>64</v>
       </c>
       <c r="F390" s="1" t="s">
-        <v>391</v>
+        <v>375</v>
       </c>
     </row>
     <row r="391" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -9637,10 +9759,10 @@
         <v>412</v>
       </c>
       <c r="B391" t="s">
-        <v>454</v>
+        <v>438</v>
       </c>
       <c r="C391" t="s">
-        <v>377</v>
+        <v>361</v>
       </c>
       <c r="D391">
         <v>3</v>
@@ -9649,7 +9771,7 @@
         <v>64</v>
       </c>
       <c r="F391" s="1" t="s">
-        <v>391</v>
+        <v>375</v>
       </c>
     </row>
     <row r="392" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -9657,10 +9779,10 @@
         <v>413</v>
       </c>
       <c r="B392" t="s">
-        <v>455</v>
+        <v>439</v>
       </c>
       <c r="C392" t="s">
-        <v>225</v>
+        <v>209</v>
       </c>
       <c r="D392">
         <v>3</v>
@@ -9669,7 +9791,7 @@
         <v>64</v>
       </c>
       <c r="F392" s="1" t="s">
-        <v>391</v>
+        <v>375</v>
       </c>
     </row>
     <row r="393" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -9677,10 +9799,10 @@
         <v>414</v>
       </c>
       <c r="B393" t="s">
-        <v>456</v>
+        <v>440</v>
       </c>
       <c r="C393" t="s">
-        <v>218</v>
+        <v>202</v>
       </c>
       <c r="D393">
         <v>3</v>
@@ -9689,7 +9811,7 @@
         <v>64</v>
       </c>
       <c r="F393" s="1" t="s">
-        <v>391</v>
+        <v>375</v>
       </c>
     </row>
     <row r="394" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -9697,10 +9819,10 @@
         <v>415</v>
       </c>
       <c r="B394" t="s">
-        <v>457</v>
+        <v>441</v>
       </c>
       <c r="C394" t="s">
-        <v>329</v>
+        <v>313</v>
       </c>
       <c r="D394">
         <v>3</v>
@@ -9709,7 +9831,7 @@
         <v>64</v>
       </c>
       <c r="F394" s="1" t="s">
-        <v>391</v>
+        <v>375</v>
       </c>
     </row>
     <row r="395" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -9717,10 +9839,10 @@
         <v>416</v>
       </c>
       <c r="B395" t="s">
-        <v>458</v>
+        <v>442</v>
       </c>
       <c r="C395" t="s">
-        <v>231</v>
+        <v>215</v>
       </c>
       <c r="D395">
         <v>3</v>
@@ -9729,7 +9851,7 @@
         <v>64</v>
       </c>
       <c r="F395" s="1" t="s">
-        <v>391</v>
+        <v>375</v>
       </c>
     </row>
     <row r="396" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -9737,10 +9859,10 @@
         <v>417</v>
       </c>
       <c r="B396" t="s">
-        <v>459</v>
+        <v>443</v>
       </c>
       <c r="C396" t="s">
-        <v>225</v>
+        <v>209</v>
       </c>
       <c r="D396">
         <v>3</v>
@@ -9749,7 +9871,7 @@
         <v>64</v>
       </c>
       <c r="F396" s="1" t="s">
-        <v>391</v>
+        <v>375</v>
       </c>
     </row>
     <row r="397" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -9757,10 +9879,10 @@
         <v>418</v>
       </c>
       <c r="B397" t="s">
-        <v>460</v>
+        <v>444</v>
       </c>
       <c r="C397" t="s">
-        <v>203</v>
+        <v>187</v>
       </c>
       <c r="D397">
         <v>3</v>
@@ -9769,7 +9891,7 @@
         <v>64</v>
       </c>
       <c r="F397" s="1" t="s">
-        <v>391</v>
+        <v>375</v>
       </c>
     </row>
     <row r="398" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -9777,10 +9899,10 @@
         <v>419</v>
       </c>
       <c r="B398" t="s">
-        <v>461</v>
+        <v>445</v>
       </c>
       <c r="C398" t="s">
-        <v>212</v>
+        <v>196</v>
       </c>
       <c r="D398">
         <v>3</v>
@@ -9789,7 +9911,7 @@
         <v>64</v>
       </c>
       <c r="F398" s="1" t="s">
-        <v>391</v>
+        <v>375</v>
       </c>
     </row>
     <row r="399" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -9797,10 +9919,10 @@
         <v>421</v>
       </c>
       <c r="B399" t="s">
-        <v>462</v>
+        <v>446</v>
       </c>
       <c r="C399" t="s">
-        <v>231</v>
+        <v>215</v>
       </c>
       <c r="D399">
         <v>3</v>
@@ -9809,7 +9931,7 @@
         <v>28</v>
       </c>
       <c r="F399" s="1" t="s">
-        <v>473</v>
+        <v>457</v>
       </c>
     </row>
     <row r="400" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -9817,10 +9939,10 @@
         <v>422</v>
       </c>
       <c r="B400" t="s">
-        <v>463</v>
+        <v>447</v>
       </c>
       <c r="C400" t="s">
-        <v>212</v>
+        <v>196</v>
       </c>
       <c r="D400">
         <v>3</v>
@@ -9829,7 +9951,7 @@
         <v>28</v>
       </c>
       <c r="F400" s="1" t="s">
-        <v>391</v>
+        <v>375</v>
       </c>
     </row>
     <row r="401" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -9837,10 +9959,10 @@
         <v>423</v>
       </c>
       <c r="B401" t="s">
-        <v>464</v>
+        <v>448</v>
       </c>
       <c r="C401" t="s">
-        <v>207</v>
+        <v>191</v>
       </c>
       <c r="D401">
         <v>3</v>
@@ -9849,7 +9971,7 @@
         <v>28</v>
       </c>
       <c r="F401" s="1" t="s">
-        <v>391</v>
+        <v>375</v>
       </c>
     </row>
     <row r="402" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -9857,10 +9979,10 @@
         <v>424</v>
       </c>
       <c r="B402" t="s">
-        <v>465</v>
+        <v>449</v>
       </c>
       <c r="C402" t="s">
-        <v>323</v>
+        <v>307</v>
       </c>
       <c r="D402">
         <v>3</v>
@@ -9869,7 +9991,7 @@
         <v>28</v>
       </c>
       <c r="F402" s="1" t="s">
-        <v>391</v>
+        <v>375</v>
       </c>
     </row>
     <row r="403" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -9877,10 +9999,10 @@
         <v>425</v>
       </c>
       <c r="B403" t="s">
-        <v>466</v>
+        <v>450</v>
       </c>
       <c r="C403" t="s">
-        <v>209</v>
+        <v>193</v>
       </c>
       <c r="D403">
         <v>3</v>
@@ -9889,7 +10011,7 @@
         <v>28</v>
       </c>
       <c r="F403" s="1" t="s">
-        <v>391</v>
+        <v>375</v>
       </c>
     </row>
     <row r="404" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -9897,10 +10019,10 @@
         <v>426</v>
       </c>
       <c r="B404" t="s">
-        <v>467</v>
+        <v>451</v>
       </c>
       <c r="C404" t="s">
-        <v>468</v>
+        <v>452</v>
       </c>
       <c r="D404">
         <v>3</v>
@@ -9909,7 +10031,7 @@
         <v>28</v>
       </c>
       <c r="F404" s="1" t="s">
-        <v>391</v>
+        <v>375</v>
       </c>
     </row>
     <row r="405" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -9917,10 +10039,10 @@
         <v>427</v>
       </c>
       <c r="B405" t="s">
-        <v>469</v>
+        <v>453</v>
       </c>
       <c r="C405" t="s">
-        <v>212</v>
+        <v>196</v>
       </c>
       <c r="D405">
         <v>3</v>
@@ -9929,7 +10051,7 @@
         <v>28</v>
       </c>
       <c r="F405" s="1" t="s">
-        <v>391</v>
+        <v>375</v>
       </c>
     </row>
     <row r="406" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -9937,10 +10059,10 @@
         <v>428</v>
       </c>
       <c r="B406" t="s">
-        <v>332</v>
+        <v>316</v>
       </c>
       <c r="C406" t="s">
-        <v>338</v>
+        <v>322</v>
       </c>
       <c r="D406">
         <v>3</v>
@@ -9949,7 +10071,7 @@
         <v>28</v>
       </c>
       <c r="F406" s="1" t="s">
-        <v>391</v>
+        <v>375</v>
       </c>
     </row>
     <row r="407" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -9957,10 +10079,10 @@
         <v>429</v>
       </c>
       <c r="B407" t="s">
-        <v>470</v>
+        <v>454</v>
       </c>
       <c r="C407" t="s">
-        <v>323</v>
+        <v>307</v>
       </c>
       <c r="D407">
         <v>3</v>
@@ -9969,7 +10091,7 @@
         <v>28</v>
       </c>
       <c r="F407" s="1" t="s">
-        <v>391</v>
+        <v>375</v>
       </c>
     </row>
     <row r="408" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -9977,10 +10099,10 @@
         <v>430</v>
       </c>
       <c r="B408" t="s">
-        <v>326</v>
+        <v>310</v>
       </c>
       <c r="C408" t="s">
-        <v>225</v>
+        <v>209</v>
       </c>
       <c r="D408">
         <v>3</v>
@@ -9989,7 +10111,7 @@
         <v>28</v>
       </c>
       <c r="F408" s="1" t="s">
-        <v>391</v>
+        <v>375</v>
       </c>
     </row>
     <row r="409" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -9997,10 +10119,10 @@
         <v>431</v>
       </c>
       <c r="B409" t="s">
-        <v>471</v>
+        <v>455</v>
       </c>
       <c r="C409" t="s">
-        <v>323</v>
+        <v>307</v>
       </c>
       <c r="D409">
         <v>3</v>
@@ -10009,7 +10131,7 @@
         <v>28</v>
       </c>
       <c r="F409" s="1" t="s">
-        <v>391</v>
+        <v>375</v>
       </c>
     </row>
     <row r="410" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -10017,10 +10139,10 @@
         <v>432</v>
       </c>
       <c r="B410" t="s">
-        <v>472</v>
+        <v>456</v>
       </c>
       <c r="C410" t="s">
-        <v>205</v>
+        <v>189</v>
       </c>
       <c r="D410">
         <v>3</v>
@@ -10029,7 +10151,7 @@
         <v>28</v>
       </c>
       <c r="F410" s="1" t="s">
-        <v>391</v>
+        <v>375</v>
       </c>
     </row>
     <row r="411" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -10037,10 +10159,10 @@
         <v>434</v>
       </c>
       <c r="B411" t="s">
-        <v>474</v>
+        <v>458</v>
       </c>
       <c r="C411" t="s">
-        <v>338</v>
+        <v>322</v>
       </c>
       <c r="D411">
         <v>3</v>
@@ -10057,10 +10179,10 @@
         <v>435</v>
       </c>
       <c r="B412" t="s">
-        <v>475</v>
+        <v>459</v>
       </c>
       <c r="C412" t="s">
-        <v>212</v>
+        <v>196</v>
       </c>
       <c r="D412">
         <v>3</v>
@@ -10077,10 +10199,10 @@
         <v>436</v>
       </c>
       <c r="B413" t="s">
-        <v>476</v>
+        <v>460</v>
       </c>
       <c r="C413" t="s">
-        <v>468</v>
+        <v>452</v>
       </c>
       <c r="D413">
         <v>3</v>
@@ -10097,10 +10219,10 @@
         <v>437</v>
       </c>
       <c r="B414" t="s">
-        <v>477</v>
+        <v>461</v>
       </c>
       <c r="C414" t="s">
-        <v>209</v>
+        <v>193</v>
       </c>
       <c r="D414">
         <v>3</v>
@@ -10117,10 +10239,10 @@
         <v>438</v>
       </c>
       <c r="B415" t="s">
-        <v>478</v>
+        <v>462</v>
       </c>
       <c r="C415" t="s">
-        <v>479</v>
+        <v>463</v>
       </c>
       <c r="D415">
         <v>3</v>
@@ -10137,10 +10259,10 @@
         <v>439</v>
       </c>
       <c r="B416" t="s">
-        <v>480</v>
+        <v>464</v>
       </c>
       <c r="C416" t="s">
-        <v>258</v>
+        <v>242</v>
       </c>
       <c r="D416">
         <v>3</v>
@@ -10149,7 +10271,7 @@
         <v>13</v>
       </c>
       <c r="F416" s="1" t="s">
-        <v>391</v>
+        <v>375</v>
       </c>
     </row>
     <row r="417" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -10157,10 +10279,10 @@
         <v>440</v>
       </c>
       <c r="B417" t="s">
-        <v>481</v>
+        <v>465</v>
       </c>
       <c r="C417" t="s">
-        <v>203</v>
+        <v>187</v>
       </c>
       <c r="D417">
         <v>3</v>
@@ -10169,7 +10291,7 @@
         <v>13</v>
       </c>
       <c r="F417" s="1" t="s">
-        <v>391</v>
+        <v>375</v>
       </c>
     </row>
     <row r="418" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -10177,10 +10299,10 @@
         <v>441</v>
       </c>
       <c r="B418" t="s">
-        <v>482</v>
+        <v>466</v>
       </c>
       <c r="C418" t="s">
-        <v>212</v>
+        <v>196</v>
       </c>
       <c r="D418">
         <v>3</v>
@@ -10189,7 +10311,7 @@
         <v>13</v>
       </c>
       <c r="F418" s="1" t="s">
-        <v>391</v>
+        <v>375</v>
       </c>
     </row>
     <row r="419" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -10197,10 +10319,10 @@
         <v>442</v>
       </c>
       <c r="B419" t="s">
-        <v>483</v>
+        <v>467</v>
       </c>
       <c r="C419" t="s">
-        <v>225</v>
+        <v>209</v>
       </c>
       <c r="D419">
         <v>3</v>
@@ -10209,7 +10331,7 @@
         <v>13</v>
       </c>
       <c r="F419" s="1" t="s">
-        <v>391</v>
+        <v>375</v>
       </c>
     </row>
     <row r="420" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -10217,10 +10339,10 @@
         <v>443</v>
       </c>
       <c r="B420" t="s">
-        <v>484</v>
+        <v>468</v>
       </c>
       <c r="C420" t="s">
-        <v>203</v>
+        <v>187</v>
       </c>
       <c r="D420">
         <v>3</v>
@@ -10229,7 +10351,7 @@
         <v>13</v>
       </c>
       <c r="F420" s="1" t="s">
-        <v>391</v>
+        <v>375</v>
       </c>
     </row>
     <row r="421" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -10237,10 +10359,10 @@
         <v>444</v>
       </c>
       <c r="B421" t="s">
-        <v>485</v>
+        <v>469</v>
       </c>
       <c r="C421" t="s">
-        <v>205</v>
+        <v>189</v>
       </c>
       <c r="D421">
         <v>3</v>
@@ -10249,7 +10371,7 @@
         <v>13</v>
       </c>
       <c r="F421" s="1" t="s">
-        <v>391</v>
+        <v>375</v>
       </c>
     </row>
     <row r="422" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -10257,10 +10379,10 @@
         <v>445</v>
       </c>
       <c r="B422" t="s">
-        <v>486</v>
+        <v>470</v>
       </c>
       <c r="C422" t="s">
-        <v>373</v>
+        <v>357</v>
       </c>
       <c r="D422">
         <v>3</v>
@@ -10269,7 +10391,7 @@
         <v>13</v>
       </c>
       <c r="F422" s="1" t="s">
-        <v>391</v>
+        <v>375</v>
       </c>
     </row>
     <row r="423" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -10277,10 +10399,10 @@
         <v>446</v>
       </c>
       <c r="B423" t="s">
-        <v>487</v>
+        <v>471</v>
       </c>
       <c r="C423" t="s">
-        <v>212</v>
+        <v>196</v>
       </c>
       <c r="D423">
         <v>3</v>
@@ -10289,7 +10411,7 @@
         <v>13</v>
       </c>
       <c r="F423" s="1" t="s">
-        <v>391</v>
+        <v>375</v>
       </c>
     </row>
     <row r="424" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -10297,10 +10419,10 @@
         <v>447</v>
       </c>
       <c r="B424" t="s">
-        <v>488</v>
+        <v>472</v>
       </c>
       <c r="C424" t="s">
-        <v>225</v>
+        <v>209</v>
       </c>
       <c r="D424">
         <v>3</v>
@@ -10309,7 +10431,7 @@
         <v>13</v>
       </c>
       <c r="F424" s="1" t="s">
-        <v>391</v>
+        <v>375</v>
       </c>
     </row>
     <row r="425" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -10317,10 +10439,10 @@
         <v>448</v>
       </c>
       <c r="B425" t="s">
-        <v>489</v>
+        <v>473</v>
       </c>
       <c r="C425" t="s">
-        <v>212</v>
+        <v>196</v>
       </c>
       <c r="D425">
         <v>3</v>
@@ -10329,7 +10451,7 @@
         <v>13</v>
       </c>
       <c r="F425" s="1" t="s">
-        <v>391</v>
+        <v>375</v>
       </c>
     </row>
     <row r="426" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -10337,10 +10459,10 @@
         <v>449</v>
       </c>
       <c r="B426" t="s">
-        <v>490</v>
+        <v>474</v>
       </c>
       <c r="C426" t="s">
-        <v>203</v>
+        <v>187</v>
       </c>
       <c r="D426">
         <v>3</v>
@@ -10349,7 +10471,7 @@
         <v>13</v>
       </c>
       <c r="F426" s="1" t="s">
-        <v>391</v>
+        <v>375</v>
       </c>
     </row>
     <row r="427" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -10357,10 +10479,10 @@
         <v>450</v>
       </c>
       <c r="B427" t="s">
-        <v>491</v>
+        <v>475</v>
       </c>
       <c r="C427" t="s">
-        <v>338</v>
+        <v>322</v>
       </c>
       <c r="D427">
         <v>3</v>
@@ -10369,7 +10491,7 @@
         <v>13</v>
       </c>
       <c r="F427" s="1" t="s">
-        <v>391</v>
+        <v>375</v>
       </c>
     </row>
     <row r="428" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -10377,10 +10499,10 @@
         <v>451</v>
       </c>
       <c r="B428" t="s">
-        <v>492</v>
+        <v>476</v>
       </c>
       <c r="C428" t="s">
-        <v>231</v>
+        <v>215</v>
       </c>
       <c r="D428">
         <v>3</v>
@@ -10389,7 +10511,7 @@
         <v>13</v>
       </c>
       <c r="F428" s="1" t="s">
-        <v>391</v>
+        <v>375</v>
       </c>
     </row>
     <row r="429" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -10397,10 +10519,10 @@
         <v>452</v>
       </c>
       <c r="B429" t="s">
-        <v>493</v>
+        <v>477</v>
       </c>
       <c r="C429" t="s">
-        <v>231</v>
+        <v>215</v>
       </c>
       <c r="D429">
         <v>3</v>
@@ -10409,7 +10531,7 @@
         <v>13</v>
       </c>
       <c r="F429" s="1" t="s">
-        <v>391</v>
+        <v>375</v>
       </c>
     </row>
     <row r="430" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -10417,10 +10539,10 @@
         <v>453</v>
       </c>
       <c r="B430" t="s">
-        <v>494</v>
+        <v>478</v>
       </c>
       <c r="C430" t="s">
-        <v>212</v>
+        <v>196</v>
       </c>
       <c r="D430">
         <v>3</v>
@@ -10429,7 +10551,7 @@
         <v>13</v>
       </c>
       <c r="F430" s="1" t="s">
-        <v>391</v>
+        <v>375</v>
       </c>
     </row>
     <row r="431" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -10437,10 +10559,10 @@
         <v>454</v>
       </c>
       <c r="B431" t="s">
-        <v>495</v>
+        <v>479</v>
       </c>
       <c r="C431" t="s">
-        <v>205</v>
+        <v>189</v>
       </c>
       <c r="D431">
         <v>3</v>
@@ -10449,7 +10571,7 @@
         <v>13</v>
       </c>
       <c r="F431" s="1" t="s">
-        <v>391</v>
+        <v>375</v>
       </c>
     </row>
     <row r="432" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -10457,10 +10579,10 @@
         <v>455</v>
       </c>
       <c r="B432" t="s">
-        <v>496</v>
+        <v>480</v>
       </c>
       <c r="C432" t="s">
-        <v>218</v>
+        <v>202</v>
       </c>
       <c r="D432">
         <v>3</v>
@@ -10469,7 +10591,7 @@
         <v>13</v>
       </c>
       <c r="F432" s="1" t="s">
-        <v>391</v>
+        <v>375</v>
       </c>
     </row>
     <row r="433" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -10477,10 +10599,10 @@
         <v>456</v>
       </c>
       <c r="B433" t="s">
-        <v>497</v>
+        <v>481</v>
       </c>
       <c r="C433" t="s">
-        <v>212</v>
+        <v>196</v>
       </c>
       <c r="D433">
         <v>3</v>
@@ -10489,7 +10611,7 @@
         <v>13</v>
       </c>
       <c r="F433" s="1" t="s">
-        <v>391</v>
+        <v>375</v>
       </c>
     </row>
     <row r="434" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -10497,10 +10619,10 @@
         <v>457</v>
       </c>
       <c r="B434" t="s">
-        <v>498</v>
+        <v>482</v>
       </c>
       <c r="C434" t="s">
-        <v>209</v>
+        <v>193</v>
       </c>
       <c r="D434">
         <v>3</v>
@@ -10509,7 +10631,7 @@
         <v>13</v>
       </c>
       <c r="F434" s="1" t="s">
-        <v>391</v>
+        <v>375</v>
       </c>
     </row>
     <row r="435" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -10517,10 +10639,10 @@
         <v>459</v>
       </c>
       <c r="B435" t="s">
-        <v>499</v>
+        <v>483</v>
       </c>
       <c r="C435" t="s">
-        <v>500</v>
+        <v>484</v>
       </c>
       <c r="D435">
         <v>3</v>
@@ -10537,10 +10659,10 @@
         <v>460</v>
       </c>
       <c r="B436" t="s">
-        <v>501</v>
+        <v>485</v>
       </c>
       <c r="C436" t="s">
-        <v>205</v>
+        <v>189</v>
       </c>
       <c r="D436">
         <v>3</v>
@@ -10557,10 +10679,10 @@
         <v>461</v>
       </c>
       <c r="B437" t="s">
-        <v>502</v>
+        <v>486</v>
       </c>
       <c r="C437" t="s">
-        <v>209</v>
+        <v>193</v>
       </c>
       <c r="D437">
         <v>3</v>
@@ -10577,10 +10699,10 @@
         <v>462</v>
       </c>
       <c r="B438" t="s">
-        <v>503</v>
+        <v>487</v>
       </c>
       <c r="C438" t="s">
-        <v>225</v>
+        <v>209</v>
       </c>
       <c r="D438">
         <v>3</v>
@@ -10597,10 +10719,10 @@
         <v>463</v>
       </c>
       <c r="B439" t="s">
-        <v>504</v>
+        <v>488</v>
       </c>
       <c r="C439" t="s">
-        <v>225</v>
+        <v>209</v>
       </c>
       <c r="D439">
         <v>3</v>
@@ -10617,10 +10739,10 @@
         <v>464</v>
       </c>
       <c r="B440" t="s">
-        <v>181</v>
+        <v>165</v>
       </c>
       <c r="C440" t="s">
-        <v>212</v>
+        <v>196</v>
       </c>
       <c r="D440">
         <v>3</v>
@@ -10637,10 +10759,10 @@
         <v>465</v>
       </c>
       <c r="B441" t="s">
-        <v>505</v>
+        <v>489</v>
       </c>
       <c r="C441" t="s">
-        <v>212</v>
+        <v>196</v>
       </c>
       <c r="D441">
         <v>3</v>
@@ -10657,10 +10779,10 @@
         <v>466</v>
       </c>
       <c r="B442" t="s">
-        <v>180</v>
+        <v>164</v>
       </c>
       <c r="C442" t="s">
-        <v>323</v>
+        <v>307</v>
       </c>
       <c r="D442">
         <v>3</v>
@@ -10677,10 +10799,10 @@
         <v>467</v>
       </c>
       <c r="B443" t="s">
-        <v>506</v>
+        <v>490</v>
       </c>
       <c r="C443" t="s">
-        <v>212</v>
+        <v>196</v>
       </c>
       <c r="D443">
         <v>3</v>
@@ -10697,10 +10819,10 @@
         <v>468</v>
       </c>
       <c r="B444" t="s">
-        <v>507</v>
+        <v>491</v>
       </c>
       <c r="C444" t="s">
-        <v>203</v>
+        <v>187</v>
       </c>
       <c r="D444">
         <v>3</v>
@@ -10709,7 +10831,7 @@
         <v>11</v>
       </c>
       <c r="F444" s="1" t="s">
-        <v>473</v>
+        <v>457</v>
       </c>
     </row>
     <row r="445" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -10717,10 +10839,10 @@
         <v>469</v>
       </c>
       <c r="B445" t="s">
-        <v>508</v>
+        <v>492</v>
       </c>
       <c r="C445" t="s">
-        <v>231</v>
+        <v>215</v>
       </c>
       <c r="D445">
         <v>3</v>
@@ -10729,7 +10851,7 @@
         <v>11</v>
       </c>
       <c r="F445" s="1" t="s">
-        <v>391</v>
+        <v>375</v>
       </c>
     </row>
     <row r="446" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -10737,10 +10859,10 @@
         <v>470</v>
       </c>
       <c r="B446" t="s">
-        <v>509</v>
+        <v>493</v>
       </c>
       <c r="C446" t="s">
-        <v>205</v>
+        <v>189</v>
       </c>
       <c r="D446">
         <v>3</v>
@@ -10749,7 +10871,7 @@
         <v>11</v>
       </c>
       <c r="F446" s="1" t="s">
-        <v>391</v>
+        <v>375</v>
       </c>
     </row>
     <row r="447" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -10757,10 +10879,10 @@
         <v>471</v>
       </c>
       <c r="B447" t="s">
-        <v>510</v>
+        <v>494</v>
       </c>
       <c r="C447" t="s">
-        <v>331</v>
+        <v>315</v>
       </c>
       <c r="D447">
         <v>3</v>
@@ -10769,7 +10891,7 @@
         <v>11</v>
       </c>
       <c r="F447" s="1" t="s">
-        <v>391</v>
+        <v>375</v>
       </c>
     </row>
     <row r="448" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -10777,10 +10899,10 @@
         <v>472</v>
       </c>
       <c r="B448" t="s">
-        <v>511</v>
+        <v>495</v>
       </c>
       <c r="C448" t="s">
-        <v>205</v>
+        <v>189</v>
       </c>
       <c r="D448">
         <v>3</v>
@@ -10789,7 +10911,7 @@
         <v>11</v>
       </c>
       <c r="F448" s="1" t="s">
-        <v>391</v>
+        <v>375</v>
       </c>
     </row>
     <row r="449" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -10797,10 +10919,10 @@
         <v>473</v>
       </c>
       <c r="B449" t="s">
-        <v>512</v>
+        <v>496</v>
       </c>
       <c r="C449" t="s">
-        <v>203</v>
+        <v>187</v>
       </c>
       <c r="D449">
         <v>3</v>
@@ -10809,7 +10931,7 @@
         <v>11</v>
       </c>
       <c r="F449" s="1" t="s">
-        <v>391</v>
+        <v>375</v>
       </c>
     </row>
     <row r="450" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -10817,10 +10939,10 @@
         <v>474</v>
       </c>
       <c r="B450" t="s">
-        <v>513</v>
+        <v>497</v>
       </c>
       <c r="C450" t="s">
-        <v>203</v>
+        <v>187</v>
       </c>
       <c r="D450">
         <v>3</v>
@@ -10829,7 +10951,7 @@
         <v>11</v>
       </c>
       <c r="F450" s="1" t="s">
-        <v>391</v>
+        <v>375</v>
       </c>
     </row>
     <row r="451" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -10837,19 +10959,19 @@
         <v>476</v>
       </c>
       <c r="B451" t="s">
-        <v>514</v>
+        <v>498</v>
       </c>
       <c r="C451" t="s">
-        <v>225</v>
+        <v>209</v>
       </c>
       <c r="D451">
         <v>3</v>
       </c>
       <c r="E451" t="s">
-        <v>515</v>
+        <v>499</v>
       </c>
       <c r="F451" s="1" t="s">
-        <v>391</v>
+        <v>375</v>
       </c>
     </row>
     <row r="452" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -10857,19 +10979,19 @@
         <v>477</v>
       </c>
       <c r="B452" t="s">
-        <v>516</v>
+        <v>500</v>
       </c>
       <c r="C452" t="s">
-        <v>207</v>
+        <v>191</v>
       </c>
       <c r="D452">
         <v>3</v>
       </c>
       <c r="E452" t="s">
-        <v>515</v>
+        <v>499</v>
       </c>
       <c r="F452" s="1" t="s">
-        <v>391</v>
+        <v>375</v>
       </c>
     </row>
     <row r="453" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -10877,19 +10999,19 @@
         <v>478</v>
       </c>
       <c r="B453" t="s">
-        <v>517</v>
+        <v>501</v>
       </c>
       <c r="C453" t="s">
-        <v>212</v>
+        <v>196</v>
       </c>
       <c r="D453">
         <v>3</v>
       </c>
       <c r="E453" t="s">
-        <v>515</v>
+        <v>499</v>
       </c>
       <c r="F453" s="1" t="s">
-        <v>391</v>
+        <v>375</v>
       </c>
     </row>
     <row r="454" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -10897,19 +11019,19 @@
         <v>479</v>
       </c>
       <c r="B454" t="s">
-        <v>518</v>
+        <v>502</v>
       </c>
       <c r="C454" t="s">
-        <v>231</v>
+        <v>215</v>
       </c>
       <c r="D454">
         <v>3</v>
       </c>
       <c r="E454" t="s">
-        <v>515</v>
+        <v>499</v>
       </c>
       <c r="F454" s="1" t="s">
-        <v>391</v>
+        <v>375</v>
       </c>
     </row>
     <row r="455" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -10917,19 +11039,19 @@
         <v>480</v>
       </c>
       <c r="B455" t="s">
-        <v>519</v>
+        <v>503</v>
       </c>
       <c r="C455" t="s">
-        <v>225</v>
+        <v>209</v>
       </c>
       <c r="D455">
         <v>3</v>
       </c>
       <c r="E455" t="s">
-        <v>515</v>
+        <v>499</v>
       </c>
       <c r="F455" s="1" t="s">
-        <v>391</v>
+        <v>375</v>
       </c>
     </row>
     <row r="456" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -10937,10 +11059,10 @@
         <v>482</v>
       </c>
       <c r="B456" t="s">
-        <v>520</v>
+        <v>504</v>
       </c>
       <c r="C456" t="s">
-        <v>479</v>
+        <v>463</v>
       </c>
       <c r="D456">
         <v>3</v>
@@ -10957,10 +11079,10 @@
         <v>483</v>
       </c>
       <c r="B457" t="s">
-        <v>521</v>
+        <v>505</v>
       </c>
       <c r="C457" t="s">
-        <v>225</v>
+        <v>209</v>
       </c>
       <c r="D457">
         <v>3</v>
@@ -10977,10 +11099,10 @@
         <v>484</v>
       </c>
       <c r="B458" t="s">
-        <v>522</v>
+        <v>506</v>
       </c>
       <c r="C458" t="s">
-        <v>209</v>
+        <v>193</v>
       </c>
       <c r="D458">
         <v>3</v>
@@ -10989,7 +11111,7 @@
         <v>16</v>
       </c>
       <c r="F458" s="1" t="s">
-        <v>391</v>
+        <v>375</v>
       </c>
     </row>
     <row r="459" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -10997,10 +11119,10 @@
         <v>485</v>
       </c>
       <c r="B459" t="s">
-        <v>523</v>
+        <v>507</v>
       </c>
       <c r="C459" t="s">
-        <v>212</v>
+        <v>196</v>
       </c>
       <c r="D459">
         <v>3</v>
@@ -11009,7 +11131,7 @@
         <v>16</v>
       </c>
       <c r="F459" s="1" t="s">
-        <v>391</v>
+        <v>375</v>
       </c>
     </row>
     <row r="460" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -11017,10 +11139,10 @@
         <v>486</v>
       </c>
       <c r="B460" t="s">
-        <v>524</v>
+        <v>508</v>
       </c>
       <c r="C460" t="s">
-        <v>225</v>
+        <v>209</v>
       </c>
       <c r="D460">
         <v>3</v>
@@ -11029,7 +11151,7 @@
         <v>16</v>
       </c>
       <c r="F460" s="1" t="s">
-        <v>391</v>
+        <v>375</v>
       </c>
     </row>
     <row r="461" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -11037,10 +11159,10 @@
         <v>487</v>
       </c>
       <c r="B461" t="s">
-        <v>525</v>
+        <v>509</v>
       </c>
       <c r="C461" t="s">
-        <v>205</v>
+        <v>189</v>
       </c>
       <c r="D461">
         <v>3</v>
@@ -11049,7 +11171,7 @@
         <v>16</v>
       </c>
       <c r="F461" s="1" t="s">
-        <v>391</v>
+        <v>375</v>
       </c>
     </row>
     <row r="462" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -11057,10 +11179,10 @@
         <v>488</v>
       </c>
       <c r="B462" t="s">
-        <v>526</v>
+        <v>510</v>
       </c>
       <c r="C462" t="s">
-        <v>203</v>
+        <v>187</v>
       </c>
       <c r="D462">
         <v>3</v>
@@ -11069,7 +11191,7 @@
         <v>16</v>
       </c>
       <c r="F462" s="1" t="s">
-        <v>391</v>
+        <v>375</v>
       </c>
     </row>
     <row r="463" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -11077,10 +11199,10 @@
         <v>489</v>
       </c>
       <c r="B463" t="s">
-        <v>527</v>
+        <v>511</v>
       </c>
       <c r="C463" t="s">
-        <v>231</v>
+        <v>215</v>
       </c>
       <c r="D463">
         <v>3</v>
@@ -11089,7 +11211,7 @@
         <v>16</v>
       </c>
       <c r="F463" s="1" t="s">
-        <v>391</v>
+        <v>375</v>
       </c>
     </row>
     <row r="464" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -11097,10 +11219,10 @@
         <v>490</v>
       </c>
       <c r="B464" t="s">
-        <v>528</v>
+        <v>512</v>
       </c>
       <c r="C464" t="s">
-        <v>231</v>
+        <v>215</v>
       </c>
       <c r="D464">
         <v>3</v>
@@ -11109,7 +11231,7 @@
         <v>16</v>
       </c>
       <c r="F464" s="1" t="s">
-        <v>391</v>
+        <v>375</v>
       </c>
     </row>
     <row r="465" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -11117,10 +11239,10 @@
         <v>492</v>
       </c>
       <c r="B465" t="s">
-        <v>529</v>
+        <v>513</v>
       </c>
       <c r="C465" t="s">
-        <v>479</v>
+        <v>463</v>
       </c>
       <c r="D465">
         <v>3</v>
@@ -11137,10 +11259,10 @@
         <v>493</v>
       </c>
       <c r="B466" t="s">
-        <v>530</v>
+        <v>514</v>
       </c>
       <c r="C466" t="s">
-        <v>205</v>
+        <v>189</v>
       </c>
       <c r="D466">
         <v>3</v>
@@ -11149,7 +11271,7 @@
         <v>7</v>
       </c>
       <c r="F466" s="1" t="s">
-        <v>391</v>
+        <v>375</v>
       </c>
     </row>
     <row r="467" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -11157,10 +11279,10 @@
         <v>495</v>
       </c>
       <c r="B467" t="s">
-        <v>531</v>
+        <v>515</v>
       </c>
       <c r="C467" t="s">
-        <v>231</v>
+        <v>215</v>
       </c>
       <c r="D467">
         <v>3</v>
@@ -11177,10 +11299,10 @@
         <v>496</v>
       </c>
       <c r="B468" t="s">
-        <v>532</v>
+        <v>516</v>
       </c>
       <c r="C468" t="s">
-        <v>205</v>
+        <v>189</v>
       </c>
       <c r="D468">
         <v>3</v>
@@ -11189,7 +11311,7 @@
         <v>8</v>
       </c>
       <c r="F468" s="1" t="s">
-        <v>391</v>
+        <v>375</v>
       </c>
     </row>
     <row r="469" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -11197,19 +11319,19 @@
         <v>498</v>
       </c>
       <c r="B469" t="s">
-        <v>533</v>
+        <v>517</v>
       </c>
       <c r="C469" t="s">
-        <v>205</v>
+        <v>189</v>
       </c>
       <c r="D469">
         <v>3</v>
       </c>
       <c r="E469" t="s">
-        <v>534</v>
+        <v>518</v>
       </c>
       <c r="F469" s="1" t="s">
-        <v>391</v>
+        <v>375</v>
       </c>
     </row>
     <row r="470" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -11217,19 +11339,19 @@
         <v>499</v>
       </c>
       <c r="B470" t="s">
-        <v>535</v>
+        <v>519</v>
       </c>
       <c r="C470" t="s">
-        <v>338</v>
+        <v>322</v>
       </c>
       <c r="D470">
         <v>3</v>
       </c>
       <c r="E470" t="s">
-        <v>534</v>
+        <v>518</v>
       </c>
       <c r="F470" s="1" t="s">
-        <v>391</v>
+        <v>375</v>
       </c>
     </row>
     <row r="471" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -11237,19 +11359,19 @@
         <v>500</v>
       </c>
       <c r="B471" t="s">
-        <v>536</v>
+        <v>520</v>
       </c>
       <c r="C471" t="s">
-        <v>212</v>
+        <v>196</v>
       </c>
       <c r="D471">
         <v>3</v>
       </c>
       <c r="E471" t="s">
-        <v>534</v>
+        <v>518</v>
       </c>
       <c r="F471" s="1" t="s">
-        <v>391</v>
+        <v>375</v>
       </c>
     </row>
     <row r="472" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -11257,19 +11379,19 @@
         <v>501</v>
       </c>
       <c r="B472" t="s">
-        <v>537</v>
+        <v>521</v>
       </c>
       <c r="C472" t="s">
-        <v>225</v>
+        <v>209</v>
       </c>
       <c r="D472">
         <v>3</v>
       </c>
       <c r="E472" t="s">
-        <v>534</v>
+        <v>518</v>
       </c>
       <c r="F472" s="1" t="s">
-        <v>391</v>
+        <v>375</v>
       </c>
     </row>
     <row r="473" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -11277,16 +11399,16 @@
         <v>503</v>
       </c>
       <c r="B473" t="s">
-        <v>538</v>
+        <v>522</v>
       </c>
       <c r="C473" t="s">
-        <v>212</v>
+        <v>196</v>
       </c>
       <c r="D473">
         <v>3</v>
       </c>
       <c r="E473" t="s">
-        <v>539</v>
+        <v>523</v>
       </c>
       <c r="F473" s="1" t="s">
         <v>62</v>
@@ -11297,16 +11419,16 @@
         <v>504</v>
       </c>
       <c r="B474" t="s">
-        <v>540</v>
+        <v>524</v>
       </c>
       <c r="C474" t="s">
-        <v>479</v>
+        <v>463</v>
       </c>
       <c r="D474">
         <v>3</v>
       </c>
       <c r="E474" t="s">
-        <v>539</v>
+        <v>523</v>
       </c>
       <c r="F474" s="1" t="s">
         <v>62</v>
@@ -11317,19 +11439,19 @@
         <v>505</v>
       </c>
       <c r="B475" t="s">
-        <v>541</v>
+        <v>525</v>
       </c>
       <c r="C475" t="s">
-        <v>543</v>
+        <v>527</v>
       </c>
       <c r="D475">
         <v>3</v>
       </c>
       <c r="E475" t="s">
-        <v>542</v>
+        <v>526</v>
       </c>
       <c r="F475" t="s">
-        <v>544</v>
+        <v>528</v>
       </c>
     </row>
     <row r="476" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -11337,19 +11459,19 @@
         <v>506</v>
       </c>
       <c r="B476" t="s">
-        <v>545</v>
+        <v>529</v>
       </c>
       <c r="C476" t="s">
-        <v>546</v>
+        <v>530</v>
       </c>
       <c r="D476">
         <v>3</v>
       </c>
       <c r="E476" t="s">
-        <v>542</v>
+        <v>526</v>
       </c>
       <c r="F476" t="s">
-        <v>544</v>
+        <v>528</v>
       </c>
     </row>
     <row r="477" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -11357,19 +11479,19 @@
         <v>507</v>
       </c>
       <c r="B477" t="s">
-        <v>547</v>
+        <v>531</v>
       </c>
       <c r="C477" t="s">
-        <v>548</v>
+        <v>532</v>
       </c>
       <c r="D477">
         <v>3</v>
       </c>
       <c r="E477" t="s">
-        <v>542</v>
+        <v>526</v>
       </c>
       <c r="F477" t="s">
-        <v>544</v>
+        <v>528</v>
       </c>
     </row>
     <row r="478" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -11377,19 +11499,19 @@
         <v>508</v>
       </c>
       <c r="B478" t="s">
-        <v>549</v>
+        <v>533</v>
       </c>
       <c r="C478" t="s">
-        <v>550</v>
+        <v>534</v>
       </c>
       <c r="D478">
         <v>3</v>
       </c>
       <c r="E478" t="s">
-        <v>542</v>
+        <v>526</v>
       </c>
       <c r="F478" t="s">
-        <v>544</v>
+        <v>528</v>
       </c>
     </row>
     <row r="479" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -11397,19 +11519,19 @@
         <v>509</v>
       </c>
       <c r="B479" t="s">
-        <v>551</v>
+        <v>535</v>
       </c>
       <c r="C479" t="s">
-        <v>548</v>
+        <v>532</v>
       </c>
       <c r="D479">
         <v>2</v>
       </c>
       <c r="E479" t="s">
-        <v>542</v>
+        <v>526</v>
       </c>
       <c r="F479" t="s">
-        <v>544</v>
+        <v>528</v>
       </c>
     </row>
     <row r="480" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -11417,19 +11539,19 @@
         <v>510</v>
       </c>
       <c r="B480" t="s">
-        <v>552</v>
+        <v>536</v>
       </c>
       <c r="C480" t="s">
-        <v>553</v>
+        <v>537</v>
       </c>
       <c r="D480">
         <v>2</v>
       </c>
       <c r="E480" t="s">
-        <v>542</v>
+        <v>526</v>
       </c>
       <c r="F480" t="s">
-        <v>544</v>
+        <v>528</v>
       </c>
     </row>
     <row r="481" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -11437,19 +11559,19 @@
         <v>511</v>
       </c>
       <c r="B481" t="s">
-        <v>554</v>
+        <v>538</v>
       </c>
       <c r="C481" t="s">
-        <v>548</v>
+        <v>532</v>
       </c>
       <c r="D481">
         <v>2</v>
       </c>
       <c r="E481" t="s">
-        <v>542</v>
+        <v>526</v>
       </c>
       <c r="F481" t="s">
-        <v>544</v>
+        <v>528</v>
       </c>
     </row>
     <row r="482" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -11457,19 +11579,19 @@
         <v>512</v>
       </c>
       <c r="B482" t="s">
-        <v>555</v>
+        <v>539</v>
       </c>
       <c r="C482" t="s">
-        <v>543</v>
+        <v>527</v>
       </c>
       <c r="D482">
         <v>2</v>
       </c>
       <c r="E482" t="s">
-        <v>542</v>
+        <v>526</v>
       </c>
       <c r="F482" t="s">
-        <v>544</v>
+        <v>528</v>
       </c>
     </row>
     <row r="483" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -11477,19 +11599,19 @@
         <v>513</v>
       </c>
       <c r="B483" t="s">
-        <v>556</v>
+        <v>540</v>
       </c>
       <c r="C483" t="s">
-        <v>548</v>
+        <v>532</v>
       </c>
       <c r="D483">
         <v>2</v>
       </c>
       <c r="E483" t="s">
-        <v>542</v>
+        <v>526</v>
       </c>
       <c r="F483" t="s">
-        <v>544</v>
+        <v>528</v>
       </c>
     </row>
     <row r="484" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -11497,19 +11619,19 @@
         <v>514</v>
       </c>
       <c r="B484" t="s">
-        <v>557</v>
+        <v>541</v>
       </c>
       <c r="C484" t="s">
-        <v>550</v>
+        <v>534</v>
       </c>
       <c r="D484">
         <v>2</v>
       </c>
       <c r="E484" t="s">
-        <v>542</v>
+        <v>526</v>
       </c>
       <c r="F484" t="s">
-        <v>544</v>
+        <v>528</v>
       </c>
     </row>
     <row r="485" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -11517,19 +11639,19 @@
         <v>515</v>
       </c>
       <c r="B485" t="s">
-        <v>558</v>
+        <v>542</v>
       </c>
       <c r="C485" t="s">
-        <v>543</v>
+        <v>527</v>
       </c>
       <c r="D485">
         <v>1</v>
       </c>
       <c r="E485" t="s">
-        <v>542</v>
+        <v>526</v>
       </c>
       <c r="F485" t="s">
-        <v>544</v>
+        <v>528</v>
       </c>
     </row>
     <row r="486" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -11537,19 +11659,19 @@
         <v>516</v>
       </c>
       <c r="B486" t="s">
-        <v>559</v>
+        <v>543</v>
       </c>
       <c r="C486" t="s">
-        <v>548</v>
+        <v>532</v>
       </c>
       <c r="D486">
         <v>1</v>
       </c>
       <c r="E486" t="s">
-        <v>542</v>
+        <v>526</v>
       </c>
       <c r="F486" t="s">
-        <v>544</v>
+        <v>528</v>
       </c>
     </row>
     <row r="487" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -11557,19 +11679,19 @@
         <v>517</v>
       </c>
       <c r="B487" t="s">
-        <v>560</v>
+        <v>544</v>
       </c>
       <c r="C487" t="s">
-        <v>550</v>
+        <v>534</v>
       </c>
       <c r="D487">
         <v>1</v>
       </c>
       <c r="E487" t="s">
-        <v>542</v>
+        <v>526</v>
       </c>
       <c r="F487" t="s">
-        <v>544</v>
+        <v>528</v>
       </c>
     </row>
     <row r="488" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -11863,21 +11985,21 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
-        <v>424</v>
+        <v>408</v>
       </c>
       <c r="B1" t="s">
-        <v>425</v>
+        <v>409</v>
       </c>
       <c r="C1" t="s">
-        <v>426</v>
+        <v>410</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>427</v>
+        <v>411</v>
       </c>
       <c r="B2" t="s">
-        <v>212</v>
+        <v>196</v>
       </c>
       <c r="C2">
         <v>3</v>
@@ -11885,10 +12007,10 @@
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>428</v>
+        <v>412</v>
       </c>
       <c r="B3" t="s">
-        <v>231</v>
+        <v>215</v>
       </c>
       <c r="C3">
         <v>3</v>
@@ -11896,10 +12018,10 @@
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>429</v>
+        <v>413</v>
       </c>
       <c r="B4" t="s">
-        <v>205</v>
+        <v>189</v>
       </c>
       <c r="C4">
         <v>3</v>
@@ -11907,10 +12029,10 @@
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>430</v>
+        <v>414</v>
       </c>
       <c r="B5" t="s">
-        <v>338</v>
+        <v>322</v>
       </c>
       <c r="C5">
         <v>3</v>
@@ -11918,10 +12040,10 @@
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>431</v>
+        <v>415</v>
       </c>
       <c r="B6" t="s">
-        <v>209</v>
+        <v>193</v>
       </c>
       <c r="C6">
         <v>3</v>
@@ -11929,10 +12051,10 @@
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>432</v>
+        <v>416</v>
       </c>
       <c r="B7" t="s">
-        <v>231</v>
+        <v>215</v>
       </c>
       <c r="C7">
         <v>3</v>

--- a/data_item.xlsx
+++ b/data_item.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\PEJUANG RUPIAH\Desktop\check-item-bot\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2636D168-7501-4FF7-A203-760F1F09B0EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FB58D2E7-9936-466D-BA49-1D056E96CD1C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -17,7 +17,7 @@
     <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$B$1:$F$540</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$B$1:$F$532</definedName>
   </definedNames>
   <calcPr calcId="191028"/>
 </workbook>
@@ -273,7 +273,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1853" uniqueCount="570">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1821" uniqueCount="566">
   <si>
     <t>type</t>
   </si>
@@ -1022,22 +1022,10 @@
     <t>SET-65 (533 mm)</t>
   </si>
   <si>
-    <t>A244 SLWT (324 mm)</t>
-  </si>
-  <si>
     <t>Yu-7 (324 mm)</t>
   </si>
   <si>
-    <t>Type-12 (533 mm)</t>
-  </si>
-  <si>
-    <t>Black Shark (533 mm)</t>
-  </si>
-  <si>
     <t>UGST Physic (533 mm)</t>
-  </si>
-  <si>
-    <t>Varunastra (533 mm)</t>
   </si>
   <si>
     <t>Mark-48 (533 mm)</t>
@@ -2341,7 +2329,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:F540"/>
+  <dimension ref="A1:F532"/>
   <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="4" hidden="1" customWidth="1"/>
@@ -2352,7 +2340,7 @@
   <sheetData>
     <row r="1" spans="1:6" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
-        <v>318</v>
+        <v>314</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>163</v>
@@ -2598,7 +2586,7 @@
         <v>135</v>
       </c>
       <c r="C13" t="s">
-        <v>322</v>
+        <v>318</v>
       </c>
       <c r="D13" s="12">
         <v>3</v>
@@ -2618,7 +2606,7 @@
         <v>141</v>
       </c>
       <c r="C14" t="s">
-        <v>322</v>
+        <v>318</v>
       </c>
       <c r="D14" s="12">
         <v>3</v>
@@ -2638,7 +2626,7 @@
         <v>148</v>
       </c>
       <c r="C15" t="s">
-        <v>322</v>
+        <v>318</v>
       </c>
       <c r="D15" s="12">
         <v>3</v>
@@ -2698,7 +2686,7 @@
         <v>67</v>
       </c>
       <c r="C18" t="s">
-        <v>534</v>
+        <v>530</v>
       </c>
       <c r="D18" s="1">
         <v>3</v>
@@ -2718,7 +2706,7 @@
         <v>184</v>
       </c>
       <c r="C19" t="s">
-        <v>545</v>
+        <v>541</v>
       </c>
       <c r="D19" s="1">
         <v>3</v>
@@ -2738,7 +2726,7 @@
         <v>183</v>
       </c>
       <c r="C20" t="s">
-        <v>527</v>
+        <v>523</v>
       </c>
       <c r="D20" s="12">
         <v>3</v>
@@ -2755,10 +2743,10 @@
         <v>21</v>
       </c>
       <c r="B21" s="7" t="s">
-        <v>547</v>
+        <v>543</v>
       </c>
       <c r="C21" t="s">
-        <v>546</v>
+        <v>542</v>
       </c>
       <c r="D21" s="12">
         <v>3</v>
@@ -2778,7 +2766,7 @@
         <v>185</v>
       </c>
       <c r="C22" t="s">
-        <v>546</v>
+        <v>542</v>
       </c>
       <c r="D22" s="12">
         <v>3</v>
@@ -2798,7 +2786,7 @@
         <v>9</v>
       </c>
       <c r="C23" t="s">
-        <v>527</v>
+        <v>523</v>
       </c>
       <c r="D23" s="1">
         <v>3</v>
@@ -2818,7 +2806,7 @@
         <v>12</v>
       </c>
       <c r="C24" t="s">
-        <v>548</v>
+        <v>544</v>
       </c>
       <c r="D24" s="1">
         <v>3</v>
@@ -2838,7 +2826,7 @@
         <v>14</v>
       </c>
       <c r="C25" t="s">
-        <v>534</v>
+        <v>530</v>
       </c>
       <c r="D25" s="1">
         <v>3</v>
@@ -2858,7 +2846,7 @@
         <v>15</v>
       </c>
       <c r="C26" t="s">
-        <v>549</v>
+        <v>545</v>
       </c>
       <c r="D26" s="1">
         <v>3</v>
@@ -2878,7 +2866,7 @@
         <v>17</v>
       </c>
       <c r="C27" t="s">
-        <v>532</v>
+        <v>528</v>
       </c>
       <c r="D27" s="1">
         <v>3</v>
@@ -2898,7 +2886,7 @@
         <v>18</v>
       </c>
       <c r="C28" t="s">
-        <v>527</v>
+        <v>523</v>
       </c>
       <c r="D28" s="1">
         <v>3</v>
@@ -2938,7 +2926,7 @@
         <v>20</v>
       </c>
       <c r="C30" t="s">
-        <v>545</v>
+        <v>541</v>
       </c>
       <c r="D30" s="1">
         <v>3</v>
@@ -2958,7 +2946,7 @@
         <v>21</v>
       </c>
       <c r="C31" t="s">
-        <v>550</v>
+        <v>546</v>
       </c>
       <c r="D31" s="1">
         <v>3</v>
@@ -2978,7 +2966,7 @@
         <v>22</v>
       </c>
       <c r="C32" t="s">
-        <v>551</v>
+        <v>547</v>
       </c>
       <c r="D32" s="1">
         <v>3</v>
@@ -2998,7 +2986,7 @@
         <v>44</v>
       </c>
       <c r="C33" t="s">
-        <v>545</v>
+        <v>541</v>
       </c>
       <c r="D33" s="1">
         <v>3</v>
@@ -3018,7 +3006,7 @@
         <v>51</v>
       </c>
       <c r="C34" t="s">
-        <v>532</v>
+        <v>528</v>
       </c>
       <c r="D34" s="1">
         <v>3</v>
@@ -3058,7 +3046,7 @@
         <v>155</v>
       </c>
       <c r="C36" t="s">
-        <v>527</v>
+        <v>523</v>
       </c>
       <c r="D36" s="12">
         <v>3</v>
@@ -3095,10 +3083,10 @@
         <v>38</v>
       </c>
       <c r="B38" t="s">
-        <v>552</v>
+        <v>548</v>
       </c>
       <c r="C38" t="s">
-        <v>553</v>
+        <v>549</v>
       </c>
       <c r="D38" s="1">
         <v>3</v>
@@ -3115,10 +3103,10 @@
         <v>39</v>
       </c>
       <c r="B39" t="s">
-        <v>554</v>
+        <v>550</v>
       </c>
       <c r="C39" t="s">
-        <v>534</v>
+        <v>530</v>
       </c>
       <c r="D39" s="1">
         <v>3</v>
@@ -3135,10 +3123,10 @@
         <v>40</v>
       </c>
       <c r="B40" t="s">
-        <v>555</v>
+        <v>551</v>
       </c>
       <c r="C40" t="s">
-        <v>530</v>
+        <v>526</v>
       </c>
       <c r="D40" s="1">
         <v>3</v>
@@ -3155,10 +3143,10 @@
         <v>41</v>
       </c>
       <c r="B41" t="s">
-        <v>556</v>
+        <v>552</v>
       </c>
       <c r="C41" t="s">
-        <v>527</v>
+        <v>523</v>
       </c>
       <c r="D41" s="1">
         <v>3</v>
@@ -3175,10 +3163,10 @@
         <v>42</v>
       </c>
       <c r="B42" t="s">
-        <v>557</v>
+        <v>553</v>
       </c>
       <c r="C42" t="s">
-        <v>532</v>
+        <v>528</v>
       </c>
       <c r="D42" s="1">
         <v>3</v>
@@ -3195,10 +3183,10 @@
         <v>43</v>
       </c>
       <c r="B43" t="s">
-        <v>558</v>
+        <v>554</v>
       </c>
       <c r="C43" t="s">
-        <v>548</v>
+        <v>544</v>
       </c>
       <c r="D43" s="1">
         <v>3</v>
@@ -3215,10 +3203,10 @@
         <v>44</v>
       </c>
       <c r="B44" t="s">
-        <v>559</v>
+        <v>555</v>
       </c>
       <c r="C44" t="s">
-        <v>532</v>
+        <v>528</v>
       </c>
       <c r="D44" s="1">
         <v>3</v>
@@ -3235,7 +3223,7 @@
         <v>45</v>
       </c>
       <c r="B45" t="s">
-        <v>560</v>
+        <v>556</v>
       </c>
       <c r="C45" t="s">
         <v>6</v>
@@ -3255,10 +3243,10 @@
         <v>46</v>
       </c>
       <c r="B46" t="s">
-        <v>561</v>
+        <v>557</v>
       </c>
       <c r="C46" t="s">
-        <v>562</v>
+        <v>558</v>
       </c>
       <c r="D46" s="1">
         <v>3</v>
@@ -3275,10 +3263,10 @@
         <v>47</v>
       </c>
       <c r="B47" t="s">
-        <v>563</v>
+        <v>559</v>
       </c>
       <c r="C47" t="s">
-        <v>534</v>
+        <v>530</v>
       </c>
       <c r="D47" s="12">
         <v>3</v>
@@ -3295,10 +3283,10 @@
         <v>48</v>
       </c>
       <c r="B48" t="s">
-        <v>564</v>
+        <v>560</v>
       </c>
       <c r="C48" t="s">
-        <v>565</v>
+        <v>561</v>
       </c>
       <c r="D48" s="12">
         <v>3</v>
@@ -3315,10 +3303,10 @@
         <v>49</v>
       </c>
       <c r="B49" t="s">
-        <v>566</v>
+        <v>562</v>
       </c>
       <c r="C49" t="s">
-        <v>534</v>
+        <v>530</v>
       </c>
       <c r="D49" s="12">
         <v>3</v>
@@ -3335,10 +3323,10 @@
         <v>50</v>
       </c>
       <c r="B50" t="s">
-        <v>567</v>
+        <v>563</v>
       </c>
       <c r="C50" t="s">
-        <v>532</v>
+        <v>528</v>
       </c>
       <c r="D50" s="12">
         <v>3</v>
@@ -3355,10 +3343,10 @@
         <v>51</v>
       </c>
       <c r="B51" t="s">
-        <v>568</v>
+        <v>564</v>
       </c>
       <c r="C51" t="s">
-        <v>532</v>
+        <v>528</v>
       </c>
       <c r="D51" s="12">
         <v>3</v>
@@ -3375,10 +3363,10 @@
         <v>52</v>
       </c>
       <c r="B52" t="s">
-        <v>569</v>
+        <v>565</v>
       </c>
       <c r="C52" t="s">
-        <v>527</v>
+        <v>523</v>
       </c>
       <c r="D52" s="12">
         <v>3</v>
@@ -6376,16 +6364,16 @@
     </row>
     <row r="219" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A219">
-        <v>238</v>
+        <v>246</v>
       </c>
       <c r="B219" t="s">
-        <v>249</v>
+        <v>253</v>
       </c>
       <c r="C219" t="s">
-        <v>202</v>
+        <v>254</v>
       </c>
       <c r="D219">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E219" s="3" t="s">
         <v>70</v>
@@ -6396,16 +6384,16 @@
     </row>
     <row r="220" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A220">
-        <v>239</v>
+        <v>247</v>
       </c>
       <c r="B220" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="C220" t="s">
         <v>196</v>
       </c>
       <c r="D220">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E220" s="3" t="s">
         <v>70</v>
@@ -6416,16 +6404,16 @@
     </row>
     <row r="221" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A221">
-        <v>240</v>
+        <v>248</v>
       </c>
       <c r="B221" t="s">
-        <v>251</v>
+        <v>255</v>
       </c>
       <c r="C221" t="s">
         <v>209</v>
       </c>
       <c r="D221">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E221" s="3" t="s">
         <v>70</v>
@@ -6436,16 +6424,16 @@
     </row>
     <row r="222" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A222">
-        <v>241</v>
+        <v>249</v>
       </c>
       <c r="B222" t="s">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="C222" t="s">
         <v>202</v>
       </c>
       <c r="D222">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E222" s="3" t="s">
         <v>70</v>
@@ -6456,16 +6444,16 @@
     </row>
     <row r="223" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A223">
-        <v>242</v>
+        <v>250</v>
       </c>
       <c r="B223" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="C223" t="s">
         <v>189</v>
       </c>
       <c r="D223">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E223" s="3" t="s">
         <v>70</v>
@@ -6476,16 +6464,16 @@
     </row>
     <row r="224" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A224">
-        <v>243</v>
+        <v>251</v>
       </c>
       <c r="B224" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="C224" t="s">
-        <v>191</v>
+        <v>202</v>
       </c>
       <c r="D224">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E224" s="3" t="s">
         <v>70</v>
@@ -6496,16 +6484,16 @@
     </row>
     <row r="225" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A225">
-        <v>244</v>
+        <v>252</v>
       </c>
       <c r="B225" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="C225" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="D225">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E225" s="3" t="s">
         <v>70</v>
@@ -6516,16 +6504,16 @@
     </row>
     <row r="226" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A226">
-        <v>245</v>
+        <v>253</v>
       </c>
       <c r="B226" t="s">
-        <v>256</v>
+        <v>251</v>
       </c>
       <c r="C226" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="D226">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E226" s="3" t="s">
         <v>70</v>
@@ -6536,13 +6524,13 @@
     </row>
     <row r="227" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A227">
-        <v>246</v>
+        <v>254</v>
       </c>
       <c r="B227" t="s">
-        <v>257</v>
+        <v>252</v>
       </c>
       <c r="C227" t="s">
-        <v>258</v>
+        <v>189</v>
       </c>
       <c r="D227">
         <v>3</v>
@@ -6556,30 +6544,30 @@
     </row>
     <row r="228" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A228">
-        <v>247</v>
+        <v>255</v>
       </c>
       <c r="B228" t="s">
-        <v>250</v>
+        <v>259</v>
       </c>
       <c r="C228" t="s">
-        <v>196</v>
+        <v>209</v>
       </c>
       <c r="D228">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E228" s="3" t="s">
         <v>70</v>
       </c>
       <c r="F228" s="1" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
     <row r="229" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A229">
-        <v>248</v>
+        <v>256</v>
       </c>
       <c r="B229" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="C229" t="s">
         <v>209</v>
@@ -6591,24 +6579,24 @@
         <v>70</v>
       </c>
       <c r="F229" s="1" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
     <row r="230" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A230">
-        <v>249</v>
+        <v>257</v>
       </c>
       <c r="B230" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="C230" t="s">
-        <v>202</v>
+        <v>215</v>
       </c>
       <c r="D230">
         <v>3</v>
       </c>
-      <c r="E230" s="3" t="s">
-        <v>70</v>
+      <c r="E230" s="11" t="s">
+        <v>68</v>
       </c>
       <c r="F230" s="1" t="s">
         <v>182</v>
@@ -6616,19 +6604,19 @@
     </row>
     <row r="231" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A231">
-        <v>250</v>
+        <v>258</v>
       </c>
       <c r="B231" t="s">
-        <v>253</v>
+        <v>262</v>
       </c>
       <c r="C231" t="s">
-        <v>189</v>
+        <v>196</v>
       </c>
       <c r="D231">
         <v>3</v>
       </c>
-      <c r="E231" s="3" t="s">
-        <v>70</v>
+      <c r="E231" s="11" t="s">
+        <v>68</v>
       </c>
       <c r="F231" s="1" t="s">
         <v>182</v>
@@ -6636,19 +6624,19 @@
     </row>
     <row r="232" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A232">
-        <v>251</v>
+        <v>259</v>
       </c>
       <c r="B232" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="C232" t="s">
-        <v>202</v>
+        <v>189</v>
       </c>
       <c r="D232">
         <v>3</v>
       </c>
-      <c r="E232" s="3" t="s">
-        <v>70</v>
+      <c r="E232" s="11" t="s">
+        <v>68</v>
       </c>
       <c r="F232" s="1" t="s">
         <v>182</v>
@@ -6656,19 +6644,19 @@
     </row>
     <row r="233" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A233">
-        <v>252</v>
+        <v>260</v>
       </c>
       <c r="B233" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="C233" t="s">
-        <v>191</v>
+        <v>202</v>
       </c>
       <c r="D233">
         <v>3</v>
       </c>
-      <c r="E233" s="3" t="s">
-        <v>70</v>
+      <c r="E233" s="11" t="s">
+        <v>68</v>
       </c>
       <c r="F233" s="1" t="s">
         <v>182</v>
@@ -6676,10 +6664,10 @@
     </row>
     <row r="234" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A234">
-        <v>253</v>
+        <v>261</v>
       </c>
       <c r="B234" t="s">
-        <v>255</v>
+        <v>265</v>
       </c>
       <c r="C234" t="s">
         <v>187</v>
@@ -6687,8 +6675,8 @@
       <c r="D234">
         <v>3</v>
       </c>
-      <c r="E234" s="3" t="s">
-        <v>70</v>
+      <c r="E234" s="11" t="s">
+        <v>68</v>
       </c>
       <c r="F234" s="1" t="s">
         <v>182</v>
@@ -6696,19 +6684,19 @@
     </row>
     <row r="235" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A235">
-        <v>254</v>
+        <v>262</v>
       </c>
       <c r="B235" t="s">
-        <v>256</v>
+        <v>266</v>
       </c>
       <c r="C235" t="s">
-        <v>189</v>
+        <v>267</v>
       </c>
       <c r="D235">
         <v>3</v>
       </c>
-      <c r="E235" s="3" t="s">
-        <v>70</v>
+      <c r="E235" s="11" t="s">
+        <v>68</v>
       </c>
       <c r="F235" s="1" t="s">
         <v>182</v>
@@ -6716,56 +6704,56 @@
     </row>
     <row r="236" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A236">
-        <v>255</v>
+        <v>263</v>
       </c>
       <c r="B236" t="s">
-        <v>263</v>
+        <v>268</v>
       </c>
       <c r="C236" t="s">
-        <v>209</v>
+        <v>189</v>
       </c>
       <c r="D236">
         <v>2</v>
       </c>
-      <c r="E236" s="3" t="s">
-        <v>70</v>
+      <c r="E236" s="11" t="s">
+        <v>68</v>
       </c>
       <c r="F236" s="1" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
     </row>
     <row r="237" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A237">
-        <v>256</v>
+        <v>264</v>
       </c>
       <c r="B237" t="s">
-        <v>264</v>
+        <v>269</v>
       </c>
       <c r="C237" t="s">
-        <v>209</v>
+        <v>187</v>
       </c>
       <c r="D237">
-        <v>3</v>
-      </c>
-      <c r="E237" s="3" t="s">
-        <v>70</v>
+        <v>2</v>
+      </c>
+      <c r="E237" s="11" t="s">
+        <v>68</v>
       </c>
       <c r="F237" s="1" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
     </row>
     <row r="238" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A238">
-        <v>257</v>
+        <v>265</v>
       </c>
       <c r="B238" t="s">
-        <v>265</v>
+        <v>270</v>
       </c>
       <c r="C238" t="s">
-        <v>215</v>
+        <v>267</v>
       </c>
       <c r="D238">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E238" s="11" t="s">
         <v>68</v>
@@ -6776,16 +6764,16 @@
     </row>
     <row r="239" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A239">
-        <v>258</v>
+        <v>266</v>
       </c>
       <c r="B239" t="s">
-        <v>266</v>
+        <v>271</v>
       </c>
       <c r="C239" t="s">
-        <v>196</v>
+        <v>200</v>
       </c>
       <c r="D239">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E239" s="11" t="s">
         <v>68</v>
@@ -6796,16 +6784,16 @@
     </row>
     <row r="240" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A240">
-        <v>259</v>
+        <v>267</v>
       </c>
       <c r="B240" t="s">
-        <v>267</v>
+        <v>272</v>
       </c>
       <c r="C240" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="D240">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E240" s="11" t="s">
         <v>68</v>
@@ -6816,13 +6804,13 @@
     </row>
     <row r="241" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A241">
-        <v>260</v>
+        <v>268</v>
       </c>
       <c r="B241" t="s">
-        <v>268</v>
+        <v>273</v>
       </c>
       <c r="C241" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="D241">
         <v>3</v>
@@ -6831,44 +6819,44 @@
         <v>68</v>
       </c>
       <c r="F241" s="1" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
     <row r="242" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A242">
-        <v>261</v>
+        <v>269</v>
       </c>
       <c r="B242" t="s">
-        <v>269</v>
+        <v>274</v>
       </c>
       <c r="C242" t="s">
-        <v>187</v>
+        <v>275</v>
       </c>
       <c r="D242">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E242" s="11" t="s">
         <v>68</v>
       </c>
       <c r="F242" s="1" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
     <row r="243" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A243">
-        <v>262</v>
+        <v>270</v>
       </c>
       <c r="B243" t="s">
-        <v>270</v>
+        <v>276</v>
       </c>
       <c r="C243" t="s">
-        <v>271</v>
+        <v>189</v>
       </c>
       <c r="D243">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E243" s="11" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="F243" s="1" t="s">
         <v>182</v>
@@ -6876,19 +6864,19 @@
     </row>
     <row r="244" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A244">
-        <v>263</v>
+        <v>271</v>
       </c>
       <c r="B244" t="s">
-        <v>272</v>
+        <v>277</v>
       </c>
       <c r="C244" t="s">
-        <v>189</v>
+        <v>196</v>
       </c>
       <c r="D244">
         <v>2</v>
       </c>
       <c r="E244" s="11" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="F244" s="1" t="s">
         <v>182</v>
@@ -6896,19 +6884,19 @@
     </row>
     <row r="245" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A245">
-        <v>264</v>
+        <v>272</v>
       </c>
       <c r="B245" t="s">
-        <v>273</v>
+        <v>278</v>
       </c>
       <c r="C245" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="D245">
         <v>2</v>
       </c>
       <c r="E245" s="11" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="F245" s="1" t="s">
         <v>182</v>
@@ -6916,19 +6904,19 @@
     </row>
     <row r="246" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A246">
-        <v>265</v>
+        <v>273</v>
       </c>
       <c r="B246" t="s">
-        <v>274</v>
+        <v>279</v>
       </c>
       <c r="C246" t="s">
-        <v>271</v>
+        <v>187</v>
       </c>
       <c r="D246">
         <v>2</v>
       </c>
       <c r="E246" s="11" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="F246" s="1" t="s">
         <v>182</v>
@@ -6936,19 +6924,19 @@
     </row>
     <row r="247" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A247">
-        <v>266</v>
+        <v>274</v>
       </c>
       <c r="B247" t="s">
-        <v>275</v>
+        <v>280</v>
       </c>
       <c r="C247" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="D247">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E247" s="11" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="F247" s="1" t="s">
         <v>182</v>
@@ -6956,19 +6944,19 @@
     </row>
     <row r="248" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A248">
-        <v>267</v>
+        <v>275</v>
       </c>
       <c r="B248" t="s">
-        <v>276</v>
+        <v>281</v>
       </c>
       <c r="C248" t="s">
         <v>187</v>
       </c>
       <c r="D248">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E248" s="11" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="F248" s="1" t="s">
         <v>182</v>
@@ -6976,56 +6964,56 @@
     </row>
     <row r="249" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A249">
-        <v>268</v>
+        <v>276</v>
       </c>
       <c r="B249" t="s">
-        <v>277</v>
+        <v>282</v>
       </c>
       <c r="C249" t="s">
-        <v>200</v>
+        <v>187</v>
       </c>
       <c r="D249">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E249" s="11" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="F249" s="1" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
     </row>
     <row r="250" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A250">
-        <v>269</v>
+        <v>277</v>
       </c>
       <c r="B250" t="s">
-        <v>278</v>
+        <v>283</v>
       </c>
       <c r="C250" t="s">
-        <v>279</v>
+        <v>189</v>
       </c>
       <c r="D250">
         <v>2</v>
       </c>
       <c r="E250" s="11" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="F250" s="1" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
     </row>
     <row r="251" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A251">
-        <v>270</v>
+        <v>278</v>
       </c>
       <c r="B251" t="s">
-        <v>280</v>
+        <v>284</v>
       </c>
       <c r="C251" t="s">
         <v>189</v>
       </c>
       <c r="D251">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E251" s="11" t="s">
         <v>64</v>
@@ -7036,10 +7024,10 @@
     </row>
     <row r="252" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A252">
-        <v>271</v>
+        <v>279</v>
       </c>
       <c r="B252" t="s">
-        <v>281</v>
+        <v>285</v>
       </c>
       <c r="C252" t="s">
         <v>196</v>
@@ -7056,10 +7044,10 @@
     </row>
     <row r="253" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A253">
-        <v>272</v>
+        <v>280</v>
       </c>
       <c r="B253" t="s">
-        <v>282</v>
+        <v>286</v>
       </c>
       <c r="C253" t="s">
         <v>189</v>
@@ -7076,13 +7064,13 @@
     </row>
     <row r="254" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A254">
-        <v>273</v>
+        <v>281</v>
       </c>
       <c r="B254" t="s">
-        <v>283</v>
+        <v>287</v>
       </c>
       <c r="C254" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="D254">
         <v>2</v>
@@ -7096,16 +7084,16 @@
     </row>
     <row r="255" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A255">
-        <v>274</v>
+        <v>282</v>
       </c>
       <c r="B255" t="s">
-        <v>284</v>
+        <v>288</v>
       </c>
       <c r="C255" t="s">
-        <v>202</v>
+        <v>189</v>
       </c>
       <c r="D255">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E255" s="11" t="s">
         <v>64</v>
@@ -7116,16 +7104,16 @@
     </row>
     <row r="256" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A256">
-        <v>275</v>
+        <v>283</v>
       </c>
       <c r="B256" t="s">
-        <v>285</v>
+        <v>289</v>
       </c>
       <c r="C256" t="s">
-        <v>187</v>
+        <v>215</v>
       </c>
       <c r="D256">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E256" s="11" t="s">
         <v>64</v>
@@ -7136,16 +7124,16 @@
     </row>
     <row r="257" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A257">
-        <v>276</v>
+        <v>284</v>
       </c>
       <c r="B257" t="s">
-        <v>286</v>
+        <v>290</v>
       </c>
       <c r="C257" t="s">
-        <v>187</v>
+        <v>196</v>
       </c>
       <c r="D257">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E257" s="11" t="s">
         <v>64</v>
@@ -7156,16 +7144,16 @@
     </row>
     <row r="258" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A258">
-        <v>277</v>
+        <v>285</v>
       </c>
       <c r="B258" t="s">
-        <v>287</v>
+        <v>291</v>
       </c>
       <c r="C258" t="s">
         <v>189</v>
       </c>
       <c r="D258">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E258" s="11" t="s">
         <v>64</v>
@@ -7176,36 +7164,36 @@
     </row>
     <row r="259" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A259">
-        <v>278</v>
+        <v>286</v>
       </c>
       <c r="B259" t="s">
-        <v>288</v>
+        <v>292</v>
       </c>
       <c r="C259" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="D259">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E259" s="11" t="s">
         <v>64</v>
       </c>
       <c r="F259" s="1" t="s">
-        <v>182</v>
+        <v>169</v>
       </c>
     </row>
     <row r="260" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A260">
-        <v>279</v>
+        <v>287</v>
       </c>
       <c r="B260" t="s">
-        <v>289</v>
+        <v>293</v>
       </c>
       <c r="C260" t="s">
-        <v>196</v>
+        <v>189</v>
       </c>
       <c r="D260">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E260" s="11" t="s">
         <v>64</v>
@@ -7216,16 +7204,16 @@
     </row>
     <row r="261" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A261">
-        <v>280</v>
+        <v>288</v>
       </c>
       <c r="B261" t="s">
-        <v>290</v>
+        <v>294</v>
       </c>
       <c r="C261" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="D261">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E261" s="11" t="s">
         <v>64</v>
@@ -7236,16 +7224,16 @@
     </row>
     <row r="262" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A262">
-        <v>281</v>
+        <v>289</v>
       </c>
       <c r="B262" t="s">
-        <v>291</v>
+        <v>295</v>
       </c>
       <c r="C262" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="D262">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E262" s="11" t="s">
         <v>64</v>
@@ -7256,13 +7244,13 @@
     </row>
     <row r="263" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A263">
-        <v>282</v>
+        <v>290</v>
       </c>
       <c r="B263" t="s">
-        <v>292</v>
+        <v>296</v>
       </c>
       <c r="C263" t="s">
-        <v>189</v>
+        <v>196</v>
       </c>
       <c r="D263">
         <v>3</v>
@@ -7276,13 +7264,13 @@
     </row>
     <row r="264" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A264">
-        <v>283</v>
+        <v>291</v>
       </c>
       <c r="B264" t="s">
-        <v>293</v>
+        <v>297</v>
       </c>
       <c r="C264" t="s">
-        <v>215</v>
+        <v>196</v>
       </c>
       <c r="D264">
         <v>3</v>
@@ -7296,13 +7284,13 @@
     </row>
     <row r="265" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A265">
-        <v>284</v>
+        <v>292</v>
       </c>
       <c r="B265" t="s">
-        <v>294</v>
+        <v>298</v>
       </c>
       <c r="C265" t="s">
-        <v>196</v>
+        <v>189</v>
       </c>
       <c r="D265">
         <v>3</v>
@@ -7316,10 +7304,10 @@
     </row>
     <row r="266" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A266">
-        <v>285</v>
+        <v>293</v>
       </c>
       <c r="B266" t="s">
-        <v>295</v>
+        <v>299</v>
       </c>
       <c r="C266" t="s">
         <v>189</v>
@@ -7336,13 +7324,13 @@
     </row>
     <row r="267" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A267">
-        <v>286</v>
+        <v>294</v>
       </c>
       <c r="B267" t="s">
-        <v>296</v>
+        <v>300</v>
       </c>
       <c r="C267" t="s">
-        <v>187</v>
+        <v>193</v>
       </c>
       <c r="D267">
         <v>3</v>
@@ -7351,18 +7339,18 @@
         <v>64</v>
       </c>
       <c r="F267" s="1" t="s">
-        <v>169</v>
+        <v>181</v>
       </c>
     </row>
     <row r="268" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A268">
-        <v>287</v>
+        <v>295</v>
       </c>
       <c r="B268" t="s">
-        <v>297</v>
+        <v>301</v>
       </c>
       <c r="C268" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="D268">
         <v>3</v>
@@ -7371,144 +7359,144 @@
         <v>64</v>
       </c>
       <c r="F268" s="1" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
     <row r="269" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A269">
-        <v>288</v>
+        <v>296</v>
       </c>
       <c r="B269" t="s">
-        <v>298</v>
+        <v>302</v>
       </c>
       <c r="C269" t="s">
-        <v>187</v>
+        <v>303</v>
       </c>
       <c r="D269">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E269" s="11" t="s">
         <v>64</v>
       </c>
       <c r="F269" s="1" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
     <row r="270" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A270">
-        <v>289</v>
+        <v>297</v>
       </c>
       <c r="B270" t="s">
-        <v>299</v>
+        <v>304</v>
       </c>
       <c r="C270" t="s">
-        <v>187</v>
+        <v>305</v>
       </c>
       <c r="D270">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E270" s="11" t="s">
         <v>64</v>
       </c>
       <c r="F270" s="1" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
     <row r="271" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A271">
-        <v>290</v>
+        <v>298</v>
       </c>
       <c r="B271" t="s">
-        <v>300</v>
+        <v>306</v>
       </c>
       <c r="C271" t="s">
-        <v>196</v>
+        <v>209</v>
       </c>
       <c r="D271">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E271" s="11" t="s">
-        <v>64</v>
+        <v>28</v>
       </c>
       <c r="F271" s="1" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
     <row r="272" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A272">
-        <v>291</v>
+        <v>299</v>
       </c>
       <c r="B272" t="s">
-        <v>301</v>
+        <v>307</v>
       </c>
       <c r="C272" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="D272">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E272" s="11" t="s">
-        <v>64</v>
+        <v>28</v>
       </c>
       <c r="F272" s="1" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
     <row r="273" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A273">
-        <v>292</v>
+        <v>300</v>
       </c>
       <c r="B273" t="s">
-        <v>302</v>
+        <v>308</v>
       </c>
       <c r="C273" t="s">
-        <v>189</v>
+        <v>309</v>
       </c>
       <c r="D273">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E273" s="11" t="s">
-        <v>64</v>
+        <v>28</v>
       </c>
       <c r="F273" s="1" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
     <row r="274" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A274">
-        <v>293</v>
+        <v>301</v>
       </c>
       <c r="B274" t="s">
-        <v>303</v>
+        <v>310</v>
       </c>
       <c r="C274" t="s">
-        <v>189</v>
+        <v>311</v>
       </c>
       <c r="D274">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E274" s="11" t="s">
-        <v>64</v>
+        <v>28</v>
       </c>
       <c r="F274" s="1" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
     <row r="275" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A275">
-        <v>294</v>
+        <v>302</v>
       </c>
       <c r="B275" t="s">
-        <v>304</v>
+        <v>312</v>
       </c>
       <c r="C275" t="s">
-        <v>193</v>
+        <v>254</v>
       </c>
       <c r="D275">
         <v>3</v>
       </c>
       <c r="E275" s="11" t="s">
-        <v>64</v>
+        <v>28</v>
       </c>
       <c r="F275" s="1" t="s">
         <v>181</v>
@@ -7516,19 +7504,19 @@
     </row>
     <row r="276" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A276">
-        <v>295</v>
+        <v>303</v>
       </c>
       <c r="B276" t="s">
-        <v>305</v>
+        <v>313</v>
       </c>
       <c r="C276" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="D276">
         <v>3</v>
       </c>
       <c r="E276" s="11" t="s">
-        <v>64</v>
+        <v>28</v>
       </c>
       <c r="F276" s="1" t="s">
         <v>181</v>
@@ -7536,170 +7524,170 @@
     </row>
     <row r="277" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A277">
-        <v>296</v>
+        <v>304</v>
       </c>
       <c r="B277" t="s">
-        <v>306</v>
+        <v>315</v>
       </c>
       <c r="C277" t="s">
-        <v>307</v>
+        <v>209</v>
       </c>
       <c r="D277">
-        <v>2</v>
-      </c>
-      <c r="E277" s="11" t="s">
-        <v>64</v>
+        <v>3</v>
+      </c>
+      <c r="E277" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="F277" s="1" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
     </row>
     <row r="278" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A278">
-        <v>297</v>
+        <v>305</v>
       </c>
       <c r="B278" t="s">
-        <v>308</v>
+        <v>316</v>
       </c>
       <c r="C278" t="s">
-        <v>309</v>
+        <v>196</v>
       </c>
       <c r="D278">
-        <v>2</v>
-      </c>
-      <c r="E278" s="11" t="s">
-        <v>64</v>
+        <v>3</v>
+      </c>
+      <c r="E278" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="F278" s="1" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
     </row>
     <row r="279" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A279">
-        <v>298</v>
+        <v>306</v>
       </c>
       <c r="B279" t="s">
-        <v>310</v>
+        <v>317</v>
       </c>
       <c r="C279" t="s">
-        <v>209</v>
+        <v>318</v>
       </c>
       <c r="D279">
-        <v>2</v>
-      </c>
-      <c r="E279" s="11" t="s">
-        <v>28</v>
+        <v>3</v>
+      </c>
+      <c r="E279" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="F279" s="1" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
     </row>
     <row r="280" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A280">
-        <v>299</v>
+        <v>307</v>
       </c>
       <c r="B280" t="s">
-        <v>311</v>
+        <v>319</v>
       </c>
       <c r="C280" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="D280">
-        <v>2</v>
-      </c>
-      <c r="E280" s="11" t="s">
-        <v>28</v>
+        <v>3</v>
+      </c>
+      <c r="E280" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="F280" s="1" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
     </row>
     <row r="281" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A281">
-        <v>300</v>
+        <v>308</v>
       </c>
       <c r="B281" t="s">
-        <v>312</v>
+        <v>320</v>
       </c>
       <c r="C281" t="s">
-        <v>313</v>
+        <v>321</v>
       </c>
       <c r="D281">
-        <v>2</v>
-      </c>
-      <c r="E281" s="11" t="s">
-        <v>28</v>
+        <v>3</v>
+      </c>
+      <c r="E281" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="F281" s="1" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
     </row>
     <row r="282" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A282">
-        <v>301</v>
+        <v>309</v>
       </c>
       <c r="B282" t="s">
-        <v>314</v>
+        <v>322</v>
       </c>
       <c r="C282" t="s">
-        <v>315</v>
+        <v>311</v>
       </c>
       <c r="D282">
-        <v>2</v>
-      </c>
-      <c r="E282" s="11" t="s">
-        <v>28</v>
+        <v>3</v>
+      </c>
+      <c r="E282" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="F282" s="1" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
     </row>
     <row r="283" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A283">
-        <v>302</v>
+        <v>310</v>
       </c>
       <c r="B283" t="s">
-        <v>316</v>
+        <v>323</v>
       </c>
       <c r="C283" t="s">
-        <v>258</v>
+        <v>193</v>
       </c>
       <c r="D283">
         <v>3</v>
       </c>
-      <c r="E283" s="11" t="s">
-        <v>28</v>
+      <c r="E283" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="F283" s="1" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
     </row>
     <row r="284" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A284">
-        <v>303</v>
+        <v>311</v>
       </c>
       <c r="B284" t="s">
-        <v>317</v>
+        <v>324</v>
       </c>
       <c r="C284" t="s">
-        <v>189</v>
+        <v>196</v>
       </c>
       <c r="D284">
         <v>3</v>
       </c>
-      <c r="E284" s="11" t="s">
-        <v>28</v>
+      <c r="E284" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="F284" s="1" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
     </row>
     <row r="285" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A285">
-        <v>304</v>
+        <v>312</v>
       </c>
       <c r="B285" t="s">
-        <v>319</v>
+        <v>325</v>
       </c>
       <c r="C285" t="s">
         <v>209</v>
@@ -7716,10 +7704,10 @@
     </row>
     <row r="286" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A286">
-        <v>305</v>
+        <v>313</v>
       </c>
       <c r="B286" t="s">
-        <v>320</v>
+        <v>326</v>
       </c>
       <c r="C286" t="s">
         <v>196</v>
@@ -7736,13 +7724,13 @@
     </row>
     <row r="287" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A287">
-        <v>306</v>
+        <v>314</v>
       </c>
       <c r="B287" t="s">
-        <v>321</v>
+        <v>327</v>
       </c>
       <c r="C287" t="s">
-        <v>322</v>
+        <v>189</v>
       </c>
       <c r="D287">
         <v>3</v>
@@ -7751,18 +7739,18 @@
         <v>5</v>
       </c>
       <c r="F287" s="1" t="s">
-        <v>182</v>
+        <v>169</v>
       </c>
     </row>
     <row r="288" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A288">
-        <v>307</v>
+        <v>315</v>
       </c>
       <c r="B288" t="s">
-        <v>323</v>
+        <v>328</v>
       </c>
       <c r="C288" t="s">
-        <v>191</v>
+        <v>196</v>
       </c>
       <c r="D288">
         <v>3</v>
@@ -7776,13 +7764,13 @@
     </row>
     <row r="289" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A289">
-        <v>308</v>
+        <v>316</v>
       </c>
       <c r="B289" t="s">
-        <v>324</v>
+        <v>329</v>
       </c>
       <c r="C289" t="s">
-        <v>325</v>
+        <v>189</v>
       </c>
       <c r="D289">
         <v>3</v>
@@ -7796,13 +7784,13 @@
     </row>
     <row r="290" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A290">
-        <v>309</v>
+        <v>317</v>
       </c>
       <c r="B290" t="s">
-        <v>326</v>
+        <v>330</v>
       </c>
       <c r="C290" t="s">
-        <v>315</v>
+        <v>187</v>
       </c>
       <c r="D290">
         <v>3</v>
@@ -7816,13 +7804,13 @@
     </row>
     <row r="291" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A291">
-        <v>310</v>
+        <v>318</v>
       </c>
       <c r="B291" t="s">
-        <v>327</v>
+        <v>331</v>
       </c>
       <c r="C291" t="s">
-        <v>193</v>
+        <v>187</v>
       </c>
       <c r="D291">
         <v>3</v>
@@ -7836,10 +7824,10 @@
     </row>
     <row r="292" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A292">
-        <v>311</v>
+        <v>319</v>
       </c>
       <c r="B292" t="s">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="C292" t="s">
         <v>196</v>
@@ -7856,13 +7844,13 @@
     </row>
     <row r="293" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A293">
-        <v>312</v>
+        <v>320</v>
       </c>
       <c r="B293" t="s">
-        <v>329</v>
+        <v>333</v>
       </c>
       <c r="C293" t="s">
-        <v>209</v>
+        <v>189</v>
       </c>
       <c r="D293">
         <v>3</v>
@@ -7876,13 +7864,13 @@
     </row>
     <row r="294" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A294">
-        <v>313</v>
+        <v>321</v>
       </c>
       <c r="B294" t="s">
-        <v>330</v>
+        <v>334</v>
       </c>
       <c r="C294" t="s">
-        <v>196</v>
+        <v>187</v>
       </c>
       <c r="D294">
         <v>3</v>
@@ -7896,13 +7884,13 @@
     </row>
     <row r="295" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A295">
-        <v>314</v>
+        <v>322</v>
       </c>
       <c r="B295" t="s">
-        <v>331</v>
+        <v>335</v>
       </c>
       <c r="C295" t="s">
-        <v>189</v>
+        <v>196</v>
       </c>
       <c r="D295">
         <v>3</v>
@@ -7911,15 +7899,15 @@
         <v>5</v>
       </c>
       <c r="F295" s="1" t="s">
-        <v>169</v>
+        <v>182</v>
       </c>
     </row>
     <row r="296" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A296">
-        <v>315</v>
+        <v>323</v>
       </c>
       <c r="B296" t="s">
-        <v>332</v>
+        <v>336</v>
       </c>
       <c r="C296" t="s">
         <v>196</v>
@@ -7936,13 +7924,13 @@
     </row>
     <row r="297" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A297">
-        <v>316</v>
+        <v>324</v>
       </c>
       <c r="B297" t="s">
-        <v>333</v>
+        <v>337</v>
       </c>
       <c r="C297" t="s">
-        <v>189</v>
+        <v>202</v>
       </c>
       <c r="D297">
         <v>3</v>
@@ -7956,10 +7944,10 @@
     </row>
     <row r="298" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A298">
-        <v>317</v>
+        <v>325</v>
       </c>
       <c r="B298" t="s">
-        <v>334</v>
+        <v>338</v>
       </c>
       <c r="C298" t="s">
         <v>187</v>
@@ -7976,13 +7964,13 @@
     </row>
     <row r="299" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A299">
-        <v>318</v>
+        <v>326</v>
       </c>
       <c r="B299" t="s">
-        <v>335</v>
+        <v>339</v>
       </c>
       <c r="C299" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="D299">
         <v>3</v>
@@ -7996,13 +7984,13 @@
     </row>
     <row r="300" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A300">
-        <v>319</v>
+        <v>327</v>
       </c>
       <c r="B300" t="s">
-        <v>336</v>
+        <v>340</v>
       </c>
       <c r="C300" t="s">
-        <v>196</v>
+        <v>189</v>
       </c>
       <c r="D300">
         <v>3</v>
@@ -8016,13 +8004,13 @@
     </row>
     <row r="301" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A301">
-        <v>320</v>
+        <v>328</v>
       </c>
       <c r="B301" t="s">
-        <v>337</v>
+        <v>341</v>
       </c>
       <c r="C301" t="s">
-        <v>189</v>
+        <v>200</v>
       </c>
       <c r="D301">
         <v>3</v>
@@ -8036,10 +8024,10 @@
     </row>
     <row r="302" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A302">
-        <v>321</v>
+        <v>329</v>
       </c>
       <c r="B302" t="s">
-        <v>338</v>
+        <v>342</v>
       </c>
       <c r="C302" t="s">
         <v>187</v>
@@ -8056,13 +8044,13 @@
     </row>
     <row r="303" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A303">
-        <v>322</v>
+        <v>330</v>
       </c>
       <c r="B303" t="s">
-        <v>339</v>
+        <v>343</v>
       </c>
       <c r="C303" t="s">
-        <v>196</v>
+        <v>187</v>
       </c>
       <c r="D303">
         <v>3</v>
@@ -8076,10 +8064,10 @@
     </row>
     <row r="304" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A304">
-        <v>323</v>
+        <v>331</v>
       </c>
       <c r="B304" t="s">
-        <v>340</v>
+        <v>344</v>
       </c>
       <c r="C304" t="s">
         <v>196</v>
@@ -8094,15 +8082,12 @@
         <v>182</v>
       </c>
     </row>
-    <row r="305" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A305">
-        <v>324</v>
-      </c>
+    <row r="305" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B305" t="s">
-        <v>341</v>
+        <v>345</v>
       </c>
       <c r="C305" t="s">
-        <v>202</v>
+        <v>187</v>
       </c>
       <c r="D305">
         <v>3</v>
@@ -8111,18 +8096,15 @@
         <v>5</v>
       </c>
       <c r="F305" s="1" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="306" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A306">
-        <v>325</v>
-      </c>
+        <v>181</v>
+      </c>
+    </row>
+    <row r="306" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B306" t="s">
-        <v>342</v>
+        <v>346</v>
       </c>
       <c r="C306" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="D306">
         <v>3</v>
@@ -8131,15 +8113,12 @@
         <v>5</v>
       </c>
       <c r="F306" s="1" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="307" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A307">
-        <v>326</v>
-      </c>
+        <v>181</v>
+      </c>
+    </row>
+    <row r="307" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B307" t="s">
-        <v>343</v>
+        <v>347</v>
       </c>
       <c r="C307" t="s">
         <v>189</v>
@@ -8151,18 +8130,15 @@
         <v>5</v>
       </c>
       <c r="F307" s="1" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="308" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A308">
-        <v>327</v>
-      </c>
+        <v>181</v>
+      </c>
+    </row>
+    <row r="308" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B308" t="s">
-        <v>344</v>
+        <v>348</v>
       </c>
       <c r="C308" t="s">
-        <v>189</v>
+        <v>209</v>
       </c>
       <c r="D308">
         <v>3</v>
@@ -8171,18 +8147,15 @@
         <v>5</v>
       </c>
       <c r="F308" s="1" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="309" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A309">
-        <v>328</v>
-      </c>
+        <v>181</v>
+      </c>
+    </row>
+    <row r="309" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B309" t="s">
-        <v>345</v>
+        <v>349</v>
       </c>
       <c r="C309" t="s">
-        <v>200</v>
+        <v>189</v>
       </c>
       <c r="D309">
         <v>3</v>
@@ -8191,18 +8164,15 @@
         <v>5</v>
       </c>
       <c r="F309" s="1" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="310" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A310">
-        <v>329</v>
-      </c>
+        <v>181</v>
+      </c>
+    </row>
+    <row r="310" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B310" t="s">
-        <v>346</v>
+        <v>350</v>
       </c>
       <c r="C310" t="s">
-        <v>187</v>
+        <v>196</v>
       </c>
       <c r="D310">
         <v>3</v>
@@ -8211,18 +8181,15 @@
         <v>5</v>
       </c>
       <c r="F310" s="1" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="311" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A311">
-        <v>330</v>
-      </c>
+        <v>371</v>
+      </c>
+    </row>
+    <row r="311" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B311" t="s">
-        <v>347</v>
+        <v>351</v>
       </c>
       <c r="C311" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="D311">
         <v>3</v>
@@ -8231,18 +8198,15 @@
         <v>5</v>
       </c>
       <c r="F311" s="1" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="312" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A312">
-        <v>331</v>
-      </c>
+        <v>371</v>
+      </c>
+    </row>
+    <row r="312" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B312" t="s">
-        <v>348</v>
+        <v>352</v>
       </c>
       <c r="C312" t="s">
-        <v>196</v>
+        <v>353</v>
       </c>
       <c r="D312">
         <v>3</v>
@@ -8251,15 +8215,15 @@
         <v>5</v>
       </c>
       <c r="F312" s="1" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="313" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="313" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B313" t="s">
-        <v>349</v>
+        <v>354</v>
       </c>
       <c r="C313" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="D313">
         <v>3</v>
@@ -8268,15 +8232,15 @@
         <v>5</v>
       </c>
       <c r="F313" s="1" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="314" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="314" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B314" t="s">
-        <v>350</v>
+        <v>355</v>
       </c>
       <c r="C314" t="s">
-        <v>191</v>
+        <v>196</v>
       </c>
       <c r="D314">
         <v>3</v>
@@ -8285,15 +8249,15 @@
         <v>5</v>
       </c>
       <c r="F314" s="1" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="315" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="315" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B315" t="s">
-        <v>351</v>
+        <v>356</v>
       </c>
       <c r="C315" t="s">
-        <v>189</v>
+        <v>357</v>
       </c>
       <c r="D315">
         <v>3</v>
@@ -8302,15 +8266,15 @@
         <v>5</v>
       </c>
       <c r="F315" s="1" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="316" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="316" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B316" t="s">
-        <v>352</v>
+        <v>358</v>
       </c>
       <c r="C316" t="s">
-        <v>209</v>
+        <v>303</v>
       </c>
       <c r="D316">
         <v>3</v>
@@ -8319,12 +8283,12 @@
         <v>5</v>
       </c>
       <c r="F316" s="1" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="317" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="317" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B317" t="s">
-        <v>353</v>
+        <v>359</v>
       </c>
       <c r="C317" t="s">
         <v>189</v>
@@ -8336,15 +8300,15 @@
         <v>5</v>
       </c>
       <c r="F317" s="1" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="318" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="318" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B318" t="s">
-        <v>354</v>
+        <v>360</v>
       </c>
       <c r="C318" t="s">
-        <v>196</v>
+        <v>187</v>
       </c>
       <c r="D318">
         <v>3</v>
@@ -8353,12 +8317,12 @@
         <v>5</v>
       </c>
       <c r="F318" s="1" t="s">
-        <v>375</v>
-      </c>
-    </row>
-    <row r="319" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="319" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B319" t="s">
-        <v>355</v>
+        <v>361</v>
       </c>
       <c r="C319" t="s">
         <v>189</v>
@@ -8370,15 +8334,15 @@
         <v>5</v>
       </c>
       <c r="F319" s="1" t="s">
-        <v>375</v>
-      </c>
-    </row>
-    <row r="320" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="320" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B320" t="s">
-        <v>356</v>
+        <v>362</v>
       </c>
       <c r="C320" t="s">
-        <v>357</v>
+        <v>196</v>
       </c>
       <c r="D320">
         <v>3</v>
@@ -8387,15 +8351,15 @@
         <v>5</v>
       </c>
       <c r="F320" s="1" t="s">
-        <v>375</v>
+        <v>371</v>
       </c>
     </row>
     <row r="321" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B321" t="s">
-        <v>358</v>
+        <v>363</v>
       </c>
       <c r="C321" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="D321">
         <v>3</v>
@@ -8404,15 +8368,15 @@
         <v>5</v>
       </c>
       <c r="F321" s="1" t="s">
-        <v>375</v>
+        <v>371</v>
       </c>
     </row>
     <row r="322" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B322" t="s">
-        <v>359</v>
+        <v>364</v>
       </c>
       <c r="C322" t="s">
-        <v>196</v>
+        <v>187</v>
       </c>
       <c r="D322">
         <v>3</v>
@@ -8421,15 +8385,15 @@
         <v>5</v>
       </c>
       <c r="F322" s="1" t="s">
-        <v>375</v>
+        <v>371</v>
       </c>
     </row>
     <row r="323" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B323" t="s">
-        <v>360</v>
+        <v>365</v>
       </c>
       <c r="C323" t="s">
-        <v>361</v>
+        <v>353</v>
       </c>
       <c r="D323">
         <v>3</v>
@@ -8438,15 +8402,15 @@
         <v>5</v>
       </c>
       <c r="F323" s="1" t="s">
-        <v>375</v>
+        <v>371</v>
       </c>
     </row>
     <row r="324" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B324" t="s">
-        <v>362</v>
+        <v>366</v>
       </c>
       <c r="C324" t="s">
-        <v>307</v>
+        <v>196</v>
       </c>
       <c r="D324">
         <v>3</v>
@@ -8455,15 +8419,18 @@
         <v>5</v>
       </c>
       <c r="F324" s="1" t="s">
-        <v>375</v>
+        <v>371</v>
       </c>
     </row>
     <row r="325" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A325">
+        <v>352</v>
+      </c>
       <c r="B325" t="s">
-        <v>363</v>
+        <v>367</v>
       </c>
       <c r="C325" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="D325">
         <v>3</v>
@@ -8472,15 +8439,18 @@
         <v>5</v>
       </c>
       <c r="F325" s="1" t="s">
-        <v>375</v>
+        <v>371</v>
       </c>
     </row>
     <row r="326" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A326">
+        <v>353</v>
+      </c>
       <c r="B326" t="s">
-        <v>364</v>
+        <v>368</v>
       </c>
       <c r="C326" t="s">
-        <v>187</v>
+        <v>369</v>
       </c>
       <c r="D326">
         <v>3</v>
@@ -8489,15 +8459,18 @@
         <v>5</v>
       </c>
       <c r="F326" s="1" t="s">
-        <v>375</v>
+        <v>371</v>
       </c>
     </row>
     <row r="327" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A327">
+        <v>354</v>
+      </c>
       <c r="B327" t="s">
-        <v>365</v>
+        <v>370</v>
       </c>
       <c r="C327" t="s">
-        <v>189</v>
+        <v>369</v>
       </c>
       <c r="D327">
         <v>3</v>
@@ -8506,29 +8479,35 @@
         <v>5</v>
       </c>
       <c r="F327" s="1" t="s">
-        <v>375</v>
+        <v>371</v>
       </c>
     </row>
     <row r="328" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A328">
+        <v>355</v>
+      </c>
       <c r="B328" t="s">
-        <v>366</v>
+        <v>372</v>
       </c>
       <c r="C328" t="s">
-        <v>196</v>
+        <v>200</v>
       </c>
       <c r="D328">
         <v>3</v>
       </c>
       <c r="E328" s="3" t="s">
-        <v>5</v>
+        <v>65</v>
       </c>
       <c r="F328" s="1" t="s">
-        <v>375</v>
+        <v>371</v>
       </c>
     </row>
     <row r="329" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A329">
+        <v>356</v>
+      </c>
       <c r="B329" t="s">
-        <v>367</v>
+        <v>373</v>
       </c>
       <c r="C329" t="s">
         <v>187</v>
@@ -8537,129 +8516,138 @@
         <v>3</v>
       </c>
       <c r="E329" s="3" t="s">
-        <v>5</v>
+        <v>65</v>
       </c>
       <c r="F329" s="1" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="330" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A330">
+        <v>357</v>
+      </c>
+      <c r="B330" t="s">
+        <v>374</v>
+      </c>
+      <c r="C330" t="s">
+        <v>303</v>
+      </c>
+      <c r="D330">
+        <v>3</v>
+      </c>
+      <c r="E330" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="F330" s="1" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="331" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A331">
+        <v>358</v>
+      </c>
+      <c r="B331" t="s">
         <v>375</v>
       </c>
-    </row>
-    <row r="330" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B330" t="s">
-        <v>368</v>
-      </c>
-      <c r="C330" t="s">
+      <c r="C331" t="s">
         <v>187</v>
       </c>
-      <c r="D330">
-        <v>3</v>
-      </c>
-      <c r="E330" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F330" s="1" t="s">
-        <v>375</v>
-      </c>
-    </row>
-    <row r="331" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B331" t="s">
-        <v>369</v>
-      </c>
-      <c r="C331" t="s">
-        <v>357</v>
-      </c>
       <c r="D331">
         <v>3</v>
       </c>
       <c r="E331" s="3" t="s">
-        <v>5</v>
+        <v>65</v>
       </c>
       <c r="F331" s="1" t="s">
-        <v>375</v>
+        <v>371</v>
       </c>
     </row>
     <row r="332" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A332">
+        <v>359</v>
+      </c>
       <c r="B332" t="s">
-        <v>370</v>
+        <v>376</v>
       </c>
       <c r="C332" t="s">
-        <v>196</v>
+        <v>209</v>
       </c>
       <c r="D332">
         <v>3</v>
       </c>
       <c r="E332" s="3" t="s">
-        <v>5</v>
+        <v>65</v>
       </c>
       <c r="F332" s="1" t="s">
-        <v>375</v>
+        <v>371</v>
       </c>
     </row>
     <row r="333" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A333">
-        <v>352</v>
+        <v>360</v>
       </c>
       <c r="B333" t="s">
-        <v>371</v>
+        <v>377</v>
       </c>
       <c r="C333" t="s">
-        <v>191</v>
+        <v>267</v>
       </c>
       <c r="D333">
         <v>3</v>
       </c>
       <c r="E333" s="3" t="s">
-        <v>5</v>
+        <v>65</v>
       </c>
       <c r="F333" s="1" t="s">
-        <v>375</v>
+        <v>371</v>
       </c>
     </row>
     <row r="334" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A334">
-        <v>353</v>
+        <v>361</v>
       </c>
       <c r="B334" t="s">
-        <v>372</v>
+        <v>378</v>
       </c>
       <c r="C334" t="s">
-        <v>373</v>
+        <v>202</v>
       </c>
       <c r="D334">
         <v>3</v>
       </c>
       <c r="E334" s="3" t="s">
-        <v>5</v>
+        <v>65</v>
       </c>
       <c r="F334" s="1" t="s">
-        <v>375</v>
+        <v>371</v>
       </c>
     </row>
     <row r="335" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A335">
-        <v>354</v>
+        <v>362</v>
       </c>
       <c r="B335" t="s">
-        <v>374</v>
+        <v>379</v>
       </c>
       <c r="C335" t="s">
-        <v>373</v>
+        <v>189</v>
       </c>
       <c r="D335">
         <v>3</v>
       </c>
       <c r="E335" s="3" t="s">
-        <v>5</v>
+        <v>65</v>
       </c>
       <c r="F335" s="1" t="s">
-        <v>375</v>
+        <v>371</v>
       </c>
     </row>
     <row r="336" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A336">
-        <v>355</v>
+        <v>363</v>
       </c>
       <c r="B336" t="s">
-        <v>376</v>
+        <v>380</v>
       </c>
       <c r="C336" t="s">
         <v>200</v>
@@ -8671,18 +8659,18 @@
         <v>65</v>
       </c>
       <c r="F336" s="1" t="s">
-        <v>375</v>
+        <v>371</v>
       </c>
     </row>
     <row r="337" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A337">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="B337" t="s">
-        <v>377</v>
+        <v>381</v>
       </c>
       <c r="C337" t="s">
-        <v>187</v>
+        <v>200</v>
       </c>
       <c r="D337">
         <v>3</v>
@@ -8691,18 +8679,18 @@
         <v>65</v>
       </c>
       <c r="F337" s="1" t="s">
-        <v>375</v>
+        <v>371</v>
       </c>
     </row>
     <row r="338" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A338">
-        <v>357</v>
+        <v>365</v>
       </c>
       <c r="B338" t="s">
-        <v>378</v>
+        <v>382</v>
       </c>
       <c r="C338" t="s">
-        <v>307</v>
+        <v>196</v>
       </c>
       <c r="D338">
         <v>3</v>
@@ -8711,18 +8699,18 @@
         <v>65</v>
       </c>
       <c r="F338" s="1" t="s">
-        <v>375</v>
+        <v>371</v>
       </c>
     </row>
     <row r="339" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A339">
-        <v>358</v>
+        <v>366</v>
       </c>
       <c r="B339" t="s">
-        <v>379</v>
+        <v>383</v>
       </c>
       <c r="C339" t="s">
-        <v>187</v>
+        <v>353</v>
       </c>
       <c r="D339">
         <v>3</v>
@@ -8731,18 +8719,18 @@
         <v>65</v>
       </c>
       <c r="F339" s="1" t="s">
-        <v>375</v>
+        <v>371</v>
       </c>
     </row>
     <row r="340" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A340">
-        <v>359</v>
+        <v>367</v>
       </c>
       <c r="B340" t="s">
-        <v>380</v>
+        <v>384</v>
       </c>
       <c r="C340" t="s">
-        <v>209</v>
+        <v>353</v>
       </c>
       <c r="D340">
         <v>3</v>
@@ -8751,18 +8739,18 @@
         <v>65</v>
       </c>
       <c r="F340" s="1" t="s">
-        <v>375</v>
+        <v>371</v>
       </c>
     </row>
     <row r="341" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A341">
-        <v>360</v>
+        <v>368</v>
       </c>
       <c r="B341" t="s">
-        <v>381</v>
+        <v>385</v>
       </c>
       <c r="C341" t="s">
-        <v>271</v>
+        <v>318</v>
       </c>
       <c r="D341">
         <v>3</v>
@@ -8771,18 +8759,18 @@
         <v>65</v>
       </c>
       <c r="F341" s="1" t="s">
-        <v>375</v>
+        <v>371</v>
       </c>
     </row>
     <row r="342" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A342">
-        <v>361</v>
+        <v>369</v>
       </c>
       <c r="B342" t="s">
-        <v>382</v>
+        <v>386</v>
       </c>
       <c r="C342" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="D342">
         <v>3</v>
@@ -8791,178 +8779,178 @@
         <v>65</v>
       </c>
       <c r="F342" s="1" t="s">
-        <v>375</v>
+        <v>371</v>
       </c>
     </row>
     <row r="343" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A343">
-        <v>362</v>
+        <v>370</v>
       </c>
       <c r="B343" t="s">
-        <v>383</v>
+        <v>387</v>
       </c>
       <c r="C343" t="s">
-        <v>189</v>
+        <v>196</v>
       </c>
       <c r="D343">
         <v>3</v>
       </c>
       <c r="E343" s="3" t="s">
-        <v>65</v>
+        <v>81</v>
       </c>
       <c r="F343" s="1" t="s">
-        <v>375</v>
+        <v>371</v>
       </c>
     </row>
     <row r="344" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A344">
-        <v>363</v>
+        <v>371</v>
       </c>
       <c r="B344" t="s">
-        <v>384</v>
+        <v>388</v>
       </c>
       <c r="C344" t="s">
-        <v>200</v>
+        <v>303</v>
       </c>
       <c r="D344">
         <v>3</v>
       </c>
       <c r="E344" s="3" t="s">
-        <v>65</v>
+        <v>81</v>
       </c>
       <c r="F344" s="1" t="s">
-        <v>375</v>
+        <v>371</v>
       </c>
     </row>
     <row r="345" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A345">
-        <v>364</v>
+        <v>372</v>
       </c>
       <c r="B345" t="s">
-        <v>385</v>
+        <v>389</v>
       </c>
       <c r="C345" t="s">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="D345">
         <v>3</v>
       </c>
       <c r="E345" s="3" t="s">
-        <v>65</v>
+        <v>81</v>
       </c>
       <c r="F345" s="1" t="s">
-        <v>375</v>
+        <v>371</v>
       </c>
     </row>
     <row r="346" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A346">
-        <v>365</v>
+        <v>373</v>
       </c>
       <c r="B346" t="s">
-        <v>386</v>
+        <v>390</v>
       </c>
       <c r="C346" t="s">
-        <v>196</v>
+        <v>309</v>
       </c>
       <c r="D346">
         <v>3</v>
       </c>
       <c r="E346" s="3" t="s">
-        <v>65</v>
+        <v>81</v>
       </c>
       <c r="F346" s="1" t="s">
-        <v>375</v>
+        <v>371</v>
       </c>
     </row>
     <row r="347" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A347">
-        <v>366</v>
+        <v>374</v>
       </c>
       <c r="B347" t="s">
-        <v>387</v>
+        <v>391</v>
       </c>
       <c r="C347" t="s">
-        <v>357</v>
+        <v>189</v>
       </c>
       <c r="D347">
         <v>3</v>
       </c>
       <c r="E347" s="3" t="s">
-        <v>65</v>
+        <v>81</v>
       </c>
       <c r="F347" s="1" t="s">
-        <v>375</v>
+        <v>371</v>
       </c>
     </row>
     <row r="348" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A348">
-        <v>367</v>
+        <v>375</v>
       </c>
       <c r="B348" t="s">
-        <v>388</v>
+        <v>392</v>
       </c>
       <c r="C348" t="s">
-        <v>357</v>
+        <v>196</v>
       </c>
       <c r="D348">
         <v>3</v>
       </c>
       <c r="E348" s="3" t="s">
-        <v>65</v>
+        <v>81</v>
       </c>
       <c r="F348" s="1" t="s">
-        <v>375</v>
+        <v>371</v>
       </c>
     </row>
     <row r="349" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A349">
-        <v>368</v>
+        <v>376</v>
       </c>
       <c r="B349" t="s">
-        <v>389</v>
+        <v>393</v>
       </c>
       <c r="C349" t="s">
-        <v>322</v>
+        <v>357</v>
       </c>
       <c r="D349">
         <v>3</v>
       </c>
       <c r="E349" s="3" t="s">
-        <v>65</v>
+        <v>81</v>
       </c>
       <c r="F349" s="1" t="s">
-        <v>375</v>
+        <v>371</v>
       </c>
     </row>
     <row r="350" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A350">
-        <v>369</v>
+        <v>377</v>
       </c>
       <c r="B350" t="s">
-        <v>390</v>
+        <v>394</v>
       </c>
       <c r="C350" t="s">
-        <v>200</v>
+        <v>187</v>
       </c>
       <c r="D350">
         <v>3</v>
       </c>
       <c r="E350" s="3" t="s">
-        <v>65</v>
+        <v>81</v>
       </c>
       <c r="F350" s="1" t="s">
-        <v>375</v>
+        <v>371</v>
       </c>
     </row>
     <row r="351" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A351">
-        <v>370</v>
+        <v>378</v>
       </c>
       <c r="B351" t="s">
-        <v>391</v>
+        <v>395</v>
       </c>
       <c r="C351" t="s">
-        <v>196</v>
+        <v>189</v>
       </c>
       <c r="D351">
         <v>3</v>
@@ -8971,18 +8959,18 @@
         <v>81</v>
       </c>
       <c r="F351" s="1" t="s">
-        <v>375</v>
+        <v>371</v>
       </c>
     </row>
     <row r="352" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A352">
-        <v>371</v>
+        <v>379</v>
       </c>
       <c r="B352" t="s">
-        <v>392</v>
+        <v>396</v>
       </c>
       <c r="C352" t="s">
-        <v>307</v>
+        <v>196</v>
       </c>
       <c r="D352">
         <v>3</v>
@@ -8991,18 +8979,18 @@
         <v>81</v>
       </c>
       <c r="F352" s="1" t="s">
-        <v>375</v>
+        <v>371</v>
       </c>
     </row>
     <row r="353" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A353">
-        <v>372</v>
+        <v>380</v>
       </c>
       <c r="B353" t="s">
-        <v>393</v>
+        <v>397</v>
       </c>
       <c r="C353" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="D353">
         <v>3</v>
@@ -9011,18 +8999,18 @@
         <v>81</v>
       </c>
       <c r="F353" s="1" t="s">
-        <v>375</v>
+        <v>371</v>
       </c>
     </row>
     <row r="354" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A354">
-        <v>373</v>
+        <v>381</v>
       </c>
       <c r="B354" t="s">
-        <v>394</v>
+        <v>398</v>
       </c>
       <c r="C354" t="s">
-        <v>313</v>
+        <v>196</v>
       </c>
       <c r="D354">
         <v>3</v>
@@ -9031,18 +9019,18 @@
         <v>81</v>
       </c>
       <c r="F354" s="1" t="s">
-        <v>375</v>
+        <v>371</v>
       </c>
     </row>
     <row r="355" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A355">
-        <v>374</v>
+        <v>382</v>
       </c>
       <c r="B355" t="s">
-        <v>395</v>
+        <v>399</v>
       </c>
       <c r="C355" t="s">
-        <v>189</v>
+        <v>309</v>
       </c>
       <c r="D355">
         <v>3</v>
@@ -9051,15 +9039,15 @@
         <v>81</v>
       </c>
       <c r="F355" s="1" t="s">
-        <v>375</v>
+        <v>371</v>
       </c>
     </row>
     <row r="356" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A356">
-        <v>375</v>
+        <v>383</v>
       </c>
       <c r="B356" t="s">
-        <v>396</v>
+        <v>400</v>
       </c>
       <c r="C356" t="s">
         <v>196</v>
@@ -9071,18 +9059,18 @@
         <v>81</v>
       </c>
       <c r="F356" s="1" t="s">
-        <v>375</v>
+        <v>371</v>
       </c>
     </row>
     <row r="357" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A357">
-        <v>376</v>
+        <v>384</v>
       </c>
       <c r="B357" t="s">
-        <v>397</v>
+        <v>401</v>
       </c>
       <c r="C357" t="s">
-        <v>361</v>
+        <v>189</v>
       </c>
       <c r="D357">
         <v>3</v>
@@ -9091,55 +9079,55 @@
         <v>81</v>
       </c>
       <c r="F357" s="1" t="s">
-        <v>375</v>
+        <v>371</v>
       </c>
     </row>
     <row r="358" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A358">
-        <v>377</v>
+        <v>385</v>
       </c>
       <c r="B358" t="s">
-        <v>398</v>
+        <v>402</v>
       </c>
       <c r="C358" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="D358">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E358" s="3" t="s">
         <v>81</v>
       </c>
       <c r="F358" s="1" t="s">
-        <v>375</v>
+        <v>371</v>
       </c>
     </row>
     <row r="359" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A359">
-        <v>378</v>
+        <v>386</v>
       </c>
       <c r="B359" t="s">
-        <v>399</v>
+        <v>403</v>
       </c>
       <c r="C359" t="s">
-        <v>189</v>
+        <v>369</v>
       </c>
       <c r="D359">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E359" s="3" t="s">
         <v>81</v>
       </c>
       <c r="F359" s="1" t="s">
-        <v>375</v>
+        <v>371</v>
       </c>
     </row>
     <row r="360" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A360">
-        <v>379</v>
+        <v>387</v>
       </c>
       <c r="B360" t="s">
-        <v>400</v>
+        <v>407</v>
       </c>
       <c r="C360" t="s">
         <v>196</v>
@@ -9147,299 +9135,299 @@
       <c r="D360">
         <v>3</v>
       </c>
-      <c r="E360" s="3" t="s">
-        <v>81</v>
+      <c r="E360" t="s">
+        <v>413</v>
       </c>
       <c r="F360" s="1" t="s">
-        <v>375</v>
+        <v>371</v>
       </c>
     </row>
     <row r="361" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A361">
-        <v>380</v>
+        <v>388</v>
       </c>
       <c r="B361" t="s">
-        <v>401</v>
+        <v>408</v>
       </c>
       <c r="C361" t="s">
-        <v>193</v>
+        <v>215</v>
       </c>
       <c r="D361">
         <v>3</v>
       </c>
-      <c r="E361" s="3" t="s">
-        <v>81</v>
+      <c r="E361" t="s">
+        <v>413</v>
       </c>
       <c r="F361" s="1" t="s">
-        <v>375</v>
+        <v>371</v>
       </c>
     </row>
     <row r="362" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A362">
-        <v>381</v>
+        <v>389</v>
       </c>
       <c r="B362" t="s">
-        <v>402</v>
+        <v>409</v>
       </c>
       <c r="C362" t="s">
-        <v>196</v>
+        <v>189</v>
       </c>
       <c r="D362">
         <v>3</v>
       </c>
-      <c r="E362" s="3" t="s">
-        <v>81</v>
+      <c r="E362" t="s">
+        <v>413</v>
       </c>
       <c r="F362" s="1" t="s">
-        <v>375</v>
+        <v>371</v>
       </c>
     </row>
     <row r="363" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A363">
-        <v>382</v>
+        <v>390</v>
       </c>
       <c r="B363" t="s">
-        <v>403</v>
+        <v>410</v>
       </c>
       <c r="C363" t="s">
-        <v>313</v>
+        <v>318</v>
       </c>
       <c r="D363">
         <v>3</v>
       </c>
-      <c r="E363" s="3" t="s">
-        <v>81</v>
+      <c r="E363" t="s">
+        <v>413</v>
       </c>
       <c r="F363" s="1" t="s">
-        <v>375</v>
+        <v>371</v>
       </c>
     </row>
     <row r="364" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A364">
-        <v>383</v>
+        <v>391</v>
       </c>
       <c r="B364" t="s">
-        <v>404</v>
+        <v>411</v>
       </c>
       <c r="C364" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="D364">
         <v>3</v>
       </c>
-      <c r="E364" s="3" t="s">
-        <v>81</v>
+      <c r="E364" t="s">
+        <v>413</v>
       </c>
       <c r="F364" s="1" t="s">
-        <v>375</v>
+        <v>371</v>
       </c>
     </row>
     <row r="365" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A365">
-        <v>384</v>
+        <v>392</v>
       </c>
       <c r="B365" t="s">
-        <v>405</v>
+        <v>412</v>
       </c>
       <c r="C365" t="s">
-        <v>189</v>
+        <v>215</v>
       </c>
       <c r="D365">
         <v>3</v>
       </c>
-      <c r="E365" s="3" t="s">
-        <v>81</v>
+      <c r="E365" t="s">
+        <v>413</v>
       </c>
       <c r="F365" s="1" t="s">
-        <v>375</v>
+        <v>371</v>
       </c>
     </row>
     <row r="366" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A366">
-        <v>385</v>
+        <v>394</v>
       </c>
       <c r="B366" t="s">
-        <v>406</v>
+        <v>414</v>
       </c>
       <c r="C366" t="s">
         <v>189</v>
       </c>
       <c r="D366">
-        <v>2</v>
-      </c>
-      <c r="E366" s="3" t="s">
-        <v>81</v>
+        <v>3</v>
+      </c>
+      <c r="E366" t="s">
+        <v>423</v>
       </c>
       <c r="F366" s="1" t="s">
-        <v>375</v>
+        <v>371</v>
       </c>
     </row>
     <row r="367" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A367">
-        <v>386</v>
+        <v>395</v>
       </c>
       <c r="B367" t="s">
-        <v>407</v>
+        <v>415</v>
       </c>
       <c r="C367" t="s">
-        <v>373</v>
+        <v>196</v>
       </c>
       <c r="D367">
-        <v>2</v>
-      </c>
-      <c r="E367" s="3" t="s">
-        <v>81</v>
+        <v>3</v>
+      </c>
+      <c r="E367" t="s">
+        <v>423</v>
       </c>
       <c r="F367" s="1" t="s">
-        <v>375</v>
+        <v>371</v>
       </c>
     </row>
     <row r="368" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A368">
-        <v>387</v>
+        <v>396</v>
       </c>
       <c r="B368" t="s">
-        <v>411</v>
+        <v>416</v>
       </c>
       <c r="C368" t="s">
-        <v>196</v>
+        <v>417</v>
       </c>
       <c r="D368">
         <v>3</v>
       </c>
       <c r="E368" t="s">
-        <v>417</v>
+        <v>423</v>
       </c>
       <c r="F368" s="1" t="s">
-        <v>375</v>
+        <v>371</v>
       </c>
     </row>
     <row r="369" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A369">
-        <v>388</v>
+        <v>397</v>
       </c>
       <c r="B369" t="s">
-        <v>412</v>
+        <v>418</v>
       </c>
       <c r="C369" t="s">
-        <v>215</v>
+        <v>196</v>
       </c>
       <c r="D369">
         <v>3</v>
       </c>
       <c r="E369" t="s">
-        <v>417</v>
+        <v>423</v>
       </c>
       <c r="F369" s="1" t="s">
-        <v>375</v>
+        <v>371</v>
       </c>
     </row>
     <row r="370" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A370">
-        <v>389</v>
+        <v>398</v>
       </c>
       <c r="B370" t="s">
-        <v>413</v>
+        <v>419</v>
       </c>
       <c r="C370" t="s">
-        <v>189</v>
+        <v>200</v>
       </c>
       <c r="D370">
         <v>3</v>
       </c>
       <c r="E370" t="s">
-        <v>417</v>
+        <v>423</v>
       </c>
       <c r="F370" s="1" t="s">
-        <v>375</v>
+        <v>371</v>
       </c>
     </row>
     <row r="371" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A371">
-        <v>390</v>
+        <v>399</v>
       </c>
       <c r="B371" t="s">
-        <v>414</v>
+        <v>420</v>
       </c>
       <c r="C371" t="s">
-        <v>322</v>
+        <v>187</v>
       </c>
       <c r="D371">
         <v>3</v>
       </c>
       <c r="E371" t="s">
-        <v>417</v>
+        <v>423</v>
       </c>
       <c r="F371" s="1" t="s">
-        <v>375</v>
+        <v>371</v>
       </c>
     </row>
     <row r="372" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A372">
-        <v>391</v>
+        <v>400</v>
       </c>
       <c r="B372" t="s">
-        <v>415</v>
+        <v>421</v>
       </c>
       <c r="C372" t="s">
-        <v>193</v>
+        <v>209</v>
       </c>
       <c r="D372">
         <v>3</v>
       </c>
       <c r="E372" t="s">
-        <v>417</v>
+        <v>423</v>
       </c>
       <c r="F372" s="1" t="s">
-        <v>375</v>
+        <v>371</v>
       </c>
     </row>
     <row r="373" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A373">
-        <v>392</v>
+        <v>401</v>
       </c>
       <c r="B373" t="s">
-        <v>416</v>
+        <v>422</v>
       </c>
       <c r="C373" t="s">
-        <v>215</v>
+        <v>357</v>
       </c>
       <c r="D373">
         <v>3</v>
       </c>
       <c r="E373" t="s">
-        <v>417</v>
+        <v>423</v>
       </c>
       <c r="F373" s="1" t="s">
-        <v>375</v>
+        <v>371</v>
       </c>
     </row>
     <row r="374" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A374">
-        <v>394</v>
+        <v>403</v>
       </c>
       <c r="B374" t="s">
-        <v>418</v>
+        <v>424</v>
       </c>
       <c r="C374" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="D374">
         <v>3</v>
       </c>
       <c r="E374" t="s">
-        <v>427</v>
+        <v>64</v>
       </c>
       <c r="F374" s="1" t="s">
-        <v>375</v>
+        <v>371</v>
       </c>
     </row>
     <row r="375" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A375">
-        <v>395</v>
+        <v>404</v>
       </c>
       <c r="B375" t="s">
-        <v>419</v>
+        <v>425</v>
       </c>
       <c r="C375" t="s">
         <v>196</v>
@@ -9448,141 +9436,141 @@
         <v>3</v>
       </c>
       <c r="E375" t="s">
-        <v>427</v>
+        <v>64</v>
       </c>
       <c r="F375" s="1" t="s">
-        <v>375</v>
+        <v>371</v>
       </c>
     </row>
     <row r="376" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A376">
-        <v>396</v>
+        <v>405</v>
       </c>
       <c r="B376" t="s">
-        <v>420</v>
+        <v>426</v>
       </c>
       <c r="C376" t="s">
-        <v>421</v>
+        <v>187</v>
       </c>
       <c r="D376">
         <v>3</v>
       </c>
       <c r="E376" t="s">
-        <v>427</v>
+        <v>64</v>
       </c>
       <c r="F376" s="1" t="s">
-        <v>375</v>
+        <v>371</v>
       </c>
     </row>
     <row r="377" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A377">
-        <v>397</v>
+        <v>406</v>
       </c>
       <c r="B377" t="s">
-        <v>422</v>
+        <v>427</v>
       </c>
       <c r="C377" t="s">
-        <v>196</v>
+        <v>428</v>
       </c>
       <c r="D377">
         <v>3</v>
       </c>
       <c r="E377" t="s">
-        <v>427</v>
+        <v>64</v>
       </c>
       <c r="F377" s="1" t="s">
-        <v>375</v>
+        <v>371</v>
       </c>
     </row>
     <row r="378" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A378">
-        <v>398</v>
+        <v>407</v>
       </c>
       <c r="B378" t="s">
-        <v>423</v>
+        <v>429</v>
       </c>
       <c r="C378" t="s">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="D378">
         <v>3</v>
       </c>
       <c r="E378" t="s">
-        <v>427</v>
+        <v>64</v>
       </c>
       <c r="F378" s="1" t="s">
-        <v>375</v>
+        <v>371</v>
       </c>
     </row>
     <row r="379" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A379">
-        <v>399</v>
+        <v>408</v>
       </c>
       <c r="B379" t="s">
-        <v>424</v>
+        <v>430</v>
       </c>
       <c r="C379" t="s">
-        <v>187</v>
+        <v>267</v>
       </c>
       <c r="D379">
         <v>3</v>
       </c>
       <c r="E379" t="s">
-        <v>427</v>
+        <v>64</v>
       </c>
       <c r="F379" s="1" t="s">
-        <v>375</v>
+        <v>371</v>
       </c>
     </row>
     <row r="380" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A380">
-        <v>400</v>
+        <v>409</v>
       </c>
       <c r="B380" t="s">
-        <v>425</v>
+        <v>431</v>
       </c>
       <c r="C380" t="s">
-        <v>209</v>
+        <v>187</v>
       </c>
       <c r="D380">
         <v>3</v>
       </c>
       <c r="E380" t="s">
-        <v>427</v>
+        <v>64</v>
       </c>
       <c r="F380" s="1" t="s">
-        <v>375</v>
+        <v>371</v>
       </c>
     </row>
     <row r="381" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A381">
-        <v>401</v>
+        <v>410</v>
       </c>
       <c r="B381" t="s">
-        <v>426</v>
+        <v>432</v>
       </c>
       <c r="C381" t="s">
-        <v>361</v>
+        <v>357</v>
       </c>
       <c r="D381">
         <v>3</v>
       </c>
       <c r="E381" t="s">
-        <v>427</v>
+        <v>64</v>
       </c>
       <c r="F381" s="1" t="s">
-        <v>375</v>
+        <v>371</v>
       </c>
     </row>
     <row r="382" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A382">
-        <v>403</v>
+        <v>411</v>
       </c>
       <c r="B382" t="s">
-        <v>428</v>
+        <v>433</v>
       </c>
       <c r="C382" t="s">
-        <v>193</v>
+        <v>309</v>
       </c>
       <c r="D382">
         <v>3</v>
@@ -9591,18 +9579,18 @@
         <v>64</v>
       </c>
       <c r="F382" s="1" t="s">
-        <v>375</v>
+        <v>371</v>
       </c>
     </row>
     <row r="383" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A383">
-        <v>404</v>
+        <v>412</v>
       </c>
       <c r="B383" t="s">
-        <v>429</v>
+        <v>434</v>
       </c>
       <c r="C383" t="s">
-        <v>196</v>
+        <v>357</v>
       </c>
       <c r="D383">
         <v>3</v>
@@ -9611,18 +9599,18 @@
         <v>64</v>
       </c>
       <c r="F383" s="1" t="s">
-        <v>375</v>
+        <v>371</v>
       </c>
     </row>
     <row r="384" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A384">
-        <v>405</v>
+        <v>413</v>
       </c>
       <c r="B384" t="s">
-        <v>430</v>
+        <v>435</v>
       </c>
       <c r="C384" t="s">
-        <v>187</v>
+        <v>209</v>
       </c>
       <c r="D384">
         <v>3</v>
@@ -9631,18 +9619,18 @@
         <v>64</v>
       </c>
       <c r="F384" s="1" t="s">
-        <v>375</v>
+        <v>371</v>
       </c>
     </row>
     <row r="385" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A385">
-        <v>406</v>
+        <v>414</v>
       </c>
       <c r="B385" t="s">
-        <v>431</v>
+        <v>436</v>
       </c>
       <c r="C385" t="s">
-        <v>432</v>
+        <v>202</v>
       </c>
       <c r="D385">
         <v>3</v>
@@ -9651,18 +9639,18 @@
         <v>64</v>
       </c>
       <c r="F385" s="1" t="s">
-        <v>375</v>
+        <v>371</v>
       </c>
     </row>
     <row r="386" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A386">
-        <v>407</v>
+        <v>415</v>
       </c>
       <c r="B386" t="s">
-        <v>433</v>
+        <v>437</v>
       </c>
       <c r="C386" t="s">
-        <v>196</v>
+        <v>309</v>
       </c>
       <c r="D386">
         <v>3</v>
@@ -9671,18 +9659,18 @@
         <v>64</v>
       </c>
       <c r="F386" s="1" t="s">
-        <v>375</v>
+        <v>371</v>
       </c>
     </row>
     <row r="387" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A387">
-        <v>408</v>
+        <v>416</v>
       </c>
       <c r="B387" t="s">
-        <v>434</v>
+        <v>438</v>
       </c>
       <c r="C387" t="s">
-        <v>271</v>
+        <v>215</v>
       </c>
       <c r="D387">
         <v>3</v>
@@ -9691,18 +9679,18 @@
         <v>64</v>
       </c>
       <c r="F387" s="1" t="s">
-        <v>375</v>
+        <v>371</v>
       </c>
     </row>
     <row r="388" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A388">
-        <v>409</v>
+        <v>417</v>
       </c>
       <c r="B388" t="s">
-        <v>435</v>
+        <v>439</v>
       </c>
       <c r="C388" t="s">
-        <v>187</v>
+        <v>209</v>
       </c>
       <c r="D388">
         <v>3</v>
@@ -9711,18 +9699,18 @@
         <v>64</v>
       </c>
       <c r="F388" s="1" t="s">
-        <v>375</v>
+        <v>371</v>
       </c>
     </row>
     <row r="389" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A389">
-        <v>410</v>
+        <v>418</v>
       </c>
       <c r="B389" t="s">
-        <v>436</v>
+        <v>440</v>
       </c>
       <c r="C389" t="s">
-        <v>361</v>
+        <v>187</v>
       </c>
       <c r="D389">
         <v>3</v>
@@ -9731,18 +9719,18 @@
         <v>64</v>
       </c>
       <c r="F389" s="1" t="s">
-        <v>375</v>
+        <v>371</v>
       </c>
     </row>
     <row r="390" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A390">
-        <v>411</v>
+        <v>419</v>
       </c>
       <c r="B390" t="s">
-        <v>437</v>
+        <v>441</v>
       </c>
       <c r="C390" t="s">
-        <v>313</v>
+        <v>196</v>
       </c>
       <c r="D390">
         <v>3</v>
@@ -9751,178 +9739,178 @@
         <v>64</v>
       </c>
       <c r="F390" s="1" t="s">
-        <v>375</v>
+        <v>371</v>
       </c>
     </row>
     <row r="391" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A391">
-        <v>412</v>
+        <v>421</v>
       </c>
       <c r="B391" t="s">
-        <v>438</v>
+        <v>442</v>
       </c>
       <c r="C391" t="s">
-        <v>361</v>
+        <v>215</v>
       </c>
       <c r="D391">
         <v>3</v>
       </c>
       <c r="E391" t="s">
-        <v>64</v>
+        <v>28</v>
       </c>
       <c r="F391" s="1" t="s">
-        <v>375</v>
+        <v>453</v>
       </c>
     </row>
     <row r="392" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A392">
-        <v>413</v>
+        <v>422</v>
       </c>
       <c r="B392" t="s">
-        <v>439</v>
+        <v>443</v>
       </c>
       <c r="C392" t="s">
-        <v>209</v>
+        <v>196</v>
       </c>
       <c r="D392">
         <v>3</v>
       </c>
       <c r="E392" t="s">
-        <v>64</v>
+        <v>28</v>
       </c>
       <c r="F392" s="1" t="s">
-        <v>375</v>
+        <v>371</v>
       </c>
     </row>
     <row r="393" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A393">
-        <v>414</v>
+        <v>423</v>
       </c>
       <c r="B393" t="s">
-        <v>440</v>
+        <v>444</v>
       </c>
       <c r="C393" t="s">
-        <v>202</v>
+        <v>191</v>
       </c>
       <c r="D393">
         <v>3</v>
       </c>
       <c r="E393" t="s">
-        <v>64</v>
+        <v>28</v>
       </c>
       <c r="F393" s="1" t="s">
-        <v>375</v>
+        <v>371</v>
       </c>
     </row>
     <row r="394" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A394">
-        <v>415</v>
+        <v>424</v>
       </c>
       <c r="B394" t="s">
-        <v>441</v>
+        <v>445</v>
       </c>
       <c r="C394" t="s">
-        <v>313</v>
+        <v>303</v>
       </c>
       <c r="D394">
         <v>3</v>
       </c>
       <c r="E394" t="s">
-        <v>64</v>
+        <v>28</v>
       </c>
       <c r="F394" s="1" t="s">
-        <v>375</v>
+        <v>371</v>
       </c>
     </row>
     <row r="395" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A395">
-        <v>416</v>
+        <v>425</v>
       </c>
       <c r="B395" t="s">
-        <v>442</v>
+        <v>446</v>
       </c>
       <c r="C395" t="s">
-        <v>215</v>
+        <v>193</v>
       </c>
       <c r="D395">
         <v>3</v>
       </c>
       <c r="E395" t="s">
-        <v>64</v>
+        <v>28</v>
       </c>
       <c r="F395" s="1" t="s">
-        <v>375</v>
+        <v>371</v>
       </c>
     </row>
     <row r="396" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A396">
-        <v>417</v>
+        <v>426</v>
       </c>
       <c r="B396" t="s">
-        <v>443</v>
+        <v>447</v>
       </c>
       <c r="C396" t="s">
-        <v>209</v>
+        <v>448</v>
       </c>
       <c r="D396">
         <v>3</v>
       </c>
       <c r="E396" t="s">
-        <v>64</v>
+        <v>28</v>
       </c>
       <c r="F396" s="1" t="s">
-        <v>375</v>
+        <v>371</v>
       </c>
     </row>
     <row r="397" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A397">
-        <v>418</v>
+        <v>427</v>
       </c>
       <c r="B397" t="s">
-        <v>444</v>
+        <v>449</v>
       </c>
       <c r="C397" t="s">
-        <v>187</v>
+        <v>196</v>
       </c>
       <c r="D397">
         <v>3</v>
       </c>
       <c r="E397" t="s">
-        <v>64</v>
+        <v>28</v>
       </c>
       <c r="F397" s="1" t="s">
-        <v>375</v>
+        <v>371</v>
       </c>
     </row>
     <row r="398" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A398">
-        <v>419</v>
+        <v>428</v>
       </c>
       <c r="B398" t="s">
-        <v>445</v>
+        <v>312</v>
       </c>
       <c r="C398" t="s">
-        <v>196</v>
+        <v>318</v>
       </c>
       <c r="D398">
         <v>3</v>
       </c>
       <c r="E398" t="s">
-        <v>64</v>
+        <v>28</v>
       </c>
       <c r="F398" s="1" t="s">
-        <v>375</v>
+        <v>371</v>
       </c>
     </row>
     <row r="399" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A399">
-        <v>421</v>
+        <v>429</v>
       </c>
       <c r="B399" t="s">
-        <v>446</v>
+        <v>450</v>
       </c>
       <c r="C399" t="s">
-        <v>215</v>
+        <v>303</v>
       </c>
       <c r="D399">
         <v>3</v>
@@ -9931,18 +9919,18 @@
         <v>28</v>
       </c>
       <c r="F399" s="1" t="s">
-        <v>457</v>
+        <v>371</v>
       </c>
     </row>
     <row r="400" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A400">
-        <v>422</v>
+        <v>430</v>
       </c>
       <c r="B400" t="s">
-        <v>447</v>
+        <v>306</v>
       </c>
       <c r="C400" t="s">
-        <v>196</v>
+        <v>209</v>
       </c>
       <c r="D400">
         <v>3</v>
@@ -9951,18 +9939,18 @@
         <v>28</v>
       </c>
       <c r="F400" s="1" t="s">
-        <v>375</v>
+        <v>371</v>
       </c>
     </row>
     <row r="401" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A401">
-        <v>423</v>
+        <v>431</v>
       </c>
       <c r="B401" t="s">
-        <v>448</v>
+        <v>451</v>
       </c>
       <c r="C401" t="s">
-        <v>191</v>
+        <v>303</v>
       </c>
       <c r="D401">
         <v>3</v>
@@ -9971,18 +9959,18 @@
         <v>28</v>
       </c>
       <c r="F401" s="1" t="s">
-        <v>375</v>
+        <v>371</v>
       </c>
     </row>
     <row r="402" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A402">
-        <v>424</v>
+        <v>432</v>
       </c>
       <c r="B402" t="s">
-        <v>449</v>
+        <v>452</v>
       </c>
       <c r="C402" t="s">
-        <v>307</v>
+        <v>189</v>
       </c>
       <c r="D402">
         <v>3</v>
@@ -9991,178 +9979,178 @@
         <v>28</v>
       </c>
       <c r="F402" s="1" t="s">
-        <v>375</v>
+        <v>371</v>
       </c>
     </row>
     <row r="403" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A403">
-        <v>425</v>
+        <v>434</v>
       </c>
       <c r="B403" t="s">
-        <v>450</v>
+        <v>454</v>
       </c>
       <c r="C403" t="s">
-        <v>193</v>
+        <v>318</v>
       </c>
       <c r="D403">
         <v>3</v>
       </c>
       <c r="E403" t="s">
-        <v>28</v>
+        <v>13</v>
       </c>
       <c r="F403" s="1" t="s">
-        <v>375</v>
+        <v>62</v>
       </c>
     </row>
     <row r="404" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A404">
-        <v>426</v>
+        <v>435</v>
       </c>
       <c r="B404" t="s">
-        <v>451</v>
+        <v>455</v>
       </c>
       <c r="C404" t="s">
-        <v>452</v>
+        <v>196</v>
       </c>
       <c r="D404">
         <v>3</v>
       </c>
       <c r="E404" t="s">
-        <v>28</v>
+        <v>13</v>
       </c>
       <c r="F404" s="1" t="s">
-        <v>375</v>
+        <v>62</v>
       </c>
     </row>
     <row r="405" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A405">
-        <v>427</v>
+        <v>436</v>
       </c>
       <c r="B405" t="s">
-        <v>453</v>
+        <v>456</v>
       </c>
       <c r="C405" t="s">
-        <v>196</v>
+        <v>448</v>
       </c>
       <c r="D405">
         <v>3</v>
       </c>
       <c r="E405" t="s">
-        <v>28</v>
+        <v>13</v>
       </c>
       <c r="F405" s="1" t="s">
-        <v>375</v>
+        <v>62</v>
       </c>
     </row>
     <row r="406" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A406">
-        <v>428</v>
+        <v>437</v>
       </c>
       <c r="B406" t="s">
-        <v>316</v>
+        <v>457</v>
       </c>
       <c r="C406" t="s">
-        <v>322</v>
+        <v>193</v>
       </c>
       <c r="D406">
         <v>3</v>
       </c>
       <c r="E406" t="s">
-        <v>28</v>
+        <v>13</v>
       </c>
       <c r="F406" s="1" t="s">
-        <v>375</v>
+        <v>62</v>
       </c>
     </row>
     <row r="407" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A407">
-        <v>429</v>
+        <v>438</v>
       </c>
       <c r="B407" t="s">
-        <v>454</v>
+        <v>458</v>
       </c>
       <c r="C407" t="s">
-        <v>307</v>
+        <v>459</v>
       </c>
       <c r="D407">
         <v>3</v>
       </c>
       <c r="E407" t="s">
-        <v>28</v>
+        <v>13</v>
       </c>
       <c r="F407" s="1" t="s">
-        <v>375</v>
+        <v>62</v>
       </c>
     </row>
     <row r="408" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A408">
-        <v>430</v>
+        <v>439</v>
       </c>
       <c r="B408" t="s">
-        <v>310</v>
+        <v>460</v>
       </c>
       <c r="C408" t="s">
-        <v>209</v>
+        <v>242</v>
       </c>
       <c r="D408">
         <v>3</v>
       </c>
       <c r="E408" t="s">
-        <v>28</v>
+        <v>13</v>
       </c>
       <c r="F408" s="1" t="s">
-        <v>375</v>
+        <v>371</v>
       </c>
     </row>
     <row r="409" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A409">
-        <v>431</v>
+        <v>440</v>
       </c>
       <c r="B409" t="s">
-        <v>455</v>
+        <v>461</v>
       </c>
       <c r="C409" t="s">
-        <v>307</v>
+        <v>187</v>
       </c>
       <c r="D409">
         <v>3</v>
       </c>
       <c r="E409" t="s">
-        <v>28</v>
+        <v>13</v>
       </c>
       <c r="F409" s="1" t="s">
-        <v>375</v>
+        <v>371</v>
       </c>
     </row>
     <row r="410" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A410">
-        <v>432</v>
+        <v>441</v>
       </c>
       <c r="B410" t="s">
-        <v>456</v>
+        <v>462</v>
       </c>
       <c r="C410" t="s">
-        <v>189</v>
+        <v>196</v>
       </c>
       <c r="D410">
         <v>3</v>
       </c>
       <c r="E410" t="s">
-        <v>28</v>
+        <v>13</v>
       </c>
       <c r="F410" s="1" t="s">
-        <v>375</v>
+        <v>371</v>
       </c>
     </row>
     <row r="411" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A411">
-        <v>434</v>
+        <v>442</v>
       </c>
       <c r="B411" t="s">
-        <v>458</v>
+        <v>463</v>
       </c>
       <c r="C411" t="s">
-        <v>322</v>
+        <v>209</v>
       </c>
       <c r="D411">
         <v>3</v>
@@ -10171,18 +10159,18 @@
         <v>13</v>
       </c>
       <c r="F411" s="1" t="s">
-        <v>62</v>
+        <v>371</v>
       </c>
     </row>
     <row r="412" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A412">
-        <v>435</v>
+        <v>443</v>
       </c>
       <c r="B412" t="s">
-        <v>459</v>
+        <v>464</v>
       </c>
       <c r="C412" t="s">
-        <v>196</v>
+        <v>187</v>
       </c>
       <c r="D412">
         <v>3</v>
@@ -10191,18 +10179,18 @@
         <v>13</v>
       </c>
       <c r="F412" s="1" t="s">
-        <v>62</v>
+        <v>371</v>
       </c>
     </row>
     <row r="413" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A413">
-        <v>436</v>
+        <v>444</v>
       </c>
       <c r="B413" t="s">
-        <v>460</v>
+        <v>465</v>
       </c>
       <c r="C413" t="s">
-        <v>452</v>
+        <v>189</v>
       </c>
       <c r="D413">
         <v>3</v>
@@ -10211,18 +10199,18 @@
         <v>13</v>
       </c>
       <c r="F413" s="1" t="s">
-        <v>62</v>
+        <v>371</v>
       </c>
     </row>
     <row r="414" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A414">
-        <v>437</v>
+        <v>445</v>
       </c>
       <c r="B414" t="s">
-        <v>461</v>
+        <v>466</v>
       </c>
       <c r="C414" t="s">
-        <v>193</v>
+        <v>353</v>
       </c>
       <c r="D414">
         <v>3</v>
@@ -10231,18 +10219,18 @@
         <v>13</v>
       </c>
       <c r="F414" s="1" t="s">
-        <v>62</v>
+        <v>371</v>
       </c>
     </row>
     <row r="415" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A415">
-        <v>438</v>
+        <v>446</v>
       </c>
       <c r="B415" t="s">
-        <v>462</v>
+        <v>467</v>
       </c>
       <c r="C415" t="s">
-        <v>463</v>
+        <v>196</v>
       </c>
       <c r="D415">
         <v>3</v>
@@ -10251,18 +10239,18 @@
         <v>13</v>
       </c>
       <c r="F415" s="1" t="s">
-        <v>62</v>
+        <v>371</v>
       </c>
     </row>
     <row r="416" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A416">
-        <v>439</v>
+        <v>447</v>
       </c>
       <c r="B416" t="s">
-        <v>464</v>
+        <v>468</v>
       </c>
       <c r="C416" t="s">
-        <v>242</v>
+        <v>209</v>
       </c>
       <c r="D416">
         <v>3</v>
@@ -10271,18 +10259,18 @@
         <v>13</v>
       </c>
       <c r="F416" s="1" t="s">
-        <v>375</v>
+        <v>371</v>
       </c>
     </row>
     <row r="417" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A417">
-        <v>440</v>
+        <v>448</v>
       </c>
       <c r="B417" t="s">
-        <v>465</v>
+        <v>469</v>
       </c>
       <c r="C417" t="s">
-        <v>187</v>
+        <v>196</v>
       </c>
       <c r="D417">
         <v>3</v>
@@ -10291,18 +10279,18 @@
         <v>13</v>
       </c>
       <c r="F417" s="1" t="s">
-        <v>375</v>
+        <v>371</v>
       </c>
     </row>
     <row r="418" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A418">
-        <v>441</v>
+        <v>449</v>
       </c>
       <c r="B418" t="s">
-        <v>466</v>
+        <v>470</v>
       </c>
       <c r="C418" t="s">
-        <v>196</v>
+        <v>187</v>
       </c>
       <c r="D418">
         <v>3</v>
@@ -10311,18 +10299,18 @@
         <v>13</v>
       </c>
       <c r="F418" s="1" t="s">
-        <v>375</v>
+        <v>371</v>
       </c>
     </row>
     <row r="419" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A419">
-        <v>442</v>
+        <v>450</v>
       </c>
       <c r="B419" t="s">
-        <v>467</v>
+        <v>471</v>
       </c>
       <c r="C419" t="s">
-        <v>209</v>
+        <v>318</v>
       </c>
       <c r="D419">
         <v>3</v>
@@ -10331,18 +10319,18 @@
         <v>13</v>
       </c>
       <c r="F419" s="1" t="s">
-        <v>375</v>
+        <v>371</v>
       </c>
     </row>
     <row r="420" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A420">
-        <v>443</v>
+        <v>451</v>
       </c>
       <c r="B420" t="s">
-        <v>468</v>
+        <v>472</v>
       </c>
       <c r="C420" t="s">
-        <v>187</v>
+        <v>215</v>
       </c>
       <c r="D420">
         <v>3</v>
@@ -10351,18 +10339,18 @@
         <v>13</v>
       </c>
       <c r="F420" s="1" t="s">
-        <v>375</v>
+        <v>371</v>
       </c>
     </row>
     <row r="421" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A421">
-        <v>444</v>
+        <v>452</v>
       </c>
       <c r="B421" t="s">
-        <v>469</v>
+        <v>473</v>
       </c>
       <c r="C421" t="s">
-        <v>189</v>
+        <v>215</v>
       </c>
       <c r="D421">
         <v>3</v>
@@ -10371,18 +10359,18 @@
         <v>13</v>
       </c>
       <c r="F421" s="1" t="s">
-        <v>375</v>
+        <v>371</v>
       </c>
     </row>
     <row r="422" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A422">
-        <v>445</v>
+        <v>453</v>
       </c>
       <c r="B422" t="s">
-        <v>470</v>
+        <v>474</v>
       </c>
       <c r="C422" t="s">
-        <v>357</v>
+        <v>196</v>
       </c>
       <c r="D422">
         <v>3</v>
@@ -10391,18 +10379,18 @@
         <v>13</v>
       </c>
       <c r="F422" s="1" t="s">
-        <v>375</v>
+        <v>371</v>
       </c>
     </row>
     <row r="423" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A423">
-        <v>446</v>
+        <v>454</v>
       </c>
       <c r="B423" t="s">
-        <v>471</v>
+        <v>475</v>
       </c>
       <c r="C423" t="s">
-        <v>196</v>
+        <v>189</v>
       </c>
       <c r="D423">
         <v>3</v>
@@ -10411,18 +10399,18 @@
         <v>13</v>
       </c>
       <c r="F423" s="1" t="s">
-        <v>375</v>
+        <v>371</v>
       </c>
     </row>
     <row r="424" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A424">
-        <v>447</v>
+        <v>455</v>
       </c>
       <c r="B424" t="s">
-        <v>472</v>
+        <v>476</v>
       </c>
       <c r="C424" t="s">
-        <v>209</v>
+        <v>202</v>
       </c>
       <c r="D424">
         <v>3</v>
@@ -10431,15 +10419,15 @@
         <v>13</v>
       </c>
       <c r="F424" s="1" t="s">
-        <v>375</v>
+        <v>371</v>
       </c>
     </row>
     <row r="425" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A425">
-        <v>448</v>
+        <v>456</v>
       </c>
       <c r="B425" t="s">
-        <v>473</v>
+        <v>477</v>
       </c>
       <c r="C425" t="s">
         <v>196</v>
@@ -10451,18 +10439,18 @@
         <v>13</v>
       </c>
       <c r="F425" s="1" t="s">
-        <v>375</v>
+        <v>371</v>
       </c>
     </row>
     <row r="426" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A426">
-        <v>449</v>
+        <v>457</v>
       </c>
       <c r="B426" t="s">
-        <v>474</v>
+        <v>478</v>
       </c>
       <c r="C426" t="s">
-        <v>187</v>
+        <v>193</v>
       </c>
       <c r="D426">
         <v>3</v>
@@ -10471,135 +10459,135 @@
         <v>13</v>
       </c>
       <c r="F426" s="1" t="s">
-        <v>375</v>
+        <v>371</v>
       </c>
     </row>
     <row r="427" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A427">
-        <v>450</v>
+        <v>459</v>
       </c>
       <c r="B427" t="s">
-        <v>475</v>
+        <v>479</v>
       </c>
       <c r="C427" t="s">
-        <v>322</v>
+        <v>480</v>
       </c>
       <c r="D427">
         <v>3</v>
       </c>
       <c r="E427" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="F427" s="1" t="s">
-        <v>375</v>
+        <v>62</v>
       </c>
     </row>
     <row r="428" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A428">
-        <v>451</v>
+        <v>460</v>
       </c>
       <c r="B428" t="s">
-        <v>476</v>
+        <v>481</v>
       </c>
       <c r="C428" t="s">
-        <v>215</v>
+        <v>189</v>
       </c>
       <c r="D428">
         <v>3</v>
       </c>
       <c r="E428" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="F428" s="1" t="s">
-        <v>375</v>
+        <v>62</v>
       </c>
     </row>
     <row r="429" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A429">
-        <v>452</v>
+        <v>461</v>
       </c>
       <c r="B429" t="s">
-        <v>477</v>
+        <v>482</v>
       </c>
       <c r="C429" t="s">
-        <v>215</v>
+        <v>193</v>
       </c>
       <c r="D429">
         <v>3</v>
       </c>
       <c r="E429" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="F429" s="1" t="s">
-        <v>375</v>
+        <v>62</v>
       </c>
     </row>
     <row r="430" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A430">
-        <v>453</v>
+        <v>462</v>
       </c>
       <c r="B430" t="s">
-        <v>478</v>
+        <v>483</v>
       </c>
       <c r="C430" t="s">
-        <v>196</v>
+        <v>209</v>
       </c>
       <c r="D430">
         <v>3</v>
       </c>
       <c r="E430" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="F430" s="1" t="s">
-        <v>375</v>
+        <v>62</v>
       </c>
     </row>
     <row r="431" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A431">
-        <v>454</v>
+        <v>463</v>
       </c>
       <c r="B431" t="s">
-        <v>479</v>
+        <v>484</v>
       </c>
       <c r="C431" t="s">
-        <v>189</v>
+        <v>209</v>
       </c>
       <c r="D431">
         <v>3</v>
       </c>
       <c r="E431" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="F431" s="1" t="s">
-        <v>375</v>
+        <v>62</v>
       </c>
     </row>
     <row r="432" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A432">
-        <v>455</v>
+        <v>464</v>
       </c>
       <c r="B432" t="s">
-        <v>480</v>
+        <v>165</v>
       </c>
       <c r="C432" t="s">
-        <v>202</v>
+        <v>196</v>
       </c>
       <c r="D432">
         <v>3</v>
       </c>
       <c r="E432" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="F432" s="1" t="s">
-        <v>375</v>
+        <v>62</v>
       </c>
     </row>
     <row r="433" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A433">
-        <v>456</v>
+        <v>465</v>
       </c>
       <c r="B433" t="s">
-        <v>481</v>
+        <v>485</v>
       </c>
       <c r="C433" t="s">
         <v>196</v>
@@ -10608,41 +10596,41 @@
         <v>3</v>
       </c>
       <c r="E433" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="F433" s="1" t="s">
-        <v>375</v>
+        <v>62</v>
       </c>
     </row>
     <row r="434" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A434">
-        <v>457</v>
+        <v>466</v>
       </c>
       <c r="B434" t="s">
-        <v>482</v>
+        <v>164</v>
       </c>
       <c r="C434" t="s">
-        <v>193</v>
+        <v>303</v>
       </c>
       <c r="D434">
         <v>3</v>
       </c>
       <c r="E434" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="F434" s="1" t="s">
-        <v>375</v>
+        <v>62</v>
       </c>
     </row>
     <row r="435" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A435">
-        <v>459</v>
+        <v>467</v>
       </c>
       <c r="B435" t="s">
-        <v>483</v>
+        <v>486</v>
       </c>
       <c r="C435" t="s">
-        <v>484</v>
+        <v>196</v>
       </c>
       <c r="D435">
         <v>3</v>
@@ -10656,13 +10644,13 @@
     </row>
     <row r="436" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A436">
-        <v>460</v>
+        <v>468</v>
       </c>
       <c r="B436" t="s">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="C436" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="D436">
         <v>3</v>
@@ -10671,18 +10659,18 @@
         <v>11</v>
       </c>
       <c r="F436" s="1" t="s">
-        <v>62</v>
+        <v>453</v>
       </c>
     </row>
     <row r="437" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A437">
-        <v>461</v>
+        <v>469</v>
       </c>
       <c r="B437" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="C437" t="s">
-        <v>193</v>
+        <v>215</v>
       </c>
       <c r="D437">
         <v>3</v>
@@ -10691,18 +10679,18 @@
         <v>11</v>
       </c>
       <c r="F437" s="1" t="s">
-        <v>62</v>
+        <v>371</v>
       </c>
     </row>
     <row r="438" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A438">
-        <v>462</v>
+        <v>470</v>
       </c>
       <c r="B438" t="s">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="C438" t="s">
-        <v>209</v>
+        <v>189</v>
       </c>
       <c r="D438">
         <v>3</v>
@@ -10711,18 +10699,18 @@
         <v>11</v>
       </c>
       <c r="F438" s="1" t="s">
-        <v>62</v>
+        <v>371</v>
       </c>
     </row>
     <row r="439" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A439">
-        <v>463</v>
+        <v>471</v>
       </c>
       <c r="B439" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="C439" t="s">
-        <v>209</v>
+        <v>311</v>
       </c>
       <c r="D439">
         <v>3</v>
@@ -10731,18 +10719,18 @@
         <v>11</v>
       </c>
       <c r="F439" s="1" t="s">
-        <v>62</v>
+        <v>371</v>
       </c>
     </row>
     <row r="440" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A440">
-        <v>464</v>
+        <v>472</v>
       </c>
       <c r="B440" t="s">
-        <v>165</v>
+        <v>491</v>
       </c>
       <c r="C440" t="s">
-        <v>196</v>
+        <v>189</v>
       </c>
       <c r="D440">
         <v>3</v>
@@ -10751,18 +10739,18 @@
         <v>11</v>
       </c>
       <c r="F440" s="1" t="s">
-        <v>62</v>
+        <v>371</v>
       </c>
     </row>
     <row r="441" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A441">
-        <v>465</v>
+        <v>473</v>
       </c>
       <c r="B441" t="s">
-        <v>489</v>
+        <v>492</v>
       </c>
       <c r="C441" t="s">
-        <v>196</v>
+        <v>187</v>
       </c>
       <c r="D441">
         <v>3</v>
@@ -10771,18 +10759,18 @@
         <v>11</v>
       </c>
       <c r="F441" s="1" t="s">
-        <v>62</v>
+        <v>371</v>
       </c>
     </row>
     <row r="442" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A442">
-        <v>466</v>
+        <v>474</v>
       </c>
       <c r="B442" t="s">
-        <v>164</v>
+        <v>493</v>
       </c>
       <c r="C442" t="s">
-        <v>307</v>
+        <v>187</v>
       </c>
       <c r="D442">
         <v>3</v>
@@ -10791,278 +10779,278 @@
         <v>11</v>
       </c>
       <c r="F442" s="1" t="s">
-        <v>62</v>
+        <v>371</v>
       </c>
     </row>
     <row r="443" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A443">
-        <v>467</v>
+        <v>476</v>
       </c>
       <c r="B443" t="s">
-        <v>490</v>
+        <v>494</v>
       </c>
       <c r="C443" t="s">
-        <v>196</v>
+        <v>209</v>
       </c>
       <c r="D443">
         <v>3</v>
       </c>
       <c r="E443" t="s">
-        <v>11</v>
+        <v>495</v>
       </c>
       <c r="F443" s="1" t="s">
-        <v>62</v>
+        <v>371</v>
       </c>
     </row>
     <row r="444" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A444">
-        <v>468</v>
+        <v>477</v>
       </c>
       <c r="B444" t="s">
-        <v>491</v>
+        <v>496</v>
       </c>
       <c r="C444" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="D444">
         <v>3</v>
       </c>
       <c r="E444" t="s">
-        <v>11</v>
+        <v>495</v>
       </c>
       <c r="F444" s="1" t="s">
-        <v>457</v>
+        <v>371</v>
       </c>
     </row>
     <row r="445" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A445">
-        <v>469</v>
+        <v>478</v>
       </c>
       <c r="B445" t="s">
-        <v>492</v>
+        <v>497</v>
       </c>
       <c r="C445" t="s">
-        <v>215</v>
+        <v>196</v>
       </c>
       <c r="D445">
         <v>3</v>
       </c>
       <c r="E445" t="s">
-        <v>11</v>
+        <v>495</v>
       </c>
       <c r="F445" s="1" t="s">
-        <v>375</v>
+        <v>371</v>
       </c>
     </row>
     <row r="446" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A446">
-        <v>470</v>
+        <v>479</v>
       </c>
       <c r="B446" t="s">
-        <v>493</v>
+        <v>498</v>
       </c>
       <c r="C446" t="s">
-        <v>189</v>
+        <v>215</v>
       </c>
       <c r="D446">
         <v>3</v>
       </c>
       <c r="E446" t="s">
-        <v>11</v>
+        <v>495</v>
       </c>
       <c r="F446" s="1" t="s">
-        <v>375</v>
+        <v>371</v>
       </c>
     </row>
     <row r="447" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A447">
-        <v>471</v>
+        <v>480</v>
       </c>
       <c r="B447" t="s">
-        <v>494</v>
+        <v>499</v>
       </c>
       <c r="C447" t="s">
-        <v>315</v>
+        <v>209</v>
       </c>
       <c r="D447">
         <v>3</v>
       </c>
       <c r="E447" t="s">
-        <v>11</v>
+        <v>495</v>
       </c>
       <c r="F447" s="1" t="s">
-        <v>375</v>
+        <v>371</v>
       </c>
     </row>
     <row r="448" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A448">
-        <v>472</v>
+        <v>482</v>
       </c>
       <c r="B448" t="s">
-        <v>495</v>
+        <v>500</v>
       </c>
       <c r="C448" t="s">
-        <v>189</v>
+        <v>459</v>
       </c>
       <c r="D448">
         <v>3</v>
       </c>
       <c r="E448" t="s">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="F448" s="1" t="s">
-        <v>375</v>
+        <v>62</v>
       </c>
     </row>
     <row r="449" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A449">
-        <v>473</v>
+        <v>483</v>
       </c>
       <c r="B449" t="s">
-        <v>496</v>
+        <v>501</v>
       </c>
       <c r="C449" t="s">
-        <v>187</v>
+        <v>209</v>
       </c>
       <c r="D449">
         <v>3</v>
       </c>
       <c r="E449" t="s">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="F449" s="1" t="s">
-        <v>375</v>
+        <v>62</v>
       </c>
     </row>
     <row r="450" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A450">
-        <v>474</v>
+        <v>484</v>
       </c>
       <c r="B450" t="s">
-        <v>497</v>
+        <v>502</v>
       </c>
       <c r="C450" t="s">
-        <v>187</v>
+        <v>193</v>
       </c>
       <c r="D450">
         <v>3</v>
       </c>
       <c r="E450" t="s">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="F450" s="1" t="s">
-        <v>375</v>
+        <v>371</v>
       </c>
     </row>
     <row r="451" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A451">
-        <v>476</v>
+        <v>485</v>
       </c>
       <c r="B451" t="s">
-        <v>498</v>
+        <v>503</v>
       </c>
       <c r="C451" t="s">
-        <v>209</v>
+        <v>196</v>
       </c>
       <c r="D451">
         <v>3</v>
       </c>
       <c r="E451" t="s">
-        <v>499</v>
+        <v>16</v>
       </c>
       <c r="F451" s="1" t="s">
-        <v>375</v>
+        <v>371</v>
       </c>
     </row>
     <row r="452" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A452">
-        <v>477</v>
+        <v>486</v>
       </c>
       <c r="B452" t="s">
-        <v>500</v>
+        <v>504</v>
       </c>
       <c r="C452" t="s">
-        <v>191</v>
+        <v>209</v>
       </c>
       <c r="D452">
         <v>3</v>
       </c>
       <c r="E452" t="s">
-        <v>499</v>
+        <v>16</v>
       </c>
       <c r="F452" s="1" t="s">
-        <v>375</v>
+        <v>371</v>
       </c>
     </row>
     <row r="453" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A453">
-        <v>478</v>
+        <v>487</v>
       </c>
       <c r="B453" t="s">
-        <v>501</v>
+        <v>505</v>
       </c>
       <c r="C453" t="s">
-        <v>196</v>
+        <v>189</v>
       </c>
       <c r="D453">
         <v>3</v>
       </c>
       <c r="E453" t="s">
-        <v>499</v>
+        <v>16</v>
       </c>
       <c r="F453" s="1" t="s">
-        <v>375</v>
+        <v>371</v>
       </c>
     </row>
     <row r="454" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A454">
-        <v>479</v>
+        <v>488</v>
       </c>
       <c r="B454" t="s">
-        <v>502</v>
+        <v>506</v>
       </c>
       <c r="C454" t="s">
-        <v>215</v>
+        <v>187</v>
       </c>
       <c r="D454">
         <v>3</v>
       </c>
       <c r="E454" t="s">
-        <v>499</v>
+        <v>16</v>
       </c>
       <c r="F454" s="1" t="s">
-        <v>375</v>
+        <v>371</v>
       </c>
     </row>
     <row r="455" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A455">
-        <v>480</v>
+        <v>489</v>
       </c>
       <c r="B455" t="s">
-        <v>503</v>
+        <v>507</v>
       </c>
       <c r="C455" t="s">
-        <v>209</v>
+        <v>215</v>
       </c>
       <c r="D455">
         <v>3</v>
       </c>
       <c r="E455" t="s">
-        <v>499</v>
+        <v>16</v>
       </c>
       <c r="F455" s="1" t="s">
-        <v>375</v>
+        <v>371</v>
       </c>
     </row>
     <row r="456" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A456">
-        <v>482</v>
+        <v>490</v>
       </c>
       <c r="B456" t="s">
-        <v>504</v>
+        <v>508</v>
       </c>
       <c r="C456" t="s">
-        <v>463</v>
+        <v>215</v>
       </c>
       <c r="D456">
         <v>3</v>
@@ -11071,24 +11059,24 @@
         <v>16</v>
       </c>
       <c r="F456" s="1" t="s">
-        <v>62</v>
+        <v>371</v>
       </c>
     </row>
     <row r="457" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A457">
-        <v>483</v>
+        <v>492</v>
       </c>
       <c r="B457" t="s">
-        <v>505</v>
+        <v>509</v>
       </c>
       <c r="C457" t="s">
-        <v>209</v>
+        <v>459</v>
       </c>
       <c r="D457">
         <v>3</v>
       </c>
       <c r="E457" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="F457" s="1" t="s">
         <v>62</v>
@@ -11096,70 +11084,70 @@
     </row>
     <row r="458" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A458">
-        <v>484</v>
+        <v>493</v>
       </c>
       <c r="B458" t="s">
-        <v>506</v>
+        <v>510</v>
       </c>
       <c r="C458" t="s">
-        <v>193</v>
+        <v>189</v>
       </c>
       <c r="D458">
         <v>3</v>
       </c>
       <c r="E458" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="F458" s="1" t="s">
-        <v>375</v>
+        <v>371</v>
       </c>
     </row>
     <row r="459" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A459">
-        <v>485</v>
+        <v>495</v>
       </c>
       <c r="B459" t="s">
-        <v>507</v>
+        <v>511</v>
       </c>
       <c r="C459" t="s">
-        <v>196</v>
+        <v>215</v>
       </c>
       <c r="D459">
         <v>3</v>
       </c>
       <c r="E459" t="s">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="F459" s="1" t="s">
-        <v>375</v>
+        <v>62</v>
       </c>
     </row>
     <row r="460" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A460">
-        <v>486</v>
+        <v>496</v>
       </c>
       <c r="B460" t="s">
-        <v>508</v>
+        <v>512</v>
       </c>
       <c r="C460" t="s">
-        <v>209</v>
+        <v>189</v>
       </c>
       <c r="D460">
         <v>3</v>
       </c>
       <c r="E460" t="s">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="F460" s="1" t="s">
-        <v>375</v>
+        <v>371</v>
       </c>
     </row>
     <row r="461" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A461">
-        <v>487</v>
+        <v>498</v>
       </c>
       <c r="B461" t="s">
-        <v>509</v>
+        <v>513</v>
       </c>
       <c r="C461" t="s">
         <v>189</v>
@@ -11168,87 +11156,87 @@
         <v>3</v>
       </c>
       <c r="E461" t="s">
-        <v>16</v>
+        <v>514</v>
       </c>
       <c r="F461" s="1" t="s">
-        <v>375</v>
+        <v>371</v>
       </c>
     </row>
     <row r="462" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A462">
-        <v>488</v>
+        <v>499</v>
       </c>
       <c r="B462" t="s">
-        <v>510</v>
+        <v>515</v>
       </c>
       <c r="C462" t="s">
-        <v>187</v>
+        <v>318</v>
       </c>
       <c r="D462">
         <v>3</v>
       </c>
       <c r="E462" t="s">
-        <v>16</v>
+        <v>514</v>
       </c>
       <c r="F462" s="1" t="s">
-        <v>375</v>
+        <v>371</v>
       </c>
     </row>
     <row r="463" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A463">
-        <v>489</v>
+        <v>500</v>
       </c>
       <c r="B463" t="s">
-        <v>511</v>
+        <v>516</v>
       </c>
       <c r="C463" t="s">
-        <v>215</v>
+        <v>196</v>
       </c>
       <c r="D463">
         <v>3</v>
       </c>
       <c r="E463" t="s">
-        <v>16</v>
+        <v>514</v>
       </c>
       <c r="F463" s="1" t="s">
-        <v>375</v>
+        <v>371</v>
       </c>
     </row>
     <row r="464" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A464">
-        <v>490</v>
+        <v>501</v>
       </c>
       <c r="B464" t="s">
-        <v>512</v>
+        <v>517</v>
       </c>
       <c r="C464" t="s">
-        <v>215</v>
+        <v>209</v>
       </c>
       <c r="D464">
         <v>3</v>
       </c>
       <c r="E464" t="s">
-        <v>16</v>
+        <v>514</v>
       </c>
       <c r="F464" s="1" t="s">
-        <v>375</v>
+        <v>371</v>
       </c>
     </row>
     <row r="465" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A465">
-        <v>492</v>
+        <v>503</v>
       </c>
       <c r="B465" t="s">
-        <v>513</v>
+        <v>518</v>
       </c>
       <c r="C465" t="s">
-        <v>463</v>
+        <v>196</v>
       </c>
       <c r="D465">
         <v>3</v>
       </c>
       <c r="E465" t="s">
-        <v>7</v>
+        <v>519</v>
       </c>
       <c r="F465" s="1" t="s">
         <v>62</v>
@@ -11256,717 +11244,557 @@
     </row>
     <row r="466" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A466">
-        <v>493</v>
+        <v>504</v>
       </c>
       <c r="B466" t="s">
-        <v>514</v>
+        <v>520</v>
       </c>
       <c r="C466" t="s">
-        <v>189</v>
+        <v>459</v>
       </c>
       <c r="D466">
         <v>3</v>
       </c>
       <c r="E466" t="s">
-        <v>7</v>
+        <v>519</v>
       </c>
       <c r="F466" s="1" t="s">
-        <v>375</v>
+        <v>62</v>
       </c>
     </row>
     <row r="467" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A467">
-        <v>495</v>
+        <v>505</v>
       </c>
       <c r="B467" t="s">
-        <v>515</v>
+        <v>521</v>
       </c>
       <c r="C467" t="s">
-        <v>215</v>
+        <v>523</v>
       </c>
       <c r="D467">
         <v>3</v>
       </c>
       <c r="E467" t="s">
-        <v>8</v>
-      </c>
-      <c r="F467" s="1" t="s">
-        <v>62</v>
+        <v>522</v>
+      </c>
+      <c r="F467" t="s">
+        <v>524</v>
       </c>
     </row>
     <row r="468" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A468">
-        <v>496</v>
+        <v>506</v>
       </c>
       <c r="B468" t="s">
-        <v>516</v>
+        <v>525</v>
       </c>
       <c r="C468" t="s">
-        <v>189</v>
+        <v>526</v>
       </c>
       <c r="D468">
         <v>3</v>
       </c>
       <c r="E468" t="s">
-        <v>8</v>
-      </c>
-      <c r="F468" s="1" t="s">
-        <v>375</v>
+        <v>522</v>
+      </c>
+      <c r="F468" t="s">
+        <v>524</v>
       </c>
     </row>
     <row r="469" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A469">
-        <v>498</v>
+        <v>507</v>
       </c>
       <c r="B469" t="s">
-        <v>517</v>
+        <v>527</v>
       </c>
       <c r="C469" t="s">
-        <v>189</v>
+        <v>528</v>
       </c>
       <c r="D469">
         <v>3</v>
       </c>
       <c r="E469" t="s">
-        <v>518</v>
-      </c>
-      <c r="F469" s="1" t="s">
-        <v>375</v>
+        <v>522</v>
+      </c>
+      <c r="F469" t="s">
+        <v>524</v>
       </c>
     </row>
     <row r="470" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A470">
-        <v>499</v>
+        <v>508</v>
       </c>
       <c r="B470" t="s">
-        <v>519</v>
+        <v>529</v>
       </c>
       <c r="C470" t="s">
-        <v>322</v>
+        <v>530</v>
       </c>
       <c r="D470">
         <v>3</v>
       </c>
       <c r="E470" t="s">
-        <v>518</v>
-      </c>
-      <c r="F470" s="1" t="s">
-        <v>375</v>
+        <v>522</v>
+      </c>
+      <c r="F470" t="s">
+        <v>524</v>
       </c>
     </row>
     <row r="471" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A471">
-        <v>500</v>
+        <v>509</v>
       </c>
       <c r="B471" t="s">
-        <v>520</v>
+        <v>531</v>
       </c>
       <c r="C471" t="s">
-        <v>196</v>
+        <v>528</v>
       </c>
       <c r="D471">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E471" t="s">
-        <v>518</v>
-      </c>
-      <c r="F471" s="1" t="s">
-        <v>375</v>
+        <v>522</v>
+      </c>
+      <c r="F471" t="s">
+        <v>524</v>
       </c>
     </row>
     <row r="472" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A472">
-        <v>501</v>
+        <v>510</v>
       </c>
       <c r="B472" t="s">
-        <v>521</v>
+        <v>532</v>
       </c>
       <c r="C472" t="s">
-        <v>209</v>
+        <v>533</v>
       </c>
       <c r="D472">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E472" t="s">
-        <v>518</v>
-      </c>
-      <c r="F472" s="1" t="s">
-        <v>375</v>
+        <v>522</v>
+      </c>
+      <c r="F472" t="s">
+        <v>524</v>
       </c>
     </row>
     <row r="473" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A473">
-        <v>503</v>
+        <v>511</v>
       </c>
       <c r="B473" t="s">
+        <v>534</v>
+      </c>
+      <c r="C473" t="s">
+        <v>528</v>
+      </c>
+      <c r="D473">
+        <v>2</v>
+      </c>
+      <c r="E473" t="s">
         <v>522</v>
       </c>
-      <c r="C473" t="s">
-        <v>196</v>
-      </c>
-      <c r="D473">
-        <v>3</v>
-      </c>
-      <c r="E473" t="s">
-        <v>523</v>
-      </c>
-      <c r="F473" s="1" t="s">
-        <v>62</v>
+      <c r="F473" t="s">
+        <v>524</v>
       </c>
     </row>
     <row r="474" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A474">
-        <v>504</v>
+        <v>512</v>
       </c>
       <c r="B474" t="s">
+        <v>535</v>
+      </c>
+      <c r="C474" t="s">
+        <v>523</v>
+      </c>
+      <c r="D474">
+        <v>2</v>
+      </c>
+      <c r="E474" t="s">
+        <v>522</v>
+      </c>
+      <c r="F474" t="s">
         <v>524</v>
-      </c>
-      <c r="C474" t="s">
-        <v>463</v>
-      </c>
-      <c r="D474">
-        <v>3</v>
-      </c>
-      <c r="E474" t="s">
-        <v>523</v>
-      </c>
-      <c r="F474" s="1" t="s">
-        <v>62</v>
       </c>
     </row>
     <row r="475" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A475">
-        <v>505</v>
+        <v>513</v>
       </c>
       <c r="B475" t="s">
-        <v>525</v>
+        <v>536</v>
       </c>
       <c r="C475" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="D475">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E475" t="s">
-        <v>526</v>
+        <v>522</v>
       </c>
       <c r="F475" t="s">
-        <v>528</v>
+        <v>524</v>
       </c>
     </row>
     <row r="476" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A476">
-        <v>506</v>
+        <v>514</v>
       </c>
       <c r="B476" t="s">
-        <v>529</v>
+        <v>537</v>
       </c>
       <c r="C476" t="s">
         <v>530</v>
       </c>
       <c r="D476">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E476" t="s">
-        <v>526</v>
+        <v>522</v>
       </c>
       <c r="F476" t="s">
-        <v>528</v>
+        <v>524</v>
       </c>
     </row>
     <row r="477" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A477">
-        <v>507</v>
+        <v>515</v>
       </c>
       <c r="B477" t="s">
-        <v>531</v>
+        <v>538</v>
       </c>
       <c r="C477" t="s">
-        <v>532</v>
+        <v>523</v>
       </c>
       <c r="D477">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E477" t="s">
-        <v>526</v>
+        <v>522</v>
       </c>
       <c r="F477" t="s">
-        <v>528</v>
+        <v>524</v>
       </c>
     </row>
     <row r="478" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A478">
-        <v>508</v>
+        <v>516</v>
       </c>
       <c r="B478" t="s">
-        <v>533</v>
+        <v>539</v>
       </c>
       <c r="C478" t="s">
-        <v>534</v>
+        <v>528</v>
       </c>
       <c r="D478">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E478" t="s">
-        <v>526</v>
+        <v>522</v>
       </c>
       <c r="F478" t="s">
-        <v>528</v>
+        <v>524</v>
       </c>
     </row>
     <row r="479" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A479">
-        <v>509</v>
+        <v>517</v>
       </c>
       <c r="B479" t="s">
-        <v>535</v>
+        <v>540</v>
       </c>
       <c r="C479" t="s">
-        <v>532</v>
+        <v>530</v>
       </c>
       <c r="D479">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E479" t="s">
-        <v>526</v>
+        <v>522</v>
       </c>
       <c r="F479" t="s">
-        <v>528</v>
+        <v>524</v>
       </c>
     </row>
     <row r="480" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A480">
-        <v>510</v>
-      </c>
-      <c r="B480" t="s">
-        <v>536</v>
-      </c>
-      <c r="C480" t="s">
-        <v>537</v>
-      </c>
-      <c r="D480">
-        <v>2</v>
-      </c>
-      <c r="E480" t="s">
+        <v>518</v>
+      </c>
+    </row>
+    <row r="481" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A481">
+        <v>519</v>
+      </c>
+    </row>
+    <row r="482" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A482">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="483" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A483">
+        <v>521</v>
+      </c>
+    </row>
+    <row r="484" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A484">
+        <v>522</v>
+      </c>
+    </row>
+    <row r="485" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A485">
+        <v>523</v>
+      </c>
+    </row>
+    <row r="486" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A486">
+        <v>524</v>
+      </c>
+    </row>
+    <row r="487" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A487">
+        <v>525</v>
+      </c>
+    </row>
+    <row r="488" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A488">
         <v>526</v>
       </c>
-      <c r="F480" t="s">
+    </row>
+    <row r="489" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A489">
+        <v>527</v>
+      </c>
+    </row>
+    <row r="490" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A490">
         <v>528</v>
       </c>
     </row>
-    <row r="481" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A481">
-        <v>511</v>
-      </c>
-      <c r="B481" t="s">
-        <v>538</v>
-      </c>
-      <c r="C481" t="s">
+    <row r="491" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A491">
+        <v>529</v>
+      </c>
+    </row>
+    <row r="492" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A492">
+        <v>530</v>
+      </c>
+    </row>
+    <row r="493" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A493">
+        <v>531</v>
+      </c>
+    </row>
+    <row r="494" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A494">
         <v>532</v>
       </c>
-      <c r="D481">
-        <v>2</v>
-      </c>
-      <c r="E481" t="s">
-        <v>526</v>
-      </c>
-      <c r="F481" t="s">
-        <v>528</v>
-      </c>
-    </row>
-    <row r="482" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A482">
-        <v>512</v>
-      </c>
-      <c r="B482" t="s">
-        <v>539</v>
-      </c>
-      <c r="C482" t="s">
-        <v>527</v>
-      </c>
-      <c r="D482">
-        <v>2</v>
-      </c>
-      <c r="E482" t="s">
-        <v>526</v>
-      </c>
-      <c r="F482" t="s">
-        <v>528</v>
-      </c>
-    </row>
-    <row r="483" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A483">
-        <v>513</v>
-      </c>
-      <c r="B483" t="s">
-        <v>540</v>
-      </c>
-      <c r="C483" t="s">
-        <v>532</v>
-      </c>
-      <c r="D483">
-        <v>2</v>
-      </c>
-      <c r="E483" t="s">
-        <v>526</v>
-      </c>
-      <c r="F483" t="s">
-        <v>528</v>
-      </c>
-    </row>
-    <row r="484" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A484">
-        <v>514</v>
-      </c>
-      <c r="B484" t="s">
-        <v>541</v>
-      </c>
-      <c r="C484" t="s">
+    </row>
+    <row r="495" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A495">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="496" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A496">
         <v>534</v>
-      </c>
-      <c r="D484">
-        <v>2</v>
-      </c>
-      <c r="E484" t="s">
-        <v>526</v>
-      </c>
-      <c r="F484" t="s">
-        <v>528</v>
-      </c>
-    </row>
-    <row r="485" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A485">
-        <v>515</v>
-      </c>
-      <c r="B485" t="s">
-        <v>542</v>
-      </c>
-      <c r="C485" t="s">
-        <v>527</v>
-      </c>
-      <c r="D485">
-        <v>1</v>
-      </c>
-      <c r="E485" t="s">
-        <v>526</v>
-      </c>
-      <c r="F485" t="s">
-        <v>528</v>
-      </c>
-    </row>
-    <row r="486" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A486">
-        <v>516</v>
-      </c>
-      <c r="B486" t="s">
-        <v>543</v>
-      </c>
-      <c r="C486" t="s">
-        <v>532</v>
-      </c>
-      <c r="D486">
-        <v>1</v>
-      </c>
-      <c r="E486" t="s">
-        <v>526</v>
-      </c>
-      <c r="F486" t="s">
-        <v>528</v>
-      </c>
-    </row>
-    <row r="487" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A487">
-        <v>517</v>
-      </c>
-      <c r="B487" t="s">
-        <v>544</v>
-      </c>
-      <c r="C487" t="s">
-        <v>534</v>
-      </c>
-      <c r="D487">
-        <v>1</v>
-      </c>
-      <c r="E487" t="s">
-        <v>526</v>
-      </c>
-      <c r="F487" t="s">
-        <v>528</v>
-      </c>
-    </row>
-    <row r="488" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A488">
-        <v>518</v>
-      </c>
-    </row>
-    <row r="489" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A489">
-        <v>519</v>
-      </c>
-    </row>
-    <row r="490" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A490">
-        <v>520</v>
-      </c>
-    </row>
-    <row r="491" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A491">
-        <v>521</v>
-      </c>
-    </row>
-    <row r="492" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A492">
-        <v>522</v>
-      </c>
-    </row>
-    <row r="493" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A493">
-        <v>523</v>
-      </c>
-    </row>
-    <row r="494" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A494">
-        <v>524</v>
-      </c>
-    </row>
-    <row r="495" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A495">
-        <v>525</v>
-      </c>
-    </row>
-    <row r="496" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A496">
-        <v>526</v>
       </c>
     </row>
     <row r="497" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A497">
-        <v>527</v>
+        <v>535</v>
       </c>
     </row>
     <row r="498" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A498">
-        <v>528</v>
+        <v>536</v>
       </c>
     </row>
     <row r="499" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A499">
-        <v>529</v>
+        <v>537</v>
       </c>
     </row>
     <row r="500" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A500">
-        <v>530</v>
+        <v>538</v>
       </c>
     </row>
     <row r="501" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A501">
-        <v>531</v>
+        <v>539</v>
       </c>
     </row>
     <row r="502" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A502">
-        <v>532</v>
+        <v>540</v>
       </c>
     </row>
     <row r="503" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A503">
-        <v>533</v>
+        <v>541</v>
       </c>
     </row>
     <row r="504" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A504">
-        <v>534</v>
+        <v>542</v>
       </c>
     </row>
     <row r="505" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A505">
-        <v>535</v>
+        <v>543</v>
       </c>
     </row>
     <row r="506" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A506">
-        <v>536</v>
+        <v>544</v>
       </c>
     </row>
     <row r="507" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A507">
-        <v>537</v>
+        <v>545</v>
       </c>
     </row>
     <row r="508" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A508">
-        <v>538</v>
+        <v>546</v>
       </c>
     </row>
     <row r="509" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A509">
-        <v>539</v>
+        <v>547</v>
       </c>
     </row>
     <row r="510" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A510">
-        <v>540</v>
+        <v>548</v>
       </c>
     </row>
     <row r="511" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A511">
-        <v>541</v>
+        <v>549</v>
       </c>
     </row>
     <row r="512" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A512">
-        <v>542</v>
+        <v>550</v>
       </c>
     </row>
     <row r="513" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A513">
-        <v>543</v>
+        <v>551</v>
       </c>
     </row>
     <row r="514" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A514">
-        <v>544</v>
+        <v>552</v>
       </c>
     </row>
     <row r="515" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A515">
-        <v>545</v>
+        <v>553</v>
       </c>
     </row>
     <row r="516" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A516">
-        <v>546</v>
+        <v>554</v>
       </c>
     </row>
     <row r="517" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A517">
-        <v>547</v>
+        <v>555</v>
       </c>
     </row>
     <row r="518" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A518">
-        <v>548</v>
+        <v>556</v>
       </c>
     </row>
     <row r="519" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A519">
-        <v>549</v>
+        <v>557</v>
       </c>
     </row>
     <row r="520" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A520">
-        <v>550</v>
+        <v>558</v>
       </c>
     </row>
     <row r="521" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A521">
-        <v>551</v>
+        <v>559</v>
       </c>
     </row>
     <row r="522" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A522">
-        <v>552</v>
+        <v>560</v>
       </c>
     </row>
     <row r="523" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A523">
-        <v>553</v>
+        <v>561</v>
       </c>
     </row>
     <row r="524" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A524">
-        <v>554</v>
+        <v>562</v>
       </c>
     </row>
     <row r="525" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A525">
-        <v>555</v>
+        <v>563</v>
       </c>
     </row>
     <row r="526" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A526">
-        <v>556</v>
+        <v>564</v>
       </c>
     </row>
     <row r="527" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A527">
-        <v>557</v>
+        <v>565</v>
       </c>
     </row>
     <row r="528" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A528">
-        <v>558</v>
+        <v>566</v>
       </c>
     </row>
     <row r="529" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A529">
-        <v>559</v>
+        <v>567</v>
       </c>
     </row>
     <row r="530" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A530">
-        <v>560</v>
+        <v>568</v>
       </c>
     </row>
     <row r="531" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A531">
-        <v>561</v>
+        <v>569</v>
       </c>
     </row>
     <row r="532" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A532">
-        <v>562</v>
-      </c>
-    </row>
-    <row r="533" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A533">
-        <v>563</v>
-      </c>
-    </row>
-    <row r="534" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A534">
-        <v>564</v>
-      </c>
-    </row>
-    <row r="535" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A535">
-        <v>565</v>
-      </c>
-    </row>
-    <row r="536" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A536">
-        <v>566</v>
-      </c>
-    </row>
-    <row r="537" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A537">
-        <v>567</v>
-      </c>
-    </row>
-    <row r="538" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A538">
-        <v>568</v>
-      </c>
-    </row>
-    <row r="539" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A539">
-        <v>569</v>
-      </c>
-    </row>
-    <row r="540" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A540">
         <v>570</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="B1:F540" xr:uid="{9FC02C4D-B240-46EA-A4A7-1A5D0B5C9EF3}">
+  <autoFilter ref="B1:F532" xr:uid="{9FC02C4D-B240-46EA-A4A7-1A5D0B5C9EF3}">
     <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B2:F151">
       <sortCondition ref="E1"/>
     </sortState>
   </autoFilter>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="E285:E367 E3:E278" xr:uid="{00000000-0002-0000-0000-000000000000}">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="E277:E359 E3:E270" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>"Corvette,Frigate,Destroyer,Cruiser,Battleship,Aircraft Carrier,Assault Carrier,Submarine,Ekranoplan,ALS,Howercraft,Missile,Missile-torpedo,Cannon,Torpedo,Grenade Launcher,Autocannon,Anti Air,UUV,Bomber,Drone,Fighter,Strike Fighter,Fighter,Helicopter,None"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="D103:D165" xr:uid="{A9B099F8-3DBD-4897-922B-2A7A6F698378}">
@@ -11985,18 +11813,18 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
-        <v>408</v>
+        <v>404</v>
       </c>
       <c r="B1" t="s">
-        <v>409</v>
+        <v>405</v>
       </c>
       <c r="C1" t="s">
-        <v>410</v>
+        <v>406</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>411</v>
+        <v>407</v>
       </c>
       <c r="B2" t="s">
         <v>196</v>
@@ -12007,7 +11835,7 @@
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>412</v>
+        <v>408</v>
       </c>
       <c r="B3" t="s">
         <v>215</v>
@@ -12018,7 +11846,7 @@
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>413</v>
+        <v>409</v>
       </c>
       <c r="B4" t="s">
         <v>189</v>
@@ -12029,10 +11857,10 @@
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>414</v>
+        <v>410</v>
       </c>
       <c r="B5" t="s">
-        <v>322</v>
+        <v>318</v>
       </c>
       <c r="C5">
         <v>3</v>
@@ -12040,7 +11868,7 @@
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>415</v>
+        <v>411</v>
       </c>
       <c r="B6" t="s">
         <v>193</v>
@@ -12051,7 +11879,7 @@
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>416</v>
+        <v>412</v>
       </c>
       <c r="B7" t="s">
         <v>215</v>
